--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买。EMA20与SAR多头信号偏积极，但价格仍受均线压制，信号可靠性中等。</t>
+          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买。EMA20与SAR多头叠加T3突破，信号偏多但受均线压制，可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.88高于50日均线0.788，EMA20与SAR均呈多头，T3形态突破；但RSI达71.49，已进入超买区，信号可靠性需留意短线过热。</t>
+          <t>现价0.88高于50日均线0.788，EMA20与SAR均呈多头，T3形态突破有效；但RSI达71.49，已进入超买区，信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.59高于50日均线0.487，EMA20与SAR均呈多头，趋势偏强；但RSI达75.95，已进入超买区，短期动能过热，信号可靠性需谨慎看待。</t>
+          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线过热。</t>
         </is>
       </c>
     </row>
@@ -6417,9 +6417,9 @@
       <c r="H131" t="n">
         <v>59.48</v>
       </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-23'!$A$1:$M$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M285"/>
+  <dimension ref="A1:M284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买。EMA20与SAR多头叠加T3突破，信号偏多但受均线压制，可靠性中等。</t>
+          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买；EMA20与SAR多头及T3突破信号偏积极，但均线位置显示上方仍有压力。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线过热。</t>
+          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线偏热。</t>
         </is>
       </c>
     </row>
@@ -11389,39 +11389,39 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>PARADIGM</t>
         </is>
       </c>
       <c r="D242" s="9" t="n">
-        <v>0.465</v>
+        <v>0.825</v>
       </c>
       <c r="E242" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>1011800</v>
+        <v>1004100</v>
       </c>
       <c r="G242" s="12" t="n">
-        <v>0.36</v>
+        <v>1.79</v>
       </c>
       <c r="H242" t="n">
-        <v>54.09</v>
-      </c>
-      <c r="I242" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.77</v>
+      </c>
+      <c r="I242" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J242" s="9" t="n">
-        <v>0.463</v>
+        <v>0.845</v>
       </c>
       <c r="K242" s="9" t="n">
-        <v>0.461</v>
+        <v>0.881</v>
       </c>
       <c r="L242" t="inlineStr"/>
       <c r="M242" s="14" t="inlineStr"/>
@@ -11434,39 +11434,39 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>0317</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>EPB</t>
         </is>
       </c>
       <c r="D243" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E243" s="17" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E243" s="10" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>1004100</v>
+        <v>1003000</v>
       </c>
       <c r="G243" s="12" t="n">
-        <v>1.79</v>
+        <v>4.14</v>
       </c>
       <c r="H243" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="I243" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.84</v>
+      </c>
+      <c r="I243" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J243" s="9" t="n">
-        <v>0.845</v>
+        <v>0.224</v>
       </c>
       <c r="K243" s="9" t="n">
-        <v>0.881</v>
+        <v>0.225</v>
       </c>
       <c r="L243" t="inlineStr"/>
       <c r="M243" s="14" t="inlineStr"/>
@@ -11479,39 +11479,39 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0317</t>
+          <t>0025</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>EPB</t>
+          <t>YBS</t>
         </is>
       </c>
       <c r="D244" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E244" s="10" t="n">
-        <v>-0.0233</v>
+        <v>0.25</v>
+      </c>
+      <c r="E244" s="16" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>1003000</v>
+        <v>1002700</v>
       </c>
       <c r="G244" s="12" t="n">
-        <v>4.14</v>
+        <v>0.79</v>
       </c>
       <c r="H244" t="n">
-        <v>40.84</v>
-      </c>
-      <c r="I244" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.37</v>
+      </c>
+      <c r="I244" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J244" s="9" t="n">
-        <v>0.224</v>
+        <v>0.264</v>
       </c>
       <c r="K244" s="9" t="n">
-        <v>0.225</v>
+        <v>0.301</v>
       </c>
       <c r="L244" t="inlineStr"/>
       <c r="M244" s="14" t="inlineStr"/>
@@ -11524,39 +11524,39 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>0025</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>YBS</t>
+          <t>SCIENTX</t>
         </is>
       </c>
       <c r="D245" s="9" t="n">
-        <v>0.25</v>
+        <v>3.75</v>
       </c>
       <c r="E245" s="16" t="n">
-        <v>0.0204</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>1002700</v>
+        <v>1002000</v>
       </c>
       <c r="G245" s="12" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="H245" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="I245" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.54</v>
+      </c>
+      <c r="I245" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J245" s="9" t="n">
-        <v>0.264</v>
+        <v>3.742</v>
       </c>
       <c r="K245" s="9" t="n">
-        <v>0.301</v>
+        <v>3.722</v>
       </c>
       <c r="L245" t="inlineStr"/>
       <c r="M245" s="14" t="inlineStr"/>
@@ -11569,28 +11569,28 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>SCIENTX</t>
+          <t>KIPREIT</t>
         </is>
       </c>
       <c r="D246" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E246" s="16" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.85</v>
+      </c>
+      <c r="E246" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>1002000</v>
+        <v>1001200</v>
       </c>
       <c r="G246" s="12" t="n">
-        <v>0.98</v>
+        <v>1.31</v>
       </c>
       <c r="H246" t="n">
-        <v>51.54</v>
+        <v>50.62</v>
       </c>
       <c r="I246" s="15" t="inlineStr">
         <is>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="J246" s="9" t="n">
-        <v>3.742</v>
+        <v>0.851</v>
       </c>
       <c r="K246" s="9" t="n">
-        <v>3.722</v>
+        <v>0.843</v>
       </c>
       <c r="L246" t="inlineStr"/>
       <c r="M246" s="14" t="inlineStr"/>
@@ -11614,28 +11614,28 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>KIPREIT</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D247" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E247" s="17" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E247" s="10" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>1001200</v>
+        <v>997500</v>
       </c>
       <c r="G247" s="12" t="n">
-        <v>1.31</v>
+        <v>0.44</v>
       </c>
       <c r="H247" t="n">
-        <v>50.62</v>
+        <v>46.18</v>
       </c>
       <c r="I247" s="15" t="inlineStr">
         <is>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="J247" s="9" t="n">
-        <v>0.851</v>
+        <v>1</v>
       </c>
       <c r="K247" s="9" t="n">
-        <v>0.843</v>
+        <v>1.017</v>
       </c>
       <c r="L247" t="inlineStr"/>
       <c r="M247" s="14" t="inlineStr"/>
@@ -11659,39 +11659,39 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>BURSA</t>
         </is>
       </c>
       <c r="D248" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E248" s="10" t="n">
-        <v>-0.005</v>
+        <v>8.1</v>
+      </c>
+      <c r="E248" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>997500</v>
+        <v>967100</v>
       </c>
       <c r="G248" s="12" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H248" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I248" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.88</v>
+      </c>
+      <c r="I248" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J248" s="9" t="n">
-        <v>1</v>
+        <v>8.365</v>
       </c>
       <c r="K248" s="9" t="n">
-        <v>1.017</v>
+        <v>8.451000000000001</v>
       </c>
       <c r="L248" t="inlineStr"/>
       <c r="M248" s="14" t="inlineStr"/>
@@ -11704,39 +11704,39 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>BURSA</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D249" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E249" s="17" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E249" s="16" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>967100</v>
+        <v>942100</v>
       </c>
       <c r="G249" s="12" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="H249" t="n">
-        <v>35.88</v>
-      </c>
-      <c r="I249" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.8</v>
+      </c>
+      <c r="I249" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J249" s="9" t="n">
-        <v>8.365</v>
+        <v>1.104</v>
       </c>
       <c r="K249" s="9" t="n">
-        <v>8.451000000000001</v>
+        <v>1.119</v>
       </c>
       <c r="L249" t="inlineStr"/>
       <c r="M249" s="14" t="inlineStr"/>
@@ -11749,39 +11749,39 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>HEIM</t>
         </is>
       </c>
       <c r="D250" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E250" s="16" t="n">
-        <v>0.0091</v>
+        <v>13.4</v>
+      </c>
+      <c r="E250" s="10" t="n">
+        <v>-0.0304</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>942100</v>
+        <v>903900</v>
       </c>
       <c r="G250" s="12" t="n">
-        <v>0.33</v>
+        <v>1.86</v>
       </c>
       <c r="H250" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="I250" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.28</v>
+      </c>
+      <c r="I250" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J250" s="9" t="n">
-        <v>1.104</v>
+        <v>14.532</v>
       </c>
       <c r="K250" s="9" t="n">
-        <v>1.119</v>
+        <v>16.318</v>
       </c>
       <c r="L250" t="inlineStr"/>
       <c r="M250" s="14" t="inlineStr"/>
@@ -11794,39 +11794,39 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>HEIM</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D251" s="9" t="n">
-        <v>13.4</v>
+        <v>1.47</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>-0.0304</v>
+        <v>-0.0134</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>903900</v>
+        <v>895600</v>
       </c>
       <c r="G251" s="12" t="n">
-        <v>1.86</v>
+        <v>0.08</v>
       </c>
       <c r="H251" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="I251" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.56</v>
+      </c>
+      <c r="I251" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J251" s="9" t="n">
-        <v>14.532</v>
+        <v>1.47</v>
       </c>
       <c r="K251" s="9" t="n">
-        <v>16.318</v>
+        <v>1.473</v>
       </c>
       <c r="L251" t="inlineStr"/>
       <c r="M251" s="14" t="inlineStr"/>
@@ -11839,39 +11839,39 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D252" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E252" s="10" t="n">
-        <v>-0.0134</v>
+        <v>0.93</v>
+      </c>
+      <c r="E252" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>895600</v>
+        <v>876500</v>
       </c>
       <c r="G252" s="12" t="n">
-        <v>0.08</v>
+        <v>0.39</v>
       </c>
       <c r="H252" t="n">
-        <v>50.56</v>
-      </c>
-      <c r="I252" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.83</v>
+      </c>
+      <c r="I252" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J252" s="9" t="n">
-        <v>1.47</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K252" s="9" t="n">
-        <v>1.473</v>
+        <v>0.957</v>
       </c>
       <c r="L252" t="inlineStr"/>
       <c r="M252" s="14" t="inlineStr"/>
@@ -11884,28 +11884,28 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>YTLREIT</t>
         </is>
       </c>
       <c r="D253" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E253" s="17" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E253" s="10" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>876500</v>
+        <v>860000</v>
       </c>
       <c r="G253" s="12" t="n">
-        <v>0.39</v>
+        <v>1.57</v>
       </c>
       <c r="H253" t="n">
-        <v>46.83</v>
+        <v>35.92</v>
       </c>
       <c r="I253" s="13" t="inlineStr">
         <is>
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="J253" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.001</v>
       </c>
       <c r="K253" s="9" t="n">
-        <v>0.957</v>
+        <v>1.005</v>
       </c>
       <c r="L253" t="inlineStr"/>
       <c r="M253" s="14" t="inlineStr"/>
@@ -11929,28 +11929,28 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>YTLREIT</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D254" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E254" s="10" t="n">
-        <v>-0.005</v>
+        <v>1.74</v>
+      </c>
+      <c r="E254" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>860000</v>
+        <v>844400</v>
       </c>
       <c r="G254" s="12" t="n">
-        <v>1.57</v>
+        <v>0.41</v>
       </c>
       <c r="H254" t="n">
-        <v>35.92</v>
+        <v>44.07</v>
       </c>
       <c r="I254" s="13" t="inlineStr">
         <is>
@@ -11958,10 +11958,10 @@
         </is>
       </c>
       <c r="J254" s="9" t="n">
-        <v>1.001</v>
+        <v>1.768</v>
       </c>
       <c r="K254" s="9" t="n">
-        <v>1.005</v>
+        <v>1.867</v>
       </c>
       <c r="L254" t="inlineStr"/>
       <c r="M254" s="14" t="inlineStr"/>
@@ -11974,39 +11974,39 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D255" s="9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E255" s="17" t="n">
-        <v>0</v>
+        <v>3.22</v>
+      </c>
+      <c r="E255" s="10" t="n">
+        <v>-0.0031</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>844400</v>
+        <v>843900</v>
       </c>
       <c r="G255" s="12" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="H255" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="I255" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.84999999999999</v>
+      </c>
+      <c r="I255" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J255" s="9" t="n">
-        <v>1.768</v>
+        <v>2.816</v>
       </c>
       <c r="K255" s="9" t="n">
-        <v>1.867</v>
+        <v>2.443</v>
       </c>
       <c r="L255" t="inlineStr"/>
       <c r="M255" s="14" t="inlineStr"/>
@@ -12019,39 +12019,39 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0157</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>FOCUSP</t>
         </is>
       </c>
       <c r="D256" s="9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="E256" s="10" t="n">
-        <v>-0.0031</v>
+        <v>0.51</v>
+      </c>
+      <c r="E256" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>843900</v>
+        <v>829600</v>
       </c>
       <c r="G256" s="12" t="n">
-        <v>0.28</v>
+        <v>2.83</v>
       </c>
       <c r="H256" t="n">
-        <v>75.84999999999999</v>
-      </c>
-      <c r="I256" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.59</v>
+      </c>
+      <c r="I256" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J256" s="9" t="n">
-        <v>2.816</v>
+        <v>0.511</v>
       </c>
       <c r="K256" s="9" t="n">
-        <v>2.443</v>
+        <v>0.507</v>
       </c>
       <c r="L256" t="inlineStr"/>
       <c r="M256" s="14" t="inlineStr"/>
@@ -12064,39 +12064,39 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>0157</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FOCUSP</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D257" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E257" s="17" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E257" s="16" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>829600</v>
+        <v>822400</v>
       </c>
       <c r="G257" s="12" t="n">
-        <v>2.83</v>
+        <v>0.89</v>
       </c>
       <c r="H257" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I257" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I257" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J257" s="9" t="n">
-        <v>0.511</v>
+        <v>2.448</v>
       </c>
       <c r="K257" s="9" t="n">
-        <v>0.507</v>
+        <v>2.245</v>
       </c>
       <c r="L257" t="inlineStr"/>
       <c r="M257" s="14" t="inlineStr"/>
@@ -12109,28 +12109,28 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>UCHITEC</t>
         </is>
       </c>
       <c r="D258" s="9" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="E258" s="16" t="n">
-        <v>0.0119</v>
+        <v>0.0121</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>822400</v>
+        <v>787600</v>
       </c>
       <c r="G258" s="12" t="n">
-        <v>0.89</v>
+        <v>3.26</v>
       </c>
       <c r="H258" t="n">
-        <v>59.96</v>
+        <v>28.24</v>
       </c>
       <c r="I258" s="15" t="inlineStr">
         <is>
@@ -12138,10 +12138,10 @@
         </is>
       </c>
       <c r="J258" s="9" t="n">
-        <v>2.448</v>
+        <v>2.603</v>
       </c>
       <c r="K258" s="9" t="n">
-        <v>2.245</v>
+        <v>2.687</v>
       </c>
       <c r="L258" t="inlineStr"/>
       <c r="M258" s="14" t="inlineStr"/>
@@ -12154,39 +12154,39 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>UCHITEC</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D259" s="9" t="n">
-        <v>2.51</v>
+        <v>0.655</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>0.0121</v>
+        <v>0.0077</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>787600</v>
+        <v>774500</v>
       </c>
       <c r="G259" s="12" t="n">
-        <v>3.26</v>
+        <v>1.03</v>
       </c>
       <c r="H259" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="I259" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.4</v>
+      </c>
+      <c r="I259" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J259" s="9" t="n">
-        <v>2.603</v>
+        <v>0.664</v>
       </c>
       <c r="K259" s="9" t="n">
-        <v>2.687</v>
+        <v>0.681</v>
       </c>
       <c r="L259" t="inlineStr"/>
       <c r="M259" s="14" t="inlineStr"/>
@@ -12199,28 +12199,28 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>TEOSENG</t>
         </is>
       </c>
       <c r="D260" s="9" t="n">
-        <v>0.655</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E260" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.0062</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>774500</v>
+        <v>773200</v>
       </c>
       <c r="G260" s="12" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="H260" t="n">
-        <v>39.4</v>
+        <v>42.67</v>
       </c>
       <c r="I260" s="13" t="inlineStr">
         <is>
@@ -12228,10 +12228,10 @@
         </is>
       </c>
       <c r="J260" s="9" t="n">
-        <v>0.664</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K260" s="9" t="n">
-        <v>0.681</v>
+        <v>0.848</v>
       </c>
       <c r="L260" t="inlineStr"/>
       <c r="M260" s="14" t="inlineStr"/>
@@ -12244,28 +12244,28 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D261" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E261" s="16" t="n">
-        <v>0.0062</v>
+        <v>1.3</v>
+      </c>
+      <c r="E261" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>773200</v>
+        <v>770400</v>
       </c>
       <c r="G261" s="12" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="H261" t="n">
-        <v>42.67</v>
+        <v>35.96</v>
       </c>
       <c r="I261" s="13" t="inlineStr">
         <is>
@@ -12273,10 +12273,10 @@
         </is>
       </c>
       <c r="J261" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>1.324</v>
       </c>
       <c r="K261" s="9" t="n">
-        <v>0.848</v>
+        <v>1.349</v>
       </c>
       <c r="L261" t="inlineStr"/>
       <c r="M261" s="14" t="inlineStr"/>
@@ -12289,39 +12289,39 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D262" s="9" t="n">
-        <v>1.3</v>
+        <v>0.51</v>
       </c>
       <c r="E262" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>770400</v>
+        <v>770000</v>
       </c>
       <c r="G262" s="12" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="H262" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="I262" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.29</v>
+      </c>
+      <c r="I262" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J262" s="9" t="n">
-        <v>1.324</v>
+        <v>0.494</v>
       </c>
       <c r="K262" s="9" t="n">
-        <v>1.349</v>
+        <v>0.494</v>
       </c>
       <c r="L262" t="inlineStr"/>
       <c r="M262" s="14" t="inlineStr"/>
@@ -12334,28 +12334,28 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>UTDPLT</t>
         </is>
       </c>
       <c r="D263" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E263" s="17" t="n">
-        <v>0</v>
+        <v>33.2</v>
+      </c>
+      <c r="E263" s="10" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>770000</v>
+        <v>756300</v>
       </c>
       <c r="G263" s="12" t="n">
-        <v>1.72</v>
+        <v>0.68</v>
       </c>
       <c r="H263" t="n">
-        <v>59.29</v>
+        <v>52.23</v>
       </c>
       <c r="I263" s="15" t="inlineStr">
         <is>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="J263" s="9" t="n">
-        <v>0.494</v>
+        <v>33.072</v>
       </c>
       <c r="K263" s="9" t="n">
-        <v>0.494</v>
+        <v>33.192</v>
       </c>
       <c r="L263" t="inlineStr"/>
       <c r="M263" s="14" t="inlineStr"/>
@@ -12379,39 +12379,39 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>UTDPLT</t>
+          <t>CCK</t>
         </is>
       </c>
       <c r="D264" s="9" t="n">
-        <v>33.2</v>
+        <v>0.88</v>
       </c>
       <c r="E264" s="10" t="n">
-        <v>-0.0101</v>
+        <v>-0.0222</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>756300</v>
+        <v>741300</v>
       </c>
       <c r="G264" s="12" t="n">
-        <v>0.68</v>
+        <v>1.29</v>
       </c>
       <c r="H264" t="n">
-        <v>52.23</v>
-      </c>
-      <c r="I264" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.61</v>
+      </c>
+      <c r="I264" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J264" s="9" t="n">
-        <v>33.072</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K264" s="9" t="n">
-        <v>33.192</v>
+        <v>1.021</v>
       </c>
       <c r="L264" t="inlineStr"/>
       <c r="M264" s="14" t="inlineStr"/>
@@ -12424,39 +12424,39 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>CCK</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D265" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E265" s="10" t="n">
-        <v>-0.0222</v>
+        <v>2.38</v>
+      </c>
+      <c r="E265" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>741300</v>
+        <v>736300</v>
       </c>
       <c r="G265" s="12" t="n">
-        <v>1.29</v>
+        <v>0.72</v>
       </c>
       <c r="H265" t="n">
-        <v>23.61</v>
-      </c>
-      <c r="I265" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.13</v>
+      </c>
+      <c r="I265" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J265" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>2.294</v>
       </c>
       <c r="K265" s="9" t="n">
-        <v>1.021</v>
+        <v>2.332</v>
       </c>
       <c r="L265" t="inlineStr"/>
       <c r="M265" s="14" t="inlineStr"/>
@@ -12469,28 +12469,28 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D266" s="9" t="n">
-        <v>2.38</v>
+        <v>0.77</v>
       </c>
       <c r="E266" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>736300</v>
+        <v>722700</v>
       </c>
       <c r="G266" s="12" t="n">
-        <v>0.72</v>
+        <v>0.29</v>
       </c>
       <c r="H266" t="n">
-        <v>56.13</v>
+        <v>52.46</v>
       </c>
       <c r="I266" s="15" t="inlineStr">
         <is>
@@ -12498,10 +12498,10 @@
         </is>
       </c>
       <c r="J266" s="9" t="n">
-        <v>2.294</v>
+        <v>0.764</v>
       </c>
       <c r="K266" s="9" t="n">
-        <v>2.332</v>
+        <v>0.753</v>
       </c>
       <c r="L266" t="inlineStr"/>
       <c r="M266" s="14" t="inlineStr"/>
@@ -12514,28 +12514,28 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D267" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E267" s="17" t="n">
-        <v>0</v>
+        <v>1.93</v>
+      </c>
+      <c r="E267" s="10" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>722700</v>
+        <v>686200</v>
       </c>
       <c r="G267" s="12" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="H267" t="n">
-        <v>52.46</v>
+        <v>41.77</v>
       </c>
       <c r="I267" s="15" t="inlineStr">
         <is>
@@ -12543,10 +12543,10 @@
         </is>
       </c>
       <c r="J267" s="9" t="n">
-        <v>0.764</v>
+        <v>1.964</v>
       </c>
       <c r="K267" s="9" t="n">
-        <v>0.753</v>
+        <v>2.032</v>
       </c>
       <c r="L267" t="inlineStr"/>
       <c r="M267" s="14" t="inlineStr"/>
@@ -12559,28 +12559,28 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>PJBUMI</t>
         </is>
       </c>
       <c r="D268" s="9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E268" s="10" t="n">
-        <v>-0.0103</v>
+        <v>4.05</v>
+      </c>
+      <c r="E268" s="16" t="n">
+        <v>0.01</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>686200</v>
+        <v>679000</v>
       </c>
       <c r="G268" s="12" t="n">
-        <v>0.38</v>
+        <v>1.05</v>
       </c>
       <c r="H268" t="n">
-        <v>41.77</v>
+        <v>72.36</v>
       </c>
       <c r="I268" s="15" t="inlineStr">
         <is>
@@ -12588,10 +12588,10 @@
         </is>
       </c>
       <c r="J268" s="9" t="n">
-        <v>1.964</v>
+        <v>3.949</v>
       </c>
       <c r="K268" s="9" t="n">
-        <v>2.032</v>
+        <v>3.84</v>
       </c>
       <c r="L268" t="inlineStr"/>
       <c r="M268" s="14" t="inlineStr"/>
@@ -12604,39 +12604,39 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>PJBUMI</t>
+          <t>SAMCHEM</t>
         </is>
       </c>
       <c r="D269" s="9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E269" s="16" t="n">
-        <v>0.01</v>
+        <v>0.51</v>
+      </c>
+      <c r="E269" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>679000</v>
+        <v>673000</v>
       </c>
       <c r="G269" s="12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H269" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="I269" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46</v>
+      </c>
+      <c r="I269" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J269" s="9" t="n">
-        <v>3.949</v>
+        <v>0.518</v>
       </c>
       <c r="K269" s="9" t="n">
-        <v>3.84</v>
+        <v>0.51</v>
       </c>
       <c r="L269" t="inlineStr"/>
       <c r="M269" s="14" t="inlineStr"/>
@@ -12649,28 +12649,28 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAMCHEM</t>
+          <t>SENFONG</t>
         </is>
       </c>
       <c r="D270" s="9" t="n">
-        <v>0.51</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E270" s="10" t="n">
-        <v>-0.0097</v>
+        <v>-0.0072</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>673000</v>
+        <v>669300</v>
       </c>
       <c r="G270" s="12" t="n">
-        <v>1.08</v>
+        <v>4.99</v>
       </c>
       <c r="H270" t="n">
-        <v>46</v>
+        <v>45.87</v>
       </c>
       <c r="I270" s="13" t="inlineStr">
         <is>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="J270" s="9" t="n">
-        <v>0.518</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K270" s="9" t="n">
-        <v>0.51</v>
+        <v>0.681</v>
       </c>
       <c r="L270" t="inlineStr"/>
       <c r="M270" s="14" t="inlineStr"/>
@@ -12694,39 +12694,39 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>PETRONM</t>
         </is>
       </c>
       <c r="D271" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>3.72</v>
       </c>
       <c r="E271" s="10" t="n">
-        <v>-0.0072</v>
+        <v>-0.0462</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>669300</v>
+        <v>665500</v>
       </c>
       <c r="G271" s="12" t="n">
-        <v>4.99</v>
+        <v>3.09</v>
       </c>
       <c r="H271" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I271" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.96</v>
+      </c>
+      <c r="I271" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J271" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>3.544</v>
       </c>
       <c r="K271" s="9" t="n">
-        <v>0.681</v>
+        <v>3.486</v>
       </c>
       <c r="L271" t="inlineStr"/>
       <c r="M271" s="14" t="inlineStr"/>
@@ -12739,28 +12739,28 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>PETRONM</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D272" s="9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="E272" s="10" t="n">
-        <v>-0.0462</v>
+        <v>0.655</v>
+      </c>
+      <c r="E272" s="16" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>665500</v>
+        <v>653900</v>
       </c>
       <c r="G272" s="12" t="n">
-        <v>3.09</v>
+        <v>1.87</v>
       </c>
       <c r="H272" t="n">
-        <v>60.96</v>
+        <v>52.93</v>
       </c>
       <c r="I272" s="15" t="inlineStr">
         <is>
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="J272" s="9" t="n">
-        <v>3.544</v>
+        <v>0.649</v>
       </c>
       <c r="K272" s="9" t="n">
-        <v>3.486</v>
+        <v>0.645</v>
       </c>
       <c r="L272" t="inlineStr"/>
       <c r="M272" s="14" t="inlineStr"/>
@@ -12784,39 +12784,39 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="D273" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E273" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.52</v>
+      </c>
+      <c r="E273" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>653900</v>
+        <v>608700</v>
       </c>
       <c r="G273" s="12" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="H273" t="n">
-        <v>52.93</v>
-      </c>
-      <c r="I273" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.05</v>
+      </c>
+      <c r="I273" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J273" s="9" t="n">
-        <v>0.649</v>
+        <v>0.521</v>
       </c>
       <c r="K273" s="9" t="n">
-        <v>0.645</v>
+        <v>0.527</v>
       </c>
       <c r="L273" t="inlineStr"/>
       <c r="M273" s="14" t="inlineStr"/>
@@ -12829,39 +12829,39 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>HLBANK</t>
         </is>
       </c>
       <c r="D274" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E274" s="17" t="n">
-        <v>0</v>
+        <v>23.2</v>
+      </c>
+      <c r="E274" s="10" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>608700</v>
+        <v>604000</v>
       </c>
       <c r="G274" s="12" t="n">
-        <v>1.59</v>
+        <v>0.9</v>
       </c>
       <c r="H274" t="n">
-        <v>47.05</v>
-      </c>
-      <c r="I274" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.05</v>
+      </c>
+      <c r="I274" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J274" s="9" t="n">
-        <v>0.521</v>
+        <v>23.206</v>
       </c>
       <c r="K274" s="9" t="n">
-        <v>0.527</v>
+        <v>22.796</v>
       </c>
       <c r="L274" t="inlineStr"/>
       <c r="M274" s="14" t="inlineStr"/>
@@ -12874,39 +12874,39 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>HLBANK</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D275" s="9" t="n">
-        <v>23.2</v>
+        <v>2.33</v>
       </c>
       <c r="E275" s="10" t="n">
-        <v>-0.0077</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>604000</v>
+        <v>588100</v>
       </c>
       <c r="G275" s="12" t="n">
         <v>0.9</v>
       </c>
       <c r="H275" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="I275" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.65</v>
+      </c>
+      <c r="I275" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J275" s="9" t="n">
-        <v>23.206</v>
+        <v>2.269</v>
       </c>
       <c r="K275" s="9" t="n">
-        <v>22.796</v>
+        <v>2.126</v>
       </c>
       <c r="L275" t="inlineStr"/>
       <c r="M275" s="14" t="inlineStr"/>
@@ -12919,39 +12919,39 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D276" s="9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E276" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>2.07</v>
+      </c>
+      <c r="E276" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>588100</v>
+        <v>568200</v>
       </c>
       <c r="G276" s="12" t="n">
-        <v>0.9</v>
+        <v>0.43</v>
       </c>
       <c r="H276" t="n">
-        <v>59.65</v>
-      </c>
-      <c r="I276" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.86</v>
+      </c>
+      <c r="I276" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J276" s="9" t="n">
-        <v>2.269</v>
+        <v>2.087</v>
       </c>
       <c r="K276" s="9" t="n">
-        <v>2.126</v>
+        <v>2.115</v>
       </c>
       <c r="L276" t="inlineStr"/>
       <c r="M276" s="14" t="inlineStr"/>
@@ -12964,39 +12964,39 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D277" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E277" s="17" t="n">
-        <v>0</v>
+        <v>4.09</v>
+      </c>
+      <c r="E277" s="10" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>568200</v>
+        <v>558600</v>
       </c>
       <c r="G277" s="12" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H277" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="I277" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.52</v>
+      </c>
+      <c r="I277" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J277" s="9" t="n">
-        <v>2.087</v>
+        <v>4.24</v>
       </c>
       <c r="K277" s="9" t="n">
-        <v>2.115</v>
+        <v>4.373</v>
       </c>
       <c r="L277" t="inlineStr"/>
       <c r="M277" s="14" t="inlineStr"/>
@@ -13009,28 +13009,28 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D278" s="9" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="E278" s="10" t="n">
-        <v>-0.0168</v>
+        <v>0.965</v>
+      </c>
+      <c r="E278" s="16" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>558600</v>
+        <v>547900</v>
       </c>
       <c r="G278" s="12" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="H278" t="n">
-        <v>42.52</v>
+        <v>32.26</v>
       </c>
       <c r="I278" s="13" t="inlineStr">
         <is>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="J278" s="9" t="n">
-        <v>4.24</v>
+        <v>0.986</v>
       </c>
       <c r="K278" s="9" t="n">
-        <v>4.373</v>
+        <v>1.019</v>
       </c>
       <c r="L278" t="inlineStr"/>
       <c r="M278" s="14" t="inlineStr"/>
@@ -13054,28 +13054,28 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D279" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E279" s="16" t="n">
-        <v>0.0105</v>
+        <v>1.77</v>
+      </c>
+      <c r="E279" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>547900</v>
+        <v>546300</v>
       </c>
       <c r="G279" s="12" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="H279" t="n">
-        <v>32.26</v>
+        <v>62.7</v>
       </c>
       <c r="I279" s="13" t="inlineStr">
         <is>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="J279" s="9" t="n">
-        <v>0.986</v>
+        <v>1.697</v>
       </c>
       <c r="K279" s="9" t="n">
-        <v>1.019</v>
+        <v>1.601</v>
       </c>
       <c r="L279" t="inlineStr"/>
       <c r="M279" s="14" t="inlineStr"/>
@@ -13099,28 +13099,28 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5235SS</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>KLCC</t>
         </is>
       </c>
       <c r="D280" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E280" s="17" t="n">
-        <v>0</v>
+        <v>8.35</v>
+      </c>
+      <c r="E280" s="16" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>546300</v>
+        <v>540500</v>
       </c>
       <c r="G280" s="12" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="H280" t="n">
-        <v>62.7</v>
+        <v>40.23</v>
       </c>
       <c r="I280" s="13" t="inlineStr">
         <is>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="J280" s="9" t="n">
-        <v>1.697</v>
+        <v>8.448</v>
       </c>
       <c r="K280" s="9" t="n">
-        <v>1.601</v>
+        <v>8.577</v>
       </c>
       <c r="L280" t="inlineStr"/>
       <c r="M280" s="14" t="inlineStr"/>
@@ -13144,39 +13144,39 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>5235SS</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>KLCC</t>
+          <t>KLK</t>
         </is>
       </c>
       <c r="D281" s="9" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="E281" s="16" t="n">
-        <v>0.0097</v>
+        <v>22.5</v>
+      </c>
+      <c r="E281" s="10" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>540500</v>
+        <v>537100</v>
       </c>
       <c r="G281" s="12" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H281" t="n">
-        <v>40.23</v>
-      </c>
-      <c r="I281" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.78</v>
+      </c>
+      <c r="I281" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J281" s="9" t="n">
-        <v>8.448</v>
+        <v>22.397</v>
       </c>
       <c r="K281" s="9" t="n">
-        <v>8.577</v>
+        <v>21.822</v>
       </c>
       <c r="L281" t="inlineStr"/>
       <c r="M281" s="14" t="inlineStr"/>
@@ -13189,39 +13189,39 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>KLK</t>
+          <t>SOP</t>
         </is>
       </c>
       <c r="D282" s="9" t="n">
-        <v>22.5</v>
+        <v>5.85</v>
       </c>
       <c r="E282" s="10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0394</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>537100</v>
+        <v>512400</v>
       </c>
       <c r="G282" s="12" t="n">
-        <v>0.46</v>
+        <v>0.82</v>
       </c>
       <c r="H282" t="n">
-        <v>54.78</v>
-      </c>
-      <c r="I282" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.74</v>
+      </c>
+      <c r="I282" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J282" s="9" t="n">
-        <v>22.397</v>
+        <v>5.927</v>
       </c>
       <c r="K282" s="9" t="n">
-        <v>21.822</v>
+        <v>5.508</v>
       </c>
       <c r="L282" t="inlineStr"/>
       <c r="M282" s="14" t="inlineStr"/>
@@ -13234,28 +13234,28 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SOP</t>
+          <t>MKH</t>
         </is>
       </c>
       <c r="D283" s="9" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E283" s="10" t="n">
-        <v>-0.0394</v>
+        <v>1.99</v>
+      </c>
+      <c r="E283" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>512400</v>
+        <v>503900</v>
       </c>
       <c r="G283" s="12" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="H283" t="n">
-        <v>50.74</v>
+        <v>65.8</v>
       </c>
       <c r="I283" s="13" t="inlineStr">
         <is>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="J283" s="9" t="n">
-        <v>5.927</v>
+        <v>1.988</v>
       </c>
       <c r="K283" s="9" t="n">
-        <v>5.508</v>
+        <v>1.979</v>
       </c>
       <c r="L283" t="inlineStr"/>
       <c r="M283" s="14" t="inlineStr"/>
@@ -13279,90 +13279,45 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>AFFIN</t>
         </is>
       </c>
       <c r="D284" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E284" s="17" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E284" s="16" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>503900</v>
+        <v>503700</v>
       </c>
       <c r="G284" s="12" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="H284" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="I284" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.58</v>
+      </c>
+      <c r="I284" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J284" s="9" t="n">
-        <v>1.988</v>
+        <v>2.046</v>
       </c>
       <c r="K284" s="9" t="n">
-        <v>1.979</v>
+        <v>2.136</v>
       </c>
       <c r="L284" t="inlineStr"/>
       <c r="M284" s="14" t="inlineStr"/>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>AFFIN</t>
-        </is>
-      </c>
-      <c r="D285" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E285" s="16" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="F285" s="11" t="n">
-        <v>503700</v>
-      </c>
-      <c r="G285" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H285" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="I285" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J285" s="9" t="n">
-        <v>2.046</v>
-      </c>
-      <c r="K285" s="9" t="n">
-        <v>2.136</v>
-      </c>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M285"/>
+  <autoFilter ref="A1:M284"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买；EMA20与SAR多头及T3突破信号偏积极，但均线位置显示上方仍有压力。</t>
+          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买；EMA20与SAR多头信号与均线位置略有背离，可靠性一般。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线偏热。</t>
+          <t>现价0.59高于50日均线0.487，EMA20与SAR均呈多头，但RSI达75.95，已进入超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-24" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +40,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,13 +94,13 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,6 +466,336 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>涨跌%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>成交量</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>相对量</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EMA20</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>50日均线</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>AI点评</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>22992500</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线过热。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>5497100</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H3" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>4205000</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>525900</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>507000</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -780,7 +1112,7 @@
       <c r="D6" s="9" t="n">
         <v>0.185</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="15" t="n">
         <v>-0.09759999999999999</v>
       </c>
       <c r="F6" s="11" t="n">
@@ -825,7 +1157,7 @@
       <c r="D7" s="9" t="n">
         <v>0.165</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="15" t="n">
         <v>-0.0294</v>
       </c>
       <c r="F7" s="11" t="n">
@@ -837,7 +1169,7 @@
       <c r="H7" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -870,7 +1202,7 @@
       <c r="D8" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
@@ -882,7 +1214,7 @@
       <c r="H8" t="n">
         <v>65.29000000000001</v>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -915,7 +1247,7 @@
       <c r="D9" s="9" t="n">
         <v>0.23</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="15" t="n">
         <v>-0.0417</v>
       </c>
       <c r="F9" s="11" t="n">
@@ -960,7 +1292,7 @@
       <c r="D10" s="9" t="n">
         <v>0.255</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="15" t="n">
         <v>-0.0556</v>
       </c>
       <c r="F10" s="11" t="n">
@@ -972,7 +1304,7 @@
       <c r="H10" t="n">
         <v>34.37</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1005,7 +1337,7 @@
       <c r="D11" s="9" t="n">
         <v>0.795</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>0.1866</v>
       </c>
       <c r="F11" s="11" t="n">
@@ -1017,7 +1349,7 @@
       <c r="H11" t="n">
         <v>70.72</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1050,7 +1382,7 @@
       <c r="D12" s="9" t="n">
         <v>0.545</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="15" t="n">
         <v>-0.0522</v>
       </c>
       <c r="F12" s="11" t="n">
@@ -1095,7 +1427,7 @@
       <c r="D13" s="9" t="n">
         <v>2.13</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="15" t="n">
         <v>-0.0184</v>
       </c>
       <c r="F13" s="11" t="n">
@@ -1140,7 +1472,7 @@
       <c r="D14" s="9" t="n">
         <v>0.225</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>0.09759999999999999</v>
       </c>
       <c r="F14" s="11" t="n">
@@ -1152,7 +1484,7 @@
       <c r="H14" t="n">
         <v>83.95999999999999</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1185,7 +1517,7 @@
       <c r="D15" s="9" t="n">
         <v>0.42</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>0.03700000000000001</v>
       </c>
       <c r="F15" s="11" t="n">
@@ -1197,7 +1529,7 @@
       <c r="H15" t="n">
         <v>65.15000000000001</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1230,7 +1562,7 @@
       <c r="D16" s="9" t="n">
         <v>2.51</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>0.0162</v>
       </c>
       <c r="F16" s="11" t="n">
@@ -1242,7 +1574,7 @@
       <c r="H16" t="n">
         <v>65.55</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1275,7 +1607,7 @@
       <c r="D17" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>0.1429</v>
       </c>
       <c r="F17" s="11" t="n">
@@ -1320,7 +1652,7 @@
       <c r="D18" s="9" t="n">
         <v>0.025</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
@@ -1365,7 +1697,7 @@
       <c r="D19" s="9" t="n">
         <v>4.78</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="15" t="n">
         <v>-0.0124</v>
       </c>
       <c r="F19" s="11" t="n">
@@ -1410,7 +1742,7 @@
       <c r="D20" s="9" t="n">
         <v>0.475</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>0.0215</v>
       </c>
       <c r="F20" s="11" t="n">
@@ -1422,7 +1754,7 @@
       <c r="H20" t="n">
         <v>53.21</v>
       </c>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1455,7 +1787,7 @@
       <c r="D21" s="9" t="n">
         <v>0.77</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>0.006500000000000001</v>
       </c>
       <c r="F21" s="11" t="n">
@@ -1467,7 +1799,7 @@
       <c r="H21" t="n">
         <v>61.79</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1500,7 +1832,7 @@
       <c r="D22" s="9" t="n">
         <v>0.395</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="15" t="n">
         <v>-0.0247</v>
       </c>
       <c r="F22" s="11" t="n">
@@ -1512,7 +1844,7 @@
       <c r="H22" t="n">
         <v>85.45999999999999</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1545,7 +1877,7 @@
       <c r="D23" s="9" t="n">
         <v>0.035</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="15" t="n">
         <v>-0.125</v>
       </c>
       <c r="F23" s="11" t="n">
@@ -1590,7 +1922,7 @@
       <c r="D24" s="9" t="n">
         <v>1.83</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="15" t="n">
         <v>-0.0161</v>
       </c>
       <c r="F24" s="11" t="n">
@@ -1602,7 +1934,7 @@
       <c r="H24" t="n">
         <v>65.5</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1635,7 +1967,7 @@
       <c r="D25" s="9" t="n">
         <v>0.67</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>0.0388</v>
       </c>
       <c r="F25" s="11" t="n">
@@ -1647,7 +1979,7 @@
       <c r="H25" t="n">
         <v>63.72</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I25" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1680,7 +2012,7 @@
       <c r="D26" s="9" t="n">
         <v>0.865</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="15" t="n">
         <v>-0.005699999999999999</v>
       </c>
       <c r="F26" s="11" t="n">
@@ -1725,7 +2057,7 @@
       <c r="D27" s="9" t="n">
         <v>7.93</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>0.0038</v>
       </c>
       <c r="F27" s="11" t="n">
@@ -1737,7 +2069,7 @@
       <c r="H27" t="n">
         <v>60.61</v>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1770,7 +2102,7 @@
       <c r="D28" s="9" t="n">
         <v>4.47</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>0.0395</v>
       </c>
       <c r="F28" s="11" t="n">
@@ -1782,7 +2114,7 @@
       <c r="H28" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="I28" s="15" t="inlineStr">
+      <c r="I28" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1815,7 +2147,7 @@
       <c r="D29" s="9" t="n">
         <v>0.55</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>0.0092</v>
       </c>
       <c r="F29" s="11" t="n">
@@ -1860,7 +2192,7 @@
       <c r="D30" s="9" t="n">
         <v>0.435</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>0.08749999999999999</v>
       </c>
       <c r="F30" s="11" t="n">
@@ -1872,7 +2204,7 @@
       <c r="H30" t="n">
         <v>62</v>
       </c>
-      <c r="I30" s="15" t="inlineStr">
+      <c r="I30" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1905,7 +2237,7 @@
       <c r="D31" s="9" t="n">
         <v>2.91</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>0.0175</v>
       </c>
       <c r="F31" s="11" t="n">
@@ -1917,7 +2249,7 @@
       <c r="H31" t="n">
         <v>63.31</v>
       </c>
-      <c r="I31" s="15" t="inlineStr">
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1950,7 +2282,7 @@
       <c r="D32" s="9" t="n">
         <v>2.43</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>0.0125</v>
       </c>
       <c r="F32" s="11" t="n">
@@ -1962,7 +2294,7 @@
       <c r="H32" t="n">
         <v>58.5</v>
       </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="I32" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1995,7 +2327,7 @@
       <c r="D33" s="9" t="n">
         <v>0.755</v>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="15" t="n">
         <v>-0.0258</v>
       </c>
       <c r="F33" s="11" t="n">
@@ -2040,7 +2372,7 @@
       <c r="D34" s="9" t="n">
         <v>0.775</v>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
@@ -2052,7 +2384,7 @@
       <c r="H34" t="n">
         <v>49.98</v>
       </c>
-      <c r="I34" s="15" t="inlineStr">
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2085,7 +2417,7 @@
       <c r="D35" s="9" t="n">
         <v>0.165</v>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
@@ -2130,7 +2462,7 @@
       <c r="D36" s="9" t="n">
         <v>0.705</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>0.0522</v>
       </c>
       <c r="F36" s="11" t="n">
@@ -2142,7 +2474,7 @@
       <c r="H36" t="n">
         <v>55.76</v>
       </c>
-      <c r="I36" s="15" t="inlineStr">
+      <c r="I36" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2175,7 +2507,7 @@
       <c r="D37" s="9" t="n">
         <v>0.54</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="15" t="n">
         <v>-0.0092</v>
       </c>
       <c r="F37" s="11" t="n">
@@ -2187,7 +2519,7 @@
       <c r="H37" t="n">
         <v>70.97</v>
       </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="I37" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2220,7 +2552,7 @@
       <c r="D38" s="9" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>0.0124</v>
       </c>
       <c r="F38" s="11" t="n">
@@ -2232,7 +2564,7 @@
       <c r="H38" t="n">
         <v>52.62</v>
       </c>
-      <c r="I38" s="15" t="inlineStr">
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2265,7 +2597,7 @@
       <c r="D39" s="9" t="n">
         <v>1.02</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>0.02</v>
       </c>
       <c r="F39" s="11" t="n">
@@ -2277,7 +2609,7 @@
       <c r="H39" t="n">
         <v>82.06</v>
       </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2310,7 +2642,7 @@
       <c r="D40" s="9" t="n">
         <v>0.31</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>0.0164</v>
       </c>
       <c r="F40" s="11" t="n">
@@ -2355,7 +2687,7 @@
       <c r="D41" s="9" t="n">
         <v>0.605</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="17" t="n">
         <v>0.0901</v>
       </c>
       <c r="F41" s="11" t="n">
@@ -2367,7 +2699,7 @@
       <c r="H41" t="n">
         <v>60.3</v>
       </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="I41" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2400,7 +2732,7 @@
       <c r="D42" s="9" t="n">
         <v>13.14</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>0.0031</v>
       </c>
       <c r="F42" s="11" t="n">
@@ -2412,7 +2744,7 @@
       <c r="H42" t="n">
         <v>27.14</v>
       </c>
-      <c r="I42" s="15" t="inlineStr">
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2445,7 +2777,7 @@
       <c r="D43" s="9" t="n">
         <v>10.14</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>0.001</v>
       </c>
       <c r="F43" s="11" t="n">
@@ -2457,7 +2789,7 @@
       <c r="H43" t="n">
         <v>44.03</v>
       </c>
-      <c r="I43" s="15" t="inlineStr">
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2490,7 +2822,7 @@
       <c r="D44" s="9" t="n">
         <v>6.29</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="17" t="n">
         <v>0.0016</v>
       </c>
       <c r="F44" s="11" t="n">
@@ -2502,7 +2834,7 @@
       <c r="H44" t="n">
         <v>44.97</v>
       </c>
-      <c r="I44" s="15" t="inlineStr">
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2535,7 +2867,7 @@
       <c r="D45" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>0.0345</v>
       </c>
       <c r="F45" s="11" t="n">
@@ -2580,7 +2912,7 @@
       <c r="D46" s="9" t="n">
         <v>5.91</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="15" t="n">
         <v>-0.0034</v>
       </c>
       <c r="F46" s="11" t="n">
@@ -2592,7 +2924,7 @@
       <c r="H46" t="n">
         <v>66.33</v>
       </c>
-      <c r="I46" s="15" t="inlineStr">
+      <c r="I46" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2625,7 +2957,7 @@
       <c r="D47" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E47" s="17" t="n">
+      <c r="E47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
@@ -2637,7 +2969,7 @@
       <c r="H47" t="n">
         <v>44.71</v>
       </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="I47" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2670,7 +3002,7 @@
       <c r="D48" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>0.0638</v>
       </c>
       <c r="F48" s="11" t="n">
@@ -2682,7 +3014,7 @@
       <c r="H48" t="n">
         <v>80.61</v>
       </c>
-      <c r="I48" s="15" t="inlineStr">
+      <c r="I48" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2715,7 +3047,7 @@
       <c r="D49" s="9" t="n">
         <v>1.02</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>0.0851</v>
       </c>
       <c r="F49" s="11" t="n">
@@ -2727,7 +3059,7 @@
       <c r="H49" t="n">
         <v>91.64</v>
       </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="I49" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2760,7 +3092,7 @@
       <c r="D50" s="9" t="n">
         <v>0.395</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>0.0128</v>
       </c>
       <c r="F50" s="11" t="n">
@@ -2805,7 +3137,7 @@
       <c r="D51" s="9" t="n">
         <v>0.035</v>
       </c>
-      <c r="E51" s="10" t="n">
+      <c r="E51" s="15" t="n">
         <v>-0.125</v>
       </c>
       <c r="F51" s="11" t="n">
@@ -2817,7 +3149,7 @@
       <c r="H51" t="n">
         <v>56.29</v>
       </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="I51" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2850,7 +3182,7 @@
       <c r="D52" s="9" t="n">
         <v>4.83</v>
       </c>
-      <c r="E52" s="10" t="n">
+      <c r="E52" s="15" t="n">
         <v>-0.0021</v>
       </c>
       <c r="F52" s="11" t="n">
@@ -2895,7 +3227,7 @@
       <c r="D53" s="9" t="n">
         <v>1.44</v>
       </c>
-      <c r="E53" s="17" t="n">
+      <c r="E53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
@@ -2907,7 +3239,7 @@
       <c r="H53" t="n">
         <v>63.01</v>
       </c>
-      <c r="I53" s="15" t="inlineStr">
+      <c r="I53" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2940,7 +3272,7 @@
       <c r="D54" s="9" t="n">
         <v>0.135</v>
       </c>
-      <c r="E54" s="10" t="n">
+      <c r="E54" s="15" t="n">
         <v>-0.06900000000000001</v>
       </c>
       <c r="F54" s="11" t="n">
@@ -2985,7 +3317,7 @@
       <c r="D55" s="9" t="n">
         <v>0.015</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="F55" s="11" t="n">
@@ -2997,7 +3329,7 @@
       <c r="H55" t="n">
         <v>70.03</v>
       </c>
-      <c r="I55" s="15" t="inlineStr">
+      <c r="I55" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3030,7 +3362,7 @@
       <c r="D56" s="9" t="n">
         <v>0.055</v>
       </c>
-      <c r="E56" s="10" t="n">
+      <c r="E56" s="15" t="n">
         <v>-0.0833</v>
       </c>
       <c r="F56" s="11" t="n">
@@ -3042,7 +3374,7 @@
       <c r="H56" t="n">
         <v>39.32</v>
       </c>
-      <c r="I56" s="15" t="inlineStr">
+      <c r="I56" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3075,7 +3407,7 @@
       <c r="D57" s="9" t="n">
         <v>7.86</v>
       </c>
-      <c r="E57" s="10" t="n">
+      <c r="E57" s="15" t="n">
         <v>-0.0051</v>
       </c>
       <c r="F57" s="11" t="n">
@@ -3087,7 +3419,7 @@
       <c r="H57" t="n">
         <v>36.24</v>
       </c>
-      <c r="I57" s="15" t="inlineStr">
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3120,7 +3452,7 @@
       <c r="D58" s="9" t="n">
         <v>0.37</v>
       </c>
-      <c r="E58" s="10" t="n">
+      <c r="E58" s="15" t="n">
         <v>-0.0263</v>
       </c>
       <c r="F58" s="11" t="n">
@@ -3132,7 +3464,7 @@
       <c r="H58" t="n">
         <v>50.08</v>
       </c>
-      <c r="I58" s="15" t="inlineStr">
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3165,7 +3497,7 @@
       <c r="D59" s="9" t="n">
         <v>1.29</v>
       </c>
-      <c r="E59" s="17" t="n">
+      <c r="E59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
@@ -3177,7 +3509,7 @@
       <c r="H59" t="n">
         <v>32.39</v>
       </c>
-      <c r="I59" s="15" t="inlineStr">
+      <c r="I59" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3210,7 +3542,7 @@
       <c r="D60" s="9" t="n">
         <v>0.57</v>
       </c>
-      <c r="E60" s="16" t="n">
+      <c r="E60" s="17" t="n">
         <v>0.0179</v>
       </c>
       <c r="F60" s="11" t="n">
@@ -3222,7 +3554,7 @@
       <c r="H60" t="n">
         <v>53.43</v>
       </c>
-      <c r="I60" s="15" t="inlineStr">
+      <c r="I60" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3255,7 +3587,7 @@
       <c r="D61" s="9" t="n">
         <v>0.285</v>
       </c>
-      <c r="E61" s="10" t="n">
+      <c r="E61" s="15" t="n">
         <v>-0.0172</v>
       </c>
       <c r="F61" s="11" t="n">
@@ -3267,7 +3599,7 @@
       <c r="H61" t="n">
         <v>65.79000000000001</v>
       </c>
-      <c r="I61" s="15" t="inlineStr">
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3300,7 +3632,7 @@
       <c r="D62" s="9" t="n">
         <v>1.69</v>
       </c>
-      <c r="E62" s="10" t="n">
+      <c r="E62" s="15" t="n">
         <v>-0.0174</v>
       </c>
       <c r="F62" s="11" t="n">
@@ -3345,7 +3677,7 @@
       <c r="D63" s="9" t="n">
         <v>0.895</v>
       </c>
-      <c r="E63" s="16" t="n">
+      <c r="E63" s="17" t="n">
         <v>0.0113</v>
       </c>
       <c r="F63" s="11" t="n">
@@ -3357,7 +3689,7 @@
       <c r="H63" t="n">
         <v>66.95</v>
       </c>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3390,7 +3722,7 @@
       <c r="D64" s="9" t="n">
         <v>0.27</v>
       </c>
-      <c r="E64" s="16" t="n">
+      <c r="E64" s="17" t="n">
         <v>0.0385</v>
       </c>
       <c r="F64" s="11" t="n">
@@ -3402,7 +3734,7 @@
       <c r="H64" t="n">
         <v>43.1</v>
       </c>
-      <c r="I64" s="15" t="inlineStr">
+      <c r="I64" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3435,7 +3767,7 @@
       <c r="D65" s="9" t="n">
         <v>0.435</v>
       </c>
-      <c r="E65" s="10" t="n">
+      <c r="E65" s="15" t="n">
         <v>-0.0114</v>
       </c>
       <c r="F65" s="11" t="n">
@@ -3447,7 +3779,7 @@
       <c r="H65" t="n">
         <v>48.81</v>
       </c>
-      <c r="I65" s="15" t="inlineStr">
+      <c r="I65" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3480,7 +3812,7 @@
       <c r="D66" s="9" t="n">
         <v>0.545</v>
       </c>
-      <c r="E66" s="17" t="n">
+      <c r="E66" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
@@ -3525,7 +3857,7 @@
       <c r="D67" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="E67" s="17" t="n">
+      <c r="E67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
@@ -3537,7 +3869,7 @@
       <c r="H67" t="n">
         <v>56.69</v>
       </c>
-      <c r="I67" s="15" t="inlineStr">
+      <c r="I67" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3570,7 +3902,7 @@
       <c r="D68" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E68" s="17" t="n">
+      <c r="E68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
@@ -3615,7 +3947,7 @@
       <c r="D69" s="9" t="n">
         <v>0.065</v>
       </c>
-      <c r="E69" s="16" t="n">
+      <c r="E69" s="17" t="n">
         <v>0.0833</v>
       </c>
       <c r="F69" s="11" t="n">
@@ -3660,7 +3992,7 @@
       <c r="D70" s="9" t="n">
         <v>0.195</v>
       </c>
-      <c r="E70" s="10" t="n">
+      <c r="E70" s="15" t="n">
         <v>-0.025</v>
       </c>
       <c r="F70" s="11" t="n">
@@ -3705,7 +4037,7 @@
       <c r="D71" s="9" t="n">
         <v>3.79</v>
       </c>
-      <c r="E71" s="16" t="n">
+      <c r="E71" s="17" t="n">
         <v>0.0243</v>
       </c>
       <c r="F71" s="11" t="n">
@@ -3717,7 +4049,7 @@
       <c r="H71" t="n">
         <v>72.43000000000001</v>
       </c>
-      <c r="I71" s="15" t="inlineStr">
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3750,7 +4082,7 @@
       <c r="D72" s="9" t="n">
         <v>0.265</v>
       </c>
-      <c r="E72" s="10" t="n">
+      <c r="E72" s="15" t="n">
         <v>-0.0185</v>
       </c>
       <c r="F72" s="11" t="n">
@@ -3762,7 +4094,7 @@
       <c r="H72" t="n">
         <v>46.71</v>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="I72" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3795,7 +4127,7 @@
       <c r="D73" s="9" t="n">
         <v>0.445</v>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E73" s="17" t="n">
         <v>0.0471</v>
       </c>
       <c r="F73" s="11" t="n">
@@ -3807,7 +4139,7 @@
       <c r="H73" t="n">
         <v>56.42</v>
       </c>
-      <c r="I73" s="15" t="inlineStr">
+      <c r="I73" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3840,7 +4172,7 @@
       <c r="D74" s="9" t="n">
         <v>0.77</v>
       </c>
-      <c r="E74" s="10" t="n">
+      <c r="E74" s="15" t="n">
         <v>-0.006500000000000001</v>
       </c>
       <c r="F74" s="11" t="n">
@@ -3885,7 +4217,7 @@
       <c r="D75" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="E75" s="17" t="n">
+      <c r="E75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
@@ -3897,7 +4229,7 @@
       <c r="H75" t="n">
         <v>64.68000000000001</v>
       </c>
-      <c r="I75" s="15" t="inlineStr">
+      <c r="I75" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3930,7 +4262,7 @@
       <c r="D76" s="9" t="n">
         <v>0.315</v>
       </c>
-      <c r="E76" s="16" t="n">
+      <c r="E76" s="17" t="n">
         <v>0.0161</v>
       </c>
       <c r="F76" s="11" t="n">
@@ -3942,7 +4274,7 @@
       <c r="H76" t="n">
         <v>72.65000000000001</v>
       </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="I76" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3975,7 +4307,7 @@
       <c r="D77" s="9" t="n">
         <v>0.01</v>
       </c>
-      <c r="E77" s="17" t="n">
+      <c r="E77" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
@@ -3987,7 +4319,7 @@
       <c r="H77" t="n">
         <v>51.13</v>
       </c>
-      <c r="I77" s="15" t="inlineStr">
+      <c r="I77" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4020,7 +4352,7 @@
       <c r="D78" s="9" t="n">
         <v>0.165</v>
       </c>
-      <c r="E78" s="16" t="n">
+      <c r="E78" s="17" t="n">
         <v>0.0313</v>
       </c>
       <c r="F78" s="11" t="n">
@@ -4032,7 +4364,7 @@
       <c r="H78" t="n">
         <v>53.7</v>
       </c>
-      <c r="I78" s="15" t="inlineStr">
+      <c r="I78" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4065,7 +4397,7 @@
       <c r="D79" s="9" t="n">
         <v>0.64</v>
       </c>
-      <c r="E79" s="16" t="n">
+      <c r="E79" s="17" t="n">
         <v>0.0579</v>
       </c>
       <c r="F79" s="11" t="n">
@@ -4110,7 +4442,7 @@
       <c r="D80" s="9" t="n">
         <v>2.55</v>
       </c>
-      <c r="E80" s="16" t="n">
+      <c r="E80" s="17" t="n">
         <v>0.0897</v>
       </c>
       <c r="F80" s="11" t="n">
@@ -4122,7 +4454,7 @@
       <c r="H80" t="n">
         <v>85.41</v>
       </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="I80" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4155,7 +4487,7 @@
       <c r="D81" s="9" t="n">
         <v>0.325</v>
       </c>
-      <c r="E81" s="17" t="n">
+      <c r="E81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
@@ -4167,7 +4499,7 @@
       <c r="H81" t="n">
         <v>49.21</v>
       </c>
-      <c r="I81" s="15" t="inlineStr">
+      <c r="I81" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4200,7 +4532,7 @@
       <c r="D82" s="9" t="n">
         <v>0.215</v>
       </c>
-      <c r="E82" s="16" t="n">
+      <c r="E82" s="17" t="n">
         <v>0.0488</v>
       </c>
       <c r="F82" s="11" t="n">
@@ -4245,7 +4577,7 @@
       <c r="D83" s="9" t="n">
         <v>0.09</v>
       </c>
-      <c r="E83" s="16" t="n">
+      <c r="E83" s="17" t="n">
         <v>0.2</v>
       </c>
       <c r="F83" s="11" t="n">
@@ -4257,7 +4589,7 @@
       <c r="H83" t="n">
         <v>78.77</v>
       </c>
-      <c r="I83" s="15" t="inlineStr">
+      <c r="I83" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4290,7 +4622,7 @@
       <c r="D84" s="9" t="n">
         <v>0.35</v>
       </c>
-      <c r="E84" s="17" t="n">
+      <c r="E84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="11" t="n">
@@ -4335,7 +4667,7 @@
       <c r="D85" s="9" t="n">
         <v>0.59</v>
       </c>
-      <c r="E85" s="16" t="n">
+      <c r="E85" s="17" t="n">
         <v>0.0172</v>
       </c>
       <c r="F85" s="11" t="n">
@@ -4380,7 +4712,7 @@
       <c r="D86" s="9" t="n">
         <v>4.49</v>
       </c>
-      <c r="E86" s="10" t="n">
+      <c r="E86" s="15" t="n">
         <v>-0.011</v>
       </c>
       <c r="F86" s="11" t="n">
@@ -4425,7 +4757,7 @@
       <c r="D87" s="9" t="n">
         <v>1.12</v>
       </c>
-      <c r="E87" s="17" t="n">
+      <c r="E87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
@@ -4437,7 +4769,7 @@
       <c r="H87" t="n">
         <v>59.72</v>
       </c>
-      <c r="I87" s="15" t="inlineStr">
+      <c r="I87" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4470,7 +4802,7 @@
       <c r="D88" s="9" t="n">
         <v>0.38</v>
       </c>
-      <c r="E88" s="16" t="n">
+      <c r="E88" s="17" t="n">
         <v>0.0133</v>
       </c>
       <c r="F88" s="11" t="n">
@@ -4482,7 +4814,7 @@
       <c r="H88" t="n">
         <v>40.08</v>
       </c>
-      <c r="I88" s="15" t="inlineStr">
+      <c r="I88" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4515,7 +4847,7 @@
       <c r="D89" s="9" t="n">
         <v>1.96</v>
       </c>
-      <c r="E89" s="10" t="n">
+      <c r="E89" s="15" t="n">
         <v>-0.02</v>
       </c>
       <c r="F89" s="11" t="n">
@@ -4527,7 +4859,7 @@
       <c r="H89" t="n">
         <v>46.47</v>
       </c>
-      <c r="I89" s="15" t="inlineStr">
+      <c r="I89" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4560,7 +4892,7 @@
       <c r="D90" s="9" t="n">
         <v>1.19</v>
       </c>
-      <c r="E90" s="16" t="n">
+      <c r="E90" s="17" t="n">
         <v>0.0259</v>
       </c>
       <c r="F90" s="11" t="n">
@@ -4572,7 +4904,7 @@
       <c r="H90" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="I90" s="15" t="inlineStr">
+      <c r="I90" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4605,7 +4937,7 @@
       <c r="D91" s="9" t="n">
         <v>7.59</v>
       </c>
-      <c r="E91" s="10" t="n">
+      <c r="E91" s="15" t="n">
         <v>-0.0013</v>
       </c>
       <c r="F91" s="11" t="n">
@@ -4650,7 +4982,7 @@
       <c r="D92" s="9" t="n">
         <v>1.81</v>
       </c>
-      <c r="E92" s="16" t="n">
+      <c r="E92" s="17" t="n">
         <v>0.0169</v>
       </c>
       <c r="F92" s="11" t="n">
@@ -4662,7 +4994,7 @@
       <c r="H92" t="n">
         <v>54.05</v>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I92" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4695,7 +5027,7 @@
       <c r="D93" s="9" t="n">
         <v>6.75</v>
       </c>
-      <c r="E93" s="16" t="n">
+      <c r="E93" s="17" t="n">
         <v>0.006</v>
       </c>
       <c r="F93" s="11" t="n">
@@ -4740,7 +5072,7 @@
       <c r="D94" s="9" t="n">
         <v>0.62</v>
       </c>
-      <c r="E94" s="10" t="n">
+      <c r="E94" s="15" t="n">
         <v>-0.0388</v>
       </c>
       <c r="F94" s="11" t="n">
@@ -4785,7 +5117,7 @@
       <c r="D95" s="9" t="n">
         <v>0.365</v>
       </c>
-      <c r="E95" s="10" t="n">
+      <c r="E95" s="15" t="n">
         <v>-0.0135</v>
       </c>
       <c r="F95" s="11" t="n">
@@ -4797,7 +5129,7 @@
       <c r="H95" t="n">
         <v>49.01</v>
       </c>
-      <c r="I95" s="15" t="inlineStr">
+      <c r="I95" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4830,7 +5162,7 @@
       <c r="D96" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="E96" s="16" t="n">
+      <c r="E96" s="17" t="n">
         <v>0.0098</v>
       </c>
       <c r="F96" s="11" t="n">
@@ -4842,7 +5174,7 @@
       <c r="H96" t="n">
         <v>58.56</v>
       </c>
-      <c r="I96" s="15" t="inlineStr">
+      <c r="I96" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4875,7 +5207,7 @@
       <c r="D97" s="9" t="n">
         <v>0.415</v>
       </c>
-      <c r="E97" s="17" t="n">
+      <c r="E97" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
@@ -4887,7 +5219,7 @@
       <c r="H97" t="n">
         <v>69.53</v>
       </c>
-      <c r="I97" s="15" t="inlineStr">
+      <c r="I97" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4920,7 +5252,7 @@
       <c r="D98" s="9" t="n">
         <v>1.29</v>
       </c>
-      <c r="E98" s="10" t="n">
+      <c r="E98" s="15" t="n">
         <v>-0.0227</v>
       </c>
       <c r="F98" s="11" t="n">
@@ -4965,7 +5297,7 @@
       <c r="D99" s="9" t="n">
         <v>2.68</v>
       </c>
-      <c r="E99" s="10" t="n">
+      <c r="E99" s="15" t="n">
         <v>-0.0074</v>
       </c>
       <c r="F99" s="11" t="n">
@@ -4977,7 +5309,7 @@
       <c r="H99" t="n">
         <v>61.45</v>
       </c>
-      <c r="I99" s="15" t="inlineStr">
+      <c r="I99" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5010,7 +5342,7 @@
       <c r="D100" s="9" t="n">
         <v>0.775</v>
       </c>
-      <c r="E100" s="16" t="n">
+      <c r="E100" s="17" t="n">
         <v>0.0131</v>
       </c>
       <c r="F100" s="11" t="n">
@@ -5022,7 +5354,7 @@
       <c r="H100" t="n">
         <v>74.29000000000001</v>
       </c>
-      <c r="I100" s="15" t="inlineStr">
+      <c r="I100" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5055,7 +5387,7 @@
       <c r="D101" s="9" t="n">
         <v>0.215</v>
       </c>
-      <c r="E101" s="16" t="n">
+      <c r="E101" s="17" t="n">
         <v>0.075</v>
       </c>
       <c r="F101" s="11" t="n">
@@ -5067,7 +5399,7 @@
       <c r="H101" t="n">
         <v>79.92</v>
       </c>
-      <c r="I101" s="15" t="inlineStr">
+      <c r="I101" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5100,7 +5432,7 @@
       <c r="D102" s="9" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E102" s="10" t="n">
+      <c r="E102" s="15" t="n">
         <v>-0.0122</v>
       </c>
       <c r="F102" s="11" t="n">
@@ -5112,7 +5444,7 @@
       <c r="H102" t="n">
         <v>51.14</v>
       </c>
-      <c r="I102" s="15" t="inlineStr">
+      <c r="I102" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5145,7 +5477,7 @@
       <c r="D103" s="9" t="n">
         <v>0.88</v>
       </c>
-      <c r="E103" s="10" t="n">
+      <c r="E103" s="15" t="n">
         <v>-0.0168</v>
       </c>
       <c r="F103" s="11" t="n">
@@ -5190,7 +5522,7 @@
       <c r="D104" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="E104" s="16" t="n">
+      <c r="E104" s="17" t="n">
         <v>0.0086</v>
       </c>
       <c r="F104" s="11" t="n">
@@ -5202,7 +5534,7 @@
       <c r="H104" t="n">
         <v>41.8</v>
       </c>
-      <c r="I104" s="15" t="inlineStr">
+      <c r="I104" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5235,7 +5567,7 @@
       <c r="D105" s="9" t="n">
         <v>0.545</v>
       </c>
-      <c r="E105" s="16" t="n">
+      <c r="E105" s="17" t="n">
         <v>0.0187</v>
       </c>
       <c r="F105" s="11" t="n">
@@ -5247,7 +5579,7 @@
       <c r="H105" t="n">
         <v>64.2</v>
       </c>
-      <c r="I105" s="15" t="inlineStr">
+      <c r="I105" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5280,7 +5612,7 @@
       <c r="D106" s="9" t="n">
         <v>1.09</v>
       </c>
-      <c r="E106" s="17" t="n">
+      <c r="E106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
@@ -5292,7 +5624,7 @@
       <c r="H106" t="n">
         <v>78.48</v>
       </c>
-      <c r="I106" s="15" t="inlineStr">
+      <c r="I106" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5325,7 +5657,7 @@
       <c r="D107" s="9" t="n">
         <v>0.255</v>
       </c>
-      <c r="E107" s="16" t="n">
+      <c r="E107" s="17" t="n">
         <v>0.0625</v>
       </c>
       <c r="F107" s="11" t="n">
@@ -5370,7 +5702,7 @@
       <c r="D108" s="9" t="n">
         <v>0.705</v>
       </c>
-      <c r="E108" s="17" t="n">
+      <c r="E108" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
@@ -5382,7 +5714,7 @@
       <c r="H108" t="n">
         <v>49.29</v>
       </c>
-      <c r="I108" s="15" t="inlineStr">
+      <c r="I108" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5415,7 +5747,7 @@
       <c r="D109" s="9" t="n">
         <v>0.295</v>
       </c>
-      <c r="E109" s="16" t="n">
+      <c r="E109" s="17" t="n">
         <v>0.0351</v>
       </c>
       <c r="F109" s="11" t="n">
@@ -5427,7 +5759,7 @@
       <c r="H109" t="n">
         <v>68.43000000000001</v>
       </c>
-      <c r="I109" s="15" t="inlineStr">
+      <c r="I109" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5460,7 +5792,7 @@
       <c r="D110" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E110" s="16" t="n">
+      <c r="E110" s="17" t="n">
         <v>0.25</v>
       </c>
       <c r="F110" s="11" t="n">
@@ -5505,7 +5837,7 @@
       <c r="D111" s="9" t="n">
         <v>0.725</v>
       </c>
-      <c r="E111" s="16" t="n">
+      <c r="E111" s="17" t="n">
         <v>0.0069</v>
       </c>
       <c r="F111" s="11" t="n">
@@ -5517,7 +5849,7 @@
       <c r="H111" t="n">
         <v>71.11</v>
       </c>
-      <c r="I111" s="15" t="inlineStr">
+      <c r="I111" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5550,7 +5882,7 @@
       <c r="D112" s="9" t="n">
         <v>0.53</v>
       </c>
-      <c r="E112" s="16" t="n">
+      <c r="E112" s="17" t="n">
         <v>0.0095</v>
       </c>
       <c r="F112" s="11" t="n">
@@ -5562,7 +5894,7 @@
       <c r="H112" t="n">
         <v>55.55</v>
       </c>
-      <c r="I112" s="15" t="inlineStr">
+      <c r="I112" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5595,7 +5927,7 @@
       <c r="D113" s="9" t="n">
         <v>0.33</v>
       </c>
-      <c r="E113" s="16" t="n">
+      <c r="E113" s="17" t="n">
         <v>0.0313</v>
       </c>
       <c r="F113" s="11" t="n">
@@ -5607,7 +5939,7 @@
       <c r="H113" t="n">
         <v>95.13</v>
       </c>
-      <c r="I113" s="15" t="inlineStr">
+      <c r="I113" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5640,7 +5972,7 @@
       <c r="D114" s="9" t="n">
         <v>0.77</v>
       </c>
-      <c r="E114" s="17" t="n">
+      <c r="E114" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
@@ -5652,7 +5984,7 @@
       <c r="H114" t="n">
         <v>76.65000000000001</v>
       </c>
-      <c r="I114" s="15" t="inlineStr">
+      <c r="I114" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5685,7 +6017,7 @@
       <c r="D115" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E115" s="10" t="n">
+      <c r="E115" s="15" t="n">
         <v>-0.0222</v>
       </c>
       <c r="F115" s="11" t="n">
@@ -5730,7 +6062,7 @@
       <c r="D116" s="9" t="n">
         <v>0.335</v>
       </c>
-      <c r="E116" s="10" t="n">
+      <c r="E116" s="15" t="n">
         <v>-0.0147</v>
       </c>
       <c r="F116" s="11" t="n">
@@ -5742,7 +6074,7 @@
       <c r="H116" t="n">
         <v>54.93</v>
       </c>
-      <c r="I116" s="15" t="inlineStr">
+      <c r="I116" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5775,7 +6107,7 @@
       <c r="D117" s="9" t="n">
         <v>0.79</v>
       </c>
-      <c r="E117" s="16" t="n">
+      <c r="E117" s="17" t="n">
         <v>0.0395</v>
       </c>
       <c r="F117" s="11" t="n">
@@ -5787,7 +6119,7 @@
       <c r="H117" t="n">
         <v>60.07</v>
       </c>
-      <c r="I117" s="15" t="inlineStr">
+      <c r="I117" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5820,7 +6152,7 @@
       <c r="D118" s="9" t="n">
         <v>3.61</v>
       </c>
-      <c r="E118" s="16" t="n">
+      <c r="E118" s="17" t="n">
         <v>0.0256</v>
       </c>
       <c r="F118" s="11" t="n">
@@ -5832,7 +6164,7 @@
       <c r="H118" t="n">
         <v>52.56</v>
       </c>
-      <c r="I118" s="15" t="inlineStr">
+      <c r="I118" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5865,7 +6197,7 @@
       <c r="D119" s="9" t="n">
         <v>4.98</v>
       </c>
-      <c r="E119" s="10" t="n">
+      <c r="E119" s="15" t="n">
         <v>-0.0254</v>
       </c>
       <c r="F119" s="11" t="n">
@@ -5877,7 +6209,7 @@
       <c r="H119" t="n">
         <v>49.62</v>
       </c>
-      <c r="I119" s="15" t="inlineStr">
+      <c r="I119" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5910,7 +6242,7 @@
       <c r="D120" s="9" t="n">
         <v>0.19</v>
       </c>
-      <c r="E120" s="10" t="n">
+      <c r="E120" s="15" t="n">
         <v>-0.0256</v>
       </c>
       <c r="F120" s="11" t="n">
@@ -5922,7 +6254,7 @@
       <c r="H120" t="n">
         <v>46.97</v>
       </c>
-      <c r="I120" s="15" t="inlineStr">
+      <c r="I120" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5955,7 +6287,7 @@
       <c r="D121" s="9" t="n">
         <v>0.87</v>
       </c>
-      <c r="E121" s="17" t="n">
+      <c r="E121" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
@@ -6000,7 +6332,7 @@
       <c r="D122" s="9" t="n">
         <v>6.62</v>
       </c>
-      <c r="E122" s="10" t="n">
+      <c r="E122" s="15" t="n">
         <v>-0.003</v>
       </c>
       <c r="F122" s="11" t="n">
@@ -6045,7 +6377,7 @@
       <c r="D123" s="9" t="n">
         <v>0.37</v>
       </c>
-      <c r="E123" s="16" t="n">
+      <c r="E123" s="17" t="n">
         <v>0.0278</v>
       </c>
       <c r="F123" s="11" t="n">
@@ -6057,7 +6389,7 @@
       <c r="H123" t="n">
         <v>77.02</v>
       </c>
-      <c r="I123" s="15" t="inlineStr">
+      <c r="I123" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6090,7 +6422,7 @@
       <c r="D124" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E124" s="16" t="n">
+      <c r="E124" s="17" t="n">
         <v>0.008399999999999999</v>
       </c>
       <c r="F124" s="11" t="n">
@@ -6102,7 +6434,7 @@
       <c r="H124" t="n">
         <v>60.13</v>
       </c>
-      <c r="I124" s="15" t="inlineStr">
+      <c r="I124" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6135,7 +6467,7 @@
       <c r="D125" s="9" t="n">
         <v>1.97</v>
       </c>
-      <c r="E125" s="16" t="n">
+      <c r="E125" s="17" t="n">
         <v>0.0051</v>
       </c>
       <c r="F125" s="11" t="n">
@@ -6147,7 +6479,7 @@
       <c r="H125" t="n">
         <v>38.8</v>
       </c>
-      <c r="I125" s="15" t="inlineStr">
+      <c r="I125" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6180,7 +6512,7 @@
       <c r="D126" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E126" s="16" t="n">
+      <c r="E126" s="17" t="n">
         <v>0.1111</v>
       </c>
       <c r="F126" s="11" t="n">
@@ -6192,7 +6524,7 @@
       <c r="H126" t="n">
         <v>75.56999999999999</v>
       </c>
-      <c r="I126" s="15" t="inlineStr">
+      <c r="I126" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6225,7 +6557,7 @@
       <c r="D127" s="9" t="n">
         <v>3.48</v>
       </c>
-      <c r="E127" s="10" t="n">
+      <c r="E127" s="15" t="n">
         <v>-0.005699999999999999</v>
       </c>
       <c r="F127" s="11" t="n">
@@ -6270,7 +6602,7 @@
       <c r="D128" s="9" t="n">
         <v>2.69</v>
       </c>
-      <c r="E128" s="16" t="n">
+      <c r="E128" s="17" t="n">
         <v>0.0151</v>
       </c>
       <c r="F128" s="11" t="n">
@@ -6282,7 +6614,7 @@
       <c r="H128" t="n">
         <v>46.68</v>
       </c>
-      <c r="I128" s="15" t="inlineStr">
+      <c r="I128" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6315,7 +6647,7 @@
       <c r="D129" s="9" t="n">
         <v>0.845</v>
       </c>
-      <c r="E129" s="10" t="n">
+      <c r="E129" s="15" t="n">
         <v>-0.0398</v>
       </c>
       <c r="F129" s="11" t="n">
@@ -6360,7 +6692,7 @@
       <c r="D130" s="9" t="n">
         <v>4.78</v>
       </c>
-      <c r="E130" s="10" t="n">
+      <c r="E130" s="15" t="n">
         <v>-0.0042</v>
       </c>
       <c r="F130" s="11" t="n">
@@ -6372,7 +6704,7 @@
       <c r="H130" t="n">
         <v>56.74</v>
       </c>
-      <c r="I130" s="15" t="inlineStr">
+      <c r="I130" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6405,7 +6737,7 @@
       <c r="D131" s="9" t="n">
         <v>2.67</v>
       </c>
-      <c r="E131" s="17" t="n">
+      <c r="E131" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
@@ -6450,7 +6782,7 @@
       <c r="D132" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E132" s="10" t="n">
+      <c r="E132" s="15" t="n">
         <v>-0.0476</v>
       </c>
       <c r="F132" s="11" t="n">
@@ -6462,7 +6794,7 @@
       <c r="H132" t="n">
         <v>51.57</v>
       </c>
-      <c r="I132" s="15" t="inlineStr">
+      <c r="I132" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6495,7 +6827,7 @@
       <c r="D133" s="9" t="n">
         <v>1.19</v>
       </c>
-      <c r="E133" s="10" t="n">
+      <c r="E133" s="15" t="n">
         <v>-0.0165</v>
       </c>
       <c r="F133" s="11" t="n">
@@ -6507,7 +6839,7 @@
       <c r="H133" t="n">
         <v>51.5</v>
       </c>
-      <c r="I133" s="15" t="inlineStr">
+      <c r="I133" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6540,7 +6872,7 @@
       <c r="D134" s="9" t="n">
         <v>4.74</v>
       </c>
-      <c r="E134" s="16" t="n">
+      <c r="E134" s="17" t="n">
         <v>0.0216</v>
       </c>
       <c r="F134" s="11" t="n">
@@ -6552,7 +6884,7 @@
       <c r="H134" t="n">
         <v>64.88</v>
       </c>
-      <c r="I134" s="15" t="inlineStr">
+      <c r="I134" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6585,7 +6917,7 @@
       <c r="D135" s="9" t="n">
         <v>0.295</v>
       </c>
-      <c r="E135" s="17" t="n">
+      <c r="E135" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
@@ -6630,7 +6962,7 @@
       <c r="D136" s="9" t="n">
         <v>0.35</v>
       </c>
-      <c r="E136" s="16" t="n">
+      <c r="E136" s="17" t="n">
         <v>0.06059999999999999</v>
       </c>
       <c r="F136" s="11" t="n">
@@ -6642,7 +6974,7 @@
       <c r="H136" t="n">
         <v>55.8</v>
       </c>
-      <c r="I136" s="15" t="inlineStr">
+      <c r="I136" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6675,7 +7007,7 @@
       <c r="D137" s="9" t="n">
         <v>1.88</v>
       </c>
-      <c r="E137" s="17" t="n">
+      <c r="E137" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
@@ -6720,7 +7052,7 @@
       <c r="D138" s="9" t="n">
         <v>1.08</v>
       </c>
-      <c r="E138" s="10" t="n">
+      <c r="E138" s="15" t="n">
         <v>-0.0182</v>
       </c>
       <c r="F138" s="11" t="n">
@@ -6765,7 +7097,7 @@
       <c r="D139" s="9" t="n">
         <v>0.205</v>
       </c>
-      <c r="E139" s="16" t="n">
+      <c r="E139" s="17" t="n">
         <v>0.0789</v>
       </c>
       <c r="F139" s="11" t="n">
@@ -6777,7 +7109,7 @@
       <c r="H139" t="n">
         <v>55.85</v>
       </c>
-      <c r="I139" s="15" t="inlineStr">
+      <c r="I139" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6810,7 +7142,7 @@
       <c r="D140" s="9" t="n">
         <v>0.245</v>
       </c>
-      <c r="E140" s="16" t="n">
+      <c r="E140" s="17" t="n">
         <v>0.0208</v>
       </c>
       <c r="F140" s="11" t="n">
@@ -6822,7 +7154,7 @@
       <c r="H140" t="n">
         <v>79.02</v>
       </c>
-      <c r="I140" s="15" t="inlineStr">
+      <c r="I140" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6855,7 +7187,7 @@
       <c r="D141" s="9" t="n">
         <v>0.36</v>
       </c>
-      <c r="E141" s="16" t="n">
+      <c r="E141" s="17" t="n">
         <v>0.1429</v>
       </c>
       <c r="F141" s="11" t="n">
@@ -6867,7 +7199,7 @@
       <c r="H141" t="n">
         <v>72.55</v>
       </c>
-      <c r="I141" s="15" t="inlineStr">
+      <c r="I141" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6900,7 +7232,7 @@
       <c r="D142" s="9" t="n">
         <v>1.27</v>
       </c>
-      <c r="E142" s="10" t="n">
+      <c r="E142" s="15" t="n">
         <v>-0.007800000000000001</v>
       </c>
       <c r="F142" s="11" t="n">
@@ -6945,7 +7277,7 @@
       <c r="D143" s="9" t="n">
         <v>0.18</v>
       </c>
-      <c r="E143" s="10" t="n">
+      <c r="E143" s="15" t="n">
         <v>-0.1</v>
       </c>
       <c r="F143" s="11" t="n">
@@ -6957,7 +7289,7 @@
       <c r="H143" t="n">
         <v>46.14</v>
       </c>
-      <c r="I143" s="15" t="inlineStr">
+      <c r="I143" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6990,7 +7322,7 @@
       <c r="D144" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="E144" s="10" t="n">
+      <c r="E144" s="15" t="n">
         <v>-0.0104</v>
       </c>
       <c r="F144" s="11" t="n">
@@ -7035,7 +7367,7 @@
       <c r="D145" s="9" t="n">
         <v>2.62</v>
       </c>
-      <c r="E145" s="16" t="n">
+      <c r="E145" s="17" t="n">
         <v>0.0116</v>
       </c>
       <c r="F145" s="11" t="n">
@@ -7047,7 +7379,7 @@
       <c r="H145" t="n">
         <v>57.2</v>
       </c>
-      <c r="I145" s="15" t="inlineStr">
+      <c r="I145" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7080,7 +7412,7 @@
       <c r="D146" s="9" t="n">
         <v>1.46</v>
       </c>
-      <c r="E146" s="10" t="n">
+      <c r="E146" s="15" t="n">
         <v>-0.0068</v>
       </c>
       <c r="F146" s="11" t="n">
@@ -7125,7 +7457,7 @@
       <c r="D147" s="9" t="n">
         <v>3.98</v>
       </c>
-      <c r="E147" s="16" t="n">
+      <c r="E147" s="17" t="n">
         <v>0.0179</v>
       </c>
       <c r="F147" s="11" t="n">
@@ -7137,7 +7469,7 @@
       <c r="H147" t="n">
         <v>54.8</v>
       </c>
-      <c r="I147" s="15" t="inlineStr">
+      <c r="I147" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7170,7 +7502,7 @@
       <c r="D148" s="9" t="n">
         <v>2.08</v>
       </c>
-      <c r="E148" s="16" t="n">
+      <c r="E148" s="17" t="n">
         <v>0.0097</v>
       </c>
       <c r="F148" s="11" t="n">
@@ -7182,7 +7514,7 @@
       <c r="H148" t="n">
         <v>50.01</v>
       </c>
-      <c r="I148" s="15" t="inlineStr">
+      <c r="I148" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7215,7 +7547,7 @@
       <c r="D149" s="9" t="n">
         <v>0.455</v>
       </c>
-      <c r="E149" s="16" t="n">
+      <c r="E149" s="17" t="n">
         <v>0.0341</v>
       </c>
       <c r="F149" s="11" t="n">
@@ -7227,7 +7559,7 @@
       <c r="H149" t="n">
         <v>51.7</v>
       </c>
-      <c r="I149" s="15" t="inlineStr">
+      <c r="I149" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7260,7 +7592,7 @@
       <c r="D150" s="9" t="n">
         <v>0.14</v>
       </c>
-      <c r="E150" s="17" t="n">
+      <c r="E150" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
@@ -7272,7 +7604,7 @@
       <c r="H150" t="n">
         <v>62.8</v>
       </c>
-      <c r="I150" s="15" t="inlineStr">
+      <c r="I150" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7305,7 +7637,7 @@
       <c r="D151" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="E151" s="16" t="n">
+      <c r="E151" s="17" t="n">
         <v>0.0573</v>
       </c>
       <c r="F151" s="11" t="n">
@@ -7317,7 +7649,7 @@
       <c r="H151" t="n">
         <v>80.95999999999999</v>
       </c>
-      <c r="I151" s="15" t="inlineStr">
+      <c r="I151" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7350,7 +7682,7 @@
       <c r="D152" s="9" t="n">
         <v>1.05</v>
       </c>
-      <c r="E152" s="16" t="n">
+      <c r="E152" s="17" t="n">
         <v>0.05</v>
       </c>
       <c r="F152" s="11" t="n">
@@ -7395,7 +7727,7 @@
       <c r="D153" s="9" t="n">
         <v>0.285</v>
       </c>
-      <c r="E153" s="10" t="n">
+      <c r="E153" s="15" t="n">
         <v>-0.0172</v>
       </c>
       <c r="F153" s="11" t="n">
@@ -7440,7 +7772,7 @@
       <c r="D154" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E154" s="17" t="n">
+      <c r="E154" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F154" s="11" t="n">
@@ -7452,7 +7784,7 @@
       <c r="H154" t="n">
         <v>51.03</v>
       </c>
-      <c r="I154" s="15" t="inlineStr">
+      <c r="I154" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7485,7 +7817,7 @@
       <c r="D155" s="9" t="n">
         <v>0.265</v>
       </c>
-      <c r="E155" s="10" t="n">
+      <c r="E155" s="15" t="n">
         <v>-0.0364</v>
       </c>
       <c r="F155" s="11" t="n">
@@ -7530,7 +7862,7 @@
       <c r="D156" s="9" t="n">
         <v>3.27</v>
       </c>
-      <c r="E156" s="16" t="n">
+      <c r="E156" s="17" t="n">
         <v>0.0124</v>
       </c>
       <c r="F156" s="11" t="n">
@@ -7575,7 +7907,7 @@
       <c r="D157" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="E157" s="16" t="n">
+      <c r="E157" s="17" t="n">
         <v>0.0039</v>
       </c>
       <c r="F157" s="11" t="n">
@@ -7587,7 +7919,7 @@
       <c r="H157" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="I157" s="15" t="inlineStr">
+      <c r="I157" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7620,7 +7952,7 @@
       <c r="D158" s="9" t="n">
         <v>6.66</v>
       </c>
-      <c r="E158" s="17" t="n">
+      <c r="E158" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F158" s="11" t="n">
@@ -7632,7 +7964,7 @@
       <c r="H158" t="n">
         <v>54.02</v>
       </c>
-      <c r="I158" s="15" t="inlineStr">
+      <c r="I158" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7665,7 +7997,7 @@
       <c r="D159" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="E159" s="16" t="n">
+      <c r="E159" s="17" t="n">
         <v>0.0051</v>
       </c>
       <c r="F159" s="11" t="n">
@@ -7677,7 +8009,7 @@
       <c r="H159" t="n">
         <v>48.84</v>
       </c>
-      <c r="I159" s="15" t="inlineStr">
+      <c r="I159" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7710,7 +8042,7 @@
       <c r="D160" s="9" t="n">
         <v>0.97</v>
       </c>
-      <c r="E160" s="17" t="n">
+      <c r="E160" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F160" s="11" t="n">
@@ -7755,7 +8087,7 @@
       <c r="D161" s="9" t="n">
         <v>2.97</v>
       </c>
-      <c r="E161" s="16" t="n">
+      <c r="E161" s="17" t="n">
         <v>0.0137</v>
       </c>
       <c r="F161" s="11" t="n">
@@ -7767,7 +8099,7 @@
       <c r="H161" t="n">
         <v>64.39</v>
       </c>
-      <c r="I161" s="15" t="inlineStr">
+      <c r="I161" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7800,7 +8132,7 @@
       <c r="D162" s="9" t="n">
         <v>1.15</v>
       </c>
-      <c r="E162" s="16" t="n">
+      <c r="E162" s="17" t="n">
         <v>0.008800000000000001</v>
       </c>
       <c r="F162" s="11" t="n">
@@ -7812,7 +8144,7 @@
       <c r="H162" t="n">
         <v>78.34999999999999</v>
       </c>
-      <c r="I162" s="15" t="inlineStr">
+      <c r="I162" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7845,7 +8177,7 @@
       <c r="D163" s="9" t="n">
         <v>1.03</v>
       </c>
-      <c r="E163" s="16" t="n">
+      <c r="E163" s="17" t="n">
         <v>0.0098</v>
       </c>
       <c r="F163" s="11" t="n">
@@ -7890,7 +8222,7 @@
       <c r="D164" s="9" t="n">
         <v>2.63</v>
       </c>
-      <c r="E164" s="16" t="n">
+      <c r="E164" s="17" t="n">
         <v>0.0038</v>
       </c>
       <c r="F164" s="11" t="n">
@@ -7935,7 +8267,7 @@
       <c r="D165" s="9" t="n">
         <v>6.13</v>
       </c>
-      <c r="E165" s="16" t="n">
+      <c r="E165" s="17" t="n">
         <v>0.0234</v>
       </c>
       <c r="F165" s="11" t="n">
@@ -7980,7 +8312,7 @@
       <c r="D166" s="9" t="n">
         <v>1.05</v>
       </c>
-      <c r="E166" s="10" t="n">
+      <c r="E166" s="15" t="n">
         <v>-0.009399999999999999</v>
       </c>
       <c r="F166" s="11" t="n">
@@ -7992,7 +8324,7 @@
       <c r="H166" t="n">
         <v>80.56999999999999</v>
       </c>
-      <c r="I166" s="15" t="inlineStr">
+      <c r="I166" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8025,7 +8357,7 @@
       <c r="D167" s="9" t="n">
         <v>0.28</v>
       </c>
-      <c r="E167" s="16" t="n">
+      <c r="E167" s="17" t="n">
         <v>0.0182</v>
       </c>
       <c r="F167" s="11" t="n">
@@ -8037,7 +8369,7 @@
       <c r="H167" t="n">
         <v>67.69</v>
       </c>
-      <c r="I167" s="15" t="inlineStr">
+      <c r="I167" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8070,7 +8402,7 @@
       <c r="D168" s="9" t="n">
         <v>0.54</v>
       </c>
-      <c r="E168" s="16" t="n">
+      <c r="E168" s="17" t="n">
         <v>0.0189</v>
       </c>
       <c r="F168" s="11" t="n">
@@ -8082,7 +8414,7 @@
       <c r="H168" t="n">
         <v>53.28</v>
       </c>
-      <c r="I168" s="15" t="inlineStr">
+      <c r="I168" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8115,7 +8447,7 @@
       <c r="D169" s="9" t="n">
         <v>1.81</v>
       </c>
-      <c r="E169" s="16" t="n">
+      <c r="E169" s="17" t="n">
         <v>0.005600000000000001</v>
       </c>
       <c r="F169" s="11" t="n">
@@ -8160,7 +8492,7 @@
       <c r="D170" s="9" t="n">
         <v>0.615</v>
       </c>
-      <c r="E170" s="17" t="n">
+      <c r="E170" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F170" s="11" t="n">
@@ -8172,7 +8504,7 @@
       <c r="H170" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="I170" s="15" t="inlineStr">
+      <c r="I170" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8205,7 +8537,7 @@
       <c r="D171" s="9" t="n">
         <v>0.845</v>
       </c>
-      <c r="E171" s="10" t="n">
+      <c r="E171" s="15" t="n">
         <v>-0.0174</v>
       </c>
       <c r="F171" s="11" t="n">
@@ -8217,7 +8549,7 @@
       <c r="H171" t="n">
         <v>65.62</v>
       </c>
-      <c r="I171" s="15" t="inlineStr">
+      <c r="I171" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8250,7 +8582,7 @@
       <c r="D172" s="9" t="n">
         <v>0.49</v>
       </c>
-      <c r="E172" s="10" t="n">
+      <c r="E172" s="15" t="n">
         <v>-0.0101</v>
       </c>
       <c r="F172" s="11" t="n">
@@ -8262,7 +8594,7 @@
       <c r="H172" t="n">
         <v>48.67</v>
       </c>
-      <c r="I172" s="15" t="inlineStr">
+      <c r="I172" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8295,7 +8627,7 @@
       <c r="D173" s="9" t="n">
         <v>8.75</v>
       </c>
-      <c r="E173" s="16" t="n">
+      <c r="E173" s="17" t="n">
         <v>0.0046</v>
       </c>
       <c r="F173" s="11" t="n">
@@ -8307,7 +8639,7 @@
       <c r="H173" t="n">
         <v>53.03</v>
       </c>
-      <c r="I173" s="15" t="inlineStr">
+      <c r="I173" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8340,7 +8672,7 @@
       <c r="D174" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="E174" s="16" t="n">
+      <c r="E174" s="17" t="n">
         <v>0.0064</v>
       </c>
       <c r="F174" s="11" t="n">
@@ -8385,7 +8717,7 @@
       <c r="D175" s="9" t="n">
         <v>0.36</v>
       </c>
-      <c r="E175" s="10" t="n">
+      <c r="E175" s="15" t="n">
         <v>-0.0137</v>
       </c>
       <c r="F175" s="11" t="n">
@@ -8397,7 +8729,7 @@
       <c r="H175" t="n">
         <v>42.14</v>
       </c>
-      <c r="I175" s="15" t="inlineStr">
+      <c r="I175" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8430,7 +8762,7 @@
       <c r="D176" s="9" t="n">
         <v>1.97</v>
       </c>
-      <c r="E176" s="16" t="n">
+      <c r="E176" s="17" t="n">
         <v>0.0423</v>
       </c>
       <c r="F176" s="11" t="n">
@@ -8442,7 +8774,7 @@
       <c r="H176" t="n">
         <v>60.57</v>
       </c>
-      <c r="I176" s="15" t="inlineStr">
+      <c r="I176" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8475,7 +8807,7 @@
       <c r="D177" s="9" t="n">
         <v>0.285</v>
       </c>
-      <c r="E177" s="16" t="n">
+      <c r="E177" s="17" t="n">
         <v>0.14</v>
       </c>
       <c r="F177" s="11" t="n">
@@ -8487,7 +8819,7 @@
       <c r="H177" t="n">
         <v>75.2</v>
       </c>
-      <c r="I177" s="15" t="inlineStr">
+      <c r="I177" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8520,7 +8852,7 @@
       <c r="D178" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E178" s="16" t="n">
+      <c r="E178" s="17" t="n">
         <v>0.0101</v>
       </c>
       <c r="F178" s="11" t="n">
@@ -8565,7 +8897,7 @@
       <c r="D179" s="9" t="n">
         <v>0.26</v>
       </c>
-      <c r="E179" s="17" t="n">
+      <c r="E179" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
@@ -8610,7 +8942,7 @@
       <c r="D180" s="9" t="n">
         <v>0.54</v>
       </c>
-      <c r="E180" s="17" t="n">
+      <c r="E180" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
@@ -8655,7 +8987,7 @@
       <c r="D181" s="9" t="n">
         <v>0.535</v>
       </c>
-      <c r="E181" s="16" t="n">
+      <c r="E181" s="17" t="n">
         <v>0.049</v>
       </c>
       <c r="F181" s="11" t="n">
@@ -8667,7 +8999,7 @@
       <c r="H181" t="n">
         <v>62.41</v>
       </c>
-      <c r="I181" s="15" t="inlineStr">
+      <c r="I181" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8700,7 +9032,7 @@
       <c r="D182" s="9" t="n">
         <v>0.215</v>
       </c>
-      <c r="E182" s="17" t="n">
+      <c r="E182" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F182" s="11" t="n">
@@ -8712,7 +9044,7 @@
       <c r="H182" t="n">
         <v>64.44</v>
       </c>
-      <c r="I182" s="15" t="inlineStr">
+      <c r="I182" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8745,7 +9077,7 @@
       <c r="D183" s="9" t="n">
         <v>4.39</v>
       </c>
-      <c r="E183" s="16" t="n">
+      <c r="E183" s="17" t="n">
         <v>0.0092</v>
       </c>
       <c r="F183" s="11" t="n">
@@ -8790,7 +9122,7 @@
       <c r="D184" s="9" t="n">
         <v>0.585</v>
       </c>
-      <c r="E184" s="10" t="n">
+      <c r="E184" s="15" t="n">
         <v>-0.0168</v>
       </c>
       <c r="F184" s="11" t="n">
@@ -8802,7 +9134,7 @@
       <c r="H184" t="n">
         <v>46.86</v>
       </c>
-      <c r="I184" s="15" t="inlineStr">
+      <c r="I184" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8835,7 +9167,7 @@
       <c r="D185" s="9" t="n">
         <v>1.57</v>
       </c>
-      <c r="E185" s="10" t="n">
+      <c r="E185" s="15" t="n">
         <v>-0.0126</v>
       </c>
       <c r="F185" s="11" t="n">
@@ -8847,7 +9179,7 @@
       <c r="H185" t="n">
         <v>42.33</v>
       </c>
-      <c r="I185" s="15" t="inlineStr">
+      <c r="I185" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8880,7 +9212,7 @@
       <c r="D186" s="9" t="n">
         <v>3.85</v>
       </c>
-      <c r="E186" s="10" t="n">
+      <c r="E186" s="15" t="n">
         <v>-0.0179</v>
       </c>
       <c r="F186" s="11" t="n">
@@ -8892,7 +9224,7 @@
       <c r="H186" t="n">
         <v>62.7</v>
       </c>
-      <c r="I186" s="15" t="inlineStr">
+      <c r="I186" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8925,7 +9257,7 @@
       <c r="D187" s="9" t="n">
         <v>3.39</v>
       </c>
-      <c r="E187" s="10" t="n">
+      <c r="E187" s="15" t="n">
         <v>-0.0117</v>
       </c>
       <c r="F187" s="11" t="n">
@@ -8970,7 +9302,7 @@
       <c r="D188" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="E188" s="16" t="n">
+      <c r="E188" s="17" t="n">
         <v>0.0145</v>
       </c>
       <c r="F188" s="11" t="n">
@@ -9015,7 +9347,7 @@
       <c r="D189" s="9" t="n">
         <v>0.98</v>
       </c>
-      <c r="E189" s="10" t="n">
+      <c r="E189" s="15" t="n">
         <v>-0.02</v>
       </c>
       <c r="F189" s="11" t="n">
@@ -9027,7 +9359,7 @@
       <c r="H189" t="n">
         <v>51.31</v>
       </c>
-      <c r="I189" s="15" t="inlineStr">
+      <c r="I189" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9060,7 +9392,7 @@
       <c r="D190" s="9" t="n">
         <v>7.77</v>
       </c>
-      <c r="E190" s="10" t="n">
+      <c r="E190" s="15" t="n">
         <v>-0.0226</v>
       </c>
       <c r="F190" s="11" t="n">
@@ -9072,7 +9404,7 @@
       <c r="H190" t="n">
         <v>43.72</v>
       </c>
-      <c r="I190" s="15" t="inlineStr">
+      <c r="I190" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9105,7 +9437,7 @@
       <c r="D191" s="9" t="n">
         <v>5.41</v>
       </c>
-      <c r="E191" s="10" t="n">
+      <c r="E191" s="15" t="n">
         <v>-0.0073</v>
       </c>
       <c r="F191" s="11" t="n">
@@ -9117,7 +9449,7 @@
       <c r="H191" t="n">
         <v>54.93</v>
       </c>
-      <c r="I191" s="15" t="inlineStr">
+      <c r="I191" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9150,7 +9482,7 @@
       <c r="D192" s="9" t="n">
         <v>1.85</v>
       </c>
-      <c r="E192" s="16" t="n">
+      <c r="E192" s="17" t="n">
         <v>0.0054</v>
       </c>
       <c r="F192" s="11" t="n">
@@ -9162,7 +9494,7 @@
       <c r="H192" t="n">
         <v>52.75</v>
       </c>
-      <c r="I192" s="15" t="inlineStr">
+      <c r="I192" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9195,7 +9527,7 @@
       <c r="D193" s="9" t="n">
         <v>0.65</v>
       </c>
-      <c r="E193" s="10" t="n">
+      <c r="E193" s="15" t="n">
         <v>-0.0076</v>
       </c>
       <c r="F193" s="11" t="n">
@@ -9207,7 +9539,7 @@
       <c r="H193" t="n">
         <v>70.55</v>
       </c>
-      <c r="I193" s="15" t="inlineStr">
+      <c r="I193" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9240,7 +9572,7 @@
       <c r="D194" s="9" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="E194" s="10" t="n">
+      <c r="E194" s="15" t="n">
         <v>-0.012</v>
       </c>
       <c r="F194" s="11" t="n">
@@ -9252,7 +9584,7 @@
       <c r="H194" t="n">
         <v>65.06999999999999</v>
       </c>
-      <c r="I194" s="15" t="inlineStr">
+      <c r="I194" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9285,7 +9617,7 @@
       <c r="D195" s="9" t="n">
         <v>0.215</v>
       </c>
-      <c r="E195" s="10" t="n">
+      <c r="E195" s="15" t="n">
         <v>-0.06519999999999999</v>
       </c>
       <c r="F195" s="11" t="n">
@@ -9297,7 +9629,7 @@
       <c r="H195" t="n">
         <v>59.01</v>
       </c>
-      <c r="I195" s="15" t="inlineStr">
+      <c r="I195" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9330,7 +9662,7 @@
       <c r="D196" s="9" t="n">
         <v>1.37</v>
       </c>
-      <c r="E196" s="10" t="n">
+      <c r="E196" s="15" t="n">
         <v>-0.0072</v>
       </c>
       <c r="F196" s="11" t="n">
@@ -9342,7 +9674,7 @@
       <c r="H196" t="n">
         <v>62.95</v>
       </c>
-      <c r="I196" s="15" t="inlineStr">
+      <c r="I196" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9375,7 +9707,7 @@
       <c r="D197" s="9" t="n">
         <v>0.645</v>
       </c>
-      <c r="E197" s="10" t="n">
+      <c r="E197" s="15" t="n">
         <v>-0.0153</v>
       </c>
       <c r="F197" s="11" t="n">
@@ -9420,7 +9752,7 @@
       <c r="D198" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E198" s="17" t="n">
+      <c r="E198" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F198" s="11" t="n">
@@ -9432,7 +9764,7 @@
       <c r="H198" t="n">
         <v>79.06</v>
       </c>
-      <c r="I198" s="15" t="inlineStr">
+      <c r="I198" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9465,7 +9797,7 @@
       <c r="D199" s="9" t="n">
         <v>0.375</v>
       </c>
-      <c r="E199" s="16" t="n">
+      <c r="E199" s="17" t="n">
         <v>0.0135</v>
       </c>
       <c r="F199" s="11" t="n">
@@ -9510,7 +9842,7 @@
       <c r="D200" s="9" t="n">
         <v>0.605</v>
       </c>
-      <c r="E200" s="16" t="n">
+      <c r="E200" s="17" t="n">
         <v>0.0168</v>
       </c>
       <c r="F200" s="11" t="n">
@@ -9555,7 +9887,7 @@
       <c r="D201" s="9" t="n">
         <v>0.595</v>
       </c>
-      <c r="E201" s="17" t="n">
+      <c r="E201" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F201" s="11" t="n">
@@ -9567,7 +9899,7 @@
       <c r="H201" t="n">
         <v>75.3</v>
       </c>
-      <c r="I201" s="15" t="inlineStr">
+      <c r="I201" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9600,7 +9932,7 @@
       <c r="D202" s="9" t="n">
         <v>0.795</v>
       </c>
-      <c r="E202" s="16" t="n">
+      <c r="E202" s="17" t="n">
         <v>0.0192</v>
       </c>
       <c r="F202" s="11" t="n">
@@ -9612,7 +9944,7 @@
       <c r="H202" t="n">
         <v>61.14</v>
       </c>
-      <c r="I202" s="15" t="inlineStr">
+      <c r="I202" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9645,7 +9977,7 @@
       <c r="D203" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E203" s="10" t="n">
+      <c r="E203" s="15" t="n">
         <v>-0.0071</v>
       </c>
       <c r="F203" s="11" t="n">
@@ -9690,7 +10022,7 @@
       <c r="D204" s="9" t="n">
         <v>2.29</v>
       </c>
-      <c r="E204" s="17" t="n">
+      <c r="E204" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F204" s="11" t="n">
@@ -9702,7 +10034,7 @@
       <c r="H204" t="n">
         <v>63.36</v>
       </c>
-      <c r="I204" s="15" t="inlineStr">
+      <c r="I204" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9735,7 +10067,7 @@
       <c r="D205" s="9" t="n">
         <v>0.38</v>
       </c>
-      <c r="E205" s="17" t="n">
+      <c r="E205" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F205" s="11" t="n">
@@ -9780,7 +10112,7 @@
       <c r="D206" s="9" t="n">
         <v>4.95</v>
       </c>
-      <c r="E206" s="10" t="n">
+      <c r="E206" s="15" t="n">
         <v>-0.012</v>
       </c>
       <c r="F206" s="11" t="n">
@@ -9792,7 +10124,7 @@
       <c r="H206" t="n">
         <v>44.86</v>
       </c>
-      <c r="I206" s="15" t="inlineStr">
+      <c r="I206" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9825,7 +10157,7 @@
       <c r="D207" s="9" t="n">
         <v>0.635</v>
       </c>
-      <c r="E207" s="17" t="n">
+      <c r="E207" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F207" s="11" t="n">
@@ -9837,7 +10169,7 @@
       <c r="H207" t="n">
         <v>55.29</v>
       </c>
-      <c r="I207" s="15" t="inlineStr">
+      <c r="I207" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9870,7 +10202,7 @@
       <c r="D208" s="9" t="n">
         <v>0.21</v>
       </c>
-      <c r="E208" s="16" t="n">
+      <c r="E208" s="17" t="n">
         <v>0.05</v>
       </c>
       <c r="F208" s="11" t="n">
@@ -9882,7 +10214,7 @@
       <c r="H208" t="n">
         <v>50.99</v>
       </c>
-      <c r="I208" s="15" t="inlineStr">
+      <c r="I208" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9915,7 +10247,7 @@
       <c r="D209" s="9" t="n">
         <v>7.57</v>
       </c>
-      <c r="E209" s="16" t="n">
+      <c r="E209" s="17" t="n">
         <v>0.0161</v>
       </c>
       <c r="F209" s="11" t="n">
@@ -9927,7 +10259,7 @@
       <c r="H209" t="n">
         <v>47.33</v>
       </c>
-      <c r="I209" s="15" t="inlineStr">
+      <c r="I209" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9960,7 +10292,7 @@
       <c r="D210" s="9" t="n">
         <v>0.255</v>
       </c>
-      <c r="E210" s="17" t="n">
+      <c r="E210" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F210" s="11" t="n">
@@ -10005,7 +10337,7 @@
       <c r="D211" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="E211" s="16" t="n">
+      <c r="E211" s="17" t="n">
         <v>0.038</v>
       </c>
       <c r="F211" s="11" t="n">
@@ -10017,7 +10349,7 @@
       <c r="H211" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="I211" s="15" t="inlineStr">
+      <c r="I211" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10050,7 +10382,7 @@
       <c r="D212" s="9" t="n">
         <v>1.38</v>
       </c>
-      <c r="E212" s="10" t="n">
+      <c r="E212" s="15" t="n">
         <v>-0.0282</v>
       </c>
       <c r="F212" s="11" t="n">
@@ -10095,7 +10427,7 @@
       <c r="D213" s="9" t="n">
         <v>0.63</v>
       </c>
-      <c r="E213" s="10" t="n">
+      <c r="E213" s="15" t="n">
         <v>-0.007900000000000001</v>
       </c>
       <c r="F213" s="11" t="n">
@@ -10140,7 +10472,7 @@
       <c r="D214" s="9" t="n">
         <v>1.01</v>
       </c>
-      <c r="E214" s="10" t="n">
+      <c r="E214" s="15" t="n">
         <v>-0.0098</v>
       </c>
       <c r="F214" s="11" t="n">
@@ -10185,7 +10517,7 @@
       <c r="D215" s="9" t="n">
         <v>0.225</v>
       </c>
-      <c r="E215" s="16" t="n">
+      <c r="E215" s="17" t="n">
         <v>0.04650000000000001</v>
       </c>
       <c r="F215" s="11" t="n">
@@ -10230,7 +10562,7 @@
       <c r="D216" s="9" t="n">
         <v>0.515</v>
       </c>
-      <c r="E216" s="17" t="n">
+      <c r="E216" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F216" s="11" t="n">
@@ -10242,7 +10574,7 @@
       <c r="H216" t="n">
         <v>66.69</v>
       </c>
-      <c r="I216" s="15" t="inlineStr">
+      <c r="I216" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10275,7 +10607,7 @@
       <c r="D217" s="9" t="n">
         <v>0.71</v>
       </c>
-      <c r="E217" s="16" t="n">
+      <c r="E217" s="17" t="n">
         <v>0.029</v>
       </c>
       <c r="F217" s="11" t="n">
@@ -10287,7 +10619,7 @@
       <c r="H217" t="n">
         <v>60.89</v>
       </c>
-      <c r="I217" s="15" t="inlineStr">
+      <c r="I217" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10320,7 +10652,7 @@
       <c r="D218" s="9" t="n">
         <v>1.52</v>
       </c>
-      <c r="E218" s="10" t="n">
+      <c r="E218" s="15" t="n">
         <v>-0.006500000000000001</v>
       </c>
       <c r="F218" s="11" t="n">
@@ -10332,7 +10664,7 @@
       <c r="H218" t="n">
         <v>32.84</v>
       </c>
-      <c r="I218" s="15" t="inlineStr">
+      <c r="I218" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10365,7 +10697,7 @@
       <c r="D219" s="9" t="n">
         <v>0.485</v>
       </c>
-      <c r="E219" s="16" t="n">
+      <c r="E219" s="17" t="n">
         <v>0.0319</v>
       </c>
       <c r="F219" s="11" t="n">
@@ -10377,7 +10709,7 @@
       <c r="H219" t="n">
         <v>55.55</v>
       </c>
-      <c r="I219" s="15" t="inlineStr">
+      <c r="I219" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10410,7 +10742,7 @@
       <c r="D220" s="9" t="n">
         <v>0.245</v>
       </c>
-      <c r="E220" s="10" t="n">
+      <c r="E220" s="15" t="n">
         <v>-0.0392</v>
       </c>
       <c r="F220" s="11" t="n">
@@ -10422,7 +10754,7 @@
       <c r="H220" t="n">
         <v>41.8</v>
       </c>
-      <c r="I220" s="15" t="inlineStr">
+      <c r="I220" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10455,7 +10787,7 @@
       <c r="D221" s="9" t="n">
         <v>0.72</v>
       </c>
-      <c r="E221" s="10" t="n">
+      <c r="E221" s="15" t="n">
         <v>-0.0137</v>
       </c>
       <c r="F221" s="11" t="n">
@@ -10500,7 +10832,7 @@
       <c r="D222" s="9" t="n">
         <v>1.25</v>
       </c>
-      <c r="E222" s="10" t="n">
+      <c r="E222" s="15" t="n">
         <v>-0.007900000000000001</v>
       </c>
       <c r="F222" s="11" t="n">
@@ -10512,7 +10844,7 @@
       <c r="H222" t="n">
         <v>41.92</v>
       </c>
-      <c r="I222" s="15" t="inlineStr">
+      <c r="I222" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10545,7 +10877,7 @@
       <c r="D223" s="9" t="n">
         <v>1.16</v>
       </c>
-      <c r="E223" s="10" t="n">
+      <c r="E223" s="15" t="n">
         <v>-0.0333</v>
       </c>
       <c r="F223" s="11" t="n">
@@ -10557,7 +10889,7 @@
       <c r="H223" t="n">
         <v>43</v>
       </c>
-      <c r="I223" s="15" t="inlineStr">
+      <c r="I223" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10590,7 +10922,7 @@
       <c r="D224" s="9" t="n">
         <v>0.875</v>
       </c>
-      <c r="E224" s="16" t="n">
+      <c r="E224" s="17" t="n">
         <v>0.0174</v>
       </c>
       <c r="F224" s="11" t="n">
@@ -10602,7 +10934,7 @@
       <c r="H224" t="n">
         <v>65.41</v>
       </c>
-      <c r="I224" s="15" t="inlineStr">
+      <c r="I224" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10635,7 +10967,7 @@
       <c r="D225" s="9" t="n">
         <v>0.61</v>
       </c>
-      <c r="E225" s="10" t="n">
+      <c r="E225" s="15" t="n">
         <v>-0.008100000000000001</v>
       </c>
       <c r="F225" s="11" t="n">
@@ -10680,7 +11012,7 @@
       <c r="D226" s="9" t="n">
         <v>0.735</v>
       </c>
-      <c r="E226" s="16" t="n">
+      <c r="E226" s="17" t="n">
         <v>0.0208</v>
       </c>
       <c r="F226" s="11" t="n">
@@ -10725,7 +11057,7 @@
       <c r="D227" s="9" t="n">
         <v>5.56</v>
       </c>
-      <c r="E227" s="16" t="n">
+      <c r="E227" s="17" t="n">
         <v>0.0091</v>
       </c>
       <c r="F227" s="11" t="n">
@@ -10770,7 +11102,7 @@
       <c r="D228" s="9" t="n">
         <v>0.64</v>
       </c>
-      <c r="E228" s="16" t="n">
+      <c r="E228" s="17" t="n">
         <v>0.0159</v>
       </c>
       <c r="F228" s="11" t="n">
@@ -10815,7 +11147,7 @@
       <c r="D229" s="9" t="n">
         <v>0.24</v>
       </c>
-      <c r="E229" s="16" t="n">
+      <c r="E229" s="17" t="n">
         <v>0.0213</v>
       </c>
       <c r="F229" s="11" t="n">
@@ -10827,7 +11159,7 @@
       <c r="H229" t="n">
         <v>38.31</v>
       </c>
-      <c r="I229" s="15" t="inlineStr">
+      <c r="I229" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10860,7 +11192,7 @@
       <c r="D230" s="9" t="n">
         <v>1.86</v>
       </c>
-      <c r="E230" s="17" t="n">
+      <c r="E230" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F230" s="11" t="n">
@@ -10872,7 +11204,7 @@
       <c r="H230" t="n">
         <v>66.63</v>
       </c>
-      <c r="I230" s="15" t="inlineStr">
+      <c r="I230" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10905,7 +11237,7 @@
       <c r="D231" s="9" t="n">
         <v>0.97</v>
       </c>
-      <c r="E231" s="16" t="n">
+      <c r="E231" s="17" t="n">
         <v>0.0052</v>
       </c>
       <c r="F231" s="11" t="n">
@@ -10917,7 +11249,7 @@
       <c r="H231" t="n">
         <v>66.77</v>
       </c>
-      <c r="I231" s="15" t="inlineStr">
+      <c r="I231" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10950,7 +11282,7 @@
       <c r="D232" s="9" t="n">
         <v>0.87</v>
       </c>
-      <c r="E232" s="17" t="n">
+      <c r="E232" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F232" s="11" t="n">
@@ -10995,7 +11327,7 @@
       <c r="D233" s="9" t="n">
         <v>0.405</v>
       </c>
-      <c r="E233" s="16" t="n">
+      <c r="E233" s="17" t="n">
         <v>0.0253</v>
       </c>
       <c r="F233" s="11" t="n">
@@ -11040,7 +11372,7 @@
       <c r="D234" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="E234" s="16" t="n">
+      <c r="E234" s="17" t="n">
         <v>0.0204</v>
       </c>
       <c r="F234" s="11" t="n">
@@ -11052,7 +11384,7 @@
       <c r="H234" t="n">
         <v>55.12</v>
       </c>
-      <c r="I234" s="15" t="inlineStr">
+      <c r="I234" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11085,7 +11417,7 @@
       <c r="D235" s="9" t="n">
         <v>1.13</v>
       </c>
-      <c r="E235" s="16" t="n">
+      <c r="E235" s="17" t="n">
         <v>0.0273</v>
       </c>
       <c r="F235" s="11" t="n">
@@ -11097,7 +11429,7 @@
       <c r="H235" t="n">
         <v>59.23</v>
       </c>
-      <c r="I235" s="15" t="inlineStr">
+      <c r="I235" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11130,7 +11462,7 @@
       <c r="D236" s="9" t="n">
         <v>1.62</v>
       </c>
-      <c r="E236" s="17" t="n">
+      <c r="E236" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F236" s="11" t="n">
@@ -11175,7 +11507,7 @@
       <c r="D237" s="9" t="n">
         <v>2.05</v>
       </c>
-      <c r="E237" s="10" t="n">
+      <c r="E237" s="15" t="n">
         <v>-0.0144</v>
       </c>
       <c r="F237" s="11" t="n">
@@ -11187,7 +11519,7 @@
       <c r="H237" t="n">
         <v>52.01</v>
       </c>
-      <c r="I237" s="15" t="inlineStr">
+      <c r="I237" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11220,7 +11552,7 @@
       <c r="D238" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="E238" s="17" t="n">
+      <c r="E238" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F238" s="11" t="n">
@@ -11265,7 +11597,7 @@
       <c r="D239" s="9" t="n">
         <v>1.51</v>
       </c>
-      <c r="E239" s="10" t="n">
+      <c r="E239" s="15" t="n">
         <v>-0.0563</v>
       </c>
       <c r="F239" s="11" t="n">
@@ -11310,7 +11642,7 @@
       <c r="D240" s="9" t="n">
         <v>0.905</v>
       </c>
-      <c r="E240" s="10" t="n">
+      <c r="E240" s="15" t="n">
         <v>-0.0163</v>
       </c>
       <c r="F240" s="11" t="n">
@@ -11322,7 +11654,7 @@
       <c r="H240" t="n">
         <v>58.53</v>
       </c>
-      <c r="I240" s="15" t="inlineStr">
+      <c r="I240" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11355,7 +11687,7 @@
       <c r="D241" s="9" t="n">
         <v>0.63</v>
       </c>
-      <c r="E241" s="17" t="n">
+      <c r="E241" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F241" s="11" t="n">
@@ -11400,7 +11732,7 @@
       <c r="D242" s="9" t="n">
         <v>0.825</v>
       </c>
-      <c r="E242" s="17" t="n">
+      <c r="E242" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F242" s="11" t="n">
@@ -11445,7 +11777,7 @@
       <c r="D243" s="9" t="n">
         <v>0.21</v>
       </c>
-      <c r="E243" s="10" t="n">
+      <c r="E243" s="15" t="n">
         <v>-0.0233</v>
       </c>
       <c r="F243" s="11" t="n">
@@ -11457,7 +11789,7 @@
       <c r="H243" t="n">
         <v>40.84</v>
       </c>
-      <c r="I243" s="15" t="inlineStr">
+      <c r="I243" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11490,7 +11822,7 @@
       <c r="D244" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="E244" s="16" t="n">
+      <c r="E244" s="17" t="n">
         <v>0.0204</v>
       </c>
       <c r="F244" s="11" t="n">
@@ -11535,7 +11867,7 @@
       <c r="D245" s="9" t="n">
         <v>3.75</v>
       </c>
-      <c r="E245" s="16" t="n">
+      <c r="E245" s="17" t="n">
         <v>0.008100000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
@@ -11547,7 +11879,7 @@
       <c r="H245" t="n">
         <v>51.54</v>
       </c>
-      <c r="I245" s="15" t="inlineStr">
+      <c r="I245" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11580,7 +11912,7 @@
       <c r="D246" s="9" t="n">
         <v>0.85</v>
       </c>
-      <c r="E246" s="17" t="n">
+      <c r="E246" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F246" s="11" t="n">
@@ -11592,7 +11924,7 @@
       <c r="H246" t="n">
         <v>50.62</v>
       </c>
-      <c r="I246" s="15" t="inlineStr">
+      <c r="I246" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11625,7 +11957,7 @@
       <c r="D247" s="9" t="n">
         <v>0.99</v>
       </c>
-      <c r="E247" s="10" t="n">
+      <c r="E247" s="15" t="n">
         <v>-0.005</v>
       </c>
       <c r="F247" s="11" t="n">
@@ -11637,7 +11969,7 @@
       <c r="H247" t="n">
         <v>46.18</v>
       </c>
-      <c r="I247" s="15" t="inlineStr">
+      <c r="I247" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11670,7 +12002,7 @@
       <c r="D248" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="E248" s="17" t="n">
+      <c r="E248" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F248" s="11" t="n">
@@ -11715,7 +12047,7 @@
       <c r="D249" s="9" t="n">
         <v>1.11</v>
       </c>
-      <c r="E249" s="16" t="n">
+      <c r="E249" s="17" t="n">
         <v>0.0091</v>
       </c>
       <c r="F249" s="11" t="n">
@@ -11727,7 +12059,7 @@
       <c r="H249" t="n">
         <v>50.8</v>
       </c>
-      <c r="I249" s="15" t="inlineStr">
+      <c r="I249" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11760,7 +12092,7 @@
       <c r="D250" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="E250" s="10" t="n">
+      <c r="E250" s="15" t="n">
         <v>-0.0304</v>
       </c>
       <c r="F250" s="11" t="n">
@@ -11805,7 +12137,7 @@
       <c r="D251" s="9" t="n">
         <v>1.47</v>
       </c>
-      <c r="E251" s="10" t="n">
+      <c r="E251" s="15" t="n">
         <v>-0.0134</v>
       </c>
       <c r="F251" s="11" t="n">
@@ -11817,7 +12149,7 @@
       <c r="H251" t="n">
         <v>50.56</v>
       </c>
-      <c r="I251" s="15" t="inlineStr">
+      <c r="I251" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11850,7 +12182,7 @@
       <c r="D252" s="9" t="n">
         <v>0.93</v>
       </c>
-      <c r="E252" s="17" t="n">
+      <c r="E252" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F252" s="11" t="n">
@@ -11895,7 +12227,7 @@
       <c r="D253" s="9" t="n">
         <v>0.99</v>
       </c>
-      <c r="E253" s="10" t="n">
+      <c r="E253" s="15" t="n">
         <v>-0.005</v>
       </c>
       <c r="F253" s="11" t="n">
@@ -11940,7 +12272,7 @@
       <c r="D254" s="9" t="n">
         <v>1.74</v>
       </c>
-      <c r="E254" s="17" t="n">
+      <c r="E254" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F254" s="11" t="n">
@@ -11985,7 +12317,7 @@
       <c r="D255" s="9" t="n">
         <v>3.22</v>
       </c>
-      <c r="E255" s="10" t="n">
+      <c r="E255" s="15" t="n">
         <v>-0.0031</v>
       </c>
       <c r="F255" s="11" t="n">
@@ -11997,7 +12329,7 @@
       <c r="H255" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="I255" s="15" t="inlineStr">
+      <c r="I255" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12030,7 +12362,7 @@
       <c r="D256" s="9" t="n">
         <v>0.51</v>
       </c>
-      <c r="E256" s="17" t="n">
+      <c r="E256" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F256" s="11" t="n">
@@ -12075,7 +12407,7 @@
       <c r="D257" s="9" t="n">
         <v>2.56</v>
       </c>
-      <c r="E257" s="16" t="n">
+      <c r="E257" s="17" t="n">
         <v>0.0119</v>
       </c>
       <c r="F257" s="11" t="n">
@@ -12087,7 +12419,7 @@
       <c r="H257" t="n">
         <v>59.96</v>
       </c>
-      <c r="I257" s="15" t="inlineStr">
+      <c r="I257" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12120,7 +12452,7 @@
       <c r="D258" s="9" t="n">
         <v>2.51</v>
       </c>
-      <c r="E258" s="16" t="n">
+      <c r="E258" s="17" t="n">
         <v>0.0121</v>
       </c>
       <c r="F258" s="11" t="n">
@@ -12132,7 +12464,7 @@
       <c r="H258" t="n">
         <v>28.24</v>
       </c>
-      <c r="I258" s="15" t="inlineStr">
+      <c r="I258" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12165,7 +12497,7 @@
       <c r="D259" s="9" t="n">
         <v>0.655</v>
       </c>
-      <c r="E259" s="16" t="n">
+      <c r="E259" s="17" t="n">
         <v>0.0077</v>
       </c>
       <c r="F259" s="11" t="n">
@@ -12210,7 +12542,7 @@
       <c r="D260" s="9" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E260" s="16" t="n">
+      <c r="E260" s="17" t="n">
         <v>0.0062</v>
       </c>
       <c r="F260" s="11" t="n">
@@ -12255,7 +12587,7 @@
       <c r="D261" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E261" s="17" t="n">
+      <c r="E261" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F261" s="11" t="n">
@@ -12300,7 +12632,7 @@
       <c r="D262" s="9" t="n">
         <v>0.51</v>
       </c>
-      <c r="E262" s="17" t="n">
+      <c r="E262" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F262" s="11" t="n">
@@ -12312,7 +12644,7 @@
       <c r="H262" t="n">
         <v>59.29</v>
       </c>
-      <c r="I262" s="15" t="inlineStr">
+      <c r="I262" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12345,7 +12677,7 @@
       <c r="D263" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="E263" s="10" t="n">
+      <c r="E263" s="15" t="n">
         <v>-0.0101</v>
       </c>
       <c r="F263" s="11" t="n">
@@ -12357,7 +12689,7 @@
       <c r="H263" t="n">
         <v>52.23</v>
       </c>
-      <c r="I263" s="15" t="inlineStr">
+      <c r="I263" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12390,7 +12722,7 @@
       <c r="D264" s="9" t="n">
         <v>0.88</v>
       </c>
-      <c r="E264" s="10" t="n">
+      <c r="E264" s="15" t="n">
         <v>-0.0222</v>
       </c>
       <c r="F264" s="11" t="n">
@@ -12435,7 +12767,7 @@
       <c r="D265" s="9" t="n">
         <v>2.38</v>
       </c>
-      <c r="E265" s="17" t="n">
+      <c r="E265" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F265" s="11" t="n">
@@ -12447,7 +12779,7 @@
       <c r="H265" t="n">
         <v>56.13</v>
       </c>
-      <c r="I265" s="15" t="inlineStr">
+      <c r="I265" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12480,7 +12812,7 @@
       <c r="D266" s="9" t="n">
         <v>0.77</v>
       </c>
-      <c r="E266" s="17" t="n">
+      <c r="E266" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F266" s="11" t="n">
@@ -12492,7 +12824,7 @@
       <c r="H266" t="n">
         <v>52.46</v>
       </c>
-      <c r="I266" s="15" t="inlineStr">
+      <c r="I266" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12525,7 +12857,7 @@
       <c r="D267" s="9" t="n">
         <v>1.93</v>
       </c>
-      <c r="E267" s="10" t="n">
+      <c r="E267" s="15" t="n">
         <v>-0.0103</v>
       </c>
       <c r="F267" s="11" t="n">
@@ -12537,7 +12869,7 @@
       <c r="H267" t="n">
         <v>41.77</v>
       </c>
-      <c r="I267" s="15" t="inlineStr">
+      <c r="I267" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12570,7 +12902,7 @@
       <c r="D268" s="9" t="n">
         <v>4.05</v>
       </c>
-      <c r="E268" s="16" t="n">
+      <c r="E268" s="17" t="n">
         <v>0.01</v>
       </c>
       <c r="F268" s="11" t="n">
@@ -12582,7 +12914,7 @@
       <c r="H268" t="n">
         <v>72.36</v>
       </c>
-      <c r="I268" s="15" t="inlineStr">
+      <c r="I268" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12615,7 +12947,7 @@
       <c r="D269" s="9" t="n">
         <v>0.51</v>
       </c>
-      <c r="E269" s="10" t="n">
+      <c r="E269" s="15" t="n">
         <v>-0.0097</v>
       </c>
       <c r="F269" s="11" t="n">
@@ -12660,7 +12992,7 @@
       <c r="D270" s="9" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="E270" s="10" t="n">
+      <c r="E270" s="15" t="n">
         <v>-0.0072</v>
       </c>
       <c r="F270" s="11" t="n">
@@ -12705,7 +13037,7 @@
       <c r="D271" s="9" t="n">
         <v>3.72</v>
       </c>
-      <c r="E271" s="10" t="n">
+      <c r="E271" s="15" t="n">
         <v>-0.0462</v>
       </c>
       <c r="F271" s="11" t="n">
@@ -12717,7 +13049,7 @@
       <c r="H271" t="n">
         <v>60.96</v>
       </c>
-      <c r="I271" s="15" t="inlineStr">
+      <c r="I271" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12750,7 +13082,7 @@
       <c r="D272" s="9" t="n">
         <v>0.655</v>
       </c>
-      <c r="E272" s="16" t="n">
+      <c r="E272" s="17" t="n">
         <v>0.0077</v>
       </c>
       <c r="F272" s="11" t="n">
@@ -12762,7 +13094,7 @@
       <c r="H272" t="n">
         <v>52.93</v>
       </c>
-      <c r="I272" s="15" t="inlineStr">
+      <c r="I272" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12795,7 +13127,7 @@
       <c r="D273" s="9" t="n">
         <v>0.52</v>
       </c>
-      <c r="E273" s="17" t="n">
+      <c r="E273" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F273" s="11" t="n">
@@ -12840,7 +13172,7 @@
       <c r="D274" s="9" t="n">
         <v>23.2</v>
       </c>
-      <c r="E274" s="10" t="n">
+      <c r="E274" s="15" t="n">
         <v>-0.0077</v>
       </c>
       <c r="F274" s="11" t="n">
@@ -12852,7 +13184,7 @@
       <c r="H274" t="n">
         <v>51.05</v>
       </c>
-      <c r="I274" s="15" t="inlineStr">
+      <c r="I274" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12885,7 +13217,7 @@
       <c r="D275" s="9" t="n">
         <v>2.33</v>
       </c>
-      <c r="E275" s="10" t="n">
+      <c r="E275" s="15" t="n">
         <v>-0.008500000000000001</v>
       </c>
       <c r="F275" s="11" t="n">
@@ -12930,7 +13262,7 @@
       <c r="D276" s="9" t="n">
         <v>2.07</v>
       </c>
-      <c r="E276" s="17" t="n">
+      <c r="E276" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F276" s="11" t="n">
@@ -12942,7 +13274,7 @@
       <c r="H276" t="n">
         <v>42.86</v>
       </c>
-      <c r="I276" s="15" t="inlineStr">
+      <c r="I276" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12975,7 +13307,7 @@
       <c r="D277" s="9" t="n">
         <v>4.09</v>
       </c>
-      <c r="E277" s="10" t="n">
+      <c r="E277" s="15" t="n">
         <v>-0.0168</v>
       </c>
       <c r="F277" s="11" t="n">
@@ -13020,7 +13352,7 @@
       <c r="D278" s="9" t="n">
         <v>0.965</v>
       </c>
-      <c r="E278" s="16" t="n">
+      <c r="E278" s="17" t="n">
         <v>0.0105</v>
       </c>
       <c r="F278" s="11" t="n">
@@ -13065,7 +13397,7 @@
       <c r="D279" s="9" t="n">
         <v>1.77</v>
       </c>
-      <c r="E279" s="17" t="n">
+      <c r="E279" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F279" s="11" t="n">
@@ -13110,7 +13442,7 @@
       <c r="D280" s="9" t="n">
         <v>8.35</v>
       </c>
-      <c r="E280" s="16" t="n">
+      <c r="E280" s="17" t="n">
         <v>0.0097</v>
       </c>
       <c r="F280" s="11" t="n">
@@ -13155,7 +13487,7 @@
       <c r="D281" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="E281" s="10" t="n">
+      <c r="E281" s="15" t="n">
         <v>-0.008800000000000001</v>
       </c>
       <c r="F281" s="11" t="n">
@@ -13167,7 +13499,7 @@
       <c r="H281" t="n">
         <v>54.78</v>
       </c>
-      <c r="I281" s="15" t="inlineStr">
+      <c r="I281" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13200,7 +13532,7 @@
       <c r="D282" s="9" t="n">
         <v>5.85</v>
       </c>
-      <c r="E282" s="10" t="n">
+      <c r="E282" s="15" t="n">
         <v>-0.0394</v>
       </c>
       <c r="F282" s="11" t="n">
@@ -13245,7 +13577,7 @@
       <c r="D283" s="9" t="n">
         <v>1.99</v>
       </c>
-      <c r="E283" s="17" t="n">
+      <c r="E283" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F283" s="11" t="n">
@@ -13290,7 +13622,7 @@
       <c r="D284" s="9" t="n">
         <v>2.04</v>
       </c>
-      <c r="E284" s="16" t="n">
+      <c r="E284" s="17" t="n">
         <v>0.009899999999999999</v>
       </c>
       <c r="F284" s="11" t="n">
@@ -13302,7 +13634,7 @@
       <c r="H284" t="n">
         <v>42.58</v>
       </c>
-      <c r="I284" s="15" t="inlineStr">
+      <c r="I284" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -568,19 +568,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0476</v>
+        <v>0.0571</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1861400</v>
+        <v>3265400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>83.77</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.946</v>
+        <v>0.947</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.78</v>
@@ -600,7 +600,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价RM1.1高于50日均线RM0.78约41%，EMA20与SAR均呈多头，但RSI达83.77，处超买区，信号可靠性受高位回调风险制约。</t>
+          <t>RSI达84.29，处超买区间；现价1.11远高于50日均线0.78，EMA20与SAR多头信号虽成立，但短线过热。</t>
         </is>
       </c>
     </row>
@@ -627,10 +627,10 @@
         <v>-0.0541</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>167952300</v>
+        <v>204714100</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="H3" t="n">
         <v>20.58</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.24</v>
+        <v>0.245</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>30228200</v>
+        <v>32551100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="H4" t="n">
-        <v>56.77</v>
+        <v>60.73</v>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.231</v>
+        <v>0.232</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.233</v>
@@ -702,28 +702,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CFM</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.095</v>
+        <v>0.3</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.0556</v>
+        <v>0.1321</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>23678800</v>
+        <v>29927500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>44.03</v>
+        <v>2.18</v>
       </c>
       <c r="H5" t="n">
-        <v>81.81</v>
+        <v>60.15</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.075</v>
+        <v>0.275</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.274</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -747,28 +747,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CFM</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.485</v>
+        <v>0.095</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0211</v>
+        <v>0.0556</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>18700900</v>
+        <v>24990500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.76</v>
+        <v>46.47</v>
       </c>
       <c r="H6" t="n">
-        <v>56.56</v>
+        <v>81.81</v>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.468</v>
+        <v>0.075</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.47</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -792,39 +792,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>16928200</v>
+        <v>23904800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="H7" t="n">
-        <v>37.55</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.95</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.243</v>
+        <v>0.538</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.25</v>
+        <v>0.489</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -837,28 +837,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.595</v>
+        <v>0.485</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0211</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>16721500</v>
+        <v>23775400</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.72</v>
+        <v>0.97</v>
       </c>
       <c r="H8" t="n">
-        <v>76.81</v>
+        <v>56.56</v>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.539</v>
+        <v>0.468</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.489</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>-0.0188</v>
+        <v>-0.0141</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>15987700</v>
+        <v>21473200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>46.56</v>
+        <v>47.59</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.137</v>
+        <v>2.138</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2.056</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.42</v>
+        <v>0.17</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.0633</v>
+        <v>0.0303</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>14961600</v>
+        <v>18482900</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.19</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.377</v>
+        <v>0.14</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.315</v>
+        <v>0.113</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -972,39 +972,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.785</v>
+        <v>0.425</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.0195</v>
+        <v>0.0759</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>14631000</v>
+        <v>18004000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.12</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.735</v>
+        <v>0.377</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.68</v>
+        <v>0.315</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1017,39 +1017,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0183</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14419000</v>
+        <v>17292300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="H12" t="n">
-        <v>71.51000000000001</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.62</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.139</v>
+        <v>0.658</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.113</v>
+        <v>0.875</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1062,28 +1062,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.0275</v>
+        <v>0.23</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13813100</v>
+        <v>17260200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.35</v>
+        <v>0.88</v>
       </c>
       <c r="H13" t="n">
-        <v>26.29</v>
+        <v>37.55</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.658</v>
+        <v>0.243</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.875</v>
+        <v>0.25</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13309200</v>
+        <v>16739200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="H14" t="n">
         <v>62.58</v>
@@ -1152,28 +1152,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.23</v>
+        <v>0.795</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.0222</v>
+        <v>0.0325</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12144100</v>
+        <v>16595300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="H15" t="n">
-        <v>85.45</v>
+        <v>65.66</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.198</v>
+        <v>0.736</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.182</v>
+        <v>0.68</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1197,28 +1197,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.0566</v>
+        <v>0.0222</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10760400</v>
+        <v>13470600</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H16" t="n">
-        <v>53.44</v>
+        <v>85.45</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.273</v>
+        <v>0.198</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.273</v>
+        <v>0.182</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1251,19 +1251,19 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.405</v>
+        <v>0.41</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.0946</v>
+        <v>0.1081</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10553500</v>
+        <v>11601500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>14.07</v>
+        <v>15.47</v>
       </c>
       <c r="H17" t="n">
-        <v>72.56</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>0.364</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1287,39 +1287,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.77</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10523700</v>
+        <v>11159700</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.3</v>
+        <v>0.93</v>
       </c>
       <c r="H18" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.082</v>
+        <v>0.774</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.076</v>
+        <v>0.774</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1332,28 +1332,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0182</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LKL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0.1429</v>
+        <v>0.805</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10105100</v>
+        <v>10978500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>95.98999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H19" t="n">
-        <v>63.02</v>
+        <v>46.93</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.034</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.034</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1377,39 +1377,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0.0127</v>
+        <v>0.0588</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8927200</v>
+        <v>10674500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.18</v>
+        <v>1.32</v>
       </c>
       <c r="H20" t="n">
-        <v>85.84999999999999</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.23</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.305</v>
+        <v>0.082</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.171</v>
+        <v>0.076</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1422,39 +1422,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0034</t>
+          <t>0182</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MMAG</t>
+          <t>LKL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="E21" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8738100</v>
+        <v>10324900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>3.9</v>
+        <v>98.08</v>
       </c>
       <c r="H21" t="n">
-        <v>49.97</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.98</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.027</v>
+        <v>0.034</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1467,28 +1467,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0</v>
+        <v>1.8</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8603400</v>
+        <v>9912800</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.11</v>
+        <v>0.29</v>
       </c>
       <c r="H22" t="n">
-        <v>56.29</v>
+        <v>62.18</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.032</v>
+        <v>1.714</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.033</v>
+        <v>1.493</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1512,39 +1512,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.035</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8510600</v>
+        <v>9703400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.47</v>
+        <v>1.25</v>
       </c>
       <c r="H23" t="n">
-        <v>61.39</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>4.71</v>
+        <v>0.032</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>4.482</v>
+        <v>0.033</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1557,39 +1557,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.605</v>
+        <v>0.4</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.0083</v>
+        <v>0.0127</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7973800</v>
+        <v>9328100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.84</v>
+        <v>0.19</v>
       </c>
       <c r="H24" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.84999999999999</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.609</v>
+        <v>0.305</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.603</v>
+        <v>0.171</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1602,39 +1602,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0219</v>
+        <v>4.82</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0.008399999999999999</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7718600</v>
+        <v>9312200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="H25" t="n">
-        <v>61.15</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.39</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.713</v>
+        <v>4.71</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.493</v>
+        <v>4.482</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1647,28 +1647,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.165</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7684000</v>
+        <v>9146800</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="H26" t="n">
-        <v>47.7</v>
+        <v>53.7</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.774</v>
+        <v>0.16</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.774</v>
+        <v>0.149</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1692,39 +1692,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MMAG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0169</v>
+        <v>0.025</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7408100</v>
+        <v>8888200</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1.26</v>
+        <v>3.97</v>
       </c>
       <c r="H27" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.97</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.27</v>
+        <v>0.025</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.268</v>
+        <v>0.027</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.775</v>
+        <v>0.29</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>-0.0252</v>
+        <v>-0.0169</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7389000</v>
+        <v>8191900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.98</v>
+        <v>1.39</v>
       </c>
       <c r="H28" t="n">
-        <v>65.91</v>
+        <v>64.13</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.681</v>
+        <v>0.268</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1782,28 +1782,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0.0303</v>
+        <v>0.6</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>7084700</v>
+        <v>8103900</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.24</v>
+        <v>0.85</v>
       </c>
       <c r="H29" t="n">
-        <v>37.08</v>
+        <v>44.4</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.186</v>
+        <v>0.609</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.228</v>
+        <v>0.603</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1827,28 +1827,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.16</v>
+        <v>0.775</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>-0.0303</v>
+        <v>-0.0252</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6270100</v>
+        <v>8060800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.15</v>
+        <v>1.07</v>
       </c>
       <c r="H30" t="n">
-        <v>51.62</v>
+        <v>65.91</v>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.16</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.148</v>
+        <v>0.681</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1872,28 +1872,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0</v>
+        <v>1.9</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5849200</v>
+        <v>7998000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="H31" t="n">
-        <v>39.23</v>
+        <v>45.5</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.141</v>
+        <v>1.924</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.165</v>
+        <v>1.973</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1917,28 +1917,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1.14</v>
+        <v>0.375</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>0.0179</v>
+        <v>0.0274</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5583700</v>
+        <v>7822200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.5</v>
+        <v>1.38</v>
       </c>
       <c r="H32" t="n">
-        <v>62.25</v>
+        <v>56.64</v>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.083</v>
+        <v>0.367</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1.02</v>
+        <v>0.366</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1962,39 +1962,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TEKSENG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.0526</v>
+        <v>0.865</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5468500</v>
+        <v>7803200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>26.6</v>
+        <v>0.44</v>
       </c>
       <c r="H33" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.39</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.251</v>
+        <v>0.868</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.238</v>
+        <v>0.871</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2007,39 +2007,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>-0.0206</v>
+        <v>0.125</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5384900</v>
+        <v>7422100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H34" t="n">
-        <v>54.07</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.29</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>2.347</v>
+        <v>0.142</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.225</v>
+        <v>0.165</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2052,28 +2052,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="E35" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5365900</v>
+        <v>7346000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.43</v>
+        <v>3.44</v>
       </c>
       <c r="H35" t="n">
-        <v>52.62</v>
+        <v>42.33</v>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.592</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.654</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2097,39 +2097,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.0345</v>
+        <v>0.165</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5190600</v>
+        <v>7176100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
       <c r="H36" t="n">
-        <v>56.96</v>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.18</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.398</v>
+        <v>0.185</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.397</v>
+        <v>0.228</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2142,28 +2142,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0055</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SERSOL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.04</v>
+        <v>2.37</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-0.2</v>
+        <v>-0.0247</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5155000</v>
+        <v>6931000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.62</v>
+        <v>0.35</v>
       </c>
       <c r="H37" t="n">
-        <v>52.2</v>
+        <v>53.27</v>
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.04</v>
+        <v>2.346</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.034</v>
+        <v>2.224</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2187,39 +2187,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5018400</v>
+        <v>6795900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="H38" t="n">
-        <v>45.39</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.25</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.868</v>
+        <v>1.083</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.871</v>
+        <v>1.02</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2232,39 +2232,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.375</v>
+        <v>4.8</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>0.0274</v>
+        <v>0.0042</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4470200</v>
+        <v>6643300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="H39" t="n">
-        <v>56.64</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.16</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.367</v>
+        <v>4.745</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.366</v>
+        <v>4.579</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2277,28 +2277,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>TEKSENG</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>4.54</v>
+        <v>0.305</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>0.0157</v>
+        <v>0.0702</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4458200</v>
+        <v>6598800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.38</v>
+        <v>32.09</v>
       </c>
       <c r="H40" t="n">
-        <v>86.17</v>
+        <v>80.11</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>3.333</v>
+        <v>0.252</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.232</v>
+        <v>0.238</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2322,28 +2322,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LBALUM</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0208</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3911400</v>
+        <v>5983800</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>12.79</v>
+        <v>0.4</v>
       </c>
       <c r="H41" t="n">
-        <v>66.51000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.478</v>
+        <v>0.462</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.471</v>
+        <v>0.394</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2367,28 +2367,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0055</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SERSOL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0.0069</v>
+        <v>0.04</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3907500</v>
+        <v>5821700</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.31</v>
+        <v>1.83</v>
       </c>
       <c r="H42" t="n">
-        <v>64.84999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.826</v>
+        <v>0.04</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.687</v>
+        <v>0.034</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2412,28 +2412,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.0405</v>
+        <v>0.78</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.013</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3820100</v>
+        <v>5563700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>65.3</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.332</v>
+        <v>0.764</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.317</v>
+        <v>0.749</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2457,39 +2457,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.0267</v>
+        <v>4.47</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3802400</v>
+        <v>5542900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="H44" t="n">
-        <v>38.42</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.379</v>
+        <v>3.326</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.392</v>
+        <v>2.23</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2502,28 +2502,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.01</v>
+        <v>0.415</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>-0.0098</v>
+        <v>-0.046</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3477500</v>
+        <v>5469900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="H45" t="n">
-        <v>79.65000000000001</v>
+        <v>55.46</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.852</v>
+        <v>0.397</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.744</v>
+        <v>0.397</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2547,28 +2547,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>7.9</v>
+        <v>0.805</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>-0.0038</v>
+        <v>-0.0062</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3476000</v>
+        <v>5295600</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.26</v>
+        <v>1.69</v>
       </c>
       <c r="H46" t="n">
-        <v>58.63</v>
+        <v>49.77</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>7.768</v>
+        <v>0.804</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>7.715</v>
+        <v>0.806</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2592,28 +2592,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.38</v>
+        <v>7.92</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>-0.0417</v>
+        <v>-0.0013</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3465500</v>
+        <v>5250100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="H47" t="n">
-        <v>52.56</v>
+        <v>59.93</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.386</v>
+        <v>7.77</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.284</v>
+        <v>7.715</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2637,39 +2637,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>0</v>
+        <v>2.93</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3458600</v>
+        <v>5042300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
       <c r="H48" t="n">
-        <v>42.28</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.84999999999999</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.922</v>
+        <v>2.826</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.972</v>
+        <v>2.687</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2682,28 +2682,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>0.013</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3370800</v>
+        <v>5007900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.61</v>
+        <v>1.41</v>
       </c>
       <c r="H49" t="n">
-        <v>83.98999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.764</v>
+        <v>0.868</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.749</v>
+        <v>0.848</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2727,39 +2727,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0.0042</v>
+        <v>1.39</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.0347</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3351100</v>
+        <v>4689500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="H50" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.06</v>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>4.745</v>
+        <v>1.387</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>4.579</v>
+        <v>1.284</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2772,28 +2772,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.27</v>
+        <v>0.155</v>
       </c>
       <c r="E51" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3256800</v>
+        <v>4330000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H51" t="n">
-        <v>43.1</v>
+        <v>44.71</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.276</v>
+        <v>0.156</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.317</v>
+        <v>0.16</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2817,39 +2817,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0.77</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3111600</v>
+        <v>4210400</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.11</v>
+        <v>0.67</v>
       </c>
       <c r="H52" t="n">
-        <v>33.17</v>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.49</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.283</v>
+        <v>0.775</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.333</v>
+        <v>0.773</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2862,28 +2862,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.525</v>
+        <v>0.355</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0405</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3021400</v>
+        <v>4166300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H53" t="n">
-        <v>52.9</v>
+        <v>65.3</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.518</v>
+        <v>0.332</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.529</v>
+        <v>0.317</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2907,28 +2907,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>0.025</v>
+        <v>5.84</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2964100</v>
+        <v>4029400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="H54" t="n">
-        <v>63.73</v>
+        <v>62.62</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.16</v>
+        <v>5.655</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.095</v>
+        <v>5.068</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2952,39 +2952,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>LBALUM</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>-0.0242</v>
+        <v>0.495</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2944600</v>
+        <v>3952300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.62</v>
+        <v>12.93</v>
       </c>
       <c r="H55" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.644</v>
+        <v>0.479</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.659</v>
+        <v>0.471</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2997,39 +2997,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0092</v>
+        <v>1.03</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2927300</v>
+        <v>3923300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="H56" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.59</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.854</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.594</v>
+        <v>0.744</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3042,39 +3042,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.67</v>
+        <v>0.54</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>-0.0074</v>
+        <v>-0.0092</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2752400</v>
+        <v>3908500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.24</v>
+        <v>0.58</v>
       </c>
       <c r="H57" t="n">
-        <v>45</v>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.04</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.68</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.893</v>
+        <v>0.594</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3087,39 +3087,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>0.01</v>
+        <v>0.605</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0242</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2646500</v>
+        <v>3897000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="H58" t="n">
-        <v>81.36</v>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.17</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.439</v>
+        <v>0.644</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.399</v>
+        <v>0.659</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3132,28 +3132,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>-0.0118</v>
+        <v>1.23</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2620500</v>
+        <v>3885900</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="H59" t="n">
-        <v>62.62</v>
+        <v>63.73</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>5.655</v>
+        <v>1.16</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>5.068</v>
+        <v>1.095</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.0625</v>
+        <v>-0.0133</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2616700</v>
+        <v>3855600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H60" t="n">
-        <v>44.92</v>
+        <v>40.98</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.399</v>
+        <v>0.379</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.37</v>
+        <v>0.392</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3222,39 +3222,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.54</v>
+        <v>1.01</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>-0.0182</v>
+        <v>-0.0098</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2589100</v>
+        <v>3797300</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.18</v>
+        <v>1.18</v>
       </c>
       <c r="H61" t="n">
-        <v>57.69</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.05</v>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.519</v>
+        <v>0.773</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.469</v>
+        <v>0.706</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3267,28 +3267,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.54</v>
+        <v>0.255</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2575800</v>
+        <v>3774500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="H62" t="n">
-        <v>70.97</v>
+        <v>34.37</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.46</v>
+        <v>0.284</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.393</v>
+        <v>0.333</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3312,28 +3312,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1</v>
+        <v>0.265</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>-0.0196</v>
+        <v>-0.0185</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2528700</v>
+        <v>3753800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.79</v>
+        <v>0.31</v>
       </c>
       <c r="H63" t="n">
-        <v>86.59999999999999</v>
+        <v>41.24</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.772</v>
+        <v>0.276</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.706</v>
+        <v>0.317</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3357,39 +3357,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.405</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2501900</v>
+        <v>3615800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H64" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.41</v>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.3</v>
+        <v>0.406</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.313</v>
+        <v>0.409</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3402,28 +3402,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0284</v>
+        <v>0.165</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0.1</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2417100</v>
+        <v>3569500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.16</v>
+        <v>6.96</v>
       </c>
       <c r="H65" t="n">
-        <v>51.73</v>
+        <v>74.59</v>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.677</v>
+        <v>0.146</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.658</v>
+        <v>0.144</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3447,39 +3447,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>10.12</v>
+        <v>0.535</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.0273</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2415600</v>
+        <v>3545300</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H66" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.36</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>10.173</v>
+        <v>0.518</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>10.345</v>
+        <v>0.469</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3492,39 +3492,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2330700</v>
+        <v>3282200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.61</v>
+        <v>0.22</v>
       </c>
       <c r="H67" t="n">
-        <v>30.81</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.68</v>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.802</v>
+        <v>0.678</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.855</v>
+        <v>0.659</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3537,39 +3537,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>0</v>
+        <v>0.525</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2245400</v>
+        <v>3275000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H68" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.9</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.059</v>
+        <v>0.518</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.072</v>
+        <v>0.529</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3582,28 +3582,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0064</v>
+        <v>-0.0168</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2222600</v>
+        <v>3240500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.04</v>
+        <v>0.43</v>
       </c>
       <c r="H69" t="n">
-        <v>40.66</v>
+        <v>48.92</v>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.591</v>
+        <v>1.185</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.654</v>
+        <v>1.131</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3627,39 +3627,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>10.18</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2142300</v>
+        <v>3192200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H70" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.46</v>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.775</v>
+        <v>10.178</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.773</v>
+        <v>10.346</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3672,39 +3672,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0375</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2135600</v>
+        <v>3094200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.6</v>
+        <v>0.97</v>
       </c>
       <c r="H71" t="n">
-        <v>68.48</v>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.36</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.868</v>
+        <v>0.4</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.848</v>
+        <v>0.37</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3717,28 +3717,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.655</v>
+        <v>2.67</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>-0.0224</v>
+        <v>-0.0074</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2037000</v>
+        <v>3020500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H72" t="n">
-        <v>59.56</v>
+        <v>45</v>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.628</v>
+        <v>2.68</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.893</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3762,28 +3762,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ENGTEX</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.455</v>
+        <v>0.505</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.0225</v>
+        <v>0.01</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1992500</v>
+        <v>2968100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>2.1</v>
+        <v>0.98</v>
       </c>
       <c r="H73" t="n">
-        <v>60.62</v>
+        <v>81.36</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.434</v>
+        <v>0.439</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.44</v>
+        <v>0.399</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3807,39 +3807,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.0168</v>
+        <v>0.285</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1972400</v>
+        <v>2883900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="H74" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="I74" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.99</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.185</v>
+        <v>0.299</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.131</v>
+        <v>0.313</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3852,28 +3852,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>-0.0075</v>
+        <v>-0.0144</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1924500</v>
+        <v>2609000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>59.41</v>
+        <v>45.19</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.589</v>
+        <v>2.069</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.425</v>
+        <v>2.113</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ENGTEX</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0238</v>
+        <v>0.445</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1911000</v>
+        <v>2522600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.17</v>
+        <v>2.65</v>
       </c>
       <c r="H76" t="n">
-        <v>52.95</v>
+        <v>56.42</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.407</v>
+        <v>0.433</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.409</v>
+        <v>0.44</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3942,28 +3942,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.05</v>
+        <v>0.66</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>-0.0144</v>
+        <v>-0.0149</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1838100</v>
+        <v>2429900</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.66</v>
+        <v>0.25</v>
       </c>
       <c r="H77" t="n">
-        <v>45.19</v>
+        <v>60.88</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.069</v>
+        <v>0.629</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>2.113</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3987,28 +3987,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0.015</v>
+        <v>1.37</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.09269999999999999</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1815100</v>
+        <v>2407900</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.3</v>
+        <v>13.19</v>
       </c>
       <c r="H78" t="n">
-        <v>62.02</v>
+        <v>40.54</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>2.592</v>
+        <v>1.435</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2.476</v>
+        <v>1.431</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4032,28 +4032,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>-0.0111</v>
+        <v>2.71</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0.015</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1802100</v>
+        <v>2369000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
       <c r="H79" t="n">
-        <v>52.86</v>
+        <v>62.02</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.444</v>
+        <v>2.592</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.4</v>
+        <v>2.476</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4077,28 +4077,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0.0196</v>
+        <v>0.75</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1702900</v>
+        <v>2355700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>2.39</v>
+        <v>0.62</v>
       </c>
       <c r="H80" t="n">
-        <v>45.51</v>
+        <v>29.9</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.262</v>
+        <v>0.801</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.267</v>
+        <v>0.855</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4122,28 +4122,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0.0223</v>
+        <v>1.01</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1692900</v>
+        <v>2322900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="H81" t="n">
-        <v>50.1</v>
+        <v>33.24</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>4.611</v>
+        <v>1.059</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>4.54</v>
+        <v>1.072</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4167,28 +4167,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SEALINK</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.335</v>
+        <v>2.46</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>0.0308</v>
+        <v>0.025</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1678000</v>
+        <v>2174700</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>2.42</v>
+        <v>1.32</v>
       </c>
       <c r="H82" t="n">
-        <v>70.29000000000001</v>
+        <v>82.66</v>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.315</v>
+        <v>2.103</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.308</v>
+        <v>1.905</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4212,28 +4212,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.28</v>
+        <v>2.65</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>-0.0175</v>
+        <v>-0.0112</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1658800</v>
+        <v>2137100</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1.07</v>
+        <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>62.61</v>
+        <v>58.44</v>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.254</v>
+        <v>2.588</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.271</v>
+        <v>2.425</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4257,28 +4257,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.615</v>
+        <v>0.55</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>0.0336</v>
+        <v>0.0092</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1645900</v>
+        <v>2134000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.16</v>
+        <v>0.46</v>
       </c>
       <c r="H84" t="n">
-        <v>78.39</v>
+        <v>65.22</v>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.544</v>
+        <v>0.511</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.485</v>
+        <v>0.459</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4302,28 +4302,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.32</v>
+        <v>13.12</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0154</v>
+        <v>-0.0015</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1575300</v>
+        <v>2129500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H85" t="n">
-        <v>46.33</v>
+        <v>26.72</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.323</v>
+        <v>13.542</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.339</v>
+        <v>14.106</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4347,39 +4347,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>-0.0083</v>
+        <v>4.84</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1479200</v>
+        <v>2098000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="H86" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.37</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.096</v>
+        <v>4.858</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.904</v>
+        <v>4.973</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4392,28 +4392,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.67</v>
+        <v>4.59</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>0.0469</v>
+        <v>0.0223</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1440200</v>
+        <v>2070600</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.36</v>
+        <v>0.27</v>
       </c>
       <c r="H87" t="n">
-        <v>52.84</v>
+        <v>50.1</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.654</v>
+        <v>4.611</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.65</v>
+        <v>4.54</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4437,28 +4437,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0138</v>
+        <v>0.37</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1384300</v>
+        <v>2064400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H88" t="n">
-        <v>67.64</v>
+        <v>50.08</v>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
@@ -4466,10 +4466,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.606</v>
+        <v>0.37</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4482,28 +4482,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>0.0015</v>
+        <v>1.29</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1345300</v>
+        <v>1992700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H89" t="n">
-        <v>28.29</v>
+        <v>32.39</v>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>13.546</v>
+        <v>1.335</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>14.106</v>
+        <v>1.459</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4527,28 +4527,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.365</v>
+        <v>0.445</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.0395</v>
+        <v>-0.0111</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1338800</v>
+        <v>1990100</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H90" t="n">
-        <v>33.95</v>
+        <v>52.86</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.393</v>
+        <v>0.444</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4572,28 +4572,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.375</v>
+        <v>3.78</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>-0.0132</v>
+        <v>-0.0026</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1323400</v>
+        <v>1977000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
       <c r="H91" t="n">
-        <v>73.53</v>
+        <v>71.75</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.352</v>
+        <v>3.407</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.317</v>
+        <v>3.178</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4617,28 +4617,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0</v>
+        <v>1.76</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0276</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1320800</v>
+        <v>1961100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H92" t="n">
-        <v>50.08</v>
+        <v>47.72</v>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.37</v>
+        <v>1.772</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.37</v>
+        <v>1.81</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4662,28 +4662,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0</v>
+        <v>4.96</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1310700</v>
+        <v>1931300</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="H93" t="n">
-        <v>64.2</v>
+        <v>48.53</v>
       </c>
       <c r="I93" s="15" t="inlineStr">
         <is>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.511</v>
+        <v>4.975</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.459</v>
+        <v>5.032</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4707,39 +4707,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0.0336</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1225800</v>
+        <v>1867300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.29</v>
+        <v>1.31</v>
       </c>
       <c r="H94" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.39</v>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.233</v>
+        <v>0.544</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.129</v>
+        <v>0.485</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4752,28 +4752,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.0068</v>
+        <v>0.22</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1224600</v>
+        <v>1853800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="H95" t="n">
-        <v>41.29</v>
+        <v>54.19</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.473</v>
+        <v>0.214</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.54</v>
+        <v>0.211</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4797,39 +4797,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1171400</v>
+        <v>1820100</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="H96" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.72</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.279</v>
+        <v>0.352</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.274</v>
+        <v>0.316</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4842,39 +4842,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.255</v>
+        <v>0.615</v>
       </c>
       <c r="E97" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1163700</v>
+        <v>1769700</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.3</v>
+        <v>0.58</v>
       </c>
       <c r="H97" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.45999999999999</v>
+      </c>
+      <c r="I97" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.25</v>
+        <v>0.608</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.254</v>
+        <v>0.586</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4887,39 +4887,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.645</v>
+        <v>1.27</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0077</v>
+        <v>-0.0155</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1154400</v>
+        <v>1750300</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="H98" t="n">
-        <v>66.18000000000001</v>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.04</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.63</v>
+        <v>1.231</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.586</v>
+        <v>1.128</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4932,28 +4932,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0254</v>
+        <v>0.26</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1145800</v>
+        <v>1702900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.41</v>
+        <v>2.39</v>
       </c>
       <c r="H99" t="n">
-        <v>40.37</v>
+        <v>45.51</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.593</v>
+        <v>0.262</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.613</v>
+        <v>0.267</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4977,28 +4977,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>4.97</v>
+        <v>0.28</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.0175</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1105100</v>
+        <v>1700900</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.21</v>
+        <v>1.09</v>
       </c>
       <c r="H100" t="n">
-        <v>49.07</v>
+        <v>62.61</v>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>4.976</v>
+        <v>0.254</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>5.032</v>
+        <v>0.271</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5022,39 +5022,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1051400</v>
+        <v>1699300</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H101" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.67</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.332</v>
+        <v>1.971</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.309</v>
+        <v>2.091</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5067,39 +5067,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SEALINK</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1041500</v>
+        <v>1688000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.14</v>
+        <v>2.43</v>
       </c>
       <c r="H102" t="n">
-        <v>51.39</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.45</v>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.213</v>
+        <v>0.314</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.211</v>
+        <v>0.308</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5112,39 +5112,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>4.82</v>
+        <v>0.315</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0021</v>
+        <v>-0.0308</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1019900</v>
+        <v>1682400</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="H103" t="n">
-        <v>42.95</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.78</v>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>4.857</v>
+        <v>0.322</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>4.973</v>
+        <v>0.339</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5157,28 +5157,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0612</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1017800</v>
+        <v>1639900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.08</v>
+        <v>1.59</v>
       </c>
       <c r="H104" t="n">
-        <v>32.39</v>
+        <v>63.48</v>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
@@ -5186,10 +5186,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.335</v>
+        <v>0.213</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.459</v>
+        <v>0.206</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5202,28 +5202,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E105" s="16" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.365</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0395</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1009900</v>
+        <v>1615800</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.33</v>
+        <v>0.98</v>
       </c>
       <c r="H105" t="n">
-        <v>28.31</v>
+        <v>33.95</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.931</v>
+        <v>0.393</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.969</v>
+        <v>0.391</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5247,39 +5247,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1007900</v>
+        <v>1591100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H106" t="n">
-        <v>56.38</v>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.46</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.44</v>
+        <v>0.655</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5292,28 +5292,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0114</v>
+        <v>-0.0118</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>996300</v>
+        <v>1582800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="H107" t="n">
-        <v>33.64</v>
+        <v>33.89</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.69</v>
+        <v>1.752</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.802</v>
+        <v>1.864</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5337,28 +5337,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.58</v>
+        <v>1.95</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.0153</v>
+        <v>-0.0051</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>994200</v>
+        <v>1577700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H108" t="n">
-        <v>52</v>
+        <v>45.25</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.567</v>
+        <v>1.987</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.529</v>
+        <v>1.977</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5382,28 +5382,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.68</v>
+        <v>0.575</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.0059</v>
+        <v>-0.0254</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>969300</v>
+        <v>1567900</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>34.87</v>
+        <v>40.37</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.753</v>
+        <v>0.593</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.864</v>
+        <v>0.613</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5427,28 +5427,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1.95</v>
+        <v>0.325</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>-0.0051</v>
+        <v>-0.0152</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>967700</v>
+        <v>1505100</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H110" t="n">
-        <v>45.25</v>
+        <v>90.75</v>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>1.987</v>
+        <v>0.253</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1.977</v>
+        <v>0.216</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5472,28 +5472,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>0</v>
+        <v>2.23</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0.0229</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>946600</v>
+        <v>1499900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="H111" t="n">
-        <v>34.81</v>
+        <v>53.37</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.127</v>
+        <v>2.216</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.155</v>
+        <v>2.094</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5517,28 +5517,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.12</v>
+        <v>7.84</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>-0.0261</v>
+        <v>-0.0025</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>892000</v>
+        <v>1494900</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.34</v>
+        <v>0.13</v>
       </c>
       <c r="H112" t="n">
-        <v>72.06999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.997</v>
+        <v>8.013</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.863</v>
+        <v>8.282</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5562,28 +5562,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>0.0237</v>
+        <v>2.56</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>845600</v>
+        <v>1494800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>1.12</v>
+        <v>0.24</v>
       </c>
       <c r="H113" t="n">
-        <v>58.75</v>
+        <v>49.74</v>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.646</v>
+        <v>2.565</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.729</v>
+        <v>2.528</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5607,39 +5607,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>0.0183</v>
+        <v>0.725</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>840400</v>
+        <v>1483600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="H114" t="n">
-        <v>52.64</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.11</v>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>2.215</v>
+        <v>0.661</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2.094</v>
+        <v>0.606</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5652,39 +5652,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3.78</v>
+        <v>1.07</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>-0.0026</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>836600</v>
+        <v>1473700</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="H115" t="n">
-        <v>71.75</v>
-      </c>
-      <c r="I115" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.09</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>3.407</v>
+        <v>1.126</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>3.178</v>
+        <v>1.155</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5697,28 +5697,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>3.92</v>
+        <v>0.46</v>
       </c>
       <c r="E116" s="16" t="n">
-        <v>0.0182</v>
+        <v>0.011</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>807000</v>
+        <v>1431400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="H116" t="n">
-        <v>65.2</v>
+        <v>57.95</v>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>3.697</v>
+        <v>0.441</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>3.352</v>
+        <v>0.43</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5742,28 +5742,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0165</v>
+        <v>1.09</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>740900</v>
+        <v>1379700</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="H117" t="n">
-        <v>57.39</v>
+        <v>78.48</v>
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.985</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.574</v>
+        <v>0.829</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5787,28 +5787,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>-0.0105</v>
+        <v>-0.0068</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>731900</v>
+        <v>1328100</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="H118" t="n">
-        <v>34.47</v>
+        <v>41.29</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.972</v>
+        <v>1.473</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>2.091</v>
+        <v>1.54</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5832,39 +5832,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.54</v>
+        <v>0.335</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0152</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>729100</v>
+        <v>1327600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="H119" t="n">
-        <v>63.07</v>
-      </c>
-      <c r="I119" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.63</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.489</v>
+        <v>0.337</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.389</v>
+        <v>0.329</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5877,28 +5877,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.17</v>
+        <v>0.59</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>-0.0168</v>
+        <v>-0.0248</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>708700</v>
+        <v>1264800</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="H120" t="n">
-        <v>67.22</v>
+        <v>56.04</v>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.089</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.991</v>
+        <v>0.574</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5922,39 +5922,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>689500</v>
+        <v>1264500</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H121" t="n">
-        <v>78.48</v>
-      </c>
-      <c r="I121" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.7</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.985</v>
+        <v>0.199</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.829</v>
+        <v>0.196</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5967,39 +5967,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E122" s="16" t="n">
-        <v>0.0095</v>
+        <v>0.64</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>684900</v>
+        <v>1222400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="H122" t="n">
-        <v>56.47</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.33</v>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.029</v>
+        <v>0.63</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.99</v>
+        <v>0.586</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6012,39 +6012,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>0.0038</v>
+        <v>2.6</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>659100</v>
+        <v>1219300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H123" t="n">
-        <v>81.98</v>
-      </c>
-      <c r="I123" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.64</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>2.398</v>
+        <v>2.69</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>2.073</v>
+        <v>2.802</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6057,28 +6057,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>0.0051</v>
+        <v>0.335</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>653700</v>
+        <v>1213200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1.25</v>
+        <v>0.12</v>
       </c>
       <c r="H124" t="n">
-        <v>53.68</v>
+        <v>54.93</v>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.979</v>
+        <v>0.332</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.974</v>
+        <v>0.309</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6102,39 +6102,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>4.66</v>
+        <v>0.25</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0196</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>639600</v>
+        <v>1209800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="H125" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="I125" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.55</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>4.753</v>
+        <v>0.249</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>5.02</v>
+        <v>0.254</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6147,39 +6147,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>637700</v>
+        <v>1176500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="H126" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.22</v>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.633</v>
+        <v>1.089</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.628</v>
+        <v>0.991</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6192,28 +6192,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>-0.0053</v>
+        <v>0.275</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>632900</v>
+        <v>1171400</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.08</v>
+        <v>1.32</v>
       </c>
       <c r="H127" t="n">
-        <v>39.75</v>
+        <v>43.77</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6221,10 +6221,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>7.743</v>
+        <v>0.279</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>7.867</v>
+        <v>0.274</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6237,39 +6237,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>-0.0166</v>
+        <v>0.885</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>630700</v>
+        <v>1164400</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H128" t="n">
-        <v>50.06</v>
-      </c>
-      <c r="I128" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.31</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.774</v>
+        <v>0.931</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.811</v>
+        <v>0.969</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6282,28 +6282,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MNRB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>0.0389</v>
+        <v>1.14</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>630500</v>
+        <v>1128600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1.28</v>
+        <v>0.43</v>
       </c>
       <c r="H129" t="n">
-        <v>58.99</v>
+        <v>76.14</v>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>2.868</v>
+        <v>0.999</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>2.857</v>
+        <v>0.863</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6327,39 +6327,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>-0.0073</v>
+        <v>6.29</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>595100</v>
+        <v>1115500</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>3.57</v>
+        <v>0.06</v>
       </c>
       <c r="H130" t="n">
-        <v>42.76</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.97</v>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>6.33</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.681</v>
+        <v>6.514</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6372,28 +6372,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>HEKTAR</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>592200</v>
+        <v>1044000</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="H131" t="n">
-        <v>66.69</v>
+        <v>49.67</v>
       </c>
       <c r="I131" s="15" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.5</v>
+        <v>0.241</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.473</v>
+        <v>0.243</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6417,39 +6417,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>-0.0129</v>
+        <v>0.44</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>578300</v>
+        <v>1034700</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.11</v>
+        <v>4.86</v>
       </c>
       <c r="H132" t="n">
-        <v>71.63</v>
-      </c>
-      <c r="I132" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.23</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.671</v>
+        <v>0.439</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.602</v>
+        <v>0.431</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6462,28 +6462,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>568600</v>
+        <v>1017700</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H133" t="n">
-        <v>56.23</v>
+        <v>55.59</v>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>3.021</v>
+        <v>7.939</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>3.042</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6507,39 +6507,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>-0.0066</v>
+        <v>1.06</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>568200</v>
+        <v>1012400</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.23</v>
+        <v>0.64</v>
       </c>
       <c r="H134" t="n">
-        <v>31.59</v>
-      </c>
-      <c r="I134" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.47</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.573</v>
+        <v>1.029</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.688</v>
+        <v>0.99</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6552,39 +6552,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.95</v>
+        <v>7.52</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0206</v>
+        <v>-0.0092</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>562100</v>
+        <v>981300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="H135" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.77</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.905</v>
+        <v>7.74</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.77</v>
+        <v>7.866</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6597,28 +6597,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>-0.0217</v>
+        <v>1.4</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>555400</v>
+        <v>980500</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
       <c r="H136" t="n">
-        <v>56.02</v>
+        <v>50.51</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.334</v>
+        <v>1.417</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.128</v>
+        <v>1.312</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6642,39 +6642,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>0</v>
+        <v>4.58</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.0338</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>546600</v>
+        <v>971200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H137" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.48</v>
+      </c>
+      <c r="I137" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.417</v>
+        <v>4.39</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.312</v>
+        <v>4.429</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6687,39 +6687,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>0</v>
+        <v>6.73</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>537900</v>
+        <v>956500</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H138" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="I138" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.77</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>2.021</v>
+        <v>6.795</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.706</v>
+        <v>6.778</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6732,28 +6732,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>-0.0059</v>
+        <v>3.91</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>537500</v>
+        <v>954000</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H139" t="n">
-        <v>64.31999999999999</v>
+        <v>64.87</v>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.792</v>
+        <v>3.697</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.709</v>
+        <v>3.351</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6777,28 +6777,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>-0.0295</v>
+        <v>1.73</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>0.0237</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>523300</v>
+        <v>929900</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.2</v>
+        <v>1.23</v>
       </c>
       <c r="H140" t="n">
-        <v>58.31</v>
+        <v>58.75</v>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>4.392</v>
+        <v>1.646</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>4.429</v>
+        <v>1.729</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6822,28 +6822,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>-0.0063</v>
+        <v>2.63</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>511600</v>
+        <v>893000</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H141" t="n">
-        <v>58.67</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="I141" s="15" t="inlineStr">
         <is>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.753</v>
+        <v>2.4</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.74</v>
+        <v>2.074</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6867,39 +6867,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="E142" s="16" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.63</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>508100</v>
+        <v>887700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.12</v>
+        <v>0.67</v>
       </c>
       <c r="H142" t="n">
-        <v>54.04</v>
-      </c>
-      <c r="I142" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.81</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>7.935</v>
+        <v>0.633</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>8.173999999999999</v>
+        <v>0.628</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6912,45 +6912,1485 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="E143" s="16" t="n">
-        <v>0.0118</v>
+        <v>0.985</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>507700</v>
+        <v>865700</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H143" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.92</v>
+      </c>
+      <c r="I143" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>3.246</v>
+        <v>0.999</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>2.836</v>
+        <v>1.015</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>-0.0161</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>855200</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H144" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="I144" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>3.018</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.0277</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>854500</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H145" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="I145" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>5.292</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>836000</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H146" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="I146" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>816500</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H147" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I147" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>788800</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H148" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="I148" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ITMAX</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>770500</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H149" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>4.418</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>4.496</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>768800</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H150" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>758500</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H151" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="I151" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>753100</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H152" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="I152" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.0309</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>736300</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H153" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>1.697</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>728000</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H154" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>3.637</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>6459</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MNRB</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>714000</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H155" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I155" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>2.868</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>701500</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H156" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="I156" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>693300</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H157" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="I157" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>689700</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H158" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="I158" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>-0.0206</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>681600</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H159" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="I159" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>HEKTAR</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>642200</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H160" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="I160" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E161" s="16" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>635000</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H161" t="n">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>3.245</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>2.836</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>613800</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H162" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="I162" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>609900</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H163" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="I163" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SENFONG</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>607100</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H164" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>597400</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H165" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I165" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>575200</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H166" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="I166" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>2.769</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MAXIS</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>563000</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H167" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I167" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>3.579</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>3.602</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H168" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0336</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>WINSTAR</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>548500</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H169" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>536600</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>6.766</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>6.874</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ECOWLD</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>531700</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H171" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="I171" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>UMSINT</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="E172" s="16" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>530100</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H172" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="I172" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>8.318</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>8.122999999999999</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>526600</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H173" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>5.827</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>5.715</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>524100</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>518300</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H175" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I175" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>2.004</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M143"/>
+  <autoFilter ref="A1:M175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$193</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -568,19 +568,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0571</v>
+        <v>0.0476</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3265400</v>
+        <v>4292800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>84.29000000000001</v>
+        <v>83.77</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.947</v>
+        <v>0.946</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.78</v>
@@ -600,7 +600,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>RSI达84.29，处超买区间；现价1.11远高于50日均线0.78，EMA20与SAR多头信号虽成立，但短线过热。</t>
+          <t>RSI达83.77，处超买区；现价1.10远高于50日均线0.78，EMA20与SAR多头信号虽确认趋势，但短线过热，可靠性存疑。</t>
         </is>
       </c>
     </row>
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.175</v>
+        <v>0.18</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-0.0541</v>
+        <v>-0.027</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>204714100</v>
+        <v>214980100</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H3" t="n">
-        <v>20.58</v>
+        <v>20.93</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.245</v>
+        <v>0.24</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32551100</v>
+        <v>32995500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>60.73</v>
+        <v>56.77</v>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.233</v>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.3</v>
+        <v>0.295</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.1321</v>
+        <v>0.1132</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>29927500</v>
+        <v>32273300</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="H5" t="n">
-        <v>60.15</v>
+        <v>58.66</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.275</v>
+        <v>0.274</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.274</v>
@@ -762,10 +762,10 @@
         <v>0.0556</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>24990500</v>
+        <v>25781300</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>46.47</v>
+        <v>47.94</v>
       </c>
       <c r="H6" t="n">
         <v>81.81</v>
@@ -792,39 +792,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>23904800</v>
+        <v>24988900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>75.95</v>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.58</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.538</v>
+        <v>2.136</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.489</v>
+        <v>2.055</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -837,28 +837,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.0211</v>
+        <v>0.59</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>23775400</v>
+        <v>24777500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="H8" t="n">
-        <v>56.56</v>
+        <v>75.95</v>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.468</v>
+        <v>0.538</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.47</v>
+        <v>0.489</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -882,39 +882,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0141</v>
+        <v>0.48</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>21473200</v>
+        <v>23826500</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.5</v>
+        <v>0.97</v>
       </c>
       <c r="H9" t="n">
-        <v>47.59</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.94</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.138</v>
+        <v>0.467</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.056</v>
+        <v>0.47</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0.0303</v>
+        <v>0.165</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18482900</v>
+        <v>19599500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H10" t="n">
-        <v>73.19</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.14</v>
+        <v>0.139</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0.113</v>
@@ -972,28 +972,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0759</v>
+        <v>0.525</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-0.0367</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>18004000</v>
+        <v>18724900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="H11" t="n">
-        <v>65.12</v>
+        <v>25.96</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.377</v>
+        <v>0.657</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.315</v>
+        <v>0.875</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1017,28 +1017,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0183</v>
+        <v>0.42</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.0633</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17292300</v>
+        <v>18197900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="H12" t="n">
-        <v>26.62</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.658</v>
+        <v>0.377</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.875</v>
+        <v>0.315</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1062,39 +1062,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>17260200</v>
+        <v>18163700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="H13" t="n">
-        <v>37.55</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.58</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.243</v>
+        <v>0.302</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.25</v>
+        <v>0.289</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1107,39 +1107,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>16739200</v>
+        <v>18100100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="H14" t="n">
-        <v>62.58</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.55</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.302</v>
+        <v>0.243</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.289</v>
+        <v>0.25</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.0325</v>
+        <v>0.026</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>16595300</v>
+        <v>17145800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="H15" t="n">
-        <v>65.66</v>
+        <v>64.95</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0.0222</v>
+        <v>0.225</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>13470600</v>
+        <v>14739900</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H16" t="n">
-        <v>85.45</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1242,39 +1242,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.1081</v>
+        <v>0.12</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11601500</v>
+        <v>13693700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>15.47</v>
+        <v>0.53</v>
       </c>
       <c r="H17" t="n">
-        <v>73.70999999999999</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.23</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.364</v>
+        <v>0.141</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.333</v>
+        <v>0.165</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.77</v>
+        <v>0.765</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0129</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11159700</v>
+        <v>12731100</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H18" t="n">
-        <v>47.7</v>
+        <v>45.62</v>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
@@ -1332,28 +1332,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>-0.0123</v>
+        <v>0.41</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.1081</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10978500</v>
+        <v>12053800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.88</v>
+        <v>16.07</v>
       </c>
       <c r="H19" t="n">
-        <v>46.93</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.364</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1377,39 +1377,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.395</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10674500</v>
+        <v>11797700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.32</v>
+        <v>0.24</v>
       </c>
       <c r="H20" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.45999999999999</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.082</v>
+        <v>0.305</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.076</v>
+        <v>0.171</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1422,28 +1422,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0182</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LKL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.0184</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10324900</v>
+        <v>11784800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>98.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>53.98</v>
+        <v>44.53</v>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.034</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.034</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1467,28 +1467,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>-0.0164</v>
+        <v>0.155</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9912800</v>
+        <v>11680000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="H22" t="n">
-        <v>62.18</v>
+        <v>44.71</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1.714</v>
+        <v>0.156</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>1.493</v>
+        <v>0.16</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1512,28 +1512,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>1.8</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9703400</v>
+        <v>11434900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1.25</v>
+        <v>0.34</v>
       </c>
       <c r="H23" t="n">
-        <v>56.29</v>
+        <v>62.18</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.032</v>
+        <v>1.714</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.033</v>
+        <v>1.493</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1557,28 +1557,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0182</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>LKL</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0.0127</v>
+        <v>0.035</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>9328100</v>
+        <v>11203000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.19</v>
+        <v>106.42</v>
       </c>
       <c r="H24" t="n">
-        <v>85.84999999999999</v>
+        <v>53.98</v>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.305</v>
+        <v>0.034</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.171</v>
+        <v>0.034</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1602,28 +1602,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>4.82</v>
+        <v>0.09</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9312200</v>
+        <v>10684500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.52</v>
+        <v>1.32</v>
       </c>
       <c r="H25" t="n">
-        <v>61.39</v>
+        <v>67.23</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>4.71</v>
+        <v>0.082</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>4.482</v>
+        <v>0.076</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1647,39 +1647,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0</v>
+        <v>4.84</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9146800</v>
+        <v>10247100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.22</v>
+        <v>0.57</v>
       </c>
       <c r="H26" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.38</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.16</v>
+        <v>4.711</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.149</v>
+        <v>4.482</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1692,28 +1692,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0034</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MMAG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.025</v>
+        <v>0.865</v>
       </c>
       <c r="E27" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8888200</v>
+        <v>10139600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>3.97</v>
+        <v>0.57</v>
       </c>
       <c r="H27" t="n">
-        <v>49.97</v>
+        <v>45.39</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.025</v>
+        <v>0.868</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.027</v>
+        <v>0.871</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1737,28 +1737,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-0.0169</v>
+        <v>0.035</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8191900</v>
+        <v>9753400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="H28" t="n">
-        <v>64.13</v>
+        <v>56.29</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.27</v>
+        <v>0.032</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.268</v>
+        <v>0.033</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1782,39 +1782,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8103900</v>
+        <v>9685100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.85</v>
+        <v>0.24</v>
       </c>
       <c r="H29" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.62</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.609</v>
+        <v>0.16</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.603</v>
+        <v>0.148</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1827,39 +1827,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>MMAG</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>-0.0252</v>
+        <v>0.025</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8060800</v>
+        <v>8938300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.07</v>
+        <v>3.99</v>
       </c>
       <c r="H30" t="n">
-        <v>65.91</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.97</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.681</v>
+        <v>0.027</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>0.0106</v>
+        <v>0.016</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7998000</v>
+        <v>8698400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="H31" t="n">
-        <v>45.5</v>
+        <v>46.98</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.924</v>
+        <v>1.925</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>1.973</v>
@@ -1917,39 +1917,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0.0274</v>
+        <v>0.6</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7822200</v>
+        <v>8501700</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.38</v>
+        <v>0.89</v>
       </c>
       <c r="H32" t="n">
-        <v>56.64</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.4</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.367</v>
+        <v>0.609</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.366</v>
+        <v>0.603</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1962,39 +1962,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.0252</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7803200</v>
+        <v>8473500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="H33" t="n">
-        <v>45.39</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.91</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.868</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.871</v>
+        <v>0.681</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2007,39 +2007,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0.0417</v>
+        <v>2.37</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0247</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7422100</v>
+        <v>8366500</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="H34" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.27</v>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.142</v>
+        <v>2.346</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.165</v>
+        <v>2.224</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2052,28 +2052,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7346000</v>
+        <v>8265400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>3.44</v>
+        <v>1.41</v>
       </c>
       <c r="H35" t="n">
-        <v>42.33</v>
+        <v>64.13</v>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.592</v>
+        <v>0.27</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.654</v>
+        <v>0.268</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2097,39 +2097,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0</v>
+        <v>0.375</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7176100</v>
+        <v>7854900</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.25</v>
+        <v>1.38</v>
       </c>
       <c r="H36" t="n">
-        <v>34.18</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.64</v>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.185</v>
+        <v>0.367</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.228</v>
+        <v>0.366</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2142,39 +2142,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.0247</v>
+        <v>0.165</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>6931000</v>
+        <v>7738300</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="H37" t="n">
-        <v>53.27</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.18</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.346</v>
+        <v>0.185</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.224</v>
+        <v>0.228</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2187,28 +2187,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>0.0179</v>
+        <v>1.57</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>6795900</v>
+        <v>7480700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="H38" t="n">
-        <v>62.25</v>
+        <v>42.33</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.083</v>
+        <v>1.592</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.02</v>
+        <v>1.654</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2232,39 +2232,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4.8</v>
+        <v>1.15</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>0.0042</v>
+        <v>0.0268</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6643300</v>
+        <v>7137300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="H39" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.4</v>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>4.745</v>
+        <v>1.084</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>4.579</v>
+        <v>1.02</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2277,28 +2277,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TEKSENG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.305</v>
+        <v>1.03</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>0.0702</v>
+        <v>0.0098</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6598800</v>
+        <v>6943900</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>32.09</v>
+        <v>2.16</v>
       </c>
       <c r="H40" t="n">
-        <v>80.11</v>
+        <v>91.87</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.252</v>
+        <v>0.775</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.238</v>
+        <v>0.706</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2331,19 +2331,19 @@
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0278</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5983800</v>
+        <v>6842800</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H41" t="n">
-        <v>73.17</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>0.394</v>
@@ -2367,39 +2367,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0055</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SERSOL</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>-0.2</v>
+        <v>4.79</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5821700</v>
+        <v>6749500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.83</v>
+        <v>0.83</v>
       </c>
       <c r="H42" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.46</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.04</v>
+        <v>4.744</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.034</v>
+        <v>4.578</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2412,28 +2412,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>TEKSENG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.78</v>
+        <v>0.305</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0.013</v>
+        <v>0.0702</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5563700</v>
+        <v>6608800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1</v>
+        <v>32.14</v>
       </c>
       <c r="H43" t="n">
-        <v>83.98999999999999</v>
+        <v>80.11</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.764</v>
+        <v>0.252</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.749</v>
+        <v>0.238</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0055</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SERSOL</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0</v>
+        <v>0.04</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5542900</v>
+        <v>6031400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.47</v>
+        <v>1.9</v>
       </c>
       <c r="H44" t="n">
-        <v>85.70999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>3.326</v>
+        <v>0.04</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.23</v>
+        <v>0.034</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2502,28 +2502,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>-0.046</v>
+        <v>4.56</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.0201</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5469900</v>
+        <v>5984800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.89</v>
+        <v>0.51</v>
       </c>
       <c r="H45" t="n">
-        <v>55.46</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.397</v>
+        <v>3.335</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.397</v>
+        <v>2.232</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2547,28 +2547,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.0062</v>
+        <v>0.785</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5295600</v>
+        <v>5884200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1.69</v>
+        <v>1.06</v>
       </c>
       <c r="H46" t="n">
-        <v>49.77</v>
+        <v>86.17</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.804</v>
+        <v>0.764</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.806</v>
+        <v>0.749</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2592,28 +2592,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0013</v>
+        <v>2.94</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0.0103</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5250100</v>
+        <v>5787500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="H47" t="n">
-        <v>59.93</v>
+        <v>65.58</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>7.77</v>
+        <v>2.827</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>7.715</v>
+        <v>2.687</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2637,28 +2637,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.93</v>
+        <v>7.94</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>0.0069</v>
+        <v>0.0013</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5042300</v>
+        <v>5699700</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="H48" t="n">
-        <v>64.84999999999999</v>
+        <v>61.05</v>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.826</v>
+        <v>7.772</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.687</v>
+        <v>7.715</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2682,28 +2682,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.42</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5007900</v>
+        <v>5633900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.41</v>
+        <v>0.92</v>
       </c>
       <c r="H49" t="n">
-        <v>68.48</v>
+        <v>56.96</v>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.868</v>
+        <v>0.398</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.848</v>
+        <v>0.397</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2727,28 +2727,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.39</v>
+        <v>5.84</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>-0.0347</v>
+        <v>-0.0118</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4689500</v>
+        <v>5468400</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="H50" t="n">
-        <v>54.06</v>
+        <v>62.62</v>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.387</v>
+        <v>5.655</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.284</v>
+        <v>5.068</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2772,28 +2772,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0</v>
+        <v>1.4</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4330000</v>
+        <v>5347300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H51" t="n">
-        <v>44.71</v>
+        <v>55.64</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.156</v>
+        <v>1.388</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.16</v>
+        <v>1.284</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2817,39 +2817,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4210400</v>
+        <v>5317200</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.67</v>
+        <v>1.7</v>
       </c>
       <c r="H52" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.48</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.775</v>
+        <v>0.804</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.773</v>
+        <v>0.806</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2862,39 +2862,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.355</v>
+        <v>1.38</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.0405</v>
+        <v>-0.0861</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4166300</v>
+        <v>5137600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.58</v>
+        <v>28.15</v>
       </c>
       <c r="H53" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.67</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.332</v>
+        <v>1.436</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.317</v>
+        <v>1.432</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2907,28 +2907,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0118</v>
+        <v>0.9</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4029400</v>
+        <v>5137100</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.25</v>
+        <v>1.45</v>
       </c>
       <c r="H54" t="n">
-        <v>62.62</v>
+        <v>68.48</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>5.655</v>
+        <v>0.868</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>5.068</v>
+        <v>0.848</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2952,39 +2952,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LBALUM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0.0313</v>
+        <v>0.54</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3952300</v>
+        <v>4777700</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>12.93</v>
+        <v>0.71</v>
       </c>
       <c r="H55" t="n">
-        <v>70</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.04</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.479</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.471</v>
+        <v>0.594</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -3006,19 +3006,19 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0.0098</v>
+        <v>1.02</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3923300</v>
+        <v>4682200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="H56" t="n">
-        <v>82.59</v>
+        <v>82.06</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.854</v>
+        <v>0.853</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0.744</v>
@@ -3042,39 +3042,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.54</v>
+        <v>0.31</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>-0.0092</v>
+        <v>-0.0159</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3908500</v>
+        <v>4497800</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H57" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.27</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.306</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.594</v>
+        <v>0.293</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3087,39 +3087,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>-0.0242</v>
+        <v>1.23</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3897000</v>
+        <v>4465000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="H58" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.73</v>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.644</v>
+        <v>1.16</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.659</v>
+        <v>1.095</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3132,28 +3132,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0.025</v>
+        <v>0.26</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3885900</v>
+        <v>4356300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H59" t="n">
-        <v>63.73</v>
+        <v>39.54</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.16</v>
+        <v>0.276</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.095</v>
+        <v>0.317</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.0133</v>
+        <v>-0.0161</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3855600</v>
+        <v>4322000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="H60" t="n">
-        <v>40.98</v>
+        <v>37.29</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.379</v>
+        <v>0.644</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.392</v>
+        <v>0.659</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3222,39 +3222,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>-0.0098</v>
+        <v>0.77</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3797300</v>
+        <v>4268800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.18</v>
+        <v>0.68</v>
       </c>
       <c r="H61" t="n">
-        <v>89.05</v>
-      </c>
-      <c r="I61" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.49</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K61" s="9" t="n">
         <v>0.773</v>
-      </c>
-      <c r="K61" s="9" t="n">
-        <v>0.706</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3267,39 +3267,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.255</v>
+        <v>0.195</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3774500</v>
+        <v>4264700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="H62" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.28</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.284</v>
+        <v>0.198</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.333</v>
+        <v>0.196</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3312,28 +3312,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.265</v>
+        <v>0.355</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>-0.0185</v>
+        <v>-0.0405</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3753800</v>
+        <v>4221400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="H63" t="n">
-        <v>41.24</v>
+        <v>65.3</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.276</v>
+        <v>0.332</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0.317</v>
@@ -3357,28 +3357,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.405</v>
+        <v>0.325</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>-0.0357</v>
+        <v>-0.0152</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3615800</v>
+        <v>4202800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
       <c r="H64" t="n">
-        <v>48.41</v>
+        <v>90.75</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.406</v>
+        <v>0.253</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.409</v>
+        <v>0.216</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3402,39 +3402,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>0.1</v>
+        <v>0.535</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3569500</v>
+        <v>4069700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>6.96</v>
+        <v>0.29</v>
       </c>
       <c r="H65" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.36</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.146</v>
+        <v>0.518</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.144</v>
+        <v>0.469</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3447,39 +3447,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>LBALUM</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.0273</v>
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3545300</v>
+        <v>4028100</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.25</v>
+        <v>13.18</v>
       </c>
       <c r="H66" t="n">
-        <v>56.36</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.83</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.518</v>
+        <v>0.479</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3492,28 +3492,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>-0.0213</v>
+        <v>-0.0196</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3282200</v>
+        <v>3930100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="H67" t="n">
-        <v>52.68</v>
+        <v>33.17</v>
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.678</v>
+        <v>0.283</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.659</v>
+        <v>0.333</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3537,39 +3537,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.525</v>
+        <v>0.37</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0133</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3275000</v>
+        <v>3860600</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.53</v>
+        <v>0.83</v>
       </c>
       <c r="H68" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.98</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.518</v>
+        <v>0.379</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.529</v>
+        <v>0.392</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3591,19 +3591,19 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0168</v>
+        <v>-0.0336</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3240500</v>
+        <v>3845200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="H69" t="n">
-        <v>48.92</v>
+        <v>46.58</v>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.185</v>
+        <v>1.183</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.131</v>
+        <v>1.13</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3627,39 +3627,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>10.18</v>
+        <v>0.29</v>
       </c>
       <c r="E70" s="16" t="n">
-        <v>0.0039</v>
+        <v>0.0175</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3192200</v>
+        <v>3816800</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.17</v>
+        <v>0.48</v>
       </c>
       <c r="H70" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.08</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>10.178</v>
+        <v>0.3</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>10.346</v>
+        <v>0.313</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3672,39 +3672,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.385</v>
+        <v>0.405</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>-0.0375</v>
+        <v>-0.0357</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3094200</v>
+        <v>3735200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.97</v>
+        <v>0.33</v>
       </c>
       <c r="H71" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.41</v>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.37</v>
+        <v>0.409</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3717,28 +3717,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.67</v>
+        <v>0.525</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>-0.0074</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3020500</v>
+        <v>3692600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="H72" t="n">
-        <v>45</v>
+        <v>52.9</v>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.68</v>
+        <v>0.518</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.893</v>
+        <v>0.529</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3762,28 +3762,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.505</v>
+        <v>0.165</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2968100</v>
+        <v>3678500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.98</v>
+        <v>7.17</v>
       </c>
       <c r="H73" t="n">
-        <v>81.36</v>
+        <v>74.59</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.439</v>
+        <v>0.146</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.399</v>
+        <v>0.144</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3807,39 +3807,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>0</v>
+        <v>2.7</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0.0037</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2883900</v>
+        <v>3628000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H74" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.66</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.299</v>
+        <v>2.682</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.313</v>
+        <v>2.894</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3852,28 +3852,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.05</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>-0.0144</v>
+        <v>-0.0284</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2609000</v>
+        <v>3484400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="H75" t="n">
-        <v>45.19</v>
+        <v>51.73</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.069</v>
+        <v>0.677</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.113</v>
+        <v>0.658</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3897,28 +3897,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ENGTEX</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0</v>
+        <v>10.16</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.002</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2522600</v>
+        <v>3395900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>2.65</v>
+        <v>0.19</v>
       </c>
       <c r="H76" t="n">
-        <v>56.42</v>
+        <v>45.8</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.433</v>
+        <v>10.176</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.44</v>
+        <v>10.345</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3942,28 +3942,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.66</v>
+        <v>0.495</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>-0.0149</v>
+        <v>-0.01</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2429900</v>
+        <v>3141600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.25</v>
+        <v>1.04</v>
       </c>
       <c r="H77" t="n">
-        <v>60.88</v>
+        <v>77.48</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.629</v>
+        <v>0.438</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.399</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3987,28 +3987,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.37</v>
+        <v>0.38</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>-0.09269999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2407900</v>
+        <v>3125000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>13.19</v>
+        <v>0.98</v>
       </c>
       <c r="H78" t="n">
-        <v>40.54</v>
+        <v>46.11</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.435</v>
+        <v>0.399</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.431</v>
+        <v>0.37</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4032,28 +4032,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>0.015</v>
+        <v>4.83</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2369000</v>
+        <v>3020000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="H79" t="n">
-        <v>62.02</v>
+        <v>44.01</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.592</v>
+        <v>4.857</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.476</v>
+        <v>4.973</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4077,39 +4077,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0066</v>
+        <v>0.37</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2355700</v>
+        <v>3007800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="H80" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.08</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.801</v>
+        <v>0.37</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.855</v>
+        <v>0.37</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>0</v>
+        <v>2.7</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2322900</v>
+        <v>2969600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="H81" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.42</v>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.059</v>
+        <v>2.591</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.072</v>
+        <v>2.476</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4167,28 +4167,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.46</v>
+        <v>1.3</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>0.025</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2174700</v>
+        <v>2954700</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.32</v>
+        <v>0.23</v>
       </c>
       <c r="H82" t="n">
-        <v>82.66</v>
+        <v>35.39</v>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.103</v>
+        <v>1.336</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.905</v>
+        <v>1.459</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4212,28 +4212,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>ENGTEX</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.0112</v>
+        <v>0.445</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2137100</v>
+        <v>2843400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.1</v>
+        <v>2.99</v>
       </c>
       <c r="H83" t="n">
-        <v>58.44</v>
+        <v>56.42</v>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>2.588</v>
+        <v>0.433</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>2.425</v>
+        <v>0.44</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4257,28 +4257,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>0.0092</v>
+        <v>2.05</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.0144</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2134000</v>
+        <v>2767000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>65.22</v>
+        <v>45.19</v>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.511</v>
+        <v>2.069</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.459</v>
+        <v>2.113</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4311,19 +4311,19 @@
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>13.12</v>
+        <v>13.1</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0015</v>
+        <v>-0.003</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2129500</v>
+        <v>2684500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="H85" t="n">
-        <v>26.72</v>
+        <v>26.3</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>13.542</v>
+        <v>13.54</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>14.106</v>
+        <v>14.105</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4347,39 +4347,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0.0021</v>
+        <v>0.66</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2098000</v>
+        <v>2661900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="H86" t="n">
-        <v>45.37</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.88</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>4.858</v>
+        <v>0.629</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>4.973</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4392,39 +4392,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0.0223</v>
+        <v>7.82</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2070600</v>
+        <v>2605000</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H87" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.59</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>4.611</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>4.54</v>
+        <v>8.282</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4437,28 +4437,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0612</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2064400</v>
+        <v>2489900</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.23</v>
+        <v>2.41</v>
       </c>
       <c r="H88" t="n">
-        <v>50.08</v>
+        <v>63.48</v>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
@@ -4466,10 +4466,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.37</v>
+        <v>0.213</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.37</v>
+        <v>0.206</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4482,39 +4482,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1992700</v>
+        <v>2466500</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.15</v>
+        <v>0.65</v>
       </c>
       <c r="H89" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.9</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.335</v>
+        <v>0.801</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.459</v>
+        <v>0.855</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4527,39 +4527,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>-0.0111</v>
+        <v>2.49</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0.0375</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1990100</v>
+        <v>2455300</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.26</v>
+        <v>1.49</v>
       </c>
       <c r="H90" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.40000000000001</v>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.444</v>
+        <v>2.106</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.4</v>
+        <v>1.906</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4572,28 +4572,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0026</v>
+        <v>0.545</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1977000</v>
+        <v>2434800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="H91" t="n">
-        <v>71.75</v>
+        <v>64.2</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>3.407</v>
+        <v>0.511</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>3.178</v>
+        <v>0.459</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4617,28 +4617,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0276</v>
+        <v>0.615</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1961100</v>
+        <v>2419700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H92" t="n">
-        <v>47.72</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.772</v>
+        <v>0.608</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.81</v>
+        <v>0.586</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4662,39 +4662,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>4.96</v>
+        <v>1</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>-0.004</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1931300</v>
+        <v>2400000</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="H93" t="n">
-        <v>48.53</v>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.5</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>4.975</v>
+        <v>1.058</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>5.032</v>
+        <v>1.072</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4707,28 +4707,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.615</v>
+        <v>3.81</v>
       </c>
       <c r="E94" s="16" t="n">
-        <v>0.0336</v>
+        <v>0.0053</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1867300</v>
+        <v>2395600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.31</v>
+        <v>0.57</v>
       </c>
       <c r="H94" t="n">
-        <v>78.39</v>
+        <v>72.94</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.544</v>
+        <v>3.41</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.485</v>
+        <v>3.179</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0.0233</v>
+        <v>4.96</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1853800</v>
+        <v>2253800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="H95" t="n">
-        <v>54.19</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.53</v>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.214</v>
+        <v>4.975</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.211</v>
+        <v>5.032</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4797,39 +4797,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>-0.0263</v>
+        <v>4.62</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>0.029</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1820100</v>
+        <v>2198200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.16</v>
+        <v>0.29</v>
       </c>
       <c r="H96" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.97</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.352</v>
+        <v>4.614</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.316</v>
+        <v>4.541</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4842,28 +4842,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1769700</v>
+        <v>2182900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.58</v>
+        <v>0.1</v>
       </c>
       <c r="H97" t="n">
-        <v>69.45999999999999</v>
+        <v>58.44</v>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.608</v>
+        <v>2.588</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.586</v>
+        <v>2.425</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4887,28 +4887,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.27</v>
+        <v>7.54</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0155</v>
+        <v>-0.0066</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1750300</v>
+        <v>2148400</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.42</v>
+        <v>0.29</v>
       </c>
       <c r="H98" t="n">
-        <v>57.04</v>
+        <v>39.42</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.231</v>
+        <v>7.742</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.128</v>
+        <v>7.866</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4932,39 +4932,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.26</v>
+        <v>0.615</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>0.0196</v>
+        <v>0.0336</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1702900</v>
+        <v>2136400</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>2.39</v>
+        <v>1.5</v>
       </c>
       <c r="H99" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.39</v>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.262</v>
+        <v>0.544</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.267</v>
+        <v>0.485</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4977,28 +4977,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.28</v>
+        <v>1.76</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.0175</v>
+        <v>-0.0276</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1700900</v>
+        <v>2119100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.09</v>
+        <v>0.32</v>
       </c>
       <c r="H100" t="n">
-        <v>62.61</v>
+        <v>47.72</v>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.254</v>
+        <v>1.772</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.271</v>
+        <v>1.81</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5022,39 +5022,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.87</v>
+        <v>0.365</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>-0.0158</v>
+        <v>-0.0395</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1699300</v>
+        <v>2077400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.38</v>
+        <v>1.32</v>
       </c>
       <c r="H101" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.51000000000001</v>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.971</v>
+        <v>0.351</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.091</v>
+        <v>0.316</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5067,28 +5067,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SEALINK</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>0.0154</v>
+        <v>2.56</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1688000</v>
+        <v>2063800</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>2.43</v>
+        <v>0.32</v>
       </c>
       <c r="H102" t="n">
-        <v>67.45</v>
+        <v>49.74</v>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.314</v>
+        <v>2.565</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.308</v>
+        <v>2.528</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5112,28 +5112,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.315</v>
+        <v>6.27</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0308</v>
+        <v>-0.0032</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1682400</v>
+        <v>2037600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="H103" t="n">
-        <v>43.78</v>
+        <v>43.74</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.322</v>
+        <v>6.328</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.339</v>
+        <v>6.514</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5157,28 +5157,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.23</v>
+        <v>1.95</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.0612</v>
+        <v>-0.0051</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1639900</v>
+        <v>2036100</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1.59</v>
+        <v>0.29</v>
       </c>
       <c r="H104" t="n">
-        <v>63.48</v>
+        <v>45.25</v>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
@@ -5186,10 +5186,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.213</v>
+        <v>1.987</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.206</v>
+        <v>1.977</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5202,28 +5202,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.365</v>
+        <v>0.445</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.0395</v>
+        <v>-0.0111</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1615800</v>
+        <v>2033700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.98</v>
+        <v>0.26</v>
       </c>
       <c r="H105" t="n">
-        <v>33.95</v>
+        <v>52.86</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.393</v>
+        <v>0.444</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5247,39 +5247,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.68</v>
+        <v>2.7</v>
       </c>
       <c r="E106" s="16" t="n">
-        <v>0.0625</v>
+        <v>0.0385</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1591100</v>
+        <v>2013900</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1.5</v>
+        <v>0.31</v>
       </c>
       <c r="H106" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.83</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.655</v>
+        <v>2.406</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.65</v>
+        <v>2.075</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5292,28 +5292,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0118</v>
+        <v>-0.0233</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1582800</v>
+        <v>1961300</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="H107" t="n">
-        <v>33.89</v>
+        <v>55.88</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.752</v>
+        <v>1.23</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.864</v>
+        <v>1.128</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5337,39 +5337,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.0051</v>
+        <v>-0.0105</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1577700</v>
+        <v>1900700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="H108" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="I108" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.47</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.987</v>
+        <v>1.972</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.977</v>
+        <v>2.091</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5382,28 +5382,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>-0.0254</v>
+        <v>0.215</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1567900</v>
+        <v>1892800</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H109" t="n">
-        <v>40.37</v>
+        <v>51.39</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.593</v>
+        <v>0.213</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.613</v>
+        <v>0.211</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5427,28 +5427,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>SEALINK</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>-0.0152</v>
+        <v>0.33</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1505100</v>
+        <v>1847000</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.17</v>
+        <v>2.66</v>
       </c>
       <c r="H110" t="n">
-        <v>90.75</v>
+        <v>67.45</v>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.253</v>
+        <v>0.314</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.216</v>
+        <v>0.308</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5481,19 +5481,19 @@
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="E111" s="16" t="n">
-        <v>0.0229</v>
+        <v>0.0321</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1499900</v>
+        <v>1834100</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H111" t="n">
-        <v>53.37</v>
+        <v>54.77</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>2.216</v>
+        <v>2.218</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.094</v>
+        <v>2.095</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5517,39 +5517,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>7.84</v>
+        <v>1.68</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>-0.0025</v>
+        <v>-0.0059</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1494900</v>
+        <v>1789300</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H112" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I112" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.87</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>8.013</v>
+        <v>1.753</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>8.282</v>
+        <v>1.864</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5562,39 +5562,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0229</v>
+        <v>0.26</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1494800</v>
+        <v>1785500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.24</v>
+        <v>2.51</v>
       </c>
       <c r="H113" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="I113" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>2.565</v>
+        <v>0.262</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>2.528</v>
+        <v>0.267</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5607,28 +5607,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.725</v>
+        <v>1.09</v>
       </c>
       <c r="E114" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1483600</v>
+        <v>1779000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H114" t="n">
-        <v>71.11</v>
+        <v>78.48</v>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.661</v>
+        <v>0.985</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.606</v>
+        <v>0.829</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5652,39 +5652,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.285</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1473700</v>
+        <v>1772200</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.63</v>
+        <v>1.14</v>
       </c>
       <c r="H115" t="n">
-        <v>33.09</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.79000000000001</v>
+      </c>
+      <c r="I115" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.126</v>
+        <v>0.254</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1.155</v>
+        <v>0.271</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5697,39 +5697,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="E116" s="16" t="n">
-        <v>0.011</v>
+        <v>0.0625</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1431400</v>
+        <v>1766200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.42</v>
+        <v>1.67</v>
       </c>
       <c r="H116" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.46</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.441</v>
+        <v>0.655</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5742,28 +5742,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1379700</v>
+        <v>1761500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="H117" t="n">
-        <v>78.48</v>
+        <v>46.33</v>
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.985</v>
+        <v>0.323</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.829</v>
+        <v>0.339</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5787,28 +5787,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.45</v>
+        <v>0.36</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>-0.0068</v>
+        <v>-0.0526</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1328100</v>
+        <v>1701400</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.5</v>
+        <v>1.03</v>
       </c>
       <c r="H118" t="n">
-        <v>41.29</v>
+        <v>32.31</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.473</v>
+        <v>0.392</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.54</v>
+        <v>0.391</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5832,28 +5832,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0.0152</v>
+        <v>2.6</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1327600</v>
+        <v>1649400</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H119" t="n">
-        <v>49.63</v>
+        <v>33.64</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.337</v>
+        <v>2.69</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.329</v>
+        <v>2.802</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5877,28 +5877,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>-0.0248</v>
+        <v>-0.0069</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1264800</v>
+        <v>1612500</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="H120" t="n">
-        <v>56.04</v>
+        <v>69.33</v>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.574</v>
+        <v>0.606</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5922,28 +5922,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>0.0256</v>
+        <v>0.575</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0254</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1264500</v>
+        <v>1603400</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.15</v>
+        <v>0.57</v>
       </c>
       <c r="H121" t="n">
-        <v>50.7</v>
+        <v>40.37</v>
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
@@ -5951,10 +5951,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.199</v>
+        <v>0.593</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.196</v>
+        <v>0.613</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5967,39 +5967,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>-0.0154</v>
+        <v>1.47</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1222400</v>
+        <v>1572100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="H122" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="I122" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.88</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.63</v>
+        <v>1.475</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.586</v>
+        <v>1.541</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6012,28 +6012,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.0114</v>
+        <v>0.44</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1219300</v>
+        <v>1534700</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.38</v>
+        <v>7.21</v>
       </c>
       <c r="H123" t="n">
-        <v>33.64</v>
+        <v>57.23</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>2.69</v>
+        <v>0.439</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>2.802</v>
+        <v>0.431</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6057,39 +6057,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1213200</v>
+        <v>1489900</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="H124" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="I124" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.09</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.332</v>
+        <v>1.126</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.309</v>
+        <v>1.155</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6102,39 +6102,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0.46</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0.011</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1209800</v>
+        <v>1464900</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="H125" t="n">
-        <v>49.55</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.95</v>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.249</v>
+        <v>0.441</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.254</v>
+        <v>0.43</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6147,28 +6147,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>1.17</v>
+        <v>0.59</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>-0.0168</v>
+        <v>-0.0248</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1176500</v>
+        <v>1420900</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="H126" t="n">
-        <v>67.22</v>
+        <v>56.04</v>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.089</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.991</v>
+        <v>0.574</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6192,39 +6192,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.275</v>
+        <v>0.245</v>
       </c>
       <c r="E127" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1171400</v>
+        <v>1400500</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>1.32</v>
+        <v>0.67</v>
       </c>
       <c r="H127" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.86</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.279</v>
+        <v>0.241</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.274</v>
+        <v>0.243</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6237,28 +6237,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E128" s="16" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.26</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1164400</v>
+        <v>1396000</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.38</v>
+        <v>1.08</v>
       </c>
       <c r="H128" t="n">
-        <v>28.31</v>
+        <v>55.36</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.931</v>
+        <v>0.256</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.969</v>
+        <v>0.259</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6282,39 +6282,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.33</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1128600</v>
+        <v>1347900</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="H129" t="n">
-        <v>76.14</v>
-      </c>
-      <c r="I129" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.27</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.999</v>
+        <v>0.337</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.863</v>
+        <v>0.329</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6327,28 +6327,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>6.29</v>
+        <v>0.335</v>
       </c>
       <c r="E130" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1115500</v>
+        <v>1317000</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H130" t="n">
-        <v>44.97</v>
+        <v>54.93</v>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>6.33</v>
+        <v>0.332</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>6.514</v>
+        <v>0.309</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6372,39 +6372,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>-0.0204</v>
+        <v>0.885</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1044000</v>
+        <v>1287600</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="H131" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.31</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.241</v>
+        <v>0.931</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.243</v>
+        <v>0.969</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6417,39 +6417,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>0</v>
+        <v>8.1</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1034700</v>
+        <v>1273100</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>4.86</v>
+        <v>0.31</v>
       </c>
       <c r="H132" t="n">
-        <v>57.23</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.21</v>
+      </c>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.439</v>
+        <v>7.938</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.431</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6462,28 +6462,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="E133" s="16" t="n">
-        <v>0.0137</v>
+        <v>1.18</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1017700</v>
+        <v>1270000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="H133" t="n">
-        <v>55.59</v>
+        <v>69.41</v>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>7.939</v>
+        <v>1.09</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>8.175000000000001</v>
+        <v>0.992</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6507,39 +6507,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E134" s="16" t="n">
-        <v>0.0095</v>
+        <v>0.99</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1012400</v>
+        <v>1266300</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H134" t="n">
-        <v>56.47</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.18</v>
+      </c>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.029</v>
+        <v>0.999</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.99</v>
+        <v>1.015</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6552,28 +6552,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>7.52</v>
+        <v>3.44</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0092</v>
+        <v>-0.0115</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>981300</v>
+        <v>1247300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="H135" t="n">
-        <v>38.77</v>
+        <v>33.41</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>7.74</v>
+        <v>3.636</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>7.866</v>
+        <v>3.709</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6597,39 +6597,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E136" s="17" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>980500</v>
+        <v>1242300</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H136" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.18000000000001</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.417</v>
+        <v>0.63</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.312</v>
+        <v>0.586</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6642,28 +6642,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>4.58</v>
+        <v>1.14</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>-0.0338</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>971200</v>
+        <v>1238100</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="H137" t="n">
-        <v>57.48</v>
+        <v>76.14</v>
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>4.39</v>
+        <v>0.999</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>4.429</v>
+        <v>0.863</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6687,28 +6687,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>6.73</v>
+        <v>0.25</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.0196</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>956500</v>
+        <v>1209800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H138" t="n">
-        <v>44.77</v>
+        <v>49.55</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>6.795</v>
+        <v>0.249</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>6.778</v>
+        <v>0.254</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6732,39 +6732,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="E139" s="16" t="n">
-        <v>0.0156</v>
+        <v>6.71</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>954000</v>
+        <v>1198400</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H139" t="n">
-        <v>64.87</v>
-      </c>
-      <c r="I139" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.37</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>3.697</v>
+        <v>6.794</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>3.351</v>
+        <v>6.778</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6777,39 +6777,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>0.0237</v>
+        <v>0.275</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>929900</v>
+        <v>1171400</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="H140" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="I140" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.77</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.646</v>
+        <v>0.279</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.729</v>
+        <v>0.274</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6822,39 +6822,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>0.0115</v>
+        <v>1.05</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>893000</v>
+        <v>1149000</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.14</v>
+        <v>0.72</v>
       </c>
       <c r="H141" t="n">
-        <v>82.70999999999999</v>
-      </c>
-      <c r="I141" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.97</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>2.4</v>
+        <v>1.028</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>2.074</v>
+        <v>0.99</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6867,39 +6867,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E142" s="17" t="n">
-        <v>0</v>
+        <v>4.57</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.0359</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>887700</v>
+        <v>1111200</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H142" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.08</v>
+      </c>
+      <c r="I142" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.633</v>
+        <v>4.389</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.628</v>
+        <v>4.428</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6912,28 +6912,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>-0.0051</v>
+        <v>3.92</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>865700</v>
+        <v>1082300</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H143" t="n">
-        <v>44.92</v>
+        <v>65.2</v>
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.999</v>
+        <v>3.697</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.015</v>
+        <v>3.352</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6957,28 +6957,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>3.05</v>
+        <v>0.76</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>-0.0161</v>
+        <v>-0.0194</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>855200</v>
+        <v>1038900</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H144" t="n">
-        <v>53.07</v>
+        <v>70.37</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>3.018</v>
+        <v>0.67</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>3.041</v>
+        <v>0.602</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7002,39 +7002,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>5.26</v>
+        <v>1.39</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>-0.0277</v>
+        <v>-0.0071</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>854500</v>
+        <v>1020700</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="H145" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="I145" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.73</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>5.292</v>
+        <v>1.416</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>5.265</v>
+        <v>1.312</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7047,28 +7047,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>0</v>
+        <v>5.26</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.0277</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>836000</v>
+        <v>1013300</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H146" t="n">
-        <v>62.41</v>
+        <v>49.46</v>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.488</v>
+        <v>5.292</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.389</v>
+        <v>5.265</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7092,39 +7092,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>-0.0132</v>
+        <v>1.12</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>816500</v>
+        <v>1005500</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="H147" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="I147" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.32</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.572</v>
+        <v>1.155</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.688</v>
+        <v>1.188</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7137,28 +7137,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.985</v>
+        <v>1.74</v>
       </c>
       <c r="E148" s="16" t="n">
-        <v>0.0051</v>
+        <v>0.0296</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>788800</v>
+        <v>986400</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="H148" t="n">
-        <v>53.68</v>
+        <v>59.68</v>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.979</v>
+        <v>1.647</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.974</v>
+        <v>1.729</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7182,39 +7182,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>0.0205</v>
+        <v>3.06</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>770500</v>
+        <v>972300</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="H149" t="n">
-        <v>53.01</v>
-      </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I149" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>4.418</v>
+        <v>3.019</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>4.496</v>
+        <v>3.041</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7227,28 +7227,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E150" s="17" t="n">
-        <v>0</v>
+        <v>4.46</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>768800</v>
+        <v>963400</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.24</v>
+        <v>0.51</v>
       </c>
       <c r="H150" t="n">
-        <v>59.59</v>
+        <v>51.87</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.336</v>
+        <v>4.416</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.128</v>
+        <v>4.495</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7272,28 +7272,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>0.0136</v>
+        <v>1.51</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>758500</v>
+        <v>952500</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="H151" t="n">
-        <v>55.77</v>
+        <v>31.59</v>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.472</v>
+        <v>1.573</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.473</v>
+        <v>1.688</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7317,28 +7317,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>-0.0127</v>
+        <v>1.48</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>753100</v>
+        <v>937800</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="H152" t="n">
-        <v>57.34</v>
+        <v>53.31</v>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.753</v>
+        <v>1.471</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.74</v>
+        <v>1.473</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7377,10 +7377,10 @@
         <v>-0.0309</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>736300</v>
+        <v>911600</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H153" t="n">
         <v>38.42</v>
@@ -7407,28 +7407,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>-0.0086</v>
+        <v>1.39</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>728000</v>
+        <v>908400</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H154" t="n">
-        <v>33.88</v>
+        <v>60.43</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>3.637</v>
+        <v>1.337</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>3.71</v>
+        <v>1.129</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7452,39 +7452,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MNRB</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E155" s="16" t="n">
-        <v>0.0389</v>
+        <v>0.63</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>714000</v>
+        <v>887700</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>1.45</v>
+        <v>0.67</v>
       </c>
       <c r="H155" t="n">
-        <v>58.99</v>
-      </c>
-      <c r="I155" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.81</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>2.868</v>
+        <v>0.633</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>2.857</v>
+        <v>0.628</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7497,28 +7497,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E156" s="17" t="n">
-        <v>0</v>
+        <v>1.96</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>701500</v>
+        <v>877000</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="H156" t="n">
-        <v>46.86</v>
+        <v>37.43</v>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.589</v>
+        <v>2.003</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.587</v>
+        <v>2.125</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7542,28 +7542,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>-0.0039</v>
+        <v>0.535</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>693300</v>
+        <v>836000</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="H157" t="n">
-        <v>84.48999999999999</v>
+        <v>62.41</v>
       </c>
       <c r="I157" s="15" t="inlineStr">
         <is>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.02</v>
+        <v>0.488</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.706</v>
+        <v>0.389</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7587,28 +7587,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>4.66</v>
+        <v>2.54</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0039</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>689700</v>
+        <v>835000</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.14</v>
+        <v>0.39</v>
       </c>
       <c r="H158" t="n">
-        <v>39.73</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>4.753</v>
+        <v>2.02</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>5.02</v>
+        <v>1.706</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7632,28 +7632,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.95</v>
+        <v>4.64</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>-0.0206</v>
+        <v>-0.0128</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>681600</v>
+        <v>834900</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.39</v>
+        <v>0.17</v>
       </c>
       <c r="H159" t="n">
-        <v>62.48</v>
+        <v>38.77</v>
       </c>
       <c r="I159" s="15" t="inlineStr">
         <is>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.905</v>
+        <v>4.751</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.77</v>
+        <v>5.02</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7677,28 +7677,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HEKTAR</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E160" s="16" t="n">
-        <v>0.0097</v>
+        <v>0.785</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>642200</v>
+        <v>815000</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.95</v>
+        <v>0.3</v>
       </c>
       <c r="H160" t="n">
-        <v>68.97</v>
+        <v>58.67</v>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.501</v>
+        <v>0.753</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.473</v>
+        <v>0.74</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7722,28 +7722,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E161" s="16" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.585</v>
+      </c>
+      <c r="E161" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>635000</v>
+        <v>804100</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H161" t="n">
-        <v>69.29000000000001</v>
+        <v>46.86</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7751,10 +7751,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>3.245</v>
+        <v>0.589</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>2.836</v>
+        <v>0.587</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7767,28 +7767,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>3.28</v>
+        <v>0.985</v>
       </c>
       <c r="E162" s="16" t="n">
-        <v>0.0186</v>
+        <v>0.0051</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>613800</v>
+        <v>788800</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.2</v>
+        <v>1.51</v>
       </c>
       <c r="H162" t="n">
-        <v>77.3</v>
+        <v>53.68</v>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>2.86</v>
+        <v>0.979</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.469</v>
+        <v>0.974</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7812,28 +7812,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MNRB</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>-0.0194</v>
+        <v>2.94</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>0.0389</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>609900</v>
+        <v>743700</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.12</v>
+        <v>1.51</v>
       </c>
       <c r="H163" t="n">
-        <v>70.37</v>
+        <v>58.99</v>
       </c>
       <c r="I163" s="15" t="inlineStr">
         <is>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.67</v>
+        <v>2.868</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.602</v>
+        <v>2.857</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7857,28 +7857,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.695</v>
+        <v>3.42</v>
       </c>
       <c r="E164" s="16" t="n">
-        <v>0.0146</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>607100</v>
+        <v>741000</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>3.65</v>
+        <v>0.24</v>
       </c>
       <c r="H164" t="n">
-        <v>52.75</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>3.245</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>2.836</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7902,28 +7902,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.84</v>
+        <v>0.945</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>-0.0059</v>
+        <v>-0.0258</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>597400</v>
+        <v>735400</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="H165" t="n">
-        <v>64.31999999999999</v>
+        <v>61.49</v>
       </c>
       <c r="I165" s="15" t="inlineStr">
         <is>
@@ -7931,10 +7931,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.792</v>
+        <v>0.904</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.709</v>
+        <v>0.77</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7947,28 +7947,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>-0.0236</v>
+        <v>3.27</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>575200</v>
+        <v>730700</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H166" t="n">
-        <v>59.46</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
@@ -7976,10 +7976,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>2.769</v>
+        <v>2.86</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>2.662</v>
+        <v>2.469</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7992,39 +7992,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>3.57</v>
+        <v>5.92</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>-0.0111</v>
+        <v>-0.0343</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>563000</v>
+        <v>694600</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H167" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I167" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.63</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>3.579</v>
+        <v>5.824</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>3.602</v>
+        <v>5.714</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8037,39 +8037,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E168" s="16" t="n">
-        <v>0.018</v>
+        <v>3.59</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>550000</v>
+        <v>693800</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="H168" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.5</v>
+      </c>
+      <c r="I168" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.156</v>
+        <v>3.581</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.188</v>
+        <v>3.603</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8082,39 +8082,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0336</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>WINSTAR</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>548500</v>
+        <v>657500</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="H169" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.26</v>
+      </c>
+      <c r="I169" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>0.651</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.608</v>
+        <v>0.598</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8136,19 +8136,19 @@
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="E170" s="16" t="n">
-        <v>0.0015</v>
+        <v>6.62</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>536600</v>
+        <v>651500</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H170" t="n">
-        <v>35.78</v>
+        <v>34.74</v>
       </c>
       <c r="I170" s="13" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>6.766</v>
+        <v>6.765</v>
       </c>
       <c r="K170" s="9" t="n">
         <v>6.874</v>
@@ -8172,28 +8172,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>HEKTAR</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>-0.0052</v>
+        <v>0.52</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>531700</v>
+        <v>642200</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.29</v>
+        <v>0.95</v>
       </c>
       <c r="H171" t="n">
-        <v>40.41</v>
+        <v>68.97</v>
       </c>
       <c r="I171" s="15" t="inlineStr">
         <is>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.96</v>
+        <v>0.501</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>2.029</v>
+        <v>0.473</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8217,28 +8217,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="E172" s="16" t="n">
-        <v>0.031</v>
+        <v>1.13</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>530100</v>
+        <v>640800</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2.35</v>
+        <v>0.28</v>
       </c>
       <c r="H172" t="n">
-        <v>60.81</v>
+        <v>59.23</v>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
@@ -8246,10 +8246,10 @@
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>8.318</v>
+        <v>1.077</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>8.122999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8262,39 +8262,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>5.95</v>
+        <v>2.9</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>-0.0294</v>
+        <v>-0.0236</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>526600</v>
+        <v>640600</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H173" t="n">
-        <v>54.51</v>
-      </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.46</v>
+      </c>
+      <c r="I173" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>5.827</v>
+        <v>2.769</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>5.715</v>
+        <v>2.662</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8307,28 +8307,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E174" s="17" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>524100</v>
+        <v>637000</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H174" t="n">
-        <v>38.02</v>
+        <v>58.68</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.007</v>
+        <v>0.614</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.051</v>
+        <v>0.577</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8352,28 +8352,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1.97</v>
+        <v>1.37</v>
       </c>
       <c r="E175" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>518300</v>
+        <v>628400</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="H175" t="n">
-        <v>38.8</v>
+        <v>62.95</v>
       </c>
       <c r="I175" s="15" t="inlineStr">
         <is>
@@ -8381,16 +8381,826 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>2.004</v>
+        <v>1.346</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>2.125</v>
+        <v>1.322</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>626900</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H176" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>625200</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H177" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I177" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>UMSINT</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>621500</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H178" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="I178" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>8.319000000000001</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>8.122999999999999</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SENFONG</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E179" s="16" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>607100</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H179" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>599500</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H180" t="n">
+        <v>60.57</v>
+      </c>
+      <c r="I180" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>1.864</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ECOWLD</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>592900</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H181" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="I181" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>1.961</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>580900</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>7034</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>TGUAN</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>560700</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H183" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>1.596</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E184" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>558300</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H184" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="I184" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E185" s="16" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>550100</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H185" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I185" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>7.646</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>7.796</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0336</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>WINSTAR</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E186" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>548500</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H186" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>544700</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H187" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>534600</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H188" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>529900</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H189" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>1.918</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>516200</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H190" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SENTRAL</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>508700</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H191" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>502000</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H192" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>2.428</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>7231</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>WELLCAL</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E193" s="16" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>500200</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H193" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="I193" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M175"/>
+  <autoFilter ref="A1:M193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.67高于50日均线0.645，EMA20与SAR均呈多头，T3形态突破；RSI 58.41处中性偏强区间，未超买，信号技术面一致性尚可。</t>
+          <t>现价0.67高于50日均线0.645，EMA20与SAR均呈多头，T3形态突破；RSI 58.41处中性偏强，未超买，信号技术面较可靠。</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
         <v>0.027</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>425152300</v>
+        <v>425202300</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>0.72</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>166667800</v>
+        <v>166867800</v>
       </c>
       <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -708,7 +708,7 @@
         <v>0.2075</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>64577400</v>
+        <v>64617400</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>4.71</v>
@@ -798,7 +798,7 @@
         <v>-0.0282</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>43454100</v>
+        <v>43462600</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>3.05</v>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>39988400</v>
+        <v>39920400</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>2.09</v>
@@ -1068,10 +1068,10 @@
         <v>-0.0556</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>29264000</v>
+        <v>29365000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>54.42</v>
+        <v>54.61</v>
       </c>
       <c r="H13" t="n">
         <v>67.5</v>
@@ -1113,7 +1113,7 @@
         <v>-0.0833</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>28929400</v>
+        <v>29009400</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>1.11</v>
@@ -1143,39 +1143,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.415</v>
+        <v>1.18</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.0506</v>
+        <v>0.1569</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>26299800</v>
+        <v>26309700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.16</v>
+        <v>8.19</v>
       </c>
       <c r="H15" t="n">
-        <v>63.43</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>94.29000000000001</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.376</v>
+        <v>0.79</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.314</v>
+        <v>0.709</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1188,39 +1188,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.18</v>
+        <v>0.415</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.1569</v>
+        <v>0.0506</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>26230700</v>
+        <v>26299800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>8.17</v>
+        <v>1.16</v>
       </c>
       <c r="H16" t="n">
-        <v>94.29000000000001</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.43</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.79</v>
+        <v>0.376</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.709</v>
+        <v>0.314</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1383,7 +1383,7 @@
         <v>0.013</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>22900100</v>
+        <v>22909100</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0.54</v>
@@ -1608,10 +1608,10 @@
         <v>0.1489</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>18544700</v>
+        <v>18928200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>0.0222</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>18199100</v>
+        <v>18247100</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0.9</v>
@@ -1781,7 +1781,7 @@
         <v>-0.03700000000000001</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>17214500</v>
+        <v>17216500</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0.88</v>
@@ -1916,10 +1916,10 @@
         <v>0.1081</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>16691200</v>
+        <v>16746200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>22.25</v>
+        <v>22.33</v>
       </c>
       <c r="H32" t="n">
         <v>73.70999999999999</v>
@@ -1961,7 +1961,7 @@
         <v>-0.0219</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>16652600</v>
+        <v>16664400</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0.49</v>
@@ -2051,7 +2051,7 @@
         <v>-0.0314</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>16310600</v>
+        <v>16335100</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>2.16</v>
@@ -2096,7 +2096,7 @@
         <v>0.0069</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>15580300</v>
+        <v>15582300</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>1.23</v>
@@ -2141,7 +2141,7 @@
         <v>-0.006500000000000001</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>15108100</v>
+        <v>15107100</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1.26</v>
@@ -2186,7 +2186,7 @@
         <v>-0.0021</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>14891700</v>
+        <v>14910200</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0.68</v>
@@ -2276,7 +2276,7 @@
         <v>-0.0229</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>14301000</v>
+        <v>14302300</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>2.25</v>
@@ -2321,10 +2321,10 @@
         <v>-0.0278</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>13463400</v>
+        <v>13572300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="H41" t="n">
         <v>66.87</v>
@@ -2906,7 +2906,7 @@
         <v>-0.0347</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>10026000</v>
+        <v>10027200</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0.77</v>
@@ -2951,7 +2951,7 @@
         <v>-0.0038</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>9990800</v>
+        <v>9991000</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0.89</v>
@@ -2996,7 +2996,7 @@
         <v>0.049</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>9901200</v>
+        <v>9902200</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>1.25</v>
@@ -3041,7 +3041,7 @@
         <v>-0.0064</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9693000</v>
+        <v>9693500</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0.55</v>
@@ -3131,7 +3131,7 @@
         <v>0.0157</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>9313400</v>
+        <v>9319100</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0.79</v>
@@ -3161,28 +3161,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>-0.03</v>
+        <v>1.08</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>9070900</v>
+        <v>9283100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="H60" t="n">
-        <v>52.44</v>
+        <v>82.63</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.581</v>
+        <v>0.944</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.474</v>
+        <v>0.779</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3206,39 +3206,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0.0286</v>
+        <v>2.59</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.03</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>9011100</v>
+        <v>9084200</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="H61" t="n">
-        <v>82.63</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.44</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.944</v>
+        <v>2.581</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.779</v>
+        <v>2.474</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
         <v>-0.046</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>8729000</v>
+        <v>8731000</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>1.43</v>
@@ -3446,7 +3446,7 @@
         <v>0.0179</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>8141300</v>
+        <v>8154300</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>0.72</v>
@@ -3626,10 +3626,10 @@
         <v>0.0702</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>7615200</v>
+        <v>7620200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>37.04</v>
+        <v>37.06</v>
       </c>
       <c r="H70" t="n">
         <v>80.11</v>
@@ -3881,39 +3881,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>-0.0256</v>
+        <v>1.23</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.025</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>6548400</v>
+        <v>6454200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>44.22</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.73</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.198</v>
+        <v>1.16</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.196</v>
+        <v>1.095</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3971,39 +3971,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.025</v>
+        <v>0.19</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>6445700</v>
+        <v>6415900</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="H78" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.22</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.16</v>
+        <v>0.198</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.095</v>
+        <v>0.196</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4121,7 +4121,7 @@
         <v>-0.0541</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>6267400</v>
+        <v>6269400</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0.87</v>
@@ -4151,39 +4151,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.0625</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>6217900</v>
+        <v>6231800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.49</v>
+        <v>2.18</v>
       </c>
       <c r="H82" t="n">
-        <v>50.91</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.36</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4196,28 +4196,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.075</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>6206800</v>
+        <v>6217900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="H83" t="n">
-        <v>35.39</v>
+        <v>50.91</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.336</v>
+        <v>0.075</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.459</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4241,39 +4241,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>4.58</v>
+        <v>1.3</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>0.02</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>6169200</v>
+        <v>6206800</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H84" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.39</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>4.61</v>
+        <v>1.336</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>4.54</v>
+        <v>1.459</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4286,28 +4286,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TFP</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>-0.07690000000000001</v>
+        <v>4.58</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>6133900</v>
+        <v>6169200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>2.15</v>
+        <v>0.82</v>
       </c>
       <c r="H85" t="n">
-        <v>41.36</v>
+        <v>49.8</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.065</v>
+        <v>4.61</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.074</v>
+        <v>4.54</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4391,7 +4391,7 @@
         <v>0.029</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>6029500</v>
+        <v>6048700</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>1.44</v>
@@ -4481,7 +4481,7 @@
         <v>-0.0364</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>5935100</v>
+        <v>5974500</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0.42</v>
@@ -4571,7 +4571,7 @@
         <v>-0.0261</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>5814800</v>
+        <v>5833900</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0.27</v>
@@ -4616,7 +4616,7 @@
         <v>-0.002</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>5724500</v>
+        <v>5724600</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0.31</v>
@@ -4706,7 +4706,7 @@
         <v>-0.03700000000000001</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>5579100</v>
+        <v>5609100</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0.46</v>
@@ -4886,7 +4886,7 @@
         <v>-0.0196</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>5427400</v>
+        <v>5429200</v>
       </c>
       <c r="G98" s="12" t="n">
         <v>0.2</v>
@@ -4976,10 +4976,10 @@
         <v>0.1</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>5321300</v>
+        <v>5356700</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="H100" t="n">
         <v>86.31999999999999</v>
@@ -5142,7 +5142,7 @@
         <v>-0.02</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>4924600</v>
+        <v>4924700</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>1.63</v>
@@ -5187,7 +5187,7 @@
         <v>-0.0426</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>4902400</v>
+        <v>4908900</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0.33</v>
@@ -5277,7 +5277,7 @@
         <v>-0.0138</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>4754300</v>
+        <v>4759300</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0.75</v>
@@ -5322,7 +5322,7 @@
         <v>-0.0373</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>4717700</v>
+        <v>4738200</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>0.49</v>
@@ -5367,7 +5367,7 @@
         <v>-0.0118</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>4648300</v>
+        <v>4650300</v>
       </c>
       <c r="G109" s="12" t="n">
         <v>0.73</v>
@@ -5487,28 +5487,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.46</v>
+        <v>0.52</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>-0.0199</v>
+        <v>-0.0189</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>4545900</v>
+        <v>4547300</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.27</v>
+        <v>0.74</v>
       </c>
       <c r="H112" t="n">
-        <v>57.88</v>
+        <v>50.5</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.429</v>
+        <v>0.517</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.258</v>
+        <v>0.529</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5532,28 +5532,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.52</v>
+        <v>2.46</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>-0.0189</v>
+        <v>-0.0199</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>4541300</v>
+        <v>4546400</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="H113" t="n">
-        <v>50.5</v>
+        <v>57.88</v>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.517</v>
+        <v>2.429</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.529</v>
+        <v>2.258</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5577,28 +5577,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>-0.0267</v>
+        <v>0.14</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>4387400</v>
+        <v>4430300</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="H114" t="n">
-        <v>38.42</v>
+        <v>38.65</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5606,10 +5606,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.379</v>
+        <v>0.148</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.392</v>
+        <v>0.153</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5622,39 +5622,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.31</v>
+        <v>0.365</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>-0.0462</v>
+        <v>-0.0267</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>4333400</v>
+        <v>4387400</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.58</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H115" t="n">
-        <v>41.49</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.42</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.322</v>
+        <v>0.379</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.339</v>
+        <v>0.392</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5667,28 +5667,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.31</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>-0.0462</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>4324100</v>
+        <v>4363400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>1.05</v>
+        <v>0.58</v>
       </c>
       <c r="H116" t="n">
-        <v>53.63</v>
+        <v>41.49</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>7.934</v>
+        <v>0.322</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>8.173999999999999</v>
+        <v>0.339</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5712,39 +5712,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>-0.0154</v>
+        <v>8.06</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>4260200</v>
+        <v>4324100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="H117" t="n">
-        <v>40.34</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.63</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.335</v>
+        <v>7.934</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.343</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5757,39 +5757,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LBALUM</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.32</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>4254700</v>
+        <v>4260200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>13.92</v>
+        <v>1.44</v>
       </c>
       <c r="H118" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.34</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.478</v>
+        <v>0.335</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.471</v>
+        <v>0.343</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5802,39 +5802,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>LBALUM</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>-0.0222</v>
+        <v>0.49</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>4188700</v>
+        <v>4254700</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.54</v>
+        <v>13.92</v>
       </c>
       <c r="H119" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.51000000000001</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.443</v>
+        <v>0.478</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.4</v>
+        <v>0.471</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5847,39 +5847,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.755</v>
+        <v>0.44</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>-0.0258</v>
+        <v>-0.0222</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>4048000</v>
+        <v>4215200</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.79</v>
+        <v>0.55</v>
       </c>
       <c r="H120" t="n">
-        <v>69.16</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.45</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.67</v>
+        <v>0.443</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.602</v>
+        <v>0.4</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5892,28 +5892,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.0672</v>
+        <v>0.755</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>3925500</v>
+        <v>4048000</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>2.76</v>
+        <v>0.79</v>
       </c>
       <c r="H121" t="n">
-        <v>80.78</v>
+        <v>69.16</v>
       </c>
       <c r="I121" s="16" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.546</v>
+        <v>0.67</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.486</v>
+        <v>0.602</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5937,39 +5937,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.89</v>
+        <v>0.635</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0672</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>3892200</v>
+        <v>3925500</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.26</v>
+        <v>2.76</v>
       </c>
       <c r="H122" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.78</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.931</v>
+        <v>0.546</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.969</v>
+        <v>0.486</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5982,28 +5982,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E123" s="15" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>3875600</v>
+        <v>3892200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.53</v>
+        <v>1.26</v>
       </c>
       <c r="H123" t="n">
-        <v>51.39</v>
+        <v>30.77</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.213</v>
+        <v>0.931</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.211</v>
+        <v>0.969</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6027,28 +6027,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>YONGTAI</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.105</v>
+        <v>0.215</v>
       </c>
       <c r="E124" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>3868300</v>
+        <v>3875600</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
       <c r="H124" t="n">
-        <v>43.4</v>
+        <v>51.39</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.111</v>
+        <v>0.213</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.114</v>
+        <v>0.211</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6072,39 +6072,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>YONGTAI</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>-0.0263</v>
+        <v>0.105</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>3852100</v>
+        <v>3868300</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>2.46</v>
+        <v>1.2</v>
       </c>
       <c r="H125" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.4</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.352</v>
+        <v>0.111</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.316</v>
+        <v>0.114</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6117,39 +6117,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>3840300</v>
+        <v>3852100</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>1.15</v>
+        <v>2.46</v>
       </c>
       <c r="H126" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.72</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.148</v>
+        <v>0.352</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.153</v>
+        <v>0.316</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>3774200</v>
+        <v>3782400</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H127" t="n">
         <v>78.48</v>
@@ -6207,28 +6207,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>2.6</v>
+        <v>1.26</v>
       </c>
       <c r="E128" s="17" t="n">
-        <v>-0.0114</v>
+        <v>-0.0233</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>3711500</v>
+        <v>3719600</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
       <c r="H128" t="n">
-        <v>33.64</v>
+        <v>55.88</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>2.69</v>
+        <v>1.23</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.802</v>
+        <v>1.128</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6252,39 +6252,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="E129" s="17" t="n">
-        <v>-0.0192</v>
+        <v>-0.0114</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>3657900</v>
+        <v>3711500</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="H129" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.64</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>2.068</v>
+        <v>2.69</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>2.113</v>
+        <v>2.802</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6297,39 +6297,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>6.72</v>
+        <v>2.04</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>-0.0044</v>
+        <v>-0.0192</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>3598400</v>
+        <v>3657900</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.82</v>
+        <v>1.32</v>
       </c>
       <c r="H130" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.79</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>6.794</v>
+        <v>2.068</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>6.778</v>
+        <v>2.113</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6342,39 +6342,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.535</v>
+        <v>6.72</v>
       </c>
       <c r="E131" s="17" t="n">
-        <v>-0.0183</v>
+        <v>-0.0044</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>3591300</v>
+        <v>3598400</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H131" t="n">
-        <v>60.64</v>
-      </c>
-      <c r="I131" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.06</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.51</v>
+        <v>6.794</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.458</v>
+        <v>6.778</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6387,39 +6387,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.26</v>
+        <v>0.535</v>
       </c>
       <c r="E132" s="17" t="n">
-        <v>-0.0233</v>
+        <v>-0.0183</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>3560700</v>
+        <v>3591300</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="H132" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.64</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.23</v>
+        <v>0.51</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.128</v>
+        <v>0.458</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6447,7 +6447,7 @@
         <v>-0.0105</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>3542200</v>
+        <v>3543600</v>
       </c>
       <c r="G133" s="12" t="n">
         <v>0.79</v>
@@ -6627,10 +6627,10 @@
         <v>0.013</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>3276900</v>
+        <v>3292600</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H137" t="n">
         <v>64.52</v>
@@ -6702,39 +6702,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0.0549</v>
+        <v>0.355</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>-0.0658</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>3150100</v>
+        <v>3188900</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="H139" t="n">
-        <v>87.31999999999999</v>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.82</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>2.034</v>
+        <v>0.392</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.709</v>
+        <v>0.391</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6747,39 +6747,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>-0.009899999999999999</v>
+        <v>2.69</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0.0549</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>3133900</v>
+        <v>3151100</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="H140" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.31999999999999</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.058</v>
+        <v>2.034</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.072</v>
+        <v>1.709</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6792,28 +6792,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="E141" s="17" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>3104900</v>
+        <v>3133900</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>1.02</v>
+        <v>0.59</v>
       </c>
       <c r="H141" t="n">
-        <v>59.86</v>
+        <v>31.5</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.607</v>
+        <v>1.058</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.586</v>
+        <v>1.072</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6837,28 +6837,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.355</v>
+        <v>0.61</v>
       </c>
       <c r="E142" s="17" t="n">
-        <v>-0.0658</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>3074000</v>
+        <v>3104900</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>1.86</v>
+        <v>1.02</v>
       </c>
       <c r="H142" t="n">
-        <v>30.82</v>
+        <v>59.86</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.392</v>
+        <v>0.607</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.391</v>
+        <v>0.586</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -7070,7 +7070,7 @@
         <v>-0.0326</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>2915000</v>
+        <v>2920000</v>
       </c>
       <c r="G147" s="12" t="n">
         <v>0.89</v>
@@ -7248,7 +7248,7 @@
         <v>0.0469</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>2787000</v>
+        <v>2788000</v>
       </c>
       <c r="G151" s="12" t="n">
         <v>2.64</v>
@@ -7473,10 +7473,10 @@
         <v>-0.0425</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>2429400</v>
+        <v>2443600</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H156" t="n">
         <v>46.96</v>
@@ -7653,7 +7653,7 @@
         <v>-0.0522</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>2292900</v>
+        <v>2290700</v>
       </c>
       <c r="G160" s="12" t="n">
         <v>0.71</v>
@@ -7683,39 +7683,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E161" s="17" t="n">
-        <v>-0.0299</v>
+        <v>0.345</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>2232500</v>
+        <v>2265800</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.22</v>
+        <v>0.85</v>
       </c>
       <c r="H161" t="n">
-        <v>50.52</v>
-      </c>
-      <c r="I161" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.77</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>0.331</v>
+        <v>0.338</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>0.309</v>
+        <v>0.329</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7728,39 +7728,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.325</v>
+      </c>
+      <c r="E162" s="17" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>2215800</v>
+        <v>2232500</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.83</v>
+        <v>0.22</v>
       </c>
       <c r="H162" t="n">
-        <v>53.77</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.52</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.338</v>
+        <v>0.331</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>0.329</v>
+        <v>0.309</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7788,7 +7788,7 @@
         <v>-0.019</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2147600</v>
+        <v>2148100</v>
       </c>
       <c r="G163" s="12" t="n">
         <v>0.78</v>
@@ -8223,39 +8223,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.57</v>
+        <v>0.28</v>
       </c>
       <c r="E173" s="17" t="n">
-        <v>-0.0309</v>
+        <v>-0.0175</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>1905500</v>
+        <v>1929000</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="H173" t="n">
-        <v>38.42</v>
-      </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.61</v>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.633</v>
+        <v>0.254</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.697</v>
+        <v>0.271</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8268,39 +8268,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E174" s="15" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>1901500</v>
+        <v>1905700</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="H174" t="n">
-        <v>78.34999999999999</v>
-      </c>
-      <c r="I174" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.39</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>0.864</v>
+        <v>1.312</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8313,28 +8313,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E175" s="10" t="n">
-        <v>0.0214</v>
+        <v>1.57</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>-0.0309</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>1898700</v>
+        <v>1905500</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="H175" t="n">
-        <v>55.39</v>
+        <v>38.42</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>1.42</v>
+        <v>1.633</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>1.312</v>
+        <v>1.697</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8358,39 +8358,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E176" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>1.15</v>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>1894300</v>
+        <v>1904500</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H176" t="n">
-        <v>33.09</v>
-      </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.34999999999999</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>1.126</v>
+        <v>1</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>1.155</v>
+        <v>0.864</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8403,28 +8403,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E177" s="10" t="n">
-        <v>0.0196</v>
+        <v>1.07</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1888300</v>
+        <v>1894300</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>2.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H177" t="n">
-        <v>45.51</v>
+        <v>33.09</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.262</v>
+        <v>1.126</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.267</v>
+        <v>1.155</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8448,39 +8448,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E178" s="17" t="n">
-        <v>-0.0175</v>
+        <v>0.26</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1852700</v>
+        <v>1888300</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1.19</v>
+        <v>2.66</v>
       </c>
       <c r="H178" t="n">
-        <v>62.61</v>
-      </c>
-      <c r="I178" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.254</v>
+        <v>0.262</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.271</v>
+        <v>0.267</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8508,10 +8508,10 @@
         <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>1851100</v>
+        <v>1876100</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="H179" t="n">
         <v>52.75</v>
@@ -8643,7 +8643,7 @@
         <v>-0.0076</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>1750700</v>
+        <v>1752700</v>
       </c>
       <c r="G182" s="12" t="n">
         <v>0.34</v>
@@ -8733,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1672000</v>
+        <v>1672200</v>
       </c>
       <c r="G184" s="12" t="n">
         <v>0.49</v>
@@ -8823,7 +8823,7 @@
         <v>-0.03700000000000001</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>1628100</v>
+        <v>1630100</v>
       </c>
       <c r="G186" s="12" t="n">
         <v>0.51</v>
@@ -8853,39 +8853,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>0.255</v>
+        <v>2.27</v>
       </c>
       <c r="E187" s="17" t="n">
-        <v>-0.0192</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>1605700</v>
+        <v>1629300</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="H187" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="I187" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.47</v>
+      </c>
+      <c r="I187" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>0.256</v>
+        <v>2.175</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>0.259</v>
+        <v>2.001</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8898,28 +8898,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E188" s="10" t="n">
-        <v>0.019</v>
+        <v>0.255</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>1591200</v>
+        <v>1605700</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="H188" t="n">
-        <v>57.87</v>
+        <v>47.35</v>
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
@@ -8927,10 +8927,10 @@
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>1.03</v>
+        <v>0.256</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>0.991</v>
+        <v>0.259</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8943,39 +8943,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E189" s="15" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0.019</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1576000</v>
+        <v>1591200</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I189" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.87</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>0.999</v>
+        <v>1.03</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>1.015</v>
+        <v>0.991</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -8988,28 +8988,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>0.245</v>
+        <v>0.99</v>
       </c>
       <c r="E190" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>1561700</v>
+        <v>1576000</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="H190" t="n">
-        <v>53.86</v>
+        <v>46.18</v>
       </c>
       <c r="I190" s="16" t="inlineStr">
         <is>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>0.241</v>
+        <v>0.999</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>0.243</v>
+        <v>1.015</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9033,39 +9033,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0612</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>1556200</v>
+        <v>1566900</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.59</v>
+        <v>3.08</v>
       </c>
       <c r="H191" t="n">
-        <v>46.07</v>
-      </c>
-      <c r="I191" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.34</v>
+      </c>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>0.64</v>
+        <v>0.253</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>0.631</v>
+        <v>0.264</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9078,39 +9078,39 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E192" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.245</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>1536900</v>
+        <v>1561700</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>0.48</v>
+        <v>0.75</v>
       </c>
       <c r="H192" t="n">
-        <v>59.03</v>
-      </c>
-      <c r="I192" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.86</v>
+      </c>
+      <c r="I192" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>0.858</v>
+        <v>0.241</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>0.855</v>
+        <v>0.243</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
@@ -9123,28 +9123,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D193" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E193" s="15" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E193" s="10" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>1534700</v>
+        <v>1556200</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>7.21</v>
+        <v>0.59</v>
       </c>
       <c r="H193" t="n">
-        <v>57.23</v>
+        <v>46.07</v>
       </c>
       <c r="I193" s="13" t="inlineStr">
         <is>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="J193" s="9" t="n">
-        <v>0.439</v>
+        <v>0.64</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>0.431</v>
+        <v>0.631</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="14" t="inlineStr"/>
@@ -9168,39 +9168,39 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D194" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E194" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.865</v>
+      </c>
+      <c r="E194" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>1513900</v>
+        <v>1536900</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>2.01</v>
+        <v>0.48</v>
       </c>
       <c r="H194" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="I194" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.03</v>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J194" s="9" t="n">
-        <v>1.646</v>
+        <v>0.858</v>
       </c>
       <c r="K194" s="9" t="n">
-        <v>1.729</v>
+        <v>0.855</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="14" t="inlineStr"/>
@@ -9213,39 +9213,39 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D195" s="9" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="E195" s="17" t="n">
-        <v>-0.0225</v>
+        <v>0.44</v>
+      </c>
+      <c r="E195" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>1488400</v>
+        <v>1534700</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>0.42</v>
+        <v>7.21</v>
       </c>
       <c r="H195" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="I195" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.23</v>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J195" s="9" t="n">
-        <v>6.524</v>
+        <v>0.439</v>
       </c>
       <c r="K195" s="9" t="n">
-        <v>6.468</v>
+        <v>0.431</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="14" t="inlineStr"/>
@@ -9258,28 +9258,28 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D196" s="9" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="E196" s="15" t="n">
-        <v>0</v>
+        <v>1.73</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>0.0237</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>1469700</v>
+        <v>1513900</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>0.35</v>
+        <v>2.01</v>
       </c>
       <c r="H196" t="n">
-        <v>47.33</v>
+        <v>58.75</v>
       </c>
       <c r="I196" s="16" t="inlineStr">
         <is>
@@ -9287,10 +9287,10 @@
         </is>
       </c>
       <c r="J196" s="9" t="n">
-        <v>7.643</v>
+        <v>1.646</v>
       </c>
       <c r="K196" s="9" t="n">
-        <v>7.796</v>
+        <v>1.729</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="14" t="inlineStr"/>
@@ -9303,28 +9303,28 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D197" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E197" s="10" t="n">
-        <v>0.0612</v>
+        <v>6.51</v>
+      </c>
+      <c r="E197" s="17" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>1455100</v>
+        <v>1489900</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>2.86</v>
+        <v>0.42</v>
       </c>
       <c r="H197" t="n">
-        <v>55.34</v>
+        <v>49.75</v>
       </c>
       <c r="I197" s="16" t="inlineStr">
         <is>
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="J197" s="9" t="n">
-        <v>0.253</v>
+        <v>6.524</v>
       </c>
       <c r="K197" s="9" t="n">
-        <v>0.264</v>
+        <v>6.468</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="14" t="inlineStr"/>
@@ -9348,28 +9348,28 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D198" s="9" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="E198" s="10" t="n">
-        <v>0.0155</v>
+        <v>7.57</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>1442000</v>
+        <v>1469700</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>6.39</v>
+        <v>0.35</v>
       </c>
       <c r="H198" t="n">
-        <v>57.86</v>
+        <v>47.33</v>
       </c>
       <c r="I198" s="16" t="inlineStr">
         <is>
@@ -9377,10 +9377,10 @@
         </is>
       </c>
       <c r="J198" s="9" t="n">
-        <v>8.305</v>
+        <v>7.643</v>
       </c>
       <c r="K198" s="9" t="n">
-        <v>8.119999999999999</v>
+        <v>7.796</v>
       </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" s="14" t="inlineStr"/>
@@ -9393,28 +9393,28 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>UMSINT</t>
         </is>
       </c>
       <c r="D199" s="9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="E199" s="17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>1429300</v>
+        <v>1442000</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>1.02</v>
+        <v>6.39</v>
       </c>
       <c r="H199" t="n">
-        <v>61.47</v>
+        <v>57.86</v>
       </c>
       <c r="I199" s="16" t="inlineStr">
         <is>
@@ -9422,10 +9422,10 @@
         </is>
       </c>
       <c r="J199" s="9" t="n">
-        <v>2.175</v>
+        <v>8.305</v>
       </c>
       <c r="K199" s="9" t="n">
-        <v>2.001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" s="14" t="inlineStr"/>
@@ -9903,7 +9903,7 @@
         <v>0.0023</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>1305100</v>
+        <v>1307600</v>
       </c>
       <c r="G210" s="12" t="n">
         <v>0.37</v>
@@ -10203,28 +10203,28 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D217" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E217" s="15" t="n">
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="E217" s="17" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>1171400</v>
+        <v>1180200</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="H217" t="n">
-        <v>43.77</v>
+        <v>36.4</v>
       </c>
       <c r="I217" s="13" t="inlineStr">
         <is>
@@ -10232,10 +10232,10 @@
         </is>
       </c>
       <c r="J217" s="9" t="n">
-        <v>0.279</v>
+        <v>0.663</v>
       </c>
       <c r="K217" s="9" t="n">
-        <v>0.274</v>
+        <v>0.68</v>
       </c>
       <c r="L217" t="inlineStr"/>
       <c r="M217" s="14" t="inlineStr"/>
@@ -10248,28 +10248,28 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D218" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E218" s="17" t="n">
-        <v>-0.0076</v>
+        <v>0.275</v>
+      </c>
+      <c r="E218" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>1170200</v>
+        <v>1171400</v>
       </c>
       <c r="G218" s="12" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="H218" t="n">
-        <v>36.4</v>
+        <v>43.77</v>
       </c>
       <c r="I218" s="13" t="inlineStr">
         <is>
@@ -10277,10 +10277,10 @@
         </is>
       </c>
       <c r="J218" s="9" t="n">
-        <v>0.663</v>
+        <v>0.279</v>
       </c>
       <c r="K218" s="9" t="n">
-        <v>0.68</v>
+        <v>0.274</v>
       </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" s="14" t="inlineStr"/>
@@ -10308,7 +10308,7 @@
         <v>0.0052</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1150000</v>
+        <v>1151000</v>
       </c>
       <c r="G219" s="12" t="n">
         <v>0.62</v>
@@ -10698,28 +10698,28 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D228" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E228" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.925</v>
+      </c>
+      <c r="E228" s="17" t="n">
+        <v>-0.0464</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>1084000</v>
+        <v>1089600</v>
       </c>
       <c r="G228" s="12" t="n">
-        <v>0.27</v>
+        <v>0.62</v>
       </c>
       <c r="H228" t="n">
-        <v>30.26</v>
+        <v>57.84</v>
       </c>
       <c r="I228" s="16" t="inlineStr">
         <is>
@@ -10727,10 +10727,10 @@
         </is>
       </c>
       <c r="J228" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.903</v>
       </c>
       <c r="K228" s="9" t="n">
-        <v>0.598</v>
+        <v>0.769</v>
       </c>
       <c r="L228" t="inlineStr"/>
       <c r="M228" s="14" t="inlineStr"/>
@@ -10743,28 +10743,28 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D229" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E229" s="17" t="n">
-        <v>-0.0464</v>
+        <v>0.545</v>
+      </c>
+      <c r="E229" s="10" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>1083600</v>
+        <v>1084000</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
       <c r="H229" t="n">
-        <v>57.84</v>
+        <v>30.26</v>
       </c>
       <c r="I229" s="16" t="inlineStr">
         <is>
@@ -10772,10 +10772,10 @@
         </is>
       </c>
       <c r="J229" s="9" t="n">
-        <v>0.903</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K229" s="9" t="n">
-        <v>0.769</v>
+        <v>0.598</v>
       </c>
       <c r="L229" t="inlineStr"/>
       <c r="M229" s="14" t="inlineStr"/>
@@ -10923,39 +10923,39 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D233" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E233" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.43</v>
+      </c>
+      <c r="E233" s="17" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>1040200</v>
+        <v>1076600</v>
       </c>
       <c r="G233" s="12" t="n">
-        <v>3.99</v>
+        <v>0.31</v>
       </c>
       <c r="H233" t="n">
-        <v>59.87</v>
-      </c>
-      <c r="I233" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.26</v>
+      </c>
+      <c r="I233" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J233" s="9" t="n">
-        <v>1.576</v>
+        <v>0.433</v>
       </c>
       <c r="K233" s="9" t="n">
-        <v>1.525</v>
+        <v>0.453</v>
       </c>
       <c r="L233" t="inlineStr"/>
       <c r="M233" s="14" t="inlineStr"/>
@@ -10968,39 +10968,39 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D234" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E234" s="17" t="n">
-        <v>-0.0115</v>
+        <v>1.6</v>
+      </c>
+      <c r="E234" s="10" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>1031600</v>
+        <v>1040200</v>
       </c>
       <c r="G234" s="12" t="n">
-        <v>0.3</v>
+        <v>3.99</v>
       </c>
       <c r="H234" t="n">
-        <v>47.26</v>
-      </c>
-      <c r="I234" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.87</v>
+      </c>
+      <c r="I234" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J234" s="9" t="n">
-        <v>0.433</v>
+        <v>1.576</v>
       </c>
       <c r="K234" s="9" t="n">
-        <v>0.453</v>
+        <v>1.525</v>
       </c>
       <c r="L234" t="inlineStr"/>
       <c r="M234" s="14" t="inlineStr"/>
@@ -11568,7 +11568,7 @@
         <v>-0.0278</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>810900</v>
+        <v>813900</v>
       </c>
       <c r="G247" s="12" t="n">
         <v>0.47</v>
@@ -11658,7 +11658,7 @@
         <v>0.0107</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>803800</v>
+        <v>805100</v>
       </c>
       <c r="G249" s="12" t="n">
         <v>0.75</v>
@@ -11733,39 +11733,39 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D251" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E251" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.74</v>
+      </c>
+      <c r="E251" s="17" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>767800</v>
+        <v>780100</v>
       </c>
       <c r="G251" s="12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H251" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="I251" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.02</v>
+      </c>
+      <c r="I251" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J251" s="9" t="n">
-        <v>0.626</v>
+        <v>1.701</v>
       </c>
       <c r="K251" s="9" t="n">
-        <v>0.605</v>
+        <v>1.607</v>
       </c>
       <c r="L251" t="inlineStr"/>
       <c r="M251" s="14" t="inlineStr"/>
@@ -11778,28 +11778,28 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>TIMWELL</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D252" s="9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="E252" s="15" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E252" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>753300</v>
+        <v>767800</v>
       </c>
       <c r="G252" s="12" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="H252" t="n">
-        <v>78.97</v>
+        <v>56.79</v>
       </c>
       <c r="I252" s="16" t="inlineStr">
         <is>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="J252" s="9" t="n">
-        <v>2.128</v>
+        <v>0.626</v>
       </c>
       <c r="K252" s="9" t="n">
-        <v>1.973</v>
+        <v>0.605</v>
       </c>
       <c r="L252" t="inlineStr"/>
       <c r="M252" s="14" t="inlineStr"/>
@@ -11823,28 +11823,28 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>KENANGA</t>
+          <t>TIMWELL</t>
         </is>
       </c>
       <c r="D253" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E253" s="10" t="n">
-        <v>0.0248</v>
+        <v>2.26</v>
+      </c>
+      <c r="E253" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>740700</v>
+        <v>753300</v>
       </c>
       <c r="G253" s="12" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="H253" t="n">
-        <v>43.29</v>
+        <v>78.97</v>
       </c>
       <c r="I253" s="16" t="inlineStr">
         <is>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="J253" s="9" t="n">
-        <v>0.623</v>
+        <v>2.128</v>
       </c>
       <c r="K253" s="9" t="n">
-        <v>0.668</v>
+        <v>1.973</v>
       </c>
       <c r="L253" t="inlineStr"/>
       <c r="M253" s="14" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
         <v>-0.008500000000000001</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>736500</v>
+        <v>741500</v>
       </c>
       <c r="G254" s="12" t="n">
         <v>0.41</v>
@@ -11913,39 +11913,39 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>KENANGA</t>
         </is>
       </c>
       <c r="D255" s="9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E255" s="17" t="n">
-        <v>-0.0169</v>
+        <v>0.62</v>
+      </c>
+      <c r="E255" s="10" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>709800</v>
+        <v>740700</v>
       </c>
       <c r="G255" s="12" t="n">
-        <v>0.51</v>
+        <v>1.45</v>
       </c>
       <c r="H255" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="I255" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.29</v>
+      </c>
+      <c r="I255" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J255" s="9" t="n">
-        <v>1.701</v>
+        <v>0.623</v>
       </c>
       <c r="K255" s="9" t="n">
-        <v>1.607</v>
+        <v>0.668</v>
       </c>
       <c r="L255" t="inlineStr"/>
       <c r="M255" s="14" t="inlineStr"/>
@@ -11958,28 +11958,28 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D256" s="9" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E256" s="17" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="F256" s="11" t="n">
+        <v>733100</v>
+      </c>
+      <c r="G256" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="E256" s="10" t="n">
-        <v>0.0219</v>
-      </c>
-      <c r="F256" s="11" t="n">
-        <v>704500</v>
-      </c>
-      <c r="G256" s="12" t="n">
-        <v>4.23</v>
-      </c>
       <c r="H256" t="n">
-        <v>55.57</v>
+        <v>28.62</v>
       </c>
       <c r="I256" s="13" t="inlineStr">
         <is>
@@ -11987,10 +11987,10 @@
         </is>
       </c>
       <c r="J256" s="9" t="n">
-        <v>0.694</v>
+        <v>0.983</v>
       </c>
       <c r="K256" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.016</v>
       </c>
       <c r="L256" t="inlineStr"/>
       <c r="M256" s="14" t="inlineStr"/>
@@ -12018,10 +12018,10 @@
         <v>-0.0282</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>697400</v>
+        <v>706400</v>
       </c>
       <c r="G257" s="12" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H257" t="n">
         <v>55.04</v>
@@ -12048,39 +12048,39 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>SPTOTO</t>
+          <t>SENFONG</t>
         </is>
       </c>
       <c r="D258" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E258" s="17" t="n">
-        <v>-0.0156</v>
+        <v>0.7</v>
+      </c>
+      <c r="E258" s="10" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>695200</v>
+        <v>704500</v>
       </c>
       <c r="G258" s="12" t="n">
-        <v>1.52</v>
+        <v>4.23</v>
       </c>
       <c r="H258" t="n">
-        <v>40.32</v>
-      </c>
-      <c r="I258" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.57</v>
+      </c>
+      <c r="I258" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J258" s="9" t="n">
-        <v>1.279</v>
+        <v>0.694</v>
       </c>
       <c r="K258" s="9" t="n">
-        <v>1.304</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L258" t="inlineStr"/>
       <c r="M258" s="14" t="inlineStr"/>
@@ -12093,28 +12093,28 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>HTPADU</t>
+          <t>SPTOTO</t>
         </is>
       </c>
       <c r="D259" s="9" t="n">
-        <v>0.905</v>
+        <v>1.26</v>
       </c>
       <c r="E259" s="17" t="n">
-        <v>-0.0622</v>
+        <v>-0.0156</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>688100</v>
+        <v>695200</v>
       </c>
       <c r="G259" s="12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="H259" t="n">
-        <v>25.08</v>
+        <v>40.32</v>
       </c>
       <c r="I259" s="16" t="inlineStr">
         <is>
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="J259" s="9" t="n">
-        <v>1.023</v>
+        <v>1.279</v>
       </c>
       <c r="K259" s="9" t="n">
-        <v>1.161</v>
+        <v>1.304</v>
       </c>
       <c r="L259" t="inlineStr"/>
       <c r="M259" s="14" t="inlineStr"/>
@@ -12138,28 +12138,28 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>AMEREIT</t>
+          <t>HTPADU</t>
         </is>
       </c>
       <c r="D260" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E260" s="10" t="n">
-        <v>0.0323</v>
+        <v>0.905</v>
+      </c>
+      <c r="E260" s="17" t="n">
+        <v>-0.0622</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>677800</v>
+        <v>688100</v>
       </c>
       <c r="G260" s="12" t="n">
-        <v>13.25</v>
+        <v>1.45</v>
       </c>
       <c r="H260" t="n">
-        <v>63.43</v>
+        <v>25.08</v>
       </c>
       <c r="I260" s="16" t="inlineStr">
         <is>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="J260" s="9" t="n">
-        <v>1.528</v>
+        <v>1.023</v>
       </c>
       <c r="K260" s="9" t="n">
-        <v>1.522</v>
+        <v>1.161</v>
       </c>
       <c r="L260" t="inlineStr"/>
       <c r="M260" s="14" t="inlineStr"/>
@@ -12183,28 +12183,28 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>AMEREIT</t>
         </is>
       </c>
       <c r="D261" s="9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E261" s="17" t="n">
-        <v>-0.0269</v>
+        <v>1.6</v>
+      </c>
+      <c r="E261" s="10" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>671800</v>
+        <v>677800</v>
       </c>
       <c r="G261" s="12" t="n">
-        <v>0.53</v>
+        <v>13.25</v>
       </c>
       <c r="H261" t="n">
-        <v>60.91</v>
+        <v>63.43</v>
       </c>
       <c r="I261" s="16" t="inlineStr">
         <is>
@@ -12212,10 +12212,10 @@
         </is>
       </c>
       <c r="J261" s="9" t="n">
-        <v>1.714</v>
+        <v>1.528</v>
       </c>
       <c r="K261" s="9" t="n">
-        <v>1.606</v>
+        <v>1.522</v>
       </c>
       <c r="L261" t="inlineStr"/>
       <c r="M261" s="14" t="inlineStr"/>
@@ -12228,39 +12228,39 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D262" s="9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E262" s="17" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="F262" s="11" t="n">
+        <v>671800</v>
+      </c>
+      <c r="G262" s="12" t="n">
         <v>0.53</v>
       </c>
-      <c r="E262" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F262" s="11" t="n">
-        <v>669100</v>
-      </c>
-      <c r="G262" s="12" t="n">
-        <v>1.02</v>
-      </c>
       <c r="H262" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="I262" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.91</v>
+      </c>
+      <c r="I262" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J262" s="9" t="n">
-        <v>0.529</v>
+        <v>1.714</v>
       </c>
       <c r="K262" s="9" t="n">
-        <v>0.526</v>
+        <v>1.606</v>
       </c>
       <c r="L262" t="inlineStr"/>
       <c r="M262" s="14" t="inlineStr"/>
@@ -12273,28 +12273,28 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D263" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E263" s="17" t="n">
-        <v>-0.0104</v>
+        <v>0.53</v>
+      </c>
+      <c r="E263" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>663100</v>
+        <v>669100</v>
       </c>
       <c r="G263" s="12" t="n">
-        <v>0.63</v>
+        <v>1.02</v>
       </c>
       <c r="H263" t="n">
-        <v>28.62</v>
+        <v>52.07</v>
       </c>
       <c r="I263" s="13" t="inlineStr">
         <is>
@@ -12302,10 +12302,10 @@
         </is>
       </c>
       <c r="J263" s="9" t="n">
-        <v>0.983</v>
+        <v>0.529</v>
       </c>
       <c r="K263" s="9" t="n">
-        <v>1.016</v>
+        <v>0.526</v>
       </c>
       <c r="L263" t="inlineStr"/>
       <c r="M263" s="14" t="inlineStr"/>
@@ -12318,39 +12318,39 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>QL</t>
+          <t>TGUAN</t>
         </is>
       </c>
       <c r="D264" s="9" t="n">
-        <v>4</v>
+        <v>1.52</v>
       </c>
       <c r="E264" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0066</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>655400</v>
+        <v>657600</v>
       </c>
       <c r="G264" s="12" t="n">
-        <v>0.38</v>
+        <v>0.99</v>
       </c>
       <c r="H264" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="I264" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.72</v>
+      </c>
+      <c r="I264" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J264" s="9" t="n">
-        <v>3.916</v>
+        <v>1.596</v>
       </c>
       <c r="K264" s="9" t="n">
-        <v>3.924</v>
+        <v>1.554</v>
       </c>
       <c r="L264" t="inlineStr"/>
       <c r="M264" s="14" t="inlineStr"/>
@@ -12363,39 +12363,39 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>TGUAN</t>
+          <t>QL</t>
         </is>
       </c>
       <c r="D265" s="9" t="n">
-        <v>1.52</v>
+        <v>4</v>
       </c>
       <c r="E265" s="10" t="n">
-        <v>0.0066</v>
+        <v>0.005</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>652600</v>
+        <v>655400</v>
       </c>
       <c r="G265" s="12" t="n">
-        <v>0.98</v>
+        <v>0.38</v>
       </c>
       <c r="H265" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="I265" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.89</v>
+      </c>
+      <c r="I265" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J265" s="9" t="n">
-        <v>1.596</v>
+        <v>3.916</v>
       </c>
       <c r="K265" s="9" t="n">
-        <v>1.554</v>
+        <v>3.924</v>
       </c>
       <c r="L265" t="inlineStr"/>
       <c r="M265" s="14" t="inlineStr"/>
@@ -12543,39 +12543,39 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D269" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E269" s="10" t="n">
-        <v>0.011</v>
+        <v>4.03</v>
+      </c>
+      <c r="E269" s="17" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>593700</v>
+        <v>597500</v>
       </c>
       <c r="G269" s="12" t="n">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="H269" t="n">
-        <v>60</v>
-      </c>
-      <c r="I269" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.54</v>
+      </c>
+      <c r="I269" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J269" s="9" t="n">
-        <v>0.881</v>
+        <v>4.22</v>
       </c>
       <c r="K269" s="9" t="n">
-        <v>0.796</v>
+        <v>4.358</v>
       </c>
       <c r="L269" t="inlineStr"/>
       <c r="M269" s="14" t="inlineStr"/>
@@ -12588,39 +12588,39 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D270" s="9" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="E270" s="17" t="n">
-        <v>-0.0147</v>
+        <v>0.915</v>
+      </c>
+      <c r="E270" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>587500</v>
+        <v>593700</v>
       </c>
       <c r="G270" s="12" t="n">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="H270" t="n">
-        <v>40.54</v>
-      </c>
-      <c r="I270" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60</v>
+      </c>
+      <c r="I270" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J270" s="9" t="n">
-        <v>4.22</v>
+        <v>0.881</v>
       </c>
       <c r="K270" s="9" t="n">
-        <v>4.358</v>
+        <v>0.796</v>
       </c>
       <c r="L270" t="inlineStr"/>
       <c r="M270" s="14" t="inlineStr"/>
@@ -12828,7 +12828,7 @@
         <v>-0.021</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>548500</v>
+        <v>548600</v>
       </c>
       <c r="G275" s="12" t="n">
         <v>0.52</v>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.67高于50日均线0.645，EMA20与SAR均呈多头，T3形态突破；RSI 58.41处中性偏强，未超买，信号技术面较可靠。</t>
+          <t>现价0.67高于50日均线0.645，EMA20与SAR均呈多头，T3形态突破；RSI 58.41处中性偏强区间，未超买，信号技术面一致性尚可。</t>
         </is>
       </c>
     </row>
@@ -3229,9 +3229,9 @@
       <c r="H61" t="n">
         <v>52.44</v>
       </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -3229,9 +3229,9 @@
       <c r="H61" t="n">
         <v>52.44</v>
       </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -7,12 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-24" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-25" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-24" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,6 +467,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>涨跌%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>成交量</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>相对量</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EMA20</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>50日均线</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>AI点评</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12856,7 +12953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
@@ -41,10 +42,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -95,13 +96,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,7 +553,241 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0397</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>523800</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>现价0.785高于50日均线0.608，EMA20与SAR均呈多头，T3形态突破。但RSI达72.25，已进入超买区，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>30895100</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>2630400</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0065</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EFORCE</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>606300</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:M6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -732,7 +967,7 @@
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -772,7 +1007,7 @@
         <v>166867800</v>
       </c>
       <c r="G4" s="12" t="n"/>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -813,7 +1048,7 @@
       <c r="H5" t="n">
         <v>65.18000000000001</v>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -858,7 +1093,7 @@
       <c r="H6" t="n">
         <v>53.3</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -903,7 +1138,7 @@
       <c r="H7" t="n">
         <v>44.64</v>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -948,7 +1183,7 @@
       <c r="H8" t="n">
         <v>44.71</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -993,7 +1228,7 @@
       <c r="H9" t="n">
         <v>46.98</v>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1038,7 +1273,7 @@
       <c r="H10" t="n">
         <v>76.81</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1083,7 +1318,7 @@
       <c r="H11" t="n">
         <v>25.96</v>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1128,7 +1363,7 @@
       <c r="H12" t="n">
         <v>54.94</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1173,7 +1408,7 @@
       <c r="H13" t="n">
         <v>67.5</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1218,7 +1453,7 @@
       <c r="H14" t="n">
         <v>36.66</v>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1263,7 +1498,7 @@
       <c r="H15" t="n">
         <v>94.29000000000001</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1308,7 +1543,7 @@
       <c r="H16" t="n">
         <v>63.43</v>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1353,7 +1588,7 @@
       <c r="H17" t="n">
         <v>51.62</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1398,7 +1633,7 @@
       <c r="H18" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1443,7 +1678,7 @@
       <c r="H19" t="n">
         <v>37.55</v>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1488,7 +1723,7 @@
       <c r="H20" t="n">
         <v>63.44</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1533,7 +1768,7 @@
       <c r="H21" t="n">
         <v>48.03</v>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1578,7 +1813,7 @@
       <c r="H22" t="n">
         <v>66.43000000000001</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1623,7 +1858,7 @@
       <c r="H23" t="n">
         <v>85.84999999999999</v>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1668,7 +1903,7 @@
       <c r="H24" t="n">
         <v>42.36</v>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1710,7 +1945,7 @@
       <c r="G25" s="12" t="n">
         <v>1.1</v>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I25" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1751,7 +1986,7 @@
       <c r="H26" t="n">
         <v>85.45</v>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1796,7 +2031,7 @@
       <c r="H27" t="n">
         <v>62.38</v>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1841,7 +2076,7 @@
       <c r="H28" t="n">
         <v>61.9</v>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1886,7 +2121,7 @@
       <c r="H29" t="n">
         <v>50.98</v>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1931,7 +2166,7 @@
       <c r="H30" t="n">
         <v>50.86</v>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I30" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1976,7 +2211,7 @@
       <c r="H31" t="n">
         <v>37.21</v>
       </c>
-      <c r="I31" s="13" t="inlineStr">
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2021,7 +2256,7 @@
       <c r="H32" t="n">
         <v>73.70999999999999</v>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2066,7 +2301,7 @@
       <c r="H33" t="n">
         <v>61.15</v>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2111,7 +2346,7 @@
       <c r="H34" t="n">
         <v>56.74</v>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2156,7 +2391,7 @@
       <c r="H35" t="n">
         <v>64.8</v>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="I35" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2201,7 +2436,7 @@
       <c r="H36" t="n">
         <v>64.84999999999999</v>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2246,7 +2481,7 @@
       <c r="H37" t="n">
         <v>47.7</v>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="I37" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2291,7 +2526,7 @@
       <c r="H38" t="n">
         <v>42.95</v>
       </c>
-      <c r="I38" s="13" t="inlineStr">
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2336,7 +2571,7 @@
       <c r="H39" t="n">
         <v>60.57</v>
       </c>
-      <c r="I39" s="13" t="inlineStr">
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2381,7 +2616,7 @@
       <c r="H40" t="n">
         <v>49.74</v>
       </c>
-      <c r="I40" s="16" t="inlineStr">
+      <c r="I40" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2426,7 +2661,7 @@
       <c r="H41" t="n">
         <v>66.87</v>
       </c>
-      <c r="I41" s="16" t="inlineStr">
+      <c r="I41" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2471,7 +2706,7 @@
       <c r="H42" t="n">
         <v>41.98</v>
       </c>
-      <c r="I42" s="13" t="inlineStr">
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2516,7 +2751,7 @@
       <c r="H43" t="n">
         <v>34.18</v>
       </c>
-      <c r="I43" s="13" t="inlineStr">
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2561,7 +2796,7 @@
       <c r="H44" t="n">
         <v>74.42</v>
       </c>
-      <c r="I44" s="16" t="inlineStr">
+      <c r="I44" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2606,7 +2841,7 @@
       <c r="H45" t="n">
         <v>63.02</v>
       </c>
-      <c r="I45" s="16" t="inlineStr">
+      <c r="I45" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2651,7 +2886,7 @@
       <c r="H46" t="n">
         <v>49.97</v>
       </c>
-      <c r="I46" s="13" t="inlineStr">
+      <c r="I46" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2696,7 +2931,7 @@
       <c r="H47" t="n">
         <v>63.2</v>
       </c>
-      <c r="I47" s="13" t="inlineStr">
+      <c r="I47" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2741,7 +2976,7 @@
       <c r="H48" t="n">
         <v>56.29</v>
       </c>
-      <c r="I48" s="16" t="inlineStr">
+      <c r="I48" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2786,7 +3021,7 @@
       <c r="H49" t="n">
         <v>60.68</v>
       </c>
-      <c r="I49" s="16" t="inlineStr">
+      <c r="I49" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2831,7 +3066,7 @@
       <c r="H50" t="n">
         <v>61.27</v>
       </c>
-      <c r="I50" s="16" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2876,7 +3111,7 @@
       <c r="H51" t="n">
         <v>62.73</v>
       </c>
-      <c r="I51" s="13" t="inlineStr">
+      <c r="I51" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2921,7 +3156,7 @@
       <c r="H52" t="n">
         <v>68.43000000000001</v>
       </c>
-      <c r="I52" s="16" t="inlineStr">
+      <c r="I52" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2966,7 +3201,7 @@
       <c r="H53" t="n">
         <v>59.86</v>
       </c>
-      <c r="I53" s="16" t="inlineStr">
+      <c r="I53" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3011,7 +3246,7 @@
       <c r="H54" t="n">
         <v>54.06</v>
       </c>
-      <c r="I54" s="16" t="inlineStr">
+      <c r="I54" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3056,7 +3291,7 @@
       <c r="H55" t="n">
         <v>34.99</v>
       </c>
-      <c r="I55" s="16" t="inlineStr">
+      <c r="I55" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3101,7 +3336,7 @@
       <c r="H56" t="n">
         <v>84.42</v>
       </c>
-      <c r="I56" s="16" t="inlineStr">
+      <c r="I56" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3146,7 +3381,7 @@
       <c r="H57" t="n">
         <v>42.58</v>
       </c>
-      <c r="I57" s="16" t="inlineStr">
+      <c r="I57" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3191,7 +3426,7 @@
       <c r="H58" t="n">
         <v>36.17</v>
       </c>
-      <c r="I58" s="13" t="inlineStr">
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3236,7 +3471,7 @@
       <c r="H59" t="n">
         <v>86.17</v>
       </c>
-      <c r="I59" s="16" t="inlineStr">
+      <c r="I59" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3281,7 +3516,7 @@
       <c r="H60" t="n">
         <v>82.63</v>
       </c>
-      <c r="I60" s="16" t="inlineStr">
+      <c r="I60" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3326,7 +3561,7 @@
       <c r="H61" t="n">
         <v>52.44</v>
       </c>
-      <c r="I61" s="13" t="inlineStr">
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3371,7 +3606,7 @@
       <c r="H62" t="n">
         <v>56.64</v>
       </c>
-      <c r="I62" s="16" t="inlineStr">
+      <c r="I62" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3416,7 +3651,7 @@
       <c r="H63" t="n">
         <v>55.46</v>
       </c>
-      <c r="I63" s="16" t="inlineStr">
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3461,7 +3696,7 @@
       <c r="H64" t="n">
         <v>45</v>
       </c>
-      <c r="I64" s="16" t="inlineStr">
+      <c r="I64" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3506,7 +3741,7 @@
       <c r="H65" t="n">
         <v>39.11</v>
       </c>
-      <c r="I65" s="16" t="inlineStr">
+      <c r="I65" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3551,7 +3786,7 @@
       <c r="H66" t="n">
         <v>62.25</v>
       </c>
-      <c r="I66" s="16" t="inlineStr">
+      <c r="I66" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3596,7 +3831,7 @@
       <c r="H67" t="n">
         <v>46.09</v>
       </c>
-      <c r="I67" s="16" t="inlineStr">
+      <c r="I67" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3641,7 +3876,7 @@
       <c r="H68" t="n">
         <v>33.56</v>
       </c>
-      <c r="I68" s="13" t="inlineStr">
+      <c r="I68" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3686,7 +3921,7 @@
       <c r="H69" t="n">
         <v>39.27</v>
       </c>
-      <c r="I69" s="16" t="inlineStr">
+      <c r="I69" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3731,7 +3966,7 @@
       <c r="H70" t="n">
         <v>80.11</v>
       </c>
-      <c r="I70" s="16" t="inlineStr">
+      <c r="I70" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3776,7 +4011,7 @@
       <c r="H71" t="n">
         <v>25.51</v>
       </c>
-      <c r="I71" s="16" t="inlineStr">
+      <c r="I71" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3821,7 +4056,7 @@
       <c r="H72" t="n">
         <v>95.13</v>
       </c>
-      <c r="I72" s="16" t="inlineStr">
+      <c r="I72" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3866,7 +4101,7 @@
       <c r="H73" t="n">
         <v>51.1</v>
       </c>
-      <c r="I73" s="16" t="inlineStr">
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3911,7 +4146,7 @@
       <c r="H74" t="n">
         <v>83.98999999999999</v>
       </c>
-      <c r="I74" s="16" t="inlineStr">
+      <c r="I74" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3956,7 +4191,7 @@
       <c r="H75" t="n">
         <v>48.48</v>
       </c>
-      <c r="I75" s="16" t="inlineStr">
+      <c r="I75" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4001,7 +4236,7 @@
       <c r="H76" t="n">
         <v>63.73</v>
       </c>
-      <c r="I76" s="16" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4046,7 +4281,7 @@
       <c r="H77" t="n">
         <v>49.22</v>
       </c>
-      <c r="I77" s="16" t="inlineStr">
+      <c r="I77" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4091,7 +4326,7 @@
       <c r="H78" t="n">
         <v>44.22</v>
       </c>
-      <c r="I78" s="13" t="inlineStr">
+      <c r="I78" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4136,7 +4371,7 @@
       <c r="H79" t="n">
         <v>47.72</v>
       </c>
-      <c r="I79" s="16" t="inlineStr">
+      <c r="I79" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4181,7 +4416,7 @@
       <c r="H80" t="n">
         <v>48</v>
       </c>
-      <c r="I80" s="16" t="inlineStr">
+      <c r="I80" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4226,7 +4461,7 @@
       <c r="H81" t="n">
         <v>62.14</v>
       </c>
-      <c r="I81" s="16" t="inlineStr">
+      <c r="I81" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4271,7 +4506,7 @@
       <c r="H82" t="n">
         <v>41.36</v>
       </c>
-      <c r="I82" s="13" t="inlineStr">
+      <c r="I82" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4316,7 +4551,7 @@
       <c r="H83" t="n">
         <v>50.91</v>
       </c>
-      <c r="I83" s="16" t="inlineStr">
+      <c r="I83" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4361,7 +4596,7 @@
       <c r="H84" t="n">
         <v>35.39</v>
       </c>
-      <c r="I84" s="16" t="inlineStr">
+      <c r="I84" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4406,7 +4641,7 @@
       <c r="H85" t="n">
         <v>49.8</v>
       </c>
-      <c r="I85" s="13" t="inlineStr">
+      <c r="I85" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4451,7 +4686,7 @@
       <c r="H86" t="n">
         <v>39.32</v>
       </c>
-      <c r="I86" s="16" t="inlineStr">
+      <c r="I86" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4496,7 +4731,7 @@
       <c r="H87" t="n">
         <v>75.02</v>
       </c>
-      <c r="I87" s="16" t="inlineStr">
+      <c r="I87" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4541,7 +4776,7 @@
       <c r="H88" t="n">
         <v>36.96</v>
       </c>
-      <c r="I88" s="13" t="inlineStr">
+      <c r="I88" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4586,7 +4821,7 @@
       <c r="H89" t="n">
         <v>55.09</v>
       </c>
-      <c r="I89" s="13" t="inlineStr">
+      <c r="I89" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4631,7 +4866,7 @@
       <c r="H90" t="n">
         <v>58.42</v>
       </c>
-      <c r="I90" s="16" t="inlineStr">
+      <c r="I90" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4676,7 +4911,7 @@
       <c r="H91" t="n">
         <v>54.86</v>
       </c>
-      <c r="I91" s="16" t="inlineStr">
+      <c r="I91" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4721,7 +4956,7 @@
       <c r="H92" t="n">
         <v>42.64</v>
       </c>
-      <c r="I92" s="16" t="inlineStr">
+      <c r="I92" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4766,7 +5001,7 @@
       <c r="H93" t="n">
         <v>57.92</v>
       </c>
-      <c r="I93" s="13" t="inlineStr">
+      <c r="I93" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4811,7 +5046,7 @@
       <c r="H94" t="n">
         <v>39.54</v>
       </c>
-      <c r="I94" s="16" t="inlineStr">
+      <c r="I94" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4856,7 +5091,7 @@
       <c r="H95" t="n">
         <v>48.49</v>
       </c>
-      <c r="I95" s="13" t="inlineStr">
+      <c r="I95" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4901,7 +5136,7 @@
       <c r="H96" t="n">
         <v>71.14</v>
       </c>
-      <c r="I96" s="16" t="inlineStr">
+      <c r="I96" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4946,7 +5181,7 @@
       <c r="H97" t="n">
         <v>53.31</v>
       </c>
-      <c r="I97" s="16" t="inlineStr">
+      <c r="I97" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4991,7 +5226,7 @@
       <c r="H98" t="n">
         <v>33.17</v>
       </c>
-      <c r="I98" s="16" t="inlineStr">
+      <c r="I98" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5036,7 +5271,7 @@
       <c r="H99" t="n">
         <v>40.46</v>
       </c>
-      <c r="I99" s="13" t="inlineStr">
+      <c r="I99" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5081,7 +5316,7 @@
       <c r="H100" t="n">
         <v>86.31999999999999</v>
       </c>
-      <c r="I100" s="16" t="inlineStr">
+      <c r="I100" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5123,7 +5358,7 @@
       <c r="G101" s="12" t="n">
         <v>0.19</v>
       </c>
-      <c r="I101" s="16" t="inlineStr">
+      <c r="I101" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5161,7 +5396,7 @@
       <c r="G102" s="12" t="n">
         <v>0.23</v>
       </c>
-      <c r="I102" s="16" t="inlineStr">
+      <c r="I102" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5202,7 +5437,7 @@
       <c r="H103" t="n">
         <v>38.86</v>
       </c>
-      <c r="I103" s="13" t="inlineStr">
+      <c r="I103" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5247,7 +5482,7 @@
       <c r="H104" t="n">
         <v>74.59</v>
       </c>
-      <c r="I104" s="16" t="inlineStr">
+      <c r="I104" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5292,7 +5527,7 @@
       <c r="H105" t="n">
         <v>49.93</v>
       </c>
-      <c r="I105" s="16" t="inlineStr">
+      <c r="I105" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5337,7 +5572,7 @@
       <c r="H106" t="n">
         <v>46.63</v>
       </c>
-      <c r="I106" s="16" t="inlineStr">
+      <c r="I106" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5382,7 +5617,7 @@
       <c r="H107" t="n">
         <v>67.64</v>
       </c>
-      <c r="I107" s="16" t="inlineStr">
+      <c r="I107" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5427,7 +5662,7 @@
       <c r="H108" t="n">
         <v>57.07</v>
       </c>
-      <c r="I108" s="16" t="inlineStr">
+      <c r="I108" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5472,7 +5707,7 @@
       <c r="H109" t="n">
         <v>33.89</v>
       </c>
-      <c r="I109" s="13" t="inlineStr">
+      <c r="I109" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5517,7 +5752,7 @@
       <c r="H110" t="n">
         <v>39.08</v>
       </c>
-      <c r="I110" s="13" t="inlineStr">
+      <c r="I110" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5562,7 +5797,7 @@
       <c r="H111" t="n">
         <v>46.11</v>
       </c>
-      <c r="I111" s="13" t="inlineStr">
+      <c r="I111" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5607,7 +5842,7 @@
       <c r="H112" t="n">
         <v>50.5</v>
       </c>
-      <c r="I112" s="16" t="inlineStr">
+      <c r="I112" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5652,7 +5887,7 @@
       <c r="H113" t="n">
         <v>57.88</v>
       </c>
-      <c r="I113" s="16" t="inlineStr">
+      <c r="I113" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5697,7 +5932,7 @@
       <c r="H114" t="n">
         <v>38.65</v>
       </c>
-      <c r="I114" s="13" t="inlineStr">
+      <c r="I114" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5742,7 +5977,7 @@
       <c r="H115" t="n">
         <v>38.42</v>
       </c>
-      <c r="I115" s="13" t="inlineStr">
+      <c r="I115" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5787,7 +6022,7 @@
       <c r="H116" t="n">
         <v>41.49</v>
       </c>
-      <c r="I116" s="16" t="inlineStr">
+      <c r="I116" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5832,7 +6067,7 @@
       <c r="H117" t="n">
         <v>53.63</v>
       </c>
-      <c r="I117" s="16" t="inlineStr">
+      <c r="I117" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5877,7 +6112,7 @@
       <c r="H118" t="n">
         <v>40.34</v>
       </c>
-      <c r="I118" s="13" t="inlineStr">
+      <c r="I118" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5922,7 +6157,7 @@
       <c r="H119" t="n">
         <v>66.51000000000001</v>
       </c>
-      <c r="I119" s="16" t="inlineStr">
+      <c r="I119" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5967,7 +6202,7 @@
       <c r="H120" t="n">
         <v>51.45</v>
       </c>
-      <c r="I120" s="13" t="inlineStr">
+      <c r="I120" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6012,7 +6247,7 @@
       <c r="H121" t="n">
         <v>69.16</v>
       </c>
-      <c r="I121" s="16" t="inlineStr">
+      <c r="I121" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6057,7 +6292,7 @@
       <c r="H122" t="n">
         <v>80.78</v>
       </c>
-      <c r="I122" s="16" t="inlineStr">
+      <c r="I122" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6102,7 +6337,7 @@
       <c r="H123" t="n">
         <v>30.77</v>
       </c>
-      <c r="I123" s="13" t="inlineStr">
+      <c r="I123" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6147,7 +6382,7 @@
       <c r="H124" t="n">
         <v>51.39</v>
       </c>
-      <c r="I124" s="13" t="inlineStr">
+      <c r="I124" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6192,7 +6427,7 @@
       <c r="H125" t="n">
         <v>43.4</v>
       </c>
-      <c r="I125" s="13" t="inlineStr">
+      <c r="I125" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6237,7 +6472,7 @@
       <c r="H126" t="n">
         <v>68.72</v>
       </c>
-      <c r="I126" s="16" t="inlineStr">
+      <c r="I126" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6282,7 +6517,7 @@
       <c r="H127" t="n">
         <v>78.48</v>
       </c>
-      <c r="I127" s="16" t="inlineStr">
+      <c r="I127" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6327,7 +6562,7 @@
       <c r="H128" t="n">
         <v>55.88</v>
       </c>
-      <c r="I128" s="13" t="inlineStr">
+      <c r="I128" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6372,7 +6607,7 @@
       <c r="H129" t="n">
         <v>33.64</v>
       </c>
-      <c r="I129" s="13" t="inlineStr">
+      <c r="I129" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6417,7 +6652,7 @@
       <c r="H130" t="n">
         <v>43.79</v>
       </c>
-      <c r="I130" s="16" t="inlineStr">
+      <c r="I130" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6462,7 +6697,7 @@
       <c r="H131" t="n">
         <v>44.06</v>
       </c>
-      <c r="I131" s="13" t="inlineStr">
+      <c r="I131" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6507,7 +6742,7 @@
       <c r="H132" t="n">
         <v>60.64</v>
       </c>
-      <c r="I132" s="16" t="inlineStr">
+      <c r="I132" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6552,7 +6787,7 @@
       <c r="H133" t="n">
         <v>34.47</v>
       </c>
-      <c r="I133" s="13" t="inlineStr">
+      <c r="I133" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6597,7 +6832,7 @@
       <c r="H134" t="n">
         <v>33.85</v>
       </c>
-      <c r="I134" s="13" t="inlineStr">
+      <c r="I134" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6642,7 +6877,7 @@
       <c r="H135" t="n">
         <v>41.81</v>
       </c>
-      <c r="I135" s="13" t="inlineStr">
+      <c r="I135" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6687,7 +6922,7 @@
       <c r="H136" t="n">
         <v>73.06</v>
       </c>
-      <c r="I136" s="16" t="inlineStr">
+      <c r="I136" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6732,7 +6967,7 @@
       <c r="H137" t="n">
         <v>64.52</v>
       </c>
-      <c r="I137" s="16" t="inlineStr">
+      <c r="I137" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6777,7 +7012,7 @@
       <c r="H138" t="n">
         <v>50.99</v>
       </c>
-      <c r="I138" s="16" t="inlineStr">
+      <c r="I138" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6822,7 +7057,7 @@
       <c r="H139" t="n">
         <v>30.82</v>
       </c>
-      <c r="I139" s="13" t="inlineStr">
+      <c r="I139" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6867,7 +7102,7 @@
       <c r="H140" t="n">
         <v>87.31999999999999</v>
       </c>
-      <c r="I140" s="16" t="inlineStr">
+      <c r="I140" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6912,7 +7147,7 @@
       <c r="H141" t="n">
         <v>31.5</v>
       </c>
-      <c r="I141" s="13" t="inlineStr">
+      <c r="I141" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6957,7 +7192,7 @@
       <c r="H142" t="n">
         <v>59.86</v>
       </c>
-      <c r="I142" s="13" t="inlineStr">
+      <c r="I142" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7002,7 +7237,7 @@
       <c r="H143" t="n">
         <v>69.41</v>
       </c>
-      <c r="I143" s="16" t="inlineStr">
+      <c r="I143" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7047,7 +7282,7 @@
       <c r="H144" t="n">
         <v>50.06</v>
       </c>
-      <c r="I144" s="13" t="inlineStr">
+      <c r="I144" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7092,7 +7327,7 @@
       <c r="H145" t="n">
         <v>30.81</v>
       </c>
-      <c r="I145" s="13" t="inlineStr">
+      <c r="I145" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7134,7 +7369,7 @@
       <c r="G146" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="I146" s="13" t="inlineStr">
+      <c r="I146" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7175,7 +7410,7 @@
       <c r="H147" t="n">
         <v>56.59</v>
       </c>
-      <c r="I147" s="16" t="inlineStr">
+      <c r="I147" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7218,7 +7453,7 @@
       <c r="H148" t="n">
         <v>39.24</v>
       </c>
-      <c r="I148" s="16" t="inlineStr">
+      <c r="I148" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7263,7 +7498,7 @@
       <c r="H149" t="n">
         <v>38.25</v>
       </c>
-      <c r="I149" s="13" t="inlineStr">
+      <c r="I149" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7308,7 +7543,7 @@
       <c r="H150" t="n">
         <v>54.38</v>
       </c>
-      <c r="I150" s="16" t="inlineStr">
+      <c r="I150" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7353,7 +7588,7 @@
       <c r="H151" t="n">
         <v>52.84</v>
       </c>
-      <c r="I151" s="13" t="inlineStr">
+      <c r="I151" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7398,7 +7633,7 @@
       <c r="H152" t="n">
         <v>54.25</v>
       </c>
-      <c r="I152" s="13" t="inlineStr">
+      <c r="I152" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7443,7 +7678,7 @@
       <c r="H153" t="n">
         <v>47.94</v>
       </c>
-      <c r="I153" s="13" t="inlineStr">
+      <c r="I153" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7488,7 +7723,7 @@
       <c r="H154" t="n">
         <v>53.16</v>
       </c>
-      <c r="I154" s="13" t="inlineStr">
+      <c r="I154" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7533,7 +7768,7 @@
       <c r="H155" t="n">
         <v>54.36</v>
       </c>
-      <c r="I155" s="16" t="inlineStr">
+      <c r="I155" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7578,7 +7813,7 @@
       <c r="H156" t="n">
         <v>46.96</v>
       </c>
-      <c r="I156" s="16" t="inlineStr">
+      <c r="I156" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7623,7 +7858,7 @@
       <c r="H157" t="n">
         <v>85.34999999999999</v>
       </c>
-      <c r="I157" s="16" t="inlineStr">
+      <c r="I157" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7668,7 +7903,7 @@
       <c r="H158" t="n">
         <v>56.08</v>
       </c>
-      <c r="I158" s="13" t="inlineStr">
+      <c r="I158" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7713,7 +7948,7 @@
       <c r="H159" t="n">
         <v>61.95</v>
       </c>
-      <c r="I159" s="16" t="inlineStr">
+      <c r="I159" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7758,7 +7993,7 @@
       <c r="H160" t="n">
         <v>50.63</v>
       </c>
-      <c r="I160" s="13" t="inlineStr">
+      <c r="I160" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7803,7 +8038,7 @@
       <c r="H161" t="n">
         <v>53.77</v>
       </c>
-      <c r="I161" s="13" t="inlineStr">
+      <c r="I161" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -7848,7 +8083,7 @@
       <c r="H162" t="n">
         <v>50.52</v>
       </c>
-      <c r="I162" s="16" t="inlineStr">
+      <c r="I162" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7893,7 +8128,7 @@
       <c r="H163" t="n">
         <v>56.07</v>
       </c>
-      <c r="I163" s="16" t="inlineStr">
+      <c r="I163" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7938,7 +8173,7 @@
       <c r="H164" t="n">
         <v>48.52</v>
       </c>
-      <c r="I164" s="16" t="inlineStr">
+      <c r="I164" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7983,7 +8218,7 @@
       <c r="H165" t="n">
         <v>57.39</v>
       </c>
-      <c r="I165" s="16" t="inlineStr">
+      <c r="I165" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8028,7 +8263,7 @@
       <c r="H166" t="n">
         <v>47.78</v>
       </c>
-      <c r="I166" s="13" t="inlineStr">
+      <c r="I166" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8073,7 +8308,7 @@
       <c r="H167" t="n">
         <v>34.77</v>
       </c>
-      <c r="I167" s="13" t="inlineStr">
+      <c r="I167" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8118,7 +8353,7 @@
       <c r="H168" t="n">
         <v>57.16</v>
       </c>
-      <c r="I168" s="13" t="inlineStr">
+      <c r="I168" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8163,7 +8398,7 @@
       <c r="H169" t="n">
         <v>37.83</v>
       </c>
-      <c r="I169" s="13" t="inlineStr">
+      <c r="I169" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8208,7 +8443,7 @@
       <c r="H170" t="n">
         <v>60.57</v>
       </c>
-      <c r="I170" s="16" t="inlineStr">
+      <c r="I170" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8253,7 +8488,7 @@
       <c r="H171" t="n">
         <v>45.88</v>
       </c>
-      <c r="I171" s="13" t="inlineStr">
+      <c r="I171" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8298,7 +8533,7 @@
       <c r="H172" t="n">
         <v>67.45</v>
       </c>
-      <c r="I172" s="16" t="inlineStr">
+      <c r="I172" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8343,7 +8578,7 @@
       <c r="H173" t="n">
         <v>62.61</v>
       </c>
-      <c r="I173" s="16" t="inlineStr">
+      <c r="I173" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8388,7 +8623,7 @@
       <c r="H174" t="n">
         <v>55.39</v>
       </c>
-      <c r="I174" s="13" t="inlineStr">
+      <c r="I174" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8433,7 +8668,7 @@
       <c r="H175" t="n">
         <v>38.42</v>
       </c>
-      <c r="I175" s="13" t="inlineStr">
+      <c r="I175" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8478,7 +8713,7 @@
       <c r="H176" t="n">
         <v>78.34999999999999</v>
       </c>
-      <c r="I176" s="16" t="inlineStr">
+      <c r="I176" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8523,7 +8758,7 @@
       <c r="H177" t="n">
         <v>33.09</v>
       </c>
-      <c r="I177" s="13" t="inlineStr">
+      <c r="I177" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8568,7 +8803,7 @@
       <c r="H178" t="n">
         <v>45.51</v>
       </c>
-      <c r="I178" s="13" t="inlineStr">
+      <c r="I178" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8613,7 +8848,7 @@
       <c r="H179" t="n">
         <v>52.75</v>
       </c>
-      <c r="I179" s="16" t="inlineStr">
+      <c r="I179" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8658,7 +8893,7 @@
       <c r="H180" t="n">
         <v>70.55</v>
       </c>
-      <c r="I180" s="16" t="inlineStr">
+      <c r="I180" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8703,7 +8938,7 @@
       <c r="H181" t="n">
         <v>38.02</v>
       </c>
-      <c r="I181" s="13" t="inlineStr">
+      <c r="I181" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8748,7 +8983,7 @@
       <c r="H182" t="n">
         <v>32.12</v>
       </c>
-      <c r="I182" s="13" t="inlineStr">
+      <c r="I182" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -8793,7 +9028,7 @@
       <c r="H183" t="n">
         <v>74.73</v>
       </c>
-      <c r="I183" s="16" t="inlineStr">
+      <c r="I183" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8838,7 +9073,7 @@
       <c r="H184" t="n">
         <v>65.06999999999999</v>
       </c>
-      <c r="I184" s="16" t="inlineStr">
+      <c r="I184" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8883,7 +9118,7 @@
       <c r="H185" t="n">
         <v>77.95999999999999</v>
       </c>
-      <c r="I185" s="16" t="inlineStr">
+      <c r="I185" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8928,7 +9163,7 @@
       <c r="H186" t="n">
         <v>56.96</v>
       </c>
-      <c r="I186" s="16" t="inlineStr">
+      <c r="I186" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -8973,7 +9208,7 @@
       <c r="H187" t="n">
         <v>61.47</v>
       </c>
-      <c r="I187" s="16" t="inlineStr">
+      <c r="I187" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9018,7 +9253,7 @@
       <c r="H188" t="n">
         <v>47.35</v>
       </c>
-      <c r="I188" s="13" t="inlineStr">
+      <c r="I188" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -9063,7 +9298,7 @@
       <c r="H189" t="n">
         <v>57.87</v>
       </c>
-      <c r="I189" s="13" t="inlineStr">
+      <c r="I189" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -9108,7 +9343,7 @@
       <c r="H190" t="n">
         <v>46.18</v>
       </c>
-      <c r="I190" s="16" t="inlineStr">
+      <c r="I190" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9153,7 +9388,7 @@
       <c r="H191" t="n">
         <v>55.34</v>
       </c>
-      <c r="I191" s="16" t="inlineStr">
+      <c r="I191" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9198,7 +9433,7 @@
       <c r="H192" t="n">
         <v>53.86</v>
       </c>
-      <c r="I192" s="16" t="inlineStr">
+      <c r="I192" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9243,7 +9478,7 @@
       <c r="H193" t="n">
         <v>46.07</v>
       </c>
-      <c r="I193" s="13" t="inlineStr">
+      <c r="I193" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -9288,7 +9523,7 @@
       <c r="H194" t="n">
         <v>59.03</v>
       </c>
-      <c r="I194" s="13" t="inlineStr">
+      <c r="I194" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -9333,7 +9568,7 @@
       <c r="H195" t="n">
         <v>57.23</v>
       </c>
-      <c r="I195" s="13" t="inlineStr">
+      <c r="I195" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -9378,7 +9613,7 @@
       <c r="H196" t="n">
         <v>58.75</v>
       </c>
-      <c r="I196" s="16" t="inlineStr">
+      <c r="I196" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9423,7 +9658,7 @@
       <c r="H197" t="n">
         <v>49.75</v>
       </c>
-      <c r="I197" s="16" t="inlineStr">
+      <c r="I197" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9468,7 +9703,7 @@
       <c r="H198" t="n">
         <v>47.33</v>
       </c>
-      <c r="I198" s="16" t="inlineStr">
+      <c r="I198" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9513,7 +9748,7 @@
       <c r="H199" t="n">
         <v>57.86</v>
       </c>
-      <c r="I199" s="16" t="inlineStr">
+      <c r="I199" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9558,7 +9793,7 @@
       <c r="H200" t="n">
         <v>50.5</v>
       </c>
-      <c r="I200" s="16" t="inlineStr">
+      <c r="I200" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9603,7 +9838,7 @@
       <c r="H201" t="n">
         <v>52.98</v>
       </c>
-      <c r="I201" s="16" t="inlineStr">
+      <c r="I201" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9648,7 +9883,7 @@
       <c r="H202" t="n">
         <v>47.49</v>
       </c>
-      <c r="I202" s="13" t="inlineStr">
+      <c r="I202" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -9693,7 +9928,7 @@
       <c r="H203" t="n">
         <v>68.86</v>
       </c>
-      <c r="I203" s="13" t="inlineStr">
+      <c r="I203" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -9738,7 +9973,7 @@
       <c r="H204" t="n">
         <v>65.62</v>
       </c>
-      <c r="I204" s="16" t="inlineStr">
+      <c r="I204" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9783,7 +10018,7 @@
       <c r="H205" t="n">
         <v>53.75</v>
       </c>
-      <c r="I205" s="16" t="inlineStr">
+      <c r="I205" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9828,7 +10063,7 @@
       <c r="H206" t="n">
         <v>46.83</v>
       </c>
-      <c r="I206" s="13" t="inlineStr">
+      <c r="I206" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -9873,7 +10108,7 @@
       <c r="H207" t="n">
         <v>65.41</v>
       </c>
-      <c r="I207" s="16" t="inlineStr">
+      <c r="I207" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9918,7 +10153,7 @@
       <c r="H208" t="n">
         <v>46.82</v>
       </c>
-      <c r="I208" s="16" t="inlineStr">
+      <c r="I208" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -9963,7 +10198,7 @@
       <c r="H209" t="n">
         <v>39.32</v>
       </c>
-      <c r="I209" s="13" t="inlineStr">
+      <c r="I209" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10008,7 +10243,7 @@
       <c r="H210" t="n">
         <v>53.54</v>
       </c>
-      <c r="I210" s="16" t="inlineStr">
+      <c r="I210" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10053,7 +10288,7 @@
       <c r="H211" t="n">
         <v>54.14</v>
       </c>
-      <c r="I211" s="13" t="inlineStr">
+      <c r="I211" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10098,7 +10333,7 @@
       <c r="H212" t="n">
         <v>50.02</v>
       </c>
-      <c r="I212" s="16" t="inlineStr">
+      <c r="I212" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10143,7 +10378,7 @@
       <c r="H213" t="n">
         <v>50.17</v>
       </c>
-      <c r="I213" s="16" t="inlineStr">
+      <c r="I213" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10188,7 +10423,7 @@
       <c r="H214" t="n">
         <v>41.6</v>
       </c>
-      <c r="I214" s="13" t="inlineStr">
+      <c r="I214" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10233,7 +10468,7 @@
       <c r="H215" t="n">
         <v>53.72</v>
       </c>
-      <c r="I215" s="13" t="inlineStr">
+      <c r="I215" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10278,7 +10513,7 @@
       <c r="H216" t="n">
         <v>47.95</v>
       </c>
-      <c r="I216" s="16" t="inlineStr">
+      <c r="I216" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10323,7 +10558,7 @@
       <c r="H217" t="n">
         <v>36.4</v>
       </c>
-      <c r="I217" s="13" t="inlineStr">
+      <c r="I217" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10368,7 +10603,7 @@
       <c r="H218" t="n">
         <v>43.77</v>
       </c>
-      <c r="I218" s="13" t="inlineStr">
+      <c r="I218" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10413,7 +10648,7 @@
       <c r="H219" t="n">
         <v>43.68</v>
       </c>
-      <c r="I219" s="16" t="inlineStr">
+      <c r="I219" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10458,7 +10693,7 @@
       <c r="H220" t="n">
         <v>59.23</v>
       </c>
-      <c r="I220" s="16" t="inlineStr">
+      <c r="I220" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10503,7 +10738,7 @@
       <c r="H221" t="n">
         <v>65.73999999999999</v>
       </c>
-      <c r="I221" s="16" t="inlineStr">
+      <c r="I221" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10548,7 +10783,7 @@
       <c r="H222" t="n">
         <v>53.13</v>
       </c>
-      <c r="I222" s="13" t="inlineStr">
+      <c r="I222" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10593,7 +10828,7 @@
       <c r="H223" t="n">
         <v>50.8</v>
       </c>
-      <c r="I223" s="16" t="inlineStr">
+      <c r="I223" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10638,7 +10873,7 @@
       <c r="H224" t="n">
         <v>30.43</v>
       </c>
-      <c r="I224" s="16" t="inlineStr">
+      <c r="I224" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10683,7 +10918,7 @@
       <c r="H225" t="n">
         <v>37.77</v>
       </c>
-      <c r="I225" s="13" t="inlineStr">
+      <c r="I225" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10728,7 +10963,7 @@
       <c r="H226" t="n">
         <v>56.96</v>
       </c>
-      <c r="I226" s="16" t="inlineStr">
+      <c r="I226" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10773,7 +11008,7 @@
       <c r="H227" t="n">
         <v>72.26000000000001</v>
       </c>
-      <c r="I227" s="16" t="inlineStr">
+      <c r="I227" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10818,7 +11053,7 @@
       <c r="H228" t="n">
         <v>57.84</v>
       </c>
-      <c r="I228" s="16" t="inlineStr">
+      <c r="I228" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10863,7 +11098,7 @@
       <c r="H229" t="n">
         <v>30.26</v>
       </c>
-      <c r="I229" s="16" t="inlineStr">
+      <c r="I229" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10908,7 +11143,7 @@
       <c r="H230" t="n">
         <v>59.27</v>
       </c>
-      <c r="I230" s="16" t="inlineStr">
+      <c r="I230" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -10953,7 +11188,7 @@
       <c r="H231" t="n">
         <v>45.47</v>
       </c>
-      <c r="I231" s="13" t="inlineStr">
+      <c r="I231" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -10998,7 +11233,7 @@
       <c r="H232" t="n">
         <v>48.02</v>
       </c>
-      <c r="I232" s="13" t="inlineStr">
+      <c r="I232" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11043,7 +11278,7 @@
       <c r="H233" t="n">
         <v>47.26</v>
       </c>
-      <c r="I233" s="16" t="inlineStr">
+      <c r="I233" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11088,7 +11323,7 @@
       <c r="H234" t="n">
         <v>59.87</v>
       </c>
-      <c r="I234" s="13" t="inlineStr">
+      <c r="I234" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11133,7 +11368,7 @@
       <c r="H235" t="n">
         <v>30.19</v>
       </c>
-      <c r="I235" s="13" t="inlineStr">
+      <c r="I235" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11178,7 +11413,7 @@
       <c r="H236" t="n">
         <v>39.77</v>
       </c>
-      <c r="I236" s="13" t="inlineStr">
+      <c r="I236" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11223,7 +11458,7 @@
       <c r="H237" t="n">
         <v>49.19</v>
       </c>
-      <c r="I237" s="16" t="inlineStr">
+      <c r="I237" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11268,7 +11503,7 @@
       <c r="H238" t="n">
         <v>41.15</v>
       </c>
-      <c r="I238" s="13" t="inlineStr">
+      <c r="I238" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11313,7 +11548,7 @@
       <c r="H239" t="n">
         <v>42.33</v>
       </c>
-      <c r="I239" s="13" t="inlineStr">
+      <c r="I239" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11358,7 +11593,7 @@
       <c r="H240" t="n">
         <v>71.48999999999999</v>
       </c>
-      <c r="I240" s="16" t="inlineStr">
+      <c r="I240" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11403,7 +11638,7 @@
       <c r="H241" t="n">
         <v>46.86</v>
       </c>
-      <c r="I241" s="13" t="inlineStr">
+      <c r="I241" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11448,7 +11683,7 @@
       <c r="H242" t="n">
         <v>41.48</v>
       </c>
-      <c r="I242" s="16" t="inlineStr">
+      <c r="I242" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11493,7 +11728,7 @@
       <c r="H243" t="n">
         <v>65.73</v>
       </c>
-      <c r="I243" s="16" t="inlineStr">
+      <c r="I243" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11538,7 +11773,7 @@
       <c r="H244" t="n">
         <v>54.67</v>
       </c>
-      <c r="I244" s="16" t="inlineStr">
+      <c r="I244" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11583,7 +11818,7 @@
       <c r="H245" t="n">
         <v>40.23</v>
       </c>
-      <c r="I245" s="13" t="inlineStr">
+      <c r="I245" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11628,7 +11863,7 @@
       <c r="H246" t="n">
         <v>42.49</v>
       </c>
-      <c r="I246" s="13" t="inlineStr">
+      <c r="I246" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11673,7 +11908,7 @@
       <c r="H247" t="n">
         <v>47.46</v>
       </c>
-      <c r="I247" s="16" t="inlineStr">
+      <c r="I247" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11718,7 +11953,7 @@
       <c r="H248" t="n">
         <v>35.92</v>
       </c>
-      <c r="I248" s="13" t="inlineStr">
+      <c r="I248" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11763,7 +11998,7 @@
       <c r="H249" t="n">
         <v>68.13</v>
       </c>
-      <c r="I249" s="16" t="inlineStr">
+      <c r="I249" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11808,7 +12043,7 @@
       <c r="H250" t="n">
         <v>53.68</v>
       </c>
-      <c r="I250" s="16" t="inlineStr">
+      <c r="I250" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11853,7 +12088,7 @@
       <c r="H251" t="n">
         <v>58.02</v>
       </c>
-      <c r="I251" s="13" t="inlineStr">
+      <c r="I251" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -11898,7 +12133,7 @@
       <c r="H252" t="n">
         <v>56.79</v>
       </c>
-      <c r="I252" s="16" t="inlineStr">
+      <c r="I252" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11943,7 +12178,7 @@
       <c r="H253" t="n">
         <v>78.97</v>
       </c>
-      <c r="I253" s="16" t="inlineStr">
+      <c r="I253" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -11988,7 +12223,7 @@
       <c r="H254" t="n">
         <v>46.69</v>
       </c>
-      <c r="I254" s="16" t="inlineStr">
+      <c r="I254" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12033,7 +12268,7 @@
       <c r="H255" t="n">
         <v>43.29</v>
       </c>
-      <c r="I255" s="16" t="inlineStr">
+      <c r="I255" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12078,7 +12313,7 @@
       <c r="H256" t="n">
         <v>28.62</v>
       </c>
-      <c r="I256" s="13" t="inlineStr">
+      <c r="I256" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -12123,7 +12358,7 @@
       <c r="H257" t="n">
         <v>55.04</v>
       </c>
-      <c r="I257" s="16" t="inlineStr">
+      <c r="I257" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12168,7 +12403,7 @@
       <c r="H258" t="n">
         <v>55.57</v>
       </c>
-      <c r="I258" s="13" t="inlineStr">
+      <c r="I258" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -12213,7 +12448,7 @@
       <c r="H259" t="n">
         <v>40.32</v>
       </c>
-      <c r="I259" s="16" t="inlineStr">
+      <c r="I259" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12258,7 +12493,7 @@
       <c r="H260" t="n">
         <v>25.08</v>
       </c>
-      <c r="I260" s="16" t="inlineStr">
+      <c r="I260" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12303,7 +12538,7 @@
       <c r="H261" t="n">
         <v>63.43</v>
       </c>
-      <c r="I261" s="16" t="inlineStr">
+      <c r="I261" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12348,7 +12583,7 @@
       <c r="H262" t="n">
         <v>60.91</v>
       </c>
-      <c r="I262" s="16" t="inlineStr">
+      <c r="I262" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12393,7 +12628,7 @@
       <c r="H263" t="n">
         <v>52.07</v>
       </c>
-      <c r="I263" s="13" t="inlineStr">
+      <c r="I263" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -12438,7 +12673,7 @@
       <c r="H264" t="n">
         <v>38.72</v>
       </c>
-      <c r="I264" s="13" t="inlineStr">
+      <c r="I264" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -12483,7 +12718,7 @@
       <c r="H265" t="n">
         <v>55.89</v>
       </c>
-      <c r="I265" s="16" t="inlineStr">
+      <c r="I265" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12528,7 +12763,7 @@
       <c r="H266" t="n">
         <v>68.97</v>
       </c>
-      <c r="I266" s="16" t="inlineStr">
+      <c r="I266" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12573,7 +12808,7 @@
       <c r="H267" t="n">
         <v>58.77</v>
       </c>
-      <c r="I267" s="16" t="inlineStr">
+      <c r="I267" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12618,7 +12853,7 @@
       <c r="H268" t="n">
         <v>41.41</v>
       </c>
-      <c r="I268" s="13" t="inlineStr">
+      <c r="I268" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -12663,7 +12898,7 @@
       <c r="H269" t="n">
         <v>40.54</v>
       </c>
-      <c r="I269" s="13" t="inlineStr">
+      <c r="I269" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -12708,7 +12943,7 @@
       <c r="H270" t="n">
         <v>60</v>
       </c>
-      <c r="I270" s="16" t="inlineStr">
+      <c r="I270" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12753,7 +12988,7 @@
       <c r="H271" t="n">
         <v>40.7</v>
       </c>
-      <c r="I271" s="16" t="inlineStr">
+      <c r="I271" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12798,7 +13033,7 @@
       <c r="H272" t="n">
         <v>72.36</v>
       </c>
-      <c r="I272" s="16" t="inlineStr">
+      <c r="I272" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12843,7 +13078,7 @@
       <c r="H273" t="n">
         <v>59.82</v>
       </c>
-      <c r="I273" s="16" t="inlineStr">
+      <c r="I273" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -12888,7 +13123,7 @@
       <c r="H274" t="n">
         <v>42.53</v>
       </c>
-      <c r="I274" s="13" t="inlineStr">
+      <c r="I274" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -12933,7 +13168,7 @@
       <c r="H275" t="n">
         <v>51.99</v>
       </c>
-      <c r="I275" s="16" t="inlineStr">
+      <c r="I275" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13287,7 +13522,7 @@
       <c r="H6" t="n">
         <v>21.29</v>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -13332,7 +13567,7 @@
       <c r="H7" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13377,7 +13612,7 @@
       <c r="H8" t="n">
         <v>65.29000000000001</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13422,7 +13657,7 @@
       <c r="H9" t="n">
         <v>37.55</v>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -13467,7 +13702,7 @@
       <c r="H10" t="n">
         <v>34.37</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13512,7 +13747,7 @@
       <c r="H11" t="n">
         <v>70.72</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13557,7 +13792,7 @@
       <c r="H12" t="n">
         <v>27.32</v>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -13602,7 +13837,7 @@
       <c r="H13" t="n">
         <v>50.95</v>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -13647,7 +13882,7 @@
       <c r="H14" t="n">
         <v>83.95999999999999</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13692,7 +13927,7 @@
       <c r="H15" t="n">
         <v>65.15000000000001</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13737,7 +13972,7 @@
       <c r="H16" t="n">
         <v>65.55</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13782,7 +14017,7 @@
       <c r="H17" t="n">
         <v>39.23</v>
       </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -13827,7 +14062,7 @@
       <c r="H18" t="n">
         <v>49.97</v>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -13872,7 +14107,7 @@
       <c r="H19" t="n">
         <v>59.23</v>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -13917,7 +14152,7 @@
       <c r="H20" t="n">
         <v>53.21</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -13962,7 +14197,7 @@
       <c r="H21" t="n">
         <v>61.79</v>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14007,7 +14242,7 @@
       <c r="H22" t="n">
         <v>85.45999999999999</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14052,7 +14287,7 @@
       <c r="H23" t="n">
         <v>48.03</v>
       </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -14097,7 +14332,7 @@
       <c r="H24" t="n">
         <v>65.5</v>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14142,7 +14377,7 @@
       <c r="H25" t="n">
         <v>63.72</v>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14187,7 +14422,7 @@
       <c r="H26" t="n">
         <v>45.39</v>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I26" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -14232,7 +14467,7 @@
       <c r="H27" t="n">
         <v>60.61</v>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14277,7 +14512,7 @@
       <c r="H28" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14322,7 +14557,7 @@
       <c r="H29" t="n">
         <v>60.55</v>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -14367,7 +14602,7 @@
       <c r="H30" t="n">
         <v>62</v>
       </c>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14412,7 +14647,7 @@
       <c r="H31" t="n">
         <v>63.31</v>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14457,7 +14692,7 @@
       <c r="H32" t="n">
         <v>58.5</v>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14502,7 +14737,7 @@
       <c r="H33" t="n">
         <v>30.81</v>
       </c>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I33" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -14547,7 +14782,7 @@
       <c r="H34" t="n">
         <v>49.98</v>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="I34" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14592,7 +14827,7 @@
       <c r="H35" t="n">
         <v>34.18</v>
       </c>
-      <c r="I35" s="13" t="inlineStr">
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -14637,7 +14872,7 @@
       <c r="H36" t="n">
         <v>55.76</v>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14682,7 +14917,7 @@
       <c r="H37" t="n">
         <v>70.97</v>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="I37" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14727,7 +14962,7 @@
       <c r="H38" t="n">
         <v>52.62</v>
       </c>
-      <c r="I38" s="16" t="inlineStr">
+      <c r="I38" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14772,7 +15007,7 @@
       <c r="H39" t="n">
         <v>82.06</v>
       </c>
-      <c r="I39" s="16" t="inlineStr">
+      <c r="I39" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14817,7 +15052,7 @@
       <c r="H40" t="n">
         <v>62.58</v>
       </c>
-      <c r="I40" s="13" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -14862,7 +15097,7 @@
       <c r="H41" t="n">
         <v>60.3</v>
       </c>
-      <c r="I41" s="16" t="inlineStr">
+      <c r="I41" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14907,7 +15142,7 @@
       <c r="H42" t="n">
         <v>27.14</v>
       </c>
-      <c r="I42" s="16" t="inlineStr">
+      <c r="I42" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14952,7 +15187,7 @@
       <c r="H43" t="n">
         <v>44.03</v>
       </c>
-      <c r="I43" s="16" t="inlineStr">
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -14997,7 +15232,7 @@
       <c r="H44" t="n">
         <v>44.97</v>
       </c>
-      <c r="I44" s="16" t="inlineStr">
+      <c r="I44" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15042,7 +15277,7 @@
       <c r="H45" t="n">
         <v>44.4</v>
       </c>
-      <c r="I45" s="13" t="inlineStr">
+      <c r="I45" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -15087,7 +15322,7 @@
       <c r="H46" t="n">
         <v>66.33</v>
       </c>
-      <c r="I46" s="16" t="inlineStr">
+      <c r="I46" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15132,7 +15367,7 @@
       <c r="H47" t="n">
         <v>44.71</v>
       </c>
-      <c r="I47" s="16" t="inlineStr">
+      <c r="I47" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15177,7 +15412,7 @@
       <c r="H48" t="n">
         <v>80.61</v>
       </c>
-      <c r="I48" s="16" t="inlineStr">
+      <c r="I48" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15222,7 +15457,7 @@
       <c r="H49" t="n">
         <v>91.64</v>
       </c>
-      <c r="I49" s="16" t="inlineStr">
+      <c r="I49" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15267,7 +15502,7 @@
       <c r="H50" t="n">
         <v>59.52</v>
       </c>
-      <c r="I50" s="13" t="inlineStr">
+      <c r="I50" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -15312,7 +15547,7 @@
       <c r="H51" t="n">
         <v>56.29</v>
       </c>
-      <c r="I51" s="16" t="inlineStr">
+      <c r="I51" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15357,7 +15592,7 @@
       <c r="H52" t="n">
         <v>44.01</v>
       </c>
-      <c r="I52" s="13" t="inlineStr">
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -15402,7 +15637,7 @@
       <c r="H53" t="n">
         <v>63.01</v>
       </c>
-      <c r="I53" s="16" t="inlineStr">
+      <c r="I53" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15447,7 +15682,7 @@
       <c r="H54" t="n">
         <v>45.94</v>
       </c>
-      <c r="I54" s="13" t="inlineStr">
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -15492,7 +15727,7 @@
       <c r="H55" t="n">
         <v>70.03</v>
       </c>
-      <c r="I55" s="16" t="inlineStr">
+      <c r="I55" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15537,7 +15772,7 @@
       <c r="H56" t="n">
         <v>39.32</v>
       </c>
-      <c r="I56" s="16" t="inlineStr">
+      <c r="I56" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15582,7 +15817,7 @@
       <c r="H57" t="n">
         <v>36.24</v>
       </c>
-      <c r="I57" s="16" t="inlineStr">
+      <c r="I57" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15627,7 +15862,7 @@
       <c r="H58" t="n">
         <v>50.08</v>
       </c>
-      <c r="I58" s="16" t="inlineStr">
+      <c r="I58" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15672,7 +15907,7 @@
       <c r="H59" t="n">
         <v>32.39</v>
       </c>
-      <c r="I59" s="16" t="inlineStr">
+      <c r="I59" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15717,7 +15952,7 @@
       <c r="H60" t="n">
         <v>53.43</v>
       </c>
-      <c r="I60" s="16" t="inlineStr">
+      <c r="I60" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15762,7 +15997,7 @@
       <c r="H61" t="n">
         <v>65.79000000000001</v>
       </c>
-      <c r="I61" s="16" t="inlineStr">
+      <c r="I61" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15807,7 +16042,7 @@
       <c r="H62" t="n">
         <v>35.91</v>
       </c>
-      <c r="I62" s="13" t="inlineStr">
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -15852,7 +16087,7 @@
       <c r="H63" t="n">
         <v>66.95</v>
       </c>
-      <c r="I63" s="16" t="inlineStr">
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15897,7 +16132,7 @@
       <c r="H64" t="n">
         <v>43.1</v>
       </c>
-      <c r="I64" s="16" t="inlineStr">
+      <c r="I64" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15942,7 +16177,7 @@
       <c r="H65" t="n">
         <v>48.81</v>
       </c>
-      <c r="I65" s="16" t="inlineStr">
+      <c r="I65" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -15987,7 +16222,7 @@
       <c r="H66" t="n">
         <v>36.64</v>
       </c>
-      <c r="I66" s="13" t="inlineStr">
+      <c r="I66" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16032,7 +16267,7 @@
       <c r="H67" t="n">
         <v>56.69</v>
       </c>
-      <c r="I67" s="16" t="inlineStr">
+      <c r="I67" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16077,7 +16312,7 @@
       <c r="H68" t="n">
         <v>54.34</v>
       </c>
-      <c r="I68" s="13" t="inlineStr">
+      <c r="I68" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16122,7 +16357,7 @@
       <c r="H69" t="n">
         <v>47.09</v>
       </c>
-      <c r="I69" s="13" t="inlineStr">
+      <c r="I69" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16167,7 +16402,7 @@
       <c r="H70" t="n">
         <v>47.28</v>
       </c>
-      <c r="I70" s="13" t="inlineStr">
+      <c r="I70" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16212,7 +16447,7 @@
       <c r="H71" t="n">
         <v>72.43000000000001</v>
       </c>
-      <c r="I71" s="16" t="inlineStr">
+      <c r="I71" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16257,7 +16492,7 @@
       <c r="H72" t="n">
         <v>46.71</v>
       </c>
-      <c r="I72" s="16" t="inlineStr">
+      <c r="I72" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16302,7 +16537,7 @@
       <c r="H73" t="n">
         <v>56.42</v>
       </c>
-      <c r="I73" s="16" t="inlineStr">
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16347,7 +16582,7 @@
       <c r="H74" t="n">
         <v>48.49</v>
       </c>
-      <c r="I74" s="13" t="inlineStr">
+      <c r="I74" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16392,7 +16627,7 @@
       <c r="H75" t="n">
         <v>64.68000000000001</v>
       </c>
-      <c r="I75" s="16" t="inlineStr">
+      <c r="I75" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16437,7 +16672,7 @@
       <c r="H76" t="n">
         <v>72.65000000000001</v>
       </c>
-      <c r="I76" s="16" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16482,7 +16717,7 @@
       <c r="H77" t="n">
         <v>51.13</v>
       </c>
-      <c r="I77" s="16" t="inlineStr">
+      <c r="I77" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16527,7 +16762,7 @@
       <c r="H78" t="n">
         <v>53.7</v>
       </c>
-      <c r="I78" s="16" t="inlineStr">
+      <c r="I78" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16572,7 +16807,7 @@
       <c r="H79" t="n">
         <v>63.03</v>
       </c>
-      <c r="I79" s="13" t="inlineStr">
+      <c r="I79" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16617,7 +16852,7 @@
       <c r="H80" t="n">
         <v>85.41</v>
       </c>
-      <c r="I80" s="16" t="inlineStr">
+      <c r="I80" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16662,7 +16897,7 @@
       <c r="H81" t="n">
         <v>49.21</v>
       </c>
-      <c r="I81" s="16" t="inlineStr">
+      <c r="I81" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16707,7 +16942,7 @@
       <c r="H82" t="n">
         <v>51.39</v>
       </c>
-      <c r="I82" s="13" t="inlineStr">
+      <c r="I82" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16752,7 +16987,7 @@
       <c r="H83" t="n">
         <v>78.77</v>
       </c>
-      <c r="I83" s="16" t="inlineStr">
+      <c r="I83" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16797,7 +17032,7 @@
       <c r="H84" t="n">
         <v>47.94</v>
       </c>
-      <c r="I84" s="13" t="inlineStr">
+      <c r="I84" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16842,7 +17077,7 @@
       <c r="H85" t="n">
         <v>45.7</v>
       </c>
-      <c r="I85" s="13" t="inlineStr">
+      <c r="I85" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16887,7 +17122,7 @@
       <c r="H86" t="n">
         <v>46.95</v>
       </c>
-      <c r="I86" s="13" t="inlineStr">
+      <c r="I86" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -16932,7 +17167,7 @@
       <c r="H87" t="n">
         <v>59.72</v>
       </c>
-      <c r="I87" s="16" t="inlineStr">
+      <c r="I87" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -16977,7 +17212,7 @@
       <c r="H88" t="n">
         <v>40.08</v>
       </c>
-      <c r="I88" s="16" t="inlineStr">
+      <c r="I88" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17022,7 +17257,7 @@
       <c r="H89" t="n">
         <v>46.47</v>
       </c>
-      <c r="I89" s="16" t="inlineStr">
+      <c r="I89" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17067,7 +17302,7 @@
       <c r="H90" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="I90" s="16" t="inlineStr">
+      <c r="I90" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17112,7 +17347,7 @@
       <c r="H91" t="n">
         <v>41.13</v>
       </c>
-      <c r="I91" s="13" t="inlineStr">
+      <c r="I91" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -17157,7 +17392,7 @@
       <c r="H92" t="n">
         <v>54.05</v>
       </c>
-      <c r="I92" s="16" t="inlineStr">
+      <c r="I92" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17202,7 +17437,7 @@
       <c r="H93" t="n">
         <v>46.26</v>
       </c>
-      <c r="I93" s="13" t="inlineStr">
+      <c r="I93" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -17247,7 +17482,7 @@
       <c r="H94" t="n">
         <v>39.75</v>
       </c>
-      <c r="I94" s="13" t="inlineStr">
+      <c r="I94" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -17292,7 +17527,7 @@
       <c r="H95" t="n">
         <v>49.01</v>
       </c>
-      <c r="I95" s="16" t="inlineStr">
+      <c r="I95" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17337,7 +17572,7 @@
       <c r="H96" t="n">
         <v>58.56</v>
       </c>
-      <c r="I96" s="16" t="inlineStr">
+      <c r="I96" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17382,7 +17617,7 @@
       <c r="H97" t="n">
         <v>69.53</v>
       </c>
-      <c r="I97" s="16" t="inlineStr">
+      <c r="I97" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17427,7 +17662,7 @@
       <c r="H98" t="n">
         <v>59.5</v>
       </c>
-      <c r="I98" s="13" t="inlineStr">
+      <c r="I98" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -17472,7 +17707,7 @@
       <c r="H99" t="n">
         <v>61.45</v>
       </c>
-      <c r="I99" s="16" t="inlineStr">
+      <c r="I99" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17517,7 +17752,7 @@
       <c r="H100" t="n">
         <v>74.29000000000001</v>
       </c>
-      <c r="I100" s="16" t="inlineStr">
+      <c r="I100" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17562,7 +17797,7 @@
       <c r="H101" t="n">
         <v>79.92</v>
       </c>
-      <c r="I101" s="16" t="inlineStr">
+      <c r="I101" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17607,7 +17842,7 @@
       <c r="H102" t="n">
         <v>51.14</v>
       </c>
-      <c r="I102" s="16" t="inlineStr">
+      <c r="I102" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17652,7 +17887,7 @@
       <c r="H103" t="n">
         <v>25.67</v>
       </c>
-      <c r="I103" s="13" t="inlineStr">
+      <c r="I103" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -17697,7 +17932,7 @@
       <c r="H104" t="n">
         <v>41.8</v>
       </c>
-      <c r="I104" s="16" t="inlineStr">
+      <c r="I104" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17742,7 +17977,7 @@
       <c r="H105" t="n">
         <v>64.2</v>
       </c>
-      <c r="I105" s="16" t="inlineStr">
+      <c r="I105" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17787,7 +18022,7 @@
       <c r="H106" t="n">
         <v>78.48</v>
       </c>
-      <c r="I106" s="16" t="inlineStr">
+      <c r="I106" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17832,7 +18067,7 @@
       <c r="H107" t="n">
         <v>51.46</v>
       </c>
-      <c r="I107" s="13" t="inlineStr">
+      <c r="I107" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -17877,7 +18112,7 @@
       <c r="H108" t="n">
         <v>49.29</v>
       </c>
-      <c r="I108" s="16" t="inlineStr">
+      <c r="I108" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17922,7 +18157,7 @@
       <c r="H109" t="n">
         <v>68.43000000000001</v>
       </c>
-      <c r="I109" s="16" t="inlineStr">
+      <c r="I109" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -17967,7 +18202,7 @@
       <c r="H110" t="n">
         <v>61.41</v>
       </c>
-      <c r="I110" s="13" t="inlineStr">
+      <c r="I110" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -18012,7 +18247,7 @@
       <c r="H111" t="n">
         <v>71.11</v>
       </c>
-      <c r="I111" s="16" t="inlineStr">
+      <c r="I111" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18057,7 +18292,7 @@
       <c r="H112" t="n">
         <v>55.55</v>
       </c>
-      <c r="I112" s="16" t="inlineStr">
+      <c r="I112" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18102,7 +18337,7 @@
       <c r="H113" t="n">
         <v>95.13</v>
       </c>
-      <c r="I113" s="16" t="inlineStr">
+      <c r="I113" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18147,7 +18382,7 @@
       <c r="H114" t="n">
         <v>76.65000000000001</v>
       </c>
-      <c r="I114" s="16" t="inlineStr">
+      <c r="I114" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18192,7 +18427,7 @@
       <c r="H115" t="n">
         <v>49.48</v>
       </c>
-      <c r="I115" s="13" t="inlineStr">
+      <c r="I115" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -18237,7 +18472,7 @@
       <c r="H116" t="n">
         <v>54.93</v>
       </c>
-      <c r="I116" s="16" t="inlineStr">
+      <c r="I116" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18282,7 +18517,7 @@
       <c r="H117" t="n">
         <v>60.07</v>
       </c>
-      <c r="I117" s="16" t="inlineStr">
+      <c r="I117" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18327,7 +18562,7 @@
       <c r="H118" t="n">
         <v>52.56</v>
       </c>
-      <c r="I118" s="16" t="inlineStr">
+      <c r="I118" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18372,7 +18607,7 @@
       <c r="H119" t="n">
         <v>49.62</v>
       </c>
-      <c r="I119" s="16" t="inlineStr">
+      <c r="I119" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18417,7 +18652,7 @@
       <c r="H120" t="n">
         <v>46.97</v>
       </c>
-      <c r="I120" s="16" t="inlineStr">
+      <c r="I120" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18462,7 +18697,7 @@
       <c r="H121" t="n">
         <v>66.04000000000001</v>
       </c>
-      <c r="I121" s="13" t="inlineStr">
+      <c r="I121" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -18507,7 +18742,7 @@
       <c r="H122" t="n">
         <v>34.74</v>
       </c>
-      <c r="I122" s="13" t="inlineStr">
+      <c r="I122" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -18552,7 +18787,7 @@
       <c r="H123" t="n">
         <v>77.02</v>
       </c>
-      <c r="I123" s="16" t="inlineStr">
+      <c r="I123" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18597,7 +18832,7 @@
       <c r="H124" t="n">
         <v>60.13</v>
       </c>
-      <c r="I124" s="16" t="inlineStr">
+      <c r="I124" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18642,7 +18877,7 @@
       <c r="H125" t="n">
         <v>38.8</v>
       </c>
-      <c r="I125" s="16" t="inlineStr">
+      <c r="I125" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18687,7 +18922,7 @@
       <c r="H126" t="n">
         <v>75.56999999999999</v>
       </c>
-      <c r="I126" s="16" t="inlineStr">
+      <c r="I126" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18732,7 +18967,7 @@
       <c r="H127" t="n">
         <v>35.37</v>
       </c>
-      <c r="I127" s="13" t="inlineStr">
+      <c r="I127" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -18777,7 +19012,7 @@
       <c r="H128" t="n">
         <v>46.68</v>
       </c>
-      <c r="I128" s="16" t="inlineStr">
+      <c r="I128" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18822,7 +19057,7 @@
       <c r="H129" t="n">
         <v>29.02</v>
       </c>
-      <c r="I129" s="13" t="inlineStr">
+      <c r="I129" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -18867,7 +19102,7 @@
       <c r="H130" t="n">
         <v>56.74</v>
       </c>
-      <c r="I130" s="16" t="inlineStr">
+      <c r="I130" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -18912,7 +19147,7 @@
       <c r="H131" t="n">
         <v>59.48</v>
       </c>
-      <c r="I131" s="13" t="inlineStr">
+      <c r="I131" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -18957,7 +19192,7 @@
       <c r="H132" t="n">
         <v>51.57</v>
       </c>
-      <c r="I132" s="16" t="inlineStr">
+      <c r="I132" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19002,7 +19237,7 @@
       <c r="H133" t="n">
         <v>51.5</v>
       </c>
-      <c r="I133" s="16" t="inlineStr">
+      <c r="I133" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19047,7 +19282,7 @@
       <c r="H134" t="n">
         <v>64.88</v>
       </c>
-      <c r="I134" s="16" t="inlineStr">
+      <c r="I134" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19092,7 +19327,7 @@
       <c r="H135" t="n">
         <v>46.56</v>
       </c>
-      <c r="I135" s="13" t="inlineStr">
+      <c r="I135" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -19137,7 +19372,7 @@
       <c r="H136" t="n">
         <v>55.8</v>
       </c>
-      <c r="I136" s="16" t="inlineStr">
+      <c r="I136" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19182,7 +19417,7 @@
       <c r="H137" t="n">
         <v>42.28</v>
       </c>
-      <c r="I137" s="13" t="inlineStr">
+      <c r="I137" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -19227,7 +19462,7 @@
       <c r="H138" t="n">
         <v>34.81</v>
       </c>
-      <c r="I138" s="13" t="inlineStr">
+      <c r="I138" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -19272,7 +19507,7 @@
       <c r="H139" t="n">
         <v>55.85</v>
       </c>
-      <c r="I139" s="16" t="inlineStr">
+      <c r="I139" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19317,7 +19552,7 @@
       <c r="H140" t="n">
         <v>79.02</v>
       </c>
-      <c r="I140" s="16" t="inlineStr">
+      <c r="I140" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19362,7 +19597,7 @@
       <c r="H141" t="n">
         <v>72.55</v>
       </c>
-      <c r="I141" s="16" t="inlineStr">
+      <c r="I141" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19407,7 +19642,7 @@
       <c r="H142" t="n">
         <v>40.36</v>
       </c>
-      <c r="I142" s="13" t="inlineStr">
+      <c r="I142" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -19452,7 +19687,7 @@
       <c r="H143" t="n">
         <v>46.14</v>
       </c>
-      <c r="I143" s="16" t="inlineStr">
+      <c r="I143" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19497,7 +19732,7 @@
       <c r="H144" t="n">
         <v>36.21</v>
       </c>
-      <c r="I144" s="13" t="inlineStr">
+      <c r="I144" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -19542,7 +19777,7 @@
       <c r="H145" t="n">
         <v>57.2</v>
       </c>
-      <c r="I145" s="16" t="inlineStr">
+      <c r="I145" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19587,7 +19822,7 @@
       <c r="H146" t="n">
         <v>43.28</v>
       </c>
-      <c r="I146" s="13" t="inlineStr">
+      <c r="I146" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -19632,7 +19867,7 @@
       <c r="H147" t="n">
         <v>54.8</v>
       </c>
-      <c r="I147" s="16" t="inlineStr">
+      <c r="I147" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19677,7 +19912,7 @@
       <c r="H148" t="n">
         <v>50.01</v>
       </c>
-      <c r="I148" s="16" t="inlineStr">
+      <c r="I148" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19722,7 +19957,7 @@
       <c r="H149" t="n">
         <v>51.7</v>
       </c>
-      <c r="I149" s="16" t="inlineStr">
+      <c r="I149" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19767,7 +20002,7 @@
       <c r="H150" t="n">
         <v>62.8</v>
       </c>
-      <c r="I150" s="16" t="inlineStr">
+      <c r="I150" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19812,7 +20047,7 @@
       <c r="H151" t="n">
         <v>80.95999999999999</v>
       </c>
-      <c r="I151" s="16" t="inlineStr">
+      <c r="I151" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19857,7 +20092,7 @@
       <c r="H152" t="n">
         <v>54.97</v>
       </c>
-      <c r="I152" s="13" t="inlineStr">
+      <c r="I152" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -19902,7 +20137,7 @@
       <c r="H153" t="n">
         <v>33.99</v>
       </c>
-      <c r="I153" s="13" t="inlineStr">
+      <c r="I153" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -19947,7 +20182,7 @@
       <c r="H154" t="n">
         <v>51.03</v>
       </c>
-      <c r="I154" s="16" t="inlineStr">
+      <c r="I154" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -19992,7 +20227,7 @@
       <c r="H155" t="n">
         <v>53.13</v>
       </c>
-      <c r="I155" s="13" t="inlineStr">
+      <c r="I155" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -20037,7 +20272,7 @@
       <c r="H156" t="n">
         <v>39.71</v>
       </c>
-      <c r="I156" s="13" t="inlineStr">
+      <c r="I156" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -20082,7 +20317,7 @@
       <c r="H157" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="I157" s="16" t="inlineStr">
+      <c r="I157" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20127,7 +20362,7 @@
       <c r="H158" t="n">
         <v>54.02</v>
       </c>
-      <c r="I158" s="16" t="inlineStr">
+      <c r="I158" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20172,7 +20407,7 @@
       <c r="H159" t="n">
         <v>48.84</v>
       </c>
-      <c r="I159" s="16" t="inlineStr">
+      <c r="I159" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20217,7 +20452,7 @@
       <c r="H160" t="n">
         <v>38.02</v>
       </c>
-      <c r="I160" s="13" t="inlineStr">
+      <c r="I160" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -20262,7 +20497,7 @@
       <c r="H161" t="n">
         <v>64.39</v>
       </c>
-      <c r="I161" s="16" t="inlineStr">
+      <c r="I161" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20307,7 +20542,7 @@
       <c r="H162" t="n">
         <v>78.34999999999999</v>
       </c>
-      <c r="I162" s="16" t="inlineStr">
+      <c r="I162" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20352,7 +20587,7 @@
       <c r="H163" t="n">
         <v>31.15</v>
       </c>
-      <c r="I163" s="13" t="inlineStr">
+      <c r="I163" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -20397,7 +20632,7 @@
       <c r="H164" t="n">
         <v>36.56</v>
       </c>
-      <c r="I164" s="13" t="inlineStr">
+      <c r="I164" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -20442,7 +20677,7 @@
       <c r="H165" t="n">
         <v>60.48</v>
       </c>
-      <c r="I165" s="13" t="inlineStr">
+      <c r="I165" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -20487,7 +20722,7 @@
       <c r="H166" t="n">
         <v>80.56999999999999</v>
       </c>
-      <c r="I166" s="16" t="inlineStr">
+      <c r="I166" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20532,7 +20767,7 @@
       <c r="H167" t="n">
         <v>67.69</v>
       </c>
-      <c r="I167" s="16" t="inlineStr">
+      <c r="I167" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20577,7 +20812,7 @@
       <c r="H168" t="n">
         <v>53.28</v>
       </c>
-      <c r="I168" s="16" t="inlineStr">
+      <c r="I168" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20622,7 +20857,7 @@
       <c r="H169" t="n">
         <v>47.72</v>
       </c>
-      <c r="I169" s="13" t="inlineStr">
+      <c r="I169" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -20667,7 +20902,7 @@
       <c r="H170" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="I170" s="16" t="inlineStr">
+      <c r="I170" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20712,7 +20947,7 @@
       <c r="H171" t="n">
         <v>65.62</v>
       </c>
-      <c r="I171" s="16" t="inlineStr">
+      <c r="I171" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20757,7 +20992,7 @@
       <c r="H172" t="n">
         <v>48.67</v>
       </c>
-      <c r="I172" s="16" t="inlineStr">
+      <c r="I172" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20802,7 +21037,7 @@
       <c r="H173" t="n">
         <v>53.03</v>
       </c>
-      <c r="I173" s="16" t="inlineStr">
+      <c r="I173" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20847,7 +21082,7 @@
       <c r="H174" t="n">
         <v>53.72</v>
       </c>
-      <c r="I174" s="13" t="inlineStr">
+      <c r="I174" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -20892,7 +21127,7 @@
       <c r="H175" t="n">
         <v>42.14</v>
       </c>
-      <c r="I175" s="16" t="inlineStr">
+      <c r="I175" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20937,7 +21172,7 @@
       <c r="H176" t="n">
         <v>60.57</v>
       </c>
-      <c r="I176" s="16" t="inlineStr">
+      <c r="I176" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -20982,7 +21217,7 @@
       <c r="H177" t="n">
         <v>75.2</v>
       </c>
-      <c r="I177" s="16" t="inlineStr">
+      <c r="I177" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21027,7 +21262,7 @@
       <c r="H178" t="n">
         <v>40.42</v>
       </c>
-      <c r="I178" s="13" t="inlineStr">
+      <c r="I178" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -21072,7 +21307,7 @@
       <c r="H179" t="n">
         <v>55.36</v>
       </c>
-      <c r="I179" s="13" t="inlineStr">
+      <c r="I179" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -21117,7 +21352,7 @@
       <c r="H180" t="n">
         <v>25.29</v>
       </c>
-      <c r="I180" s="13" t="inlineStr">
+      <c r="I180" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -21162,7 +21397,7 @@
       <c r="H181" t="n">
         <v>62.41</v>
       </c>
-      <c r="I181" s="16" t="inlineStr">
+      <c r="I181" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21207,7 +21442,7 @@
       <c r="H182" t="n">
         <v>64.44</v>
       </c>
-      <c r="I182" s="16" t="inlineStr">
+      <c r="I182" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21252,7 +21487,7 @@
       <c r="H183" t="n">
         <v>47.41</v>
       </c>
-      <c r="I183" s="13" t="inlineStr">
+      <c r="I183" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -21297,7 +21532,7 @@
       <c r="H184" t="n">
         <v>46.86</v>
       </c>
-      <c r="I184" s="16" t="inlineStr">
+      <c r="I184" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21342,7 +21577,7 @@
       <c r="H185" t="n">
         <v>42.33</v>
       </c>
-      <c r="I185" s="16" t="inlineStr">
+      <c r="I185" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21387,7 +21622,7 @@
       <c r="H186" t="n">
         <v>62.7</v>
       </c>
-      <c r="I186" s="16" t="inlineStr">
+      <c r="I186" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21432,7 +21667,7 @@
       <c r="H187" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="I187" s="13" t="inlineStr">
+      <c r="I187" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -21477,7 +21712,7 @@
       <c r="H188" t="n">
         <v>59.49</v>
       </c>
-      <c r="I188" s="13" t="inlineStr">
+      <c r="I188" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -21522,7 +21757,7 @@
       <c r="H189" t="n">
         <v>51.31</v>
       </c>
-      <c r="I189" s="16" t="inlineStr">
+      <c r="I189" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21567,7 +21802,7 @@
       <c r="H190" t="n">
         <v>43.72</v>
       </c>
-      <c r="I190" s="16" t="inlineStr">
+      <c r="I190" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21612,7 +21847,7 @@
       <c r="H191" t="n">
         <v>54.93</v>
       </c>
-      <c r="I191" s="16" t="inlineStr">
+      <c r="I191" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21657,7 +21892,7 @@
       <c r="H192" t="n">
         <v>52.75</v>
       </c>
-      <c r="I192" s="16" t="inlineStr">
+      <c r="I192" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21702,7 +21937,7 @@
       <c r="H193" t="n">
         <v>70.55</v>
       </c>
-      <c r="I193" s="16" t="inlineStr">
+      <c r="I193" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21747,7 +21982,7 @@
       <c r="H194" t="n">
         <v>65.06999999999999</v>
       </c>
-      <c r="I194" s="16" t="inlineStr">
+      <c r="I194" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21792,7 +22027,7 @@
       <c r="H195" t="n">
         <v>59.01</v>
       </c>
-      <c r="I195" s="16" t="inlineStr">
+      <c r="I195" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21837,7 +22072,7 @@
       <c r="H196" t="n">
         <v>62.95</v>
       </c>
-      <c r="I196" s="16" t="inlineStr">
+      <c r="I196" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21882,7 +22117,7 @@
       <c r="H197" t="n">
         <v>50.83</v>
       </c>
-      <c r="I197" s="13" t="inlineStr">
+      <c r="I197" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -21927,7 +22162,7 @@
       <c r="H198" t="n">
         <v>79.06</v>
       </c>
-      <c r="I198" s="16" t="inlineStr">
+      <c r="I198" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -21972,7 +22207,7 @@
       <c r="H199" t="n">
         <v>43.89</v>
       </c>
-      <c r="I199" s="13" t="inlineStr">
+      <c r="I199" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22017,7 +22252,7 @@
       <c r="H200" t="n">
         <v>33.05</v>
       </c>
-      <c r="I200" s="13" t="inlineStr">
+      <c r="I200" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22062,7 +22297,7 @@
       <c r="H201" t="n">
         <v>75.3</v>
       </c>
-      <c r="I201" s="16" t="inlineStr">
+      <c r="I201" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22107,7 +22342,7 @@
       <c r="H202" t="n">
         <v>61.14</v>
       </c>
-      <c r="I202" s="16" t="inlineStr">
+      <c r="I202" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22152,7 +22387,7 @@
       <c r="H203" t="n">
         <v>50.51</v>
       </c>
-      <c r="I203" s="13" t="inlineStr">
+      <c r="I203" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22197,7 +22432,7 @@
       <c r="H204" t="n">
         <v>63.36</v>
       </c>
-      <c r="I204" s="16" t="inlineStr">
+      <c r="I204" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22242,7 +22477,7 @@
       <c r="H205" t="n">
         <v>53.1</v>
       </c>
-      <c r="I205" s="13" t="inlineStr">
+      <c r="I205" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22287,7 +22522,7 @@
       <c r="H206" t="n">
         <v>44.86</v>
       </c>
-      <c r="I206" s="16" t="inlineStr">
+      <c r="I206" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22332,7 +22567,7 @@
       <c r="H207" t="n">
         <v>55.29</v>
       </c>
-      <c r="I207" s="16" t="inlineStr">
+      <c r="I207" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22377,7 +22612,7 @@
       <c r="H208" t="n">
         <v>50.99</v>
       </c>
-      <c r="I208" s="16" t="inlineStr">
+      <c r="I208" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22422,7 +22657,7 @@
       <c r="H209" t="n">
         <v>47.33</v>
       </c>
-      <c r="I209" s="16" t="inlineStr">
+      <c r="I209" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22467,7 +22702,7 @@
       <c r="H210" t="n">
         <v>36.72</v>
       </c>
-      <c r="I210" s="13" t="inlineStr">
+      <c r="I210" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22512,7 +22747,7 @@
       <c r="H211" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="I211" s="16" t="inlineStr">
+      <c r="I211" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22557,7 +22792,7 @@
       <c r="H212" t="n">
         <v>59.59</v>
       </c>
-      <c r="I212" s="13" t="inlineStr">
+      <c r="I212" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22602,7 +22837,7 @@
       <c r="H213" t="n">
         <v>46.81</v>
       </c>
-      <c r="I213" s="13" t="inlineStr">
+      <c r="I213" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22647,7 +22882,7 @@
       <c r="H214" t="n">
         <v>33.24</v>
       </c>
-      <c r="I214" s="13" t="inlineStr">
+      <c r="I214" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22692,7 +22927,7 @@
       <c r="H215" t="n">
         <v>35.46</v>
       </c>
-      <c r="I215" s="13" t="inlineStr">
+      <c r="I215" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -22737,7 +22972,7 @@
       <c r="H216" t="n">
         <v>66.69</v>
       </c>
-      <c r="I216" s="16" t="inlineStr">
+      <c r="I216" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22782,7 +23017,7 @@
       <c r="H217" t="n">
         <v>60.89</v>
       </c>
-      <c r="I217" s="16" t="inlineStr">
+      <c r="I217" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22827,7 +23062,7 @@
       <c r="H218" t="n">
         <v>32.84</v>
       </c>
-      <c r="I218" s="16" t="inlineStr">
+      <c r="I218" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22872,7 +23107,7 @@
       <c r="H219" t="n">
         <v>55.55</v>
       </c>
-      <c r="I219" s="16" t="inlineStr">
+      <c r="I219" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22917,7 +23152,7 @@
       <c r="H220" t="n">
         <v>41.8</v>
       </c>
-      <c r="I220" s="16" t="inlineStr">
+      <c r="I220" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -22962,7 +23197,7 @@
       <c r="H221" t="n">
         <v>38.99</v>
       </c>
-      <c r="I221" s="13" t="inlineStr">
+      <c r="I221" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23007,7 +23242,7 @@
       <c r="H222" t="n">
         <v>41.92</v>
       </c>
-      <c r="I222" s="16" t="inlineStr">
+      <c r="I222" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23052,7 +23287,7 @@
       <c r="H223" t="n">
         <v>43</v>
       </c>
-      <c r="I223" s="16" t="inlineStr">
+      <c r="I223" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23097,7 +23332,7 @@
       <c r="H224" t="n">
         <v>65.41</v>
       </c>
-      <c r="I224" s="16" t="inlineStr">
+      <c r="I224" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23142,7 +23377,7 @@
       <c r="H225" t="n">
         <v>36.76</v>
       </c>
-      <c r="I225" s="13" t="inlineStr">
+      <c r="I225" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23187,7 +23422,7 @@
       <c r="H226" t="n">
         <v>46.4</v>
       </c>
-      <c r="I226" s="13" t="inlineStr">
+      <c r="I226" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23232,7 +23467,7 @@
       <c r="H227" t="n">
         <v>37.29</v>
       </c>
-      <c r="I227" s="13" t="inlineStr">
+      <c r="I227" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23277,7 +23512,7 @@
       <c r="H228" t="n">
         <v>47.21</v>
       </c>
-      <c r="I228" s="13" t="inlineStr">
+      <c r="I228" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23322,7 +23557,7 @@
       <c r="H229" t="n">
         <v>38.31</v>
       </c>
-      <c r="I229" s="16" t="inlineStr">
+      <c r="I229" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23367,7 +23602,7 @@
       <c r="H230" t="n">
         <v>66.63</v>
       </c>
-      <c r="I230" s="16" t="inlineStr">
+      <c r="I230" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23412,7 +23647,7 @@
       <c r="H231" t="n">
         <v>66.77</v>
       </c>
-      <c r="I231" s="16" t="inlineStr">
+      <c r="I231" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23457,7 +23692,7 @@
       <c r="H232" t="n">
         <v>51.51</v>
       </c>
-      <c r="I232" s="13" t="inlineStr">
+      <c r="I232" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23502,7 +23737,7 @@
       <c r="H233" t="n">
         <v>50.99</v>
       </c>
-      <c r="I233" s="13" t="inlineStr">
+      <c r="I233" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23547,7 +23782,7 @@
       <c r="H234" t="n">
         <v>55.12</v>
       </c>
-      <c r="I234" s="16" t="inlineStr">
+      <c r="I234" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23592,7 +23827,7 @@
       <c r="H235" t="n">
         <v>59.23</v>
       </c>
-      <c r="I235" s="16" t="inlineStr">
+      <c r="I235" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23637,7 +23872,7 @@
       <c r="H236" t="n">
         <v>44.51</v>
       </c>
-      <c r="I236" s="13" t="inlineStr">
+      <c r="I236" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23682,7 +23917,7 @@
       <c r="H237" t="n">
         <v>52.01</v>
       </c>
-      <c r="I237" s="16" t="inlineStr">
+      <c r="I237" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23727,7 +23962,7 @@
       <c r="H238" t="n">
         <v>31.29</v>
       </c>
-      <c r="I238" s="13" t="inlineStr">
+      <c r="I238" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23772,7 +24007,7 @@
       <c r="H239" t="n">
         <v>36.83</v>
       </c>
-      <c r="I239" s="13" t="inlineStr">
+      <c r="I239" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23817,7 +24052,7 @@
       <c r="H240" t="n">
         <v>58.53</v>
       </c>
-      <c r="I240" s="16" t="inlineStr">
+      <c r="I240" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23862,7 +24097,7 @@
       <c r="H241" t="n">
         <v>48.02</v>
       </c>
-      <c r="I241" s="13" t="inlineStr">
+      <c r="I241" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23907,7 +24142,7 @@
       <c r="H242" t="n">
         <v>24.77</v>
       </c>
-      <c r="I242" s="13" t="inlineStr">
+      <c r="I242" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -23952,7 +24187,7 @@
       <c r="H243" t="n">
         <v>40.84</v>
       </c>
-      <c r="I243" s="16" t="inlineStr">
+      <c r="I243" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -23997,7 +24232,7 @@
       <c r="H244" t="n">
         <v>41.37</v>
       </c>
-      <c r="I244" s="13" t="inlineStr">
+      <c r="I244" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24042,7 +24277,7 @@
       <c r="H245" t="n">
         <v>51.54</v>
       </c>
-      <c r="I245" s="16" t="inlineStr">
+      <c r="I245" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24087,7 +24322,7 @@
       <c r="H246" t="n">
         <v>50.62</v>
       </c>
-      <c r="I246" s="16" t="inlineStr">
+      <c r="I246" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24132,7 +24367,7 @@
       <c r="H247" t="n">
         <v>46.18</v>
       </c>
-      <c r="I247" s="16" t="inlineStr">
+      <c r="I247" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24177,7 +24412,7 @@
       <c r="H248" t="n">
         <v>35.88</v>
       </c>
-      <c r="I248" s="13" t="inlineStr">
+      <c r="I248" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24222,7 +24457,7 @@
       <c r="H249" t="n">
         <v>50.8</v>
       </c>
-      <c r="I249" s="16" t="inlineStr">
+      <c r="I249" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24267,7 +24502,7 @@
       <c r="H250" t="n">
         <v>18.28</v>
       </c>
-      <c r="I250" s="13" t="inlineStr">
+      <c r="I250" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24312,7 +24547,7 @@
       <c r="H251" t="n">
         <v>50.56</v>
       </c>
-      <c r="I251" s="16" t="inlineStr">
+      <c r="I251" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24357,7 +24592,7 @@
       <c r="H252" t="n">
         <v>46.83</v>
       </c>
-      <c r="I252" s="13" t="inlineStr">
+      <c r="I252" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24402,7 +24637,7 @@
       <c r="H253" t="n">
         <v>35.92</v>
       </c>
-      <c r="I253" s="13" t="inlineStr">
+      <c r="I253" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24447,7 +24682,7 @@
       <c r="H254" t="n">
         <v>44.07</v>
       </c>
-      <c r="I254" s="13" t="inlineStr">
+      <c r="I254" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24492,7 +24727,7 @@
       <c r="H255" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="I255" s="16" t="inlineStr">
+      <c r="I255" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24537,7 +24772,7 @@
       <c r="H256" t="n">
         <v>49.59</v>
       </c>
-      <c r="I256" s="13" t="inlineStr">
+      <c r="I256" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24582,7 +24817,7 @@
       <c r="H257" t="n">
         <v>59.96</v>
       </c>
-      <c r="I257" s="16" t="inlineStr">
+      <c r="I257" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24627,7 +24862,7 @@
       <c r="H258" t="n">
         <v>28.24</v>
       </c>
-      <c r="I258" s="16" t="inlineStr">
+      <c r="I258" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24672,7 +24907,7 @@
       <c r="H259" t="n">
         <v>39.4</v>
       </c>
-      <c r="I259" s="13" t="inlineStr">
+      <c r="I259" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24717,7 +24952,7 @@
       <c r="H260" t="n">
         <v>42.67</v>
       </c>
-      <c r="I260" s="13" t="inlineStr">
+      <c r="I260" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24762,7 +24997,7 @@
       <c r="H261" t="n">
         <v>35.96</v>
       </c>
-      <c r="I261" s="13" t="inlineStr">
+      <c r="I261" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24807,7 +25042,7 @@
       <c r="H262" t="n">
         <v>59.29</v>
       </c>
-      <c r="I262" s="16" t="inlineStr">
+      <c r="I262" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24852,7 +25087,7 @@
       <c r="H263" t="n">
         <v>52.23</v>
       </c>
-      <c r="I263" s="16" t="inlineStr">
+      <c r="I263" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24897,7 +25132,7 @@
       <c r="H264" t="n">
         <v>23.61</v>
       </c>
-      <c r="I264" s="13" t="inlineStr">
+      <c r="I264" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -24942,7 +25177,7 @@
       <c r="H265" t="n">
         <v>56.13</v>
       </c>
-      <c r="I265" s="16" t="inlineStr">
+      <c r="I265" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -24987,7 +25222,7 @@
       <c r="H266" t="n">
         <v>52.46</v>
       </c>
-      <c r="I266" s="16" t="inlineStr">
+      <c r="I266" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -25032,7 +25267,7 @@
       <c r="H267" t="n">
         <v>41.77</v>
       </c>
-      <c r="I267" s="16" t="inlineStr">
+      <c r="I267" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -25077,7 +25312,7 @@
       <c r="H268" t="n">
         <v>72.36</v>
       </c>
-      <c r="I268" s="16" t="inlineStr">
+      <c r="I268" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -25122,7 +25357,7 @@
       <c r="H269" t="n">
         <v>46</v>
       </c>
-      <c r="I269" s="13" t="inlineStr">
+      <c r="I269" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25167,7 +25402,7 @@
       <c r="H270" t="n">
         <v>45.87</v>
       </c>
-      <c r="I270" s="13" t="inlineStr">
+      <c r="I270" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25212,7 +25447,7 @@
       <c r="H271" t="n">
         <v>60.96</v>
       </c>
-      <c r="I271" s="16" t="inlineStr">
+      <c r="I271" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -25257,7 +25492,7 @@
       <c r="H272" t="n">
         <v>52.93</v>
       </c>
-      <c r="I272" s="16" t="inlineStr">
+      <c r="I272" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -25302,7 +25537,7 @@
       <c r="H273" t="n">
         <v>47.05</v>
       </c>
-      <c r="I273" s="13" t="inlineStr">
+      <c r="I273" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25347,7 +25582,7 @@
       <c r="H274" t="n">
         <v>51.05</v>
       </c>
-      <c r="I274" s="16" t="inlineStr">
+      <c r="I274" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -25392,7 +25627,7 @@
       <c r="H275" t="n">
         <v>59.65</v>
       </c>
-      <c r="I275" s="13" t="inlineStr">
+      <c r="I275" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25437,7 +25672,7 @@
       <c r="H276" t="n">
         <v>42.86</v>
       </c>
-      <c r="I276" s="16" t="inlineStr">
+      <c r="I276" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -25482,7 +25717,7 @@
       <c r="H277" t="n">
         <v>42.52</v>
       </c>
-      <c r="I277" s="13" t="inlineStr">
+      <c r="I277" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25527,7 +25762,7 @@
       <c r="H278" t="n">
         <v>32.26</v>
       </c>
-      <c r="I278" s="13" t="inlineStr">
+      <c r="I278" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25572,7 +25807,7 @@
       <c r="H279" t="n">
         <v>62.7</v>
       </c>
-      <c r="I279" s="13" t="inlineStr">
+      <c r="I279" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25617,7 +25852,7 @@
       <c r="H280" t="n">
         <v>40.23</v>
       </c>
-      <c r="I280" s="13" t="inlineStr">
+      <c r="I280" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25662,7 +25897,7 @@
       <c r="H281" t="n">
         <v>54.78</v>
       </c>
-      <c r="I281" s="16" t="inlineStr">
+      <c r="I281" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -25707,7 +25942,7 @@
       <c r="H282" t="n">
         <v>50.74</v>
       </c>
-      <c r="I282" s="13" t="inlineStr">
+      <c r="I282" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25752,7 +25987,7 @@
       <c r="H283" t="n">
         <v>65.8</v>
       </c>
-      <c r="I283" s="13" t="inlineStr">
+      <c r="I283" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -25797,7 +26032,7 @@
       <c r="H284" t="n">
         <v>42.58</v>
       </c>
-      <c r="I284" s="16" t="inlineStr">
+      <c r="I284" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.39</v>
+        <v>0.395</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0395</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>9271000</v>
+        <v>12961000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.84999999999999</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.39高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破；RSI 66.85接近超买区，信号偏强但需留意短线过热。</t>
+          <t>现价0.395高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破。RSI 69.51接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -614,266 +614,315 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>0369</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>JSSOLAR</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>6199400</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>71.13</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>现价RM 0.25高于50日均线RM 0.197，EMA20与SAR均呈多头，T3形态突破。但RSI达71.13，已进入超买区，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5667400</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>RSI 81.89已处超买区，现价高于50日均线约29.8%，EMA20与SAR多头信号虽一致，但短线过热。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>0455</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BUSCAP</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.555</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.0673</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>1586900</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H3" s="2" t="n">
+      <c r="F5" s="5" t="n">
+        <v>2564800</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>63.85</v>
       </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.493</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>0.395</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>现价0.555高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破。RSI 63.85未超买，信号技术面偏可靠。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0041</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AIMAX</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>251394100</v>
-      </c>
-      <c r="G4" s="12" t="n"/>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="14" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7079</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TWL</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>26942700</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H5" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>现价0.555高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破；RSI 63.85偏强但未超买，信号技术面较可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>-0.0263</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>26672600</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H6" t="n">
-        <v>22.21</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="14" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1160600</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>73.56</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>现价0.895高于50日均线0.794，EMA20与SAR均呈多头，T3形态突破；但RSI达73.56，已进入超买区，信号可靠性需留意短线过热。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5243</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VELESTO</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.0217</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>22413600</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="H7" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" s="14" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>20625800</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>现价0.84高于50日均线0.684，EMA20与SAR均呈多头，T3形态突破。但RSI达71.89，已进入超买区，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7192</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.008399999999999999</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>20309800</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H8" t="n">
-        <v>73.97</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" s="14" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1147100</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3突破有效；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -883,40 +932,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.0083</v>
+        <v>0.015</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>17256000</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H9" t="n">
-        <v>59.08</v>
-      </c>
+        <v>253892200</v>
+      </c>
+      <c r="G9" s="12" t="n"/>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>4.494</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
     </row>
@@ -928,39 +968,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.02</v>
+        <v>0.19</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>15315300</v>
+        <v>50076000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H10" t="n">
-        <v>31.96</v>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.61</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.279</v>
+        <v>0.284</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.33</v>
+        <v>0.502</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -973,28 +1013,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.025</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>15208100</v>
+        <v>27142700</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.36</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
-        <v>64.27</v>
+        <v>51.85</v>
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
@@ -1002,10 +1042,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.74</v>
+        <v>0.025</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.024</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1018,39 +1058,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14478400</v>
+        <v>24137800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="H12" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.72</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.053</v>
+        <v>0.241</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.043</v>
+        <v>0.25</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1063,39 +1103,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.305</v>
+        <v>4.83</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0469</v>
+        <v>-0.0021</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13448000</v>
+        <v>22991400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="H13" t="n">
-        <v>59.16</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.51</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.279</v>
+        <v>4.723</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.275</v>
+        <v>4.495</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1108,28 +1148,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>12823700</v>
+        <v>20606100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H14" t="n">
-        <v>53.3</v>
+        <v>71.34</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
@@ -1137,10 +1177,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.231</v>
+        <v>0.543</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.232</v>
+        <v>0.491</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1153,28 +1193,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.475</v>
+        <v>0.24</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-0.0104</v>
+        <v>-0.04</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10559200</v>
+        <v>17831100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="H15" t="n">
-        <v>52.83</v>
+        <v>30.84</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1182,10 +1222,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.468</v>
+        <v>0.279</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1198,28 +1238,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.84</v>
+        <v>0.785</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.0279</v>
+        <v>0.0064</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10465100</v>
+        <v>17341300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H16" t="n">
-        <v>64.33</v>
+        <v>64.27</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1227,10 +1267,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.725</v>
+        <v>0.74</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.51</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1243,28 +1283,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0.1271</v>
+        <v>0.155</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10306700</v>
+        <v>16073700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.31</v>
+        <v>0.78</v>
       </c>
       <c r="H17" t="n">
-        <v>95.67</v>
+        <v>44.71</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1272,10 +1312,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.841</v>
+        <v>0.156</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.722</v>
+        <v>0.16</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1288,39 +1328,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0.0145</v>
+        <v>0.31</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>9856300</v>
+        <v>15444000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.62</v>
+        <v>0.95</v>
       </c>
       <c r="H18" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.04</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2.132</v>
+        <v>0.28</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2.059</v>
+        <v>0.275</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1333,39 +1373,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.095</v>
+        <v>2.1</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0.0556</v>
+        <v>0.0145</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9816800</v>
+        <v>14869000</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1.71</v>
+        <v>0.93</v>
       </c>
       <c r="H19" t="n">
-        <v>79.43000000000001</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.078</v>
+        <v>2.132</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.067</v>
+        <v>2.059</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1378,39 +1418,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.795</v>
+        <v>0.055</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9332800</v>
+        <v>14638400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.72</v>
+        <v>1.66</v>
       </c>
       <c r="H20" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.043</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1423,39 +1463,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>-0.0125</v>
+        <v>0.795</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9110800</v>
+        <v>13417000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.19</v>
+        <v>1.03</v>
       </c>
       <c r="H21" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.314</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.178</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1468,28 +1508,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0.09320000000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8538300</v>
+        <v>13271900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.41</v>
+        <v>2.98</v>
       </c>
       <c r="H22" t="n">
-        <v>44.71</v>
+        <v>95.37</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1497,10 +1537,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.156</v>
+        <v>0.837</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.16</v>
+        <v>0.721</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1513,39 +1553,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8301600</v>
+        <v>13049300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H23" t="n">
-        <v>25.94</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.17</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.644</v>
+        <v>0.313</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.863</v>
+        <v>0.178</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1558,39 +1598,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.425</v>
+        <v>0.24</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.0241</v>
+        <v>0.0213</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7862800</v>
+        <v>12948100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.34</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>65.23999999999999</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.381</v>
+        <v>0.232</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.318</v>
+        <v>0.233</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1603,28 +1643,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.95</v>
+        <v>1.86</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.027</v>
+        <v>0.0391</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7160400</v>
+        <v>12406900</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2.03</v>
+        <v>0.48</v>
       </c>
       <c r="H25" t="n">
-        <v>78.73</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
@@ -1632,10 +1672,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.878</v>
+        <v>1.727</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.85</v>
+        <v>1.511</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1648,39 +1688,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>-0.0303</v>
+        <v>-0.0435</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7049700</v>
+        <v>11968400</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
-        <v>32.54</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.25</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K26" s="9" t="n">
         <v>0.183</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>0.224</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1693,28 +1733,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.765</v>
+        <v>0.31</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0159</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6896000</v>
+        <v>11685300</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H27" t="n">
-        <v>45.47</v>
+        <v>59.8</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1722,10 +1762,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.773</v>
+        <v>0.303</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.774</v>
+        <v>0.29</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1738,28 +1778,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6700800</v>
+        <v>11520400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
       <c r="H28" t="n">
-        <v>71.51000000000001</v>
+        <v>50.88</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1767,10 +1807,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.142</v>
+        <v>0.468</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.114</v>
+        <v>0.47</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1783,39 +1823,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.775</v>
+        <v>0.53</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>0.0265</v>
+        <v>0.0095</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6594000</v>
+        <v>10958200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1.27</v>
+        <v>0.28</v>
       </c>
       <c r="H29" t="n">
-        <v>71.29000000000001</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.92</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.68</v>
+        <v>0.645</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.608</v>
+        <v>0.863</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1828,28 +1868,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.095</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6104500</v>
+        <v>10111800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.15</v>
+        <v>1.77</v>
       </c>
       <c r="H30" t="n">
-        <v>49.56</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
@@ -1857,10 +1897,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.159</v>
+        <v>0.078</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.148</v>
+        <v>0.067</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1873,39 +1913,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>-0.0159</v>
+        <v>0.45</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5960800</v>
+        <v>9801000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.31</v>
+        <v>1.26</v>
       </c>
       <c r="H31" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.303</v>
+        <v>0.444</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.29</v>
+        <v>0.403</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1927,19 +1967,19 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.0239</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5923200</v>
+        <v>9685400</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H32" t="n">
-        <v>69.65000000000001</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
@@ -1947,10 +1987,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.843</v>
+        <v>2.848</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.701</v>
+        <v>2.702</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1963,39 +2003,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>1.36</v>
+        <v>0.765</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>-0.0216</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5868200</v>
+        <v>9656000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H33" t="n">
-        <v>49.51</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.47</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.384</v>
+        <v>0.773</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.288</v>
+        <v>0.774</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2008,33 +2048,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>2.85</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0.1004</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5841100</v>
+        <v>9558900</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="9" t="n"/>
+        <v>1.49</v>
+      </c>
+      <c r="H34" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>2.606</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>2.484</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
     </row>
@@ -2046,39 +2093,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.775</v>
+        <v>0.43</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0361</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5682000</v>
+        <v>8859800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="H35" t="n">
-        <v>65.42</v>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.08</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.698</v>
+        <v>0.381</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.318</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2091,28 +2138,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.865</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5672400</v>
+        <v>8816600</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.88</v>
+        <v>0.49</v>
       </c>
       <c r="H36" t="n">
-        <v>63.03</v>
+        <v>45.91</v>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
@@ -2120,10 +2167,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>2.599</v>
+        <v>0.868</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>2.483</v>
+        <v>0.871</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2136,39 +2183,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.165</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5443000</v>
+        <v>8459100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="H37" t="n">
-        <v>95.37</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.16</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.262</v>
+        <v>0.183</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.218</v>
+        <v>0.224</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2181,28 +2228,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.225</v>
+        <v>0.76</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.0066</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5393700</v>
+        <v>8368700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.37</v>
+        <v>1.61</v>
       </c>
       <c r="H38" t="n">
-        <v>65.45</v>
+        <v>69.72</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2210,10 +2257,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.196</v>
+        <v>0.678</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.171</v>
+        <v>0.607</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2226,28 +2273,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>-0.0063</v>
+        <v>0.95</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0.027</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5003300</v>
+        <v>7831700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.48</v>
+        <v>2.22</v>
       </c>
       <c r="H39" t="n">
-        <v>47.18</v>
+        <v>78.73</v>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
@@ -2255,10 +2302,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.803</v>
+        <v>0.878</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.806</v>
+        <v>0.85</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2271,28 +2318,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4974100</v>
+        <v>7785600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="H40" t="n">
-        <v>54.5</v>
+        <v>44.21</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2300,10 +2347,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.103</v>
+        <v>0.197</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.096</v>
+        <v>0.196</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2316,39 +2363,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0.0169</v>
+        <v>1.33</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>-0.0432</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4827800</v>
+        <v>7619000</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="H41" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.67</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.274</v>
+        <v>1.381</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.269</v>
+        <v>1.287</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2361,39 +2408,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0.0168</v>
+        <v>0.165</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4758300</v>
+        <v>7393400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="H42" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.51000000000001</v>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.608</v>
+        <v>0.142</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.603</v>
+        <v>0.114</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2406,28 +2453,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.155</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4400300</v>
+        <v>6720100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.78</v>
+        <v>0.16</v>
       </c>
       <c r="H43" t="n">
-        <v>86.31</v>
+        <v>49.56</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2435,10 +2482,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.766</v>
+        <v>0.159</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.751</v>
+        <v>0.148</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2451,40 +2498,33 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0.0138</v>
+        <v>0.265</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4296300</v>
+        <v>6681700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H44" t="n">
-        <v>63.13</v>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>5.673</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>5.099</v>
-      </c>
+        <v>0.38</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2496,28 +2536,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>2.39</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4171200</v>
+        <v>6430600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="H45" t="n">
-        <v>45.91</v>
+        <v>54.48</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2525,10 +2565,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.868</v>
+        <v>2.348</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.871</v>
+        <v>2.232</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2541,28 +2581,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.37</v>
+        <v>5.9</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>0.0128</v>
+        <v>0.0172</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3614600</v>
+        <v>6282400</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="H46" t="n">
-        <v>53.14</v>
+        <v>63.7</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2570,10 +2610,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.346</v>
+        <v>5.675</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.231</v>
+        <v>5.1</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2586,28 +2626,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>0.0452</v>
+        <v>0.0455</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3566100</v>
+        <v>6141000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>1.35</v>
+        <v>0.42</v>
       </c>
       <c r="H47" t="n">
-        <v>62.36</v>
+        <v>66.81</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -2615,10 +2655,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.758</v>
+        <v>0.197</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.74</v>
+        <v>0.171</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2631,28 +2671,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.22</v>
+        <v>0.605</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0233</v>
+        <v>0.0168</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3560900</v>
+        <v>6007200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H48" t="n">
-        <v>54.39</v>
+        <v>48.06</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2660,10 +2700,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.214</v>
+        <v>0.608</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.211</v>
+        <v>0.603</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2676,28 +2716,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.115</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3546000</v>
+        <v>5799300</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0.46</v>
       </c>
       <c r="H49" t="n">
-        <v>54.08</v>
+        <v>48.46</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2705,10 +2745,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.444</v>
+        <v>0.119</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.403</v>
+        <v>0.106</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2721,28 +2761,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>-0.0133</v>
+        <v>0.785</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3319200</v>
+        <v>5695800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>52.41</v>
+        <v>86.31</v>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
@@ -2750,10 +2790,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.367</v>
+        <v>0.766</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.366</v>
+        <v>0.751</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2766,28 +2806,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.545</v>
+        <v>0.8</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>0.0381</v>
+        <v>0.0323</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3239700</v>
+        <v>5522200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.22</v>
+        <v>2.09</v>
       </c>
       <c r="H51" t="n">
-        <v>69.40000000000001</v>
+        <v>60.75</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2795,10 +2835,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.467</v>
+        <v>0.757</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.397</v>
+        <v>0.74</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2811,28 +2851,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>-0.0086</v>
+        <v>0.335</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3209900</v>
+        <v>5512000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H52" t="n">
-        <v>46.5</v>
+        <v>95.37</v>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
@@ -2840,10 +2880,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.181</v>
+        <v>0.262</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>1.135</v>
+        <v>0.218</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2856,28 +2896,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>0.0667</v>
+        <v>0.295</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2948800</v>
+        <v>5082800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>4.97</v>
+        <v>0.84</v>
       </c>
       <c r="H53" t="n">
-        <v>68.40000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -2885,10 +2925,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.206</v>
+        <v>0.273</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.197</v>
+        <v>0.269</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2901,28 +2941,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>-0.0187</v>
+        <v>0.805</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2894700</v>
+        <v>5026400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.36</v>
+        <v>1.49</v>
       </c>
       <c r="H54" t="n">
-        <v>79.89</v>
+        <v>49.91</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2930,10 +2970,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.876</v>
+        <v>0.804</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.752</v>
+        <v>0.806</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2946,39 +2986,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.26</v>
+        <v>0.105</v>
       </c>
       <c r="E55" s="17" t="n">
-        <v>0.09570000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2819700</v>
+        <v>4983800</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>1.1</v>
       </c>
       <c r="H55" t="n">
-        <v>83.89</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.5</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.024</v>
+        <v>0.103</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.876</v>
+        <v>0.096</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2991,28 +3031,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>-0.0175</v>
+        <v>0.54</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2799000</v>
+        <v>4982500</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H56" t="n">
-        <v>58.3</v>
+        <v>68.8</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
@@ -3020,10 +3060,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.086</v>
+        <v>0.466</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.023</v>
+        <v>0.397</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3036,28 +3076,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>0.0513</v>
+        <v>1.04</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2793500</v>
+        <v>4372300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="H57" t="n">
-        <v>78.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
@@ -3065,10 +3105,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>3.484</v>
+        <v>0.875</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>3.203</v>
+        <v>0.752</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3081,28 +3121,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>4.15</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0.0641</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2753000</v>
+        <v>4104700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>4.75</v>
+        <v>0.93</v>
       </c>
       <c r="H58" t="n">
-        <v>55.34</v>
+        <v>79.69</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3110,10 +3150,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.253</v>
+        <v>3.488</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.264</v>
+        <v>3.204</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3126,33 +3166,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.29</v>
+        <v>0.225</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.0357</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2733400</v>
+        <v>4103400</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
+        <v>0.67</v>
+      </c>
+      <c r="H59" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>0.211</v>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
     </row>
@@ -3164,28 +3211,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>0.0367</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2720500</v>
+        <v>3990200</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0.32</v>
       </c>
       <c r="H60" t="n">
-        <v>50.52</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
@@ -3193,10 +3240,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.33</v>
+        <v>0.998</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.31</v>
+        <v>0.838</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3209,28 +3256,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
+        <v>2.86</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0.06320000000000001</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2705400</v>
+        <v>3932600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.13</v>
+        <v>1.74</v>
       </c>
       <c r="H61" t="n">
-        <v>85.45</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
@@ -3238,10 +3285,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.201</v>
+        <v>2.113</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.183</v>
+        <v>1.739</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3254,28 +3301,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>0.0161</v>
+        <v>0.365</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2576900</v>
+        <v>3731900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="H62" t="n">
-        <v>44.61</v>
+        <v>48.77</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
@@ -3283,10 +3330,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.321</v>
+        <v>0.367</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.339</v>
+        <v>0.366</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3299,33 +3346,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>0.0104</v>
+        <v>1.12</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2561000</v>
+        <v>3451900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
+      </c>
+      <c r="H63" t="n">
+        <v>58.3</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J63" s="9" t="n"/>
-      <c r="K63" s="9" t="n"/>
+      <c r="J63" s="9" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>1.023</v>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
     </row>
@@ -3337,28 +3391,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>0.0459</v>
+        <v>1.15</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2419900</v>
+        <v>3328100</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="H64" t="n">
-        <v>82.13</v>
+        <v>46.5</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3366,10 +3420,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.999</v>
+        <v>1.181</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.838</v>
+        <v>1.135</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3382,40 +3436,33 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0.0189</v>
+        <v>0.48</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2409300</v>
+        <v>3324200</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H65" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K65" s="9" t="n">
-        <v>0.473</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
     </row>
@@ -3427,39 +3474,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>-0.0077</v>
+        <v>0.535</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2387500</v>
+        <v>3292700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H66" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.16</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.332</v>
+        <v>0.519</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.452</v>
+        <v>0.473</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3472,39 +3519,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0.0208</v>
+        <v>3.44</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2379900</v>
+        <v>3259500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>2.07</v>
+        <v>0.72</v>
       </c>
       <c r="H67" t="n">
-        <v>75.09</v>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.09</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.217</v>
+        <v>3.623</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.207</v>
+        <v>3.707</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3517,39 +3564,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>0.052</v>
+        <v>0.77</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2342100</v>
+        <v>3146700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="H68" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.5</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.11</v>
+        <v>0.774</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.738</v>
+        <v>0.773</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3562,28 +3609,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0.09570000000000001</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2300100</v>
+        <v>3077000</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.25</v>
+        <v>1.2</v>
       </c>
       <c r="H69" t="n">
-        <v>63.73</v>
+        <v>83.89</v>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
@@ -3591,10 +3638,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.167</v>
+        <v>1.024</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.098</v>
+        <v>0.876</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3607,39 +3654,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>-0.0348</v>
+        <v>0.32</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2258300</v>
+        <v>3019600</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="H70" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.222</v>
+        <v>0.321</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.099</v>
+        <v>0.339</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3652,28 +3699,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>-0.0331</v>
+        <v>0.335</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0.0469</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2242700</v>
+        <v>3010000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.39</v>
+        <v>0.95</v>
       </c>
       <c r="H71" t="n">
-        <v>73.29000000000001</v>
+        <v>48.96</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3681,10 +3728,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.429</v>
+        <v>0.335</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.096</v>
+        <v>0.342</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3697,39 +3744,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="E72" s="16" t="n">
-        <v>-0.0308</v>
+        <v>-0.0391</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2121500</v>
+        <v>2993500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="H72" t="n">
-        <v>80.62</v>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.04</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>3.435</v>
+        <v>2.221</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.294</v>
+        <v>2.099</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3742,39 +3789,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>-0.0218</v>
+        <v>2.48</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2105500</v>
+        <v>2962100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="H73" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.9</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>4.598</v>
+        <v>2.434</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>4.539</v>
+        <v>2.267</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3787,40 +3834,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0.0536</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2081100</v>
+        <v>2943600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H74" t="n">
-        <v>40.8</v>
+        <v>0.13</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J74" s="9" t="n">
-        <v>4.851</v>
-      </c>
-      <c r="K74" s="9" t="n">
-        <v>4.967</v>
-      </c>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3832,28 +3872,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0.0833</v>
+        <v>1.29</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2068000</v>
+        <v>2924600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1.09</v>
+        <v>0.24</v>
       </c>
       <c r="H75" t="n">
-        <v>89.28</v>
+        <v>33.75</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3861,10 +3901,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.191</v>
+        <v>1.332</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.93</v>
+        <v>1.452</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3877,39 +3917,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.905</v>
+        <v>0.33</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>0.0169</v>
+        <v>0.0154</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1944200</v>
+        <v>2908400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.64</v>
+        <v>0.35</v>
       </c>
       <c r="H76" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.57</v>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.929</v>
+        <v>0.331</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.969</v>
+        <v>0.31</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3922,38 +3962,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>-0.0135</v>
+        <v>0.605</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1820700</v>
+        <v>2777300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H77" t="n">
-        <v>54.48</v>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.16</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.854</v>
-      </c>
-      <c r="K77" s="9" t="n"/>
+        <v>0.64</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>0.658</v>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
     </row>
@@ -3965,28 +4007,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>0.0148</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1794700</v>
+        <v>2777200</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.17</v>
+        <v>1.09</v>
       </c>
       <c r="H78" t="n">
-        <v>51.73</v>
+        <v>41.51</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -3994,10 +4036,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.677</v>
+        <v>1.587</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.66</v>
+        <v>1.65</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4010,28 +4052,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0.0392</v>
+        <v>0.26</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1757300</v>
+        <v>2762200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.35</v>
+        <v>4.76</v>
       </c>
       <c r="H79" t="n">
-        <v>59.89</v>
+        <v>55.34</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4039,10 +4081,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.257</v>
+        <v>0.253</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.259</v>
+        <v>0.264</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4055,39 +4097,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>0.0278</v>
+        <v>0.265</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1746800</v>
+        <v>2733700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.38</v>
+        <v>0.87</v>
       </c>
       <c r="H80" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="I80" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.13</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.96</v>
+        <v>0.262</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.79</v>
+        <v>0.25</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4100,39 +4142,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1677300</v>
+        <v>2732700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H81" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.73</v>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.166</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.592</v>
+        <v>1.098</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4145,39 +4187,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>-0.0377</v>
+        <v>2.88</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1656300</v>
+        <v>2688800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.53</v>
+        <v>1.42</v>
       </c>
       <c r="H82" t="n">
-        <v>48.14</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.48999999999999</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.261</v>
+        <v>2.193</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.25</v>
+        <v>1.931</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4190,39 +4232,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>0.0383</v>
+        <v>0.0112</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1653400</v>
+        <v>2668600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="H83" t="n">
-        <v>64.73</v>
-      </c>
-      <c r="I83" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.53</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.888</v>
+        <v>0.928</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.801</v>
+        <v>0.969</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4235,39 +4277,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>0.0492</v>
+        <v>4.49</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>-0.0197</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1550900</v>
+        <v>2657800</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.88</v>
+        <v>0.35</v>
       </c>
       <c r="H84" t="n">
-        <v>71.23</v>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.1</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.297</v>
+        <v>4.599</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.28</v>
+        <v>4.54</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4280,28 +4322,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>0.0233</v>
+        <v>4.44</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.022</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1534600</v>
+        <v>2627400</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H85" t="n">
-        <v>59.78</v>
+        <v>82.14</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4309,10 +4351,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.63</v>
+        <v>3.438</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.571</v>
+        <v>2.295</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4325,39 +4367,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0.0204</v>
+        <v>4.8</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1507800</v>
+        <v>2522300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="H86" t="n">
-        <v>52.87</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.477</v>
+        <v>4.851</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.536</v>
+        <v>4.967</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4370,28 +4412,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0</v>
+        <v>0.965</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>-0.0446</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1503200</v>
+        <v>2439500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>46.56</v>
+        <v>36.63</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4399,10 +4441,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.295</v>
+        <v>1.053</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.297</v>
+        <v>1.011</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4415,40 +4457,38 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.38</v>
+        <v>2.93</v>
       </c>
       <c r="E88" s="16" t="n">
-        <v>-0.035</v>
+        <v>-0.0135</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1481600</v>
+        <v>2428200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="H88" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.48</v>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.416</v>
-      </c>
-      <c r="K88" s="9" t="n">
-        <v>1.315</v>
-      </c>
+        <v>2.854</v>
+      </c>
+      <c r="K88" s="9" t="n"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
     </row>
@@ -4460,39 +4500,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1473100</v>
+        <v>2379200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H89" t="n">
-        <v>59.03</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.859</v>
+        <v>0.96</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.856</v>
+        <v>0.79</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4505,39 +4545,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1470100</v>
+        <v>2346200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H90" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.78</v>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.658</v>
+        <v>0.571</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4550,28 +4590,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>-0.0122</v>
+        <v>0.59</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1398800</v>
+        <v>2331300</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H91" t="n">
-        <v>70.53</v>
+        <v>47.34</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4579,10 +4619,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.368</v>
+        <v>0.592</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.336</v>
+        <v>0.611</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4595,28 +4635,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>3.48</v>
+        <v>2.62</v>
       </c>
       <c r="E92" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0368</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1384300</v>
+        <v>2296000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H92" t="n">
-        <v>36.11</v>
+        <v>72.16</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4624,10 +4664,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>3.627</v>
+        <v>2.428</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>3.708</v>
+        <v>2.096</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4640,39 +4680,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1374900</v>
+        <v>2276100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="H93" t="n">
-        <v>58.41</v>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.96</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.408</v>
+        <v>1.742</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.409</v>
+        <v>1.856</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4685,28 +4725,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0272</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1322400</v>
+        <v>2238400</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.38</v>
+        <v>0.89</v>
       </c>
       <c r="H94" t="n">
-        <v>70.44</v>
+        <v>54.82</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
@@ -4714,10 +4754,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.099</v>
+        <v>1.478</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.999</v>
+        <v>1.536</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4730,33 +4770,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>-0.0169</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>0.0148</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1292800</v>
+        <v>2152400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
+      </c>
+      <c r="H95" t="n">
+        <v>51.73</v>
       </c>
       <c r="I95" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
+      <c r="J95" s="9" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>0.66</v>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
     </row>
@@ -4768,39 +4815,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>0.0244</v>
+        <v>0.0492</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1282600</v>
+        <v>2120000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.37</v>
+        <v>0.74</v>
       </c>
       <c r="H96" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.88</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.614</v>
+        <v>0.889</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.579</v>
+        <v>0.802</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4813,28 +4860,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>-0.0102</v>
+        <v>0.26</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1235200</v>
+        <v>2110300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="H97" t="n">
-        <v>71.70999999999999</v>
+        <v>39.54</v>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
@@ -4842,10 +4889,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.442</v>
+        <v>0.274</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.402</v>
+        <v>0.316</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4858,39 +4905,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LAYHONG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1211600</v>
+        <v>2017700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>2.09</v>
+        <v>0.3</v>
       </c>
       <c r="H98" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.45</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.247</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.244</v>
+        <v>0.592</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4903,39 +4950,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>0.0054</v>
+        <v>0.31</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1201400</v>
+        <v>1761000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H99" t="n">
-        <v>39</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.25</v>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>7.712</v>
+        <v>0.307</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>7.854</v>
+        <v>0.294</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4948,39 +4995,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1177600</v>
+        <v>1760100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="H100" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.89</v>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.365</v>
+        <v>0.257</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.395</v>
+        <v>0.259</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4993,39 +5040,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>-0.027</v>
+        <v>1</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1150800</v>
+        <v>1760000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.73</v>
+        <v>0.35</v>
       </c>
       <c r="H101" t="n">
-        <v>60.24</v>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.5</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.352</v>
+        <v>1.053</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.318</v>
+        <v>1.073</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5038,39 +5085,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>10.16</v>
+        <v>0.775</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>0.004</v>
+        <v>0.0265</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1149400</v>
+        <v>1759300</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H102" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I102" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.81</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>10.171</v>
+        <v>0.799</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>10.334</v>
+        <v>0.853</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5083,28 +5130,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>2.62</v>
+        <v>0.42</v>
       </c>
       <c r="E103" s="17" t="n">
-        <v>0.0038</v>
+        <v>0.012</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1148400</v>
+        <v>1707700</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H103" t="n">
-        <v>55.6</v>
+        <v>62.57</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5112,10 +5159,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.587</v>
+        <v>0.408</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2.433</v>
+        <v>0.409</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5128,39 +5175,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1142100</v>
+        <v>1697900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.18</v>
+        <v>1.09</v>
       </c>
       <c r="H104" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.53</v>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.774</v>
+        <v>0.368</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.773</v>
+        <v>0.336</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5173,28 +5220,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>0.02</v>
+        <v>1.38</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>-0.035</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1117700</v>
+        <v>1668500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.22</v>
+        <v>0.73</v>
       </c>
       <c r="H105" t="n">
-        <v>38.46</v>
+        <v>47.07</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5202,10 +5249,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.055</v>
+        <v>1.416</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.073</v>
+        <v>1.315</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5218,39 +5265,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0.0325</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1097500</v>
+        <v>1622600</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="H106" t="n">
-        <v>55.46</v>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.73</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.399</v>
+        <v>0.614</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.398</v>
+        <v>0.579</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5263,39 +5310,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>0.0286</v>
+        <v>4.77</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1081600</v>
+        <v>1617000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H107" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="I107" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.72</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.334</v>
+        <v>4.746</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.318</v>
+        <v>4.584</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5308,28 +5355,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>2.63</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1075800</v>
+        <v>1603500</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="H108" t="n">
-        <v>49.25</v>
+        <v>56.31</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
@@ -5337,10 +5384,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.989</v>
+        <v>2.588</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.976</v>
+        <v>2.433</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5353,28 +5400,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>3.96</v>
+        <v>1.19</v>
       </c>
       <c r="E109" s="17" t="n">
-        <v>0.0154</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1046500</v>
+        <v>1599500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="H109" t="n">
-        <v>66.63</v>
+        <v>70.44</v>
       </c>
       <c r="I109" s="15" t="inlineStr">
         <is>
@@ -5382,10 +5429,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>3.721</v>
+        <v>1.099</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>3.373</v>
+        <v>0.999</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5407,19 +5454,19 @@
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1041400</v>
+        <v>1586800</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.65</v>
+        <v>0.99</v>
       </c>
       <c r="H110" t="n">
-        <v>41.59</v>
+        <v>44.16</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5427,7 +5474,7 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0.753</v>
@@ -5443,28 +5490,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.7</v>
+        <v>0.485</v>
       </c>
       <c r="E111" s="16" t="n">
-        <v>-0.0173</v>
+        <v>-0.0102</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1026700</v>
+        <v>1579500</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1.3</v>
+        <v>0.49</v>
       </c>
       <c r="H111" t="n">
-        <v>54.71</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
@@ -5472,10 +5519,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.651</v>
+        <v>0.442</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.727</v>
+        <v>0.402</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5488,28 +5535,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.48</v>
+        <v>4.01</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0282</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1020700</v>
+        <v>1567200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
       <c r="H112" t="n">
-        <v>59.9</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
@@ -5517,10 +5564,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.434</v>
+        <v>3.726</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.267</v>
+        <v>3.374</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5533,28 +5580,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.655</v>
+        <v>0.32</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>0.0077</v>
+        <v>0.0492</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1000600</v>
+        <v>1552000</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.29</v>
+        <v>1.88</v>
       </c>
       <c r="H113" t="n">
-        <v>72.5</v>
+        <v>71.23</v>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
@@ -5562,10 +5609,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.633</v>
+        <v>0.297</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.589</v>
+        <v>0.28</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5578,39 +5625,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0.0108</v>
+        <v>2.58</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>980200</v>
+        <v>1538900</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="H114" t="n">
-        <v>59.15</v>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.82</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.906</v>
+        <v>2.68</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.776</v>
+        <v>2.796</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5623,28 +5670,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.89</v>
+        <v>3.54</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>0.0053</v>
+        <v>0.0381</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>970300</v>
+        <v>1521100</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.21</v>
+        <v>0.49</v>
       </c>
       <c r="H115" t="n">
-        <v>36.12</v>
+        <v>73.88</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5652,10 +5699,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.964</v>
+        <v>3.272</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.085</v>
+        <v>2.859</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5668,39 +5715,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>0.0123</v>
+        <v>0.295</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>961500</v>
+        <v>1503200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.1</v>
+        <v>0.97</v>
       </c>
       <c r="H116" t="n">
-        <v>34.04</v>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.56</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>13.506</v>
+        <v>0.295</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>14.083</v>
+        <v>0.297</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5713,39 +5760,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0.0199</v>
+        <v>6.25</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>960900</v>
+        <v>1492700</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="H117" t="n">
-        <v>36.99</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.59</v>
+      </c>
+      <c r="I117" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.799</v>
+        <v>6.319</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.852</v>
+        <v>6.506</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5758,28 +5805,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E118" s="16" t="n">
-        <v>-0.009300000000000001</v>
+        <v>1.98</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>945500</v>
+        <v>1479100</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="H118" t="n">
-        <v>58.87</v>
+        <v>49.25</v>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
@@ -5787,10 +5834,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.512</v>
+        <v>1.989</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.461</v>
+        <v>1.976</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5803,39 +5850,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.0116</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>944400</v>
+        <v>1476600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.39</v>
+        <v>1.87</v>
       </c>
       <c r="H119" t="n">
-        <v>40.92</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56</v>
+      </c>
+      <c r="I119" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.056</v>
+        <v>1.652</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.011</v>
+        <v>1.727</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5848,39 +5895,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>1476100</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H120" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="K120" s="9" t="n">
         <v>0.855</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="F120" s="11" t="n">
-        <v>939700</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H120" t="n">
-        <v>67.06</v>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="K120" s="9" t="n">
-        <v>0.714</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5893,39 +5940,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>-0.0038</v>
+        <v>10.14</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0.002</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>932600</v>
+        <v>1468200</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.29</v>
+        <v>0.08</v>
       </c>
       <c r="H121" t="n">
-        <v>32.71</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.52</v>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.681</v>
+        <v>10.17</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.796</v>
+        <v>10.333</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5938,40 +5985,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>0.0121</v>
+        <v>0.295</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>924600</v>
+        <v>1453200</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H122" t="n">
-        <v>78.84</v>
+        <v>0.08</v>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J122" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K122" s="9" t="n">
-        <v>2.497</v>
-      </c>
+      <c r="J122" s="9" t="n"/>
+      <c r="K122" s="9" t="n"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
     </row>
@@ -5983,39 +6023,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>-0.012</v>
+        <v>13.22</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>921900</v>
+        <v>1449800</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="H123" t="n">
-        <v>31.96</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.04</v>
+      </c>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.742</v>
+        <v>13.506</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.856</v>
+        <v>14.083</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6028,28 +6068,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>0.0117</v>
+        <v>0.41</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>878900</v>
+        <v>1429200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="H124" t="n">
-        <v>53.03</v>
+        <v>53.93</v>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
@@ -6057,10 +6097,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>2.567</v>
+        <v>0.399</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>2.532</v>
+        <v>0.398</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6073,28 +6113,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0</v>
+        <v>7.47</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>0.0013</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>866900</v>
+        <v>1418800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H125" t="n">
-        <v>56.74</v>
+        <v>37.48</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6102,10 +6142,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>4.746</v>
+        <v>7.709</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>4.584</v>
+        <v>7.853</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6118,39 +6158,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.575</v>
+        <v>0.36</v>
       </c>
       <c r="E126" s="17" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0286</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>848000</v>
+        <v>1400400</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H126" t="n">
-        <v>41.22</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.7</v>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.591</v>
+        <v>0.334</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.611</v>
+        <v>0.318</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6163,39 +6203,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>1.4</v>
+        <v>0.945</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>0.0294</v>
+        <v>0.0216</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>819800</v>
+        <v>1348500</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.26</v>
+        <v>0.78</v>
       </c>
       <c r="H127" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.38</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>1.341</v>
+        <v>0.907</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.138</v>
+        <v>0.776</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6208,39 +6248,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="E128" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>775000</v>
+        <v>1292300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H128" t="n">
-        <v>41.51</v>
-      </c>
-      <c r="I128" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.55</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.587</v>
+        <v>1.292</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.65</v>
+        <v>1.324</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6253,28 +6293,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>743300</v>
+        <v>1284300</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.23</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H129" t="n">
-        <v>48.52</v>
+        <v>53.62</v>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
@@ -6282,10 +6322,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>3.012</v>
+        <v>0.351</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>3.04</v>
+        <v>0.318</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6298,39 +6338,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E130" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.525</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>737300</v>
+        <v>1259900</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H130" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.8</v>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.633</v>
+        <v>0.518</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.628</v>
+        <v>0.53</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6343,28 +6383,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.89</v>
+        <v>2.4</v>
       </c>
       <c r="E131" s="17" t="n">
-        <v>0.0114</v>
+        <v>0.0573</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>723300</v>
+        <v>1258300</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="H131" t="n">
-        <v>72.90000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="I131" s="15" t="inlineStr">
         <is>
@@ -6372,10 +6412,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.197</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.794</v>
+        <v>2.016</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6388,28 +6428,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>0.0381</v>
+        <v>0.58</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>707900</v>
+        <v>1256800</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H132" t="n">
-        <v>73.88</v>
+        <v>43.05</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6417,10 +6457,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>3.272</v>
+        <v>0.588</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>2.859</v>
+        <v>0.587</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6433,28 +6473,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.84</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>702900</v>
+        <v>1255900</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>2.36</v>
+        <v>0.44</v>
       </c>
       <c r="H133" t="n">
-        <v>61.01</v>
+        <v>64.22</v>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
@@ -6462,10 +6502,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>8.339</v>
+        <v>0.797</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>8.127000000000001</v>
+        <v>0.714</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6478,39 +6518,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>EPICON</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.63</v>
+        <v>0.205</v>
       </c>
       <c r="E134" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>700000</v>
+        <v>1233800</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="H134" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.84</v>
+      </c>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.631</v>
+        <v>0.199</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.637</v>
+        <v>0.206</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6523,28 +6563,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.27</v>
+        <v>1.89</v>
       </c>
       <c r="E135" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0053</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>675800</v>
+        <v>1230700</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="H135" t="n">
-        <v>41.55</v>
+        <v>36.12</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6552,10 +6592,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.292</v>
+        <v>1.964</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.324</v>
+        <v>2.085</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6568,28 +6608,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>LAYHONG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>6.25</v>
+        <v>0.25</v>
       </c>
       <c r="E136" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>661900</v>
+        <v>1223600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.04</v>
+        <v>2.11</v>
       </c>
       <c r="H136" t="n">
-        <v>42.59</v>
+        <v>55.11</v>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
@@ -6597,10 +6637,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>6.319</v>
+        <v>0.247</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>6.506</v>
+        <v>0.244</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6613,28 +6653,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>0.0114</v>
+        <v>0.53</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>628400</v>
+        <v>1220900</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="H137" t="n">
-        <v>49.13</v>
+        <v>58.87</v>
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
@@ -6642,10 +6682,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.771</v>
+        <v>0.512</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.807</v>
+        <v>0.461</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6658,28 +6698,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.73</v>
+        <v>3.34</v>
       </c>
       <c r="E138" s="17" t="n">
-        <v>0.021</v>
+        <v>0.0091</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>620800</v>
+        <v>1211700</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="H138" t="n">
-        <v>70</v>
+        <v>78.62</v>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
@@ -6687,10 +6727,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.667</v>
+        <v>2.909</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.61</v>
+        <v>2.497</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6703,28 +6743,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0</v>
+        <v>1.76</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>604800</v>
+        <v>1194100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H139" t="n">
-        <v>50.49</v>
+        <v>47.91</v>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
@@ -6732,10 +6772,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.517</v>
+        <v>1.77</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.53</v>
+        <v>1.807</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6748,39 +6788,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>-0.0037</v>
+        <v>0.36</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>595200</v>
+        <v>1181600</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>44.15</v>
-      </c>
-      <c r="I140" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.39</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.678</v>
+        <v>0.365</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.883</v>
+        <v>0.395</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6793,39 +6833,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5.77</v>
+        <v>2.99</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.0069</v>
+        <v>-0.0033</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>566200</v>
+        <v>1159100</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="H141" t="n">
-        <v>49.54</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.64</v>
+      </c>
+      <c r="I141" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>5.81</v>
+        <v>3.011</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>5.732</v>
+        <v>3.04</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6838,39 +6878,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>EITA</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E142" s="17" t="n">
-        <v>0.0274</v>
+        <v>1.88</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>558700</v>
+        <v>1142600</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>4.39</v>
+        <v>0.17</v>
       </c>
       <c r="H142" t="n">
-        <v>74.87</v>
-      </c>
-      <c r="I142" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.19</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.672</v>
+        <v>1.92</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.609</v>
+        <v>1.971</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6883,28 +6923,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>3.21</v>
+        <v>0.615</v>
       </c>
       <c r="E143" s="17" t="n">
-        <v>0.0031</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>531200</v>
+        <v>1091800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="H143" t="n">
-        <v>36</v>
+        <v>65.06</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6912,10 +6952,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>3.311</v>
+        <v>0.608</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>3.497</v>
+        <v>0.587</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6928,28 +6968,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="E144" s="16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>2.58</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>517600</v>
+        <v>1077600</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H144" t="n">
-        <v>57.19</v>
+        <v>51.98</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6957,10 +6997,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>7.785</v>
+        <v>2.566</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>7.723</v>
+        <v>2.532</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6973,28 +7013,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0</v>
+        <v>0.655</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>511300</v>
+        <v>1055900</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H145" t="n">
-        <v>57.39</v>
+        <v>72.5</v>
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
@@ -7002,10 +7042,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.569</v>
+        <v>0.633</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.574</v>
+        <v>0.589</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7018,28 +7058,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E146" s="16" t="n">
-        <v>-0.0052</v>
+        <v>1.4</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>510300</v>
+        <v>1021300</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="H146" t="n">
-        <v>45.64</v>
+        <v>60.62</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7047,10 +7087,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.922</v>
+        <v>1.341</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.971</v>
+        <v>1.138</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7063,28 +7103,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.99</v>
+        <v>0.74</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.0258</v>
+        <v>0.035</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>506200</v>
+        <v>1001300</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H147" t="n">
-        <v>52.13</v>
+        <v>71.39</v>
       </c>
       <c r="I147" s="15" t="inlineStr">
         <is>
@@ -7092,16 +7132,1501 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.964</v>
+        <v>0.668</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.026</v>
+        <v>0.61</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>939100</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H148" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>5.808</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>5.731</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>901200</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H149" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="I149" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>867300</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H150" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>857200</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H151" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="I151" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>7.723</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>826300</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H152" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="I152" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>817700</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H153" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>2.884</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>809700</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H154" t="n">
+        <v>63.89</v>
+      </c>
+      <c r="I154" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>756400</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H155" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>748500</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H156" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="I156" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>7.652</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>7.801</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E157" s="16" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>745500</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H157" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>3.309</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>3.497</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>0366</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ICENTS</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>718100</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H158" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I158" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>UMSINT</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>702900</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H159" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="I159" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>8.339</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>8.127000000000001</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H160" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>686000</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H161" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="I161" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>2.066</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>660400</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H162" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I162" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E163" s="17" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>658400</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H163" t="n">
+        <v>58.47</v>
+      </c>
+      <c r="I163" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>646600</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H164" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="I164" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>2.781</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>2.673</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ECOWLD</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>637400</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H165" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="I165" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>631600</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H166" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="I166" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>7.992</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>8.272</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>625700</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H167" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EITA</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>621100</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="H168" t="n">
+        <v>74.87</v>
+      </c>
+      <c r="I168" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>615200</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H169" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>6.785</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>598700</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H170" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="I170" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>TEOSENG</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>597800</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H171" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>596300</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H172" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>7.791</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>588300</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H173" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="I173" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>4.742</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>5.008</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>583500</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H174" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="I174" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>581400</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H175" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>581400</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H176" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>3.081</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>3.156</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E177" s="16" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>564600</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H177" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I177" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>5.722</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>6.099</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="E178" s="17" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>525300</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I178" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>4.975</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>5.035</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>505100</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H179" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="I179" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>8.689</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>8.548999999999999</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>501400</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H180" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="I180" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M147"/>
+  <autoFilter ref="A1:M180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$191</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0395</v>
+        <v>0.0263</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>12961000</v>
+        <v>14778000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>69.51000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.395高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破。RSI 69.51接近超买区，信号偏强但需留意短线过热。</t>
+          <t>现价0.39高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破；RSI 66.85接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>6199400</v>
+        <v>6696600</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>10.45</v>
+        <v>11.29</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.13</v>
+        <v>69.83</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价RM 0.25高于50日均线RM 0.197，EMA20与SAR均呈多头，T3形态突破。但RSI达71.13，已进入超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.245高于50日均线0.197，EMA20与SAR均呈多头，T3突破信号偏强；但RSI达69.83，接近超买区，可靠性略受抑制。</t>
         </is>
       </c>
     </row>
@@ -682,10 +682,10 @@
         <v>0.125</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>5667400</v>
+        <v>7372200</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>4.93</v>
+        <v>6.42</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>81.89</v>
@@ -708,7 +708,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>RSI 81.89已处超买区，现价高于50日均线约29.8%，EMA20与SAR多头信号虽一致，但短线过热。</t>
+          <t>RSI达81.89，处超买区间；现价0.27高于50日均线0.208约30%，EMA20与SAR多头排列，T3突破信号偏强，但超买或加大回调风险。</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.555</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0673</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2564800</v>
+        <v>2748400</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.85</v>
+        <v>64.42</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.493</v>
+        <v>0.494</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.395</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.555高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破；RSI 63.85偏强但未超买，信号技术面较可靠。</t>
+          <t>现价0.56高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破。RSI 64.42接近超买区但未破70，信号偏强。</t>
         </is>
       </c>
     </row>
@@ -788,10 +788,10 @@
         <v>0.017</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1160600</v>
+        <v>1244100</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>73.56</v>
@@ -814,7 +814,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>现价0.895高于50日均线0.794，EMA20与SAR均呈多头，T3形态突破；但RSI达73.56，已进入超买区，信号可靠性需留意短线过热。</t>
+          <t>现价0.895高于50日均线0.794，EMA20与SAR均呈多头，T3突破有效；但RSI达73.56，已进入超买区，信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.84</v>
+        <v>0.865</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1234</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>20625800</v>
+        <v>23676300</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>71.89</v>
+        <v>73.77</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.704</v>
+        <v>0.707</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.84高于50日均线0.684，EMA20与SAR均呈多头，T3形态突破。但RSI达71.89，已进入超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.865高于50日均线0.685，EMA20与SAR均呈多头，T3形态突破；但RSI达73.77，已进入超买区，信号可靠性需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -894,10 +894,10 @@
         <v>0.0217</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1147100</v>
+        <v>1322500</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>72.40000000000001</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3突破有效；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
+          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3形态突破；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>253892200</v>
+        <v>257407400</v>
       </c>
       <c r="G9" s="12" t="n"/>
       <c r="I9" s="13" t="inlineStr">
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>50076000</v>
+        <v>50531300</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>0.08</v>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>-0.0217</v>
+        <v>-0.0435</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>24137800</v>
+        <v>26044400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="H12" t="n">
-        <v>34.72</v>
+        <v>32.28</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0021</v>
+        <v>4.85</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>22991400</v>
+        <v>24416900</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="H13" t="n">
-        <v>61.51</v>
+        <v>62.88</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>4.723</v>
+        <v>4.725</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>4.495</v>
@@ -1163,10 +1163,10 @@
         <v>-0.0168</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>20606100</v>
+        <v>24215700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="H14" t="n">
         <v>71.34</v>
@@ -1208,10 +1208,10 @@
         <v>-0.04</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>17831100</v>
+        <v>22800200</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.65</v>
+        <v>0.83</v>
       </c>
       <c r="H15" t="n">
         <v>30.84</v>
@@ -1238,28 +1238,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.385</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>-0.0375</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>17341300</v>
+        <v>18156300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="H16" t="n">
-        <v>64.27</v>
+        <v>79.02</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.74</v>
+        <v>0.313</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.178</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1283,28 +1283,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.155</v>
+        <v>0.78</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>16073700</v>
+        <v>17841500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
       <c r="H17" t="n">
-        <v>44.71</v>
+        <v>63.44</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.156</v>
+        <v>0.739</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.16</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
         <v>-0.0313</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>15444000</v>
+        <v>16585700</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="H18" t="n">
         <v>61.04</v>
@@ -1373,39 +1373,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0.0145</v>
+        <v>0.155</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>14869000</v>
+        <v>16073700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="H19" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.71</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2.132</v>
+        <v>0.156</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>2.059</v>
+        <v>0.16</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>14638400</v>
+        <v>15511400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="H20" t="n">
         <v>56.29</v>
@@ -1463,28 +1463,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>2.1</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>13417000</v>
+        <v>15258800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.03</v>
+        <v>0.95</v>
       </c>
       <c r="H21" t="n">
-        <v>42.35</v>
+        <v>48.11</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.132</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.059</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>13271900</v>
+        <v>14871200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2.98</v>
+        <v>3.33</v>
       </c>
       <c r="H22" t="n">
         <v>95.37</v>
@@ -1553,28 +1553,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-0.025</v>
+        <v>-0.0159</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13049300</v>
+        <v>13943300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
       <c r="H23" t="n">
-        <v>81.17</v>
+        <v>59.8</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.313</v>
+        <v>0.303</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.178</v>
+        <v>0.29</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1598,28 +1598,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.24</v>
+        <v>1.86</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.0213</v>
+        <v>0.0391</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>12948100</v>
+        <v>13605700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="n">
-        <v>56.19</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.232</v>
+        <v>1.727</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.233</v>
+        <v>1.511</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1643,39 +1643,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>0.0391</v>
+        <v>0.795</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>12406900</v>
+        <v>13431000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.48</v>
+        <v>1.03</v>
       </c>
       <c r="H25" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.727</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.511</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1688,28 +1688,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>-0.0435</v>
+        <v>0.24</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>11968400</v>
+        <v>13072100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="n">
-        <v>71.25</v>
+        <v>56.19</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.2</v>
+        <v>0.232</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.183</v>
+        <v>0.233</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1733,28 +1733,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.0159</v>
+        <v>-0.0435</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>11685300</v>
+        <v>12776000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H27" t="n">
-        <v>59.8</v>
+        <v>71.25</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.303</v>
+        <v>0.2</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.29</v>
+        <v>0.183</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1778,28 +1778,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>-0.0208</v>
+        <v>3.06</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>11520400</v>
+        <v>11601700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.46</v>
+        <v>0.93</v>
       </c>
       <c r="H28" t="n">
-        <v>50.88</v>
+        <v>72.83</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.468</v>
+        <v>2.848</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.47</v>
+        <v>2.702</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1823,39 +1823,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0.0095</v>
+        <v>0.475</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>10958200</v>
+        <v>11581700</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="H29" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.83</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.645</v>
+        <v>0.468</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.863</v>
+        <v>0.47</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1868,39 +1868,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>0.0556</v>
+        <v>0.52</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>10111800</v>
+        <v>11428500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.77</v>
+        <v>0.29</v>
       </c>
       <c r="H30" t="n">
-        <v>79.43000000000001</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.6</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.078</v>
+        <v>0.644</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.067</v>
+        <v>0.863</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1913,39 +1913,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.865</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>9801000</v>
+        <v>11049200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.26</v>
+        <v>0.62</v>
       </c>
       <c r="H31" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.91</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.444</v>
+        <v>0.868</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.403</v>
+        <v>0.871</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1958,39 +1958,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3.05</v>
+        <v>0.45</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0227</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>9685400</v>
+        <v>10633600</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.77</v>
+        <v>1.37</v>
       </c>
       <c r="H32" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.848</v>
+        <v>0.444</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.702</v>
+        <v>0.403</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -2003,28 +2003,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-0.006500000000000001</v>
+        <v>2.87</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0.1081</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>9656000</v>
+        <v>10445500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.8</v>
+        <v>1.63</v>
       </c>
       <c r="H33" t="n">
-        <v>45.47</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.773</v>
+        <v>2.608</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.774</v>
+        <v>2.485</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2048,28 +2048,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.85</v>
+        <v>0.095</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0.1004</v>
+        <v>0.0556</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>9558900</v>
+        <v>10111800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="H34" t="n">
-        <v>66.36</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>2.606</v>
+        <v>0.078</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.484</v>
+        <v>0.067</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2093,39 +2093,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0.0361</v>
+        <v>0.76</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>8859800</v>
+        <v>9936400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
       <c r="H35" t="n">
-        <v>66.08</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.44</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.381</v>
+        <v>0.773</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.318</v>
+        <v>0.774</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2138,39 +2138,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.43</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>8816600</v>
+        <v>9039400</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="H36" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.08</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.868</v>
+        <v>0.381</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.871</v>
+        <v>0.318</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8459100</v>
+        <v>8898100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H37" t="n">
         <v>34.16</v>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.76</v>
+        <v>0.765</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.0066</v>
+        <v>0.0132</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>8368700</v>
+        <v>8587000</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H38" t="n">
-        <v>69.72</v>
+        <v>70.27</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.678</v>
+        <v>0.679</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>0.607</v>
@@ -2273,39 +2273,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0.027</v>
+        <v>1.33</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>-0.0432</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>7831700</v>
+        <v>8551500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>2.22</v>
+        <v>0.73</v>
       </c>
       <c r="H39" t="n">
-        <v>78.73</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.67</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.878</v>
+        <v>1.381</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.85</v>
+        <v>1.287</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2318,39 +2318,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>0.955</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0.03240000000000001</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>7785600</v>
+        <v>8459500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.95</v>
+        <v>2.39</v>
       </c>
       <c r="H40" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.42</v>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.197</v>
+        <v>0.878</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.196</v>
+        <v>0.85</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2363,28 +2363,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>-0.0432</v>
+        <v>0.19</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7619000</v>
+        <v>8069100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.65</v>
+        <v>0.98</v>
       </c>
       <c r="H41" t="n">
-        <v>45.67</v>
+        <v>44.21</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.381</v>
+        <v>0.197</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.287</v>
+        <v>0.196</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2408,28 +2408,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0</v>
+        <v>5.9</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>7393400</v>
+        <v>7939100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="H42" t="n">
-        <v>71.51000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.142</v>
+        <v>5.675</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.114</v>
+        <v>5.1</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2453,28 +2453,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.17</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6720100</v>
+        <v>7776300</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H43" t="n">
-        <v>49.56</v>
+        <v>73.31</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.159</v>
+        <v>0.142</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.148</v>
+        <v>0.114</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2498,33 +2498,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>-0.0185</v>
+        <v>2.41</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>6681700</v>
+        <v>7773600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
+        <v>0.44</v>
+      </c>
+      <c r="H44" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>2.232</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2536,40 +2543,33 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>0.0214</v>
+        <v>0.265</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>6430600</v>
+        <v>6815700</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H45" t="n">
-        <v>54.48</v>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>2.232</v>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
     </row>
@@ -2581,28 +2581,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0.0172</v>
+        <v>0.155</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>6282400</v>
+        <v>6756800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
       <c r="H46" t="n">
-        <v>63.7</v>
+        <v>49.56</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>5.675</v>
+        <v>0.159</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>5.1</v>
+        <v>0.148</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2626,39 +2626,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0.0455</v>
+        <v>0.115</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>6141000</v>
+        <v>6314300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>66.81</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.46</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.197</v>
+        <v>0.119</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.171</v>
+        <v>0.106</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2671,39 +2671,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.605</v>
+        <v>0.235</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0168</v>
+        <v>0.0682</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>6007200</v>
+        <v>6143500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="H48" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.06</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.608</v>
+        <v>0.197</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.603</v>
+        <v>0.171</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2716,39 +2716,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5799300</v>
+        <v>6108200</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="H49" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.31</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.119</v>
+        <v>0.766</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.106</v>
+        <v>0.751</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.785</v>
+        <v>0.6</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>5695800</v>
+        <v>6007500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="H50" t="n">
-        <v>86.31</v>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.18</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.766</v>
+        <v>0.608</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.751</v>
+        <v>0.603</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2815,19 +2815,19 @@
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.8</v>
+        <v>0.795</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>0.0323</v>
+        <v>0.0258</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>5522200</v>
+        <v>5918600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="H51" t="n">
-        <v>60.75</v>
+        <v>59.89</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0.74</v>
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.33</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5512000</v>
+        <v>5575900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H52" t="n">
-        <v>95.37</v>
+        <v>95.13</v>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.262</v>
+        <v>0.261</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0.218</v>
@@ -2911,10 +2911,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>5082800</v>
+        <v>5382800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="H53" t="n">
         <v>68.41</v>
@@ -2941,28 +2941,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.805</v>
+        <v>0.54</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>0.0063</v>
+        <v>0.0286</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5026400</v>
+        <v>5178200</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.49</v>
+        <v>0.35</v>
       </c>
       <c r="H54" t="n">
-        <v>49.91</v>
+        <v>68.8</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.804</v>
+        <v>0.466</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.806</v>
+        <v>0.397</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2986,39 +2986,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>0.05</v>
+        <v>1.04</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4983800</v>
+        <v>5158700</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1.1</v>
+        <v>0.64</v>
       </c>
       <c r="H55" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.8</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.103</v>
+        <v>0.875</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.096</v>
+        <v>0.752</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -3031,28 +3031,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.54</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>0.0286</v>
+        <v>0.0125</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4982500</v>
+        <v>5118100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.34</v>
+        <v>1.52</v>
       </c>
       <c r="H56" t="n">
-        <v>68.8</v>
+        <v>51.24</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.466</v>
+        <v>0.804</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.397</v>
+        <v>0.806</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3076,39 +3076,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>-0.028</v>
+        <v>0.1</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4372300</v>
+        <v>5028300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.54</v>
+        <v>1.11</v>
       </c>
       <c r="H57" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.875</v>
+        <v>0.102</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.752</v>
+        <v>0.096</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3121,28 +3121,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>4.15</v>
+        <v>1.11</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>0.0641</v>
+        <v>0.0183</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4104700</v>
+        <v>4773100</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.93</v>
+        <v>0.39</v>
       </c>
       <c r="H58" t="n">
-        <v>79.69</v>
+        <v>80.11</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>3.488</v>
+        <v>0.997</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>3.204</v>
+        <v>0.837</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3166,28 +3166,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.225</v>
+        <v>4.18</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0718</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4103400</v>
+        <v>4613200</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.67</v>
+        <v>1.04</v>
       </c>
       <c r="H59" t="n">
-        <v>57.04</v>
+        <v>80.14</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.214</v>
+        <v>3.491</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.211</v>
+        <v>3.205</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3211,28 +3211,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.13</v>
+        <v>2.9</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>0.0367</v>
+        <v>0.0781</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3990200</v>
+        <v>4397200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.32</v>
+        <v>1.94</v>
       </c>
       <c r="H60" t="n">
-        <v>81.51000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.998</v>
+        <v>2.117</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.838</v>
+        <v>1.74</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3256,28 +3256,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.365</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3932600</v>
+        <v>4182100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.74</v>
+        <v>0.72</v>
       </c>
       <c r="H61" t="n">
-        <v>89.18000000000001</v>
+        <v>48.77</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>2.113</v>
+        <v>0.367</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.739</v>
+        <v>0.366</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3301,28 +3301,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>-0.0267</v>
+        <v>0.225</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3731900</v>
+        <v>4136200</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H62" t="n">
-        <v>48.77</v>
+        <v>57.04</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.367</v>
+        <v>0.214</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.366</v>
+        <v>0.211</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3346,28 +3346,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>-0.0175</v>
+        <v>-0.0086</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3451900</v>
+        <v>3875200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>58.3</v>
+        <v>46.5</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.086</v>
+        <v>1.181</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.023</v>
+        <v>1.135</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3391,28 +3391,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>-0.0086</v>
+        <v>0.31</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3328100</v>
+        <v>3851400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H64" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.181</v>
+        <v>0.307</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.135</v>
+        <v>0.294</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3436,33 +3436,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3324200</v>
+        <v>3769300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
+      </c>
+      <c r="H65" t="n">
+        <v>56.51</v>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
+      <c r="J65" s="9" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>1.023</v>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
     </row>
@@ -3474,28 +3481,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0.009399999999999999</v>
+        <v>2.21</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>-0.0391</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3292700</v>
+        <v>3721000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H66" t="n">
-        <v>56.16</v>
+        <v>51.04</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3503,10 +3510,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.519</v>
+        <v>2.221</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.473</v>
+        <v>2.099</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3519,28 +3526,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>-0.0171</v>
+        <v>0.535</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3259500</v>
+        <v>3510100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.72</v>
+        <v>0.25</v>
       </c>
       <c r="H67" t="n">
-        <v>34.09</v>
+        <v>56.16</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3548,10 +3555,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>3.623</v>
+        <v>0.519</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>3.707</v>
+        <v>0.473</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3564,39 +3571,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.77</v>
+        <v>0.26</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3146700</v>
+        <v>3503000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H68" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.54</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.774</v>
+        <v>0.274</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.773</v>
+        <v>0.316</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3609,40 +3616,33 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.26</v>
+        <v>0.295</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>0.09570000000000001</v>
+        <v>0.0536</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3077000</v>
+        <v>3493100</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H69" t="n">
-        <v>83.89</v>
-      </c>
-      <c r="I69" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="n">
-        <v>1.024</v>
-      </c>
-      <c r="K69" s="9" t="n">
-        <v>0.876</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n"/>
+      <c r="K69" s="9" t="n"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
     </row>
@@ -3654,39 +3654,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0.0323</v>
+        <v>0.765</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3019600</v>
+        <v>3443700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="H70" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.15</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.321</v>
+        <v>0.774</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.339</v>
+        <v>0.773</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3699,39 +3699,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.335</v>
+        <v>2.48</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>0.0469</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3010000</v>
+        <v>3417600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.95</v>
+        <v>0.21</v>
       </c>
       <c r="H71" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.9</v>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.335</v>
+        <v>2.434</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.342</v>
+        <v>2.267</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3744,28 +3744,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.21</v>
+        <v>3.44</v>
       </c>
       <c r="E72" s="16" t="n">
-        <v>-0.0391</v>
+        <v>-0.0171</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2993500</v>
+        <v>3362800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="H72" t="n">
-        <v>51.04</v>
+        <v>34.09</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.221</v>
+        <v>3.623</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.099</v>
+        <v>3.707</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3789,40 +3789,33 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.48</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2962100</v>
+        <v>3357200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H73" t="n">
-        <v>59.9</v>
+        <v>0.14</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J73" s="9" t="n">
-        <v>2.434</v>
-      </c>
-      <c r="K73" s="9" t="n">
-        <v>2.267</v>
-      </c>
+      <c r="J73" s="9" t="n"/>
+      <c r="K73" s="9" t="n"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3834,33 +3827,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>0.0536</v>
+        <v>2.58</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>-0.0515</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2943600</v>
+        <v>3279500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
+      </c>
+      <c r="H74" t="n">
+        <v>67.95999999999999</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J74" s="9" t="n"/>
-      <c r="K74" s="9" t="n"/>
+      <c r="J74" s="9" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>2.095</v>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3872,28 +3872,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>-0.0077</v>
+        <v>1.25</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2924600</v>
+        <v>3241000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.24</v>
+        <v>1.26</v>
       </c>
       <c r="H75" t="n">
-        <v>33.75</v>
+        <v>83.5</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.332</v>
+        <v>1.023</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.452</v>
+        <v>0.876</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3917,28 +3917,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0.0154</v>
+        <v>1.3</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2908400</v>
+        <v>3222800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="H76" t="n">
-        <v>52.57</v>
+        <v>35.36</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.331</v>
+        <v>1.333</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.31</v>
+        <v>1.452</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3962,39 +3962,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>2.93</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0.1098</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2777300</v>
+        <v>3210400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.55</v>
+        <v>1.7</v>
       </c>
       <c r="H77" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.98</v>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.64</v>
+        <v>2.197</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.658</v>
+        <v>1.932</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -4007,28 +4007,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.325</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2777200</v>
+        <v>3205400</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.09</v>
+        <v>0.38</v>
       </c>
       <c r="H78" t="n">
-        <v>41.51</v>
+        <v>50.52</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.587</v>
+        <v>0.33</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.65</v>
+        <v>0.31</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4052,28 +4052,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.26</v>
+        <v>1.55</v>
       </c>
       <c r="E79" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2762200</v>
+        <v>3117500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>4.76</v>
+        <v>1.22</v>
       </c>
       <c r="H79" t="n">
-        <v>55.34</v>
+        <v>39.12</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.253</v>
+        <v>1.586</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.264</v>
+        <v>1.65</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4097,28 +4097,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.265</v>
+        <v>0.605</v>
       </c>
       <c r="E80" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2733700</v>
+        <v>3102100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
       <c r="H80" t="n">
-        <v>53.13</v>
+        <v>36.16</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.262</v>
+        <v>0.64</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.25</v>
+        <v>0.658</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4142,28 +4142,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.315</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2732700</v>
+        <v>3065600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="H81" t="n">
-        <v>61.73</v>
+        <v>44.61</v>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.166</v>
+        <v>0.321</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.098</v>
+        <v>0.339</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4187,39 +4187,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.88</v>
+        <v>0.9</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0112</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2688800</v>
+        <v>3060800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="H82" t="n">
-        <v>89.48999999999999</v>
-      </c>
-      <c r="I82" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.53</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.193</v>
+        <v>0.928</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.931</v>
+        <v>0.969</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4232,28 +4232,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.9</v>
+        <v>0.335</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>0.0112</v>
+        <v>0.0469</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2668600</v>
+        <v>3010000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H83" t="n">
-        <v>35.53</v>
+        <v>48.96</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.928</v>
+        <v>0.335</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.969</v>
+        <v>0.342</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4277,39 +4277,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>4.49</v>
+        <v>1.21</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>-0.0197</v>
+        <v>-0.0163</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2657800</v>
+        <v>2789900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.85</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>4.599</v>
+        <v>1.165</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>4.54</v>
+        <v>1.098</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4322,39 +4322,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>-0.022</v>
+        <v>0.265</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2627400</v>
+        <v>2786200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.22</v>
+        <v>0.88</v>
       </c>
       <c r="H85" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.13</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>3.438</v>
+        <v>0.262</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>2.295</v>
+        <v>0.25</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4367,39 +4367,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>4.8</v>
+        <v>4.44</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.022</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2522300</v>
+        <v>2773500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="H86" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.14</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>4.851</v>
+        <v>3.438</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>4.967</v>
+        <v>2.295</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4412,28 +4412,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.965</v>
+        <v>4.49</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.0446</v>
+        <v>-0.0197</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2439500</v>
+        <v>2772000</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1</v>
+        <v>0.37</v>
       </c>
       <c r="H87" t="n">
-        <v>36.63</v>
+        <v>47.1</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.053</v>
+        <v>4.599</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.011</v>
+        <v>4.54</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4457,28 +4457,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>-0.0135</v>
+        <v>0.26</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2428200</v>
+        <v>2763800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.77</v>
+        <v>4.77</v>
       </c>
       <c r="H88" t="n">
-        <v>54.48</v>
+        <v>55.34</v>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
@@ -4486,9 +4486,11 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.854</v>
-      </c>
-      <c r="K88" s="9" t="n"/>
+        <v>0.253</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.264</v>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
     </row>
@@ -4500,28 +4502,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0.0278</v>
+        <v>2.92</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2379200</v>
+        <v>2710900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.51</v>
+        <v>0.86</v>
       </c>
       <c r="H89" t="n">
-        <v>84.40000000000001</v>
+        <v>53.97</v>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
@@ -4529,11 +4531,9 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K89" s="9" t="n">
-        <v>0.79</v>
-      </c>
+        <v>2.853</v>
+      </c>
+      <c r="K89" s="9" t="n"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
     </row>
@@ -4545,39 +4545,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>0.0233</v>
+        <v>4.8</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2346200</v>
+        <v>2686600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="H90" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="I90" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.63</v>
+        <v>4.851</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.571</v>
+        <v>4.967</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4590,39 +4590,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0.0351</v>
+        <v>0.97</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>-0.0396</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2331300</v>
+        <v>2611400</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.85</v>
+        <v>1.07</v>
       </c>
       <c r="H91" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I91" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.19</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.592</v>
+        <v>1.053</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.611</v>
+        <v>1.011</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4635,39 +4635,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>-0.0368</v>
+        <v>1.11</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2296000</v>
+        <v>2462100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="H92" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.428</v>
+        <v>0.96</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.096</v>
+        <v>0.79</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         <v>-0.012</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2276100</v>
+        <v>2444900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H93" t="n">
         <v>31.96</v>
@@ -4725,28 +4725,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.51</v>
+        <v>0.66</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>0.0272</v>
+        <v>0.0233</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2238400</v>
+        <v>2419300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.89</v>
+        <v>0.25</v>
       </c>
       <c r="H94" t="n">
-        <v>54.82</v>
+        <v>59.78</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.478</v>
+        <v>0.63</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.536</v>
+        <v>0.571</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4770,39 +4770,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>0.0148</v>
+        <v>0.0331</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2152400</v>
+        <v>2397900</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="H95" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.53</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.677</v>
+        <v>0.8</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.66</v>
+        <v>0.853</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4815,39 +4815,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>0.0492</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2120000</v>
+        <v>2336200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.74</v>
+        <v>0.34</v>
       </c>
       <c r="H96" t="n">
-        <v>65.88</v>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.45</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.889</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.802</v>
+        <v>0.592</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4860,28 +4860,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2110300</v>
+        <v>2332300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.18</v>
+        <v>0.85</v>
       </c>
       <c r="H97" t="n">
-        <v>39.54</v>
+        <v>47.34</v>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.274</v>
+        <v>0.592</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.316</v>
+        <v>0.611</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4905,39 +4905,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.54</v>
+        <v>1.52</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2017700</v>
+        <v>2298900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.3</v>
+        <v>0.92</v>
       </c>
       <c r="H98" t="n">
-        <v>36.45</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.61</v>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.479</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.592</v>
+        <v>1.536</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4950,28 +4950,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>0.96</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0.0492</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1761000</v>
+        <v>2240200</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.23</v>
+        <v>0.78</v>
       </c>
       <c r="H99" t="n">
-        <v>61.25</v>
+        <v>65.88</v>
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.307</v>
+        <v>0.889</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.294</v>
+        <v>0.802</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4995,28 +4995,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.265</v>
+        <v>0.68</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>0.0392</v>
+        <v>0.0074</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1760100</v>
+        <v>2173800</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.35</v>
+        <v>0.21</v>
       </c>
       <c r="H100" t="n">
-        <v>59.89</v>
+        <v>50.85</v>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.257</v>
+        <v>0.677</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.259</v>
+        <v>0.66</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5040,28 +5040,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>2.57</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1760000</v>
+        <v>2085000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="H101" t="n">
-        <v>31.5</v>
+        <v>30.98</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.053</v>
+        <v>2.679</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.073</v>
+        <v>2.795</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5085,39 +5085,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0.0265</v>
+        <v>1.75</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1759300</v>
+        <v>2081400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="H102" t="n">
-        <v>38.81</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.62</v>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.799</v>
+        <v>1.769</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.853</v>
+        <v>1.807</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5130,28 +5130,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>0.012</v>
+        <v>6.24</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1707700</v>
+        <v>2022700</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H103" t="n">
-        <v>62.57</v>
+        <v>41.98</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.408</v>
+        <v>6.318</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.409</v>
+        <v>6.506</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5175,39 +5175,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.405</v>
+        <v>4.77</v>
       </c>
       <c r="E104" s="16" t="n">
-        <v>-0.0122</v>
+        <v>-0.0021</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1697900</v>
+        <v>1947200</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1.09</v>
+        <v>0.23</v>
       </c>
       <c r="H104" t="n">
-        <v>70.53</v>
-      </c>
-      <c r="I104" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.72</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.368</v>
+        <v>4.746</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.336</v>
+        <v>4.584</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5220,28 +5220,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.38</v>
+        <v>0.58</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>-0.035</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1668500</v>
+        <v>1944900</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.73</v>
+        <v>0.51</v>
       </c>
       <c r="H105" t="n">
-        <v>47.07</v>
+        <v>43.05</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.416</v>
+        <v>0.588</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.315</v>
+        <v>0.587</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5265,40 +5265,33 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0.0325</v>
+        <v>0.29</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1622600</v>
+        <v>1928100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H106" t="n">
-        <v>58.73</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="K106" s="9" t="n">
-        <v>0.579</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5310,39 +5303,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>-0.0021</v>
+        <v>3.53</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>0.0352</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1617000</v>
+        <v>1921200</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.19</v>
+        <v>0.62</v>
       </c>
       <c r="H107" t="n">
-        <v>55.72</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.55</v>
+      </c>
+      <c r="I107" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>4.746</v>
+        <v>3.271</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>4.584</v>
+        <v>2.859</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5364,19 +5357,19 @@
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>0.0077</v>
+        <v>2.61</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1603500</v>
+        <v>1881400</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H108" t="n">
-        <v>56.31</v>
+        <v>54.87</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
@@ -5384,10 +5377,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.588</v>
+        <v>2.586</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.433</v>
+        <v>2.432</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5400,39 +5393,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="E109" s="17" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1599500</v>
+        <v>1880200</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H109" t="n">
-        <v>70.44</v>
-      </c>
-      <c r="I109" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.46</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.099</v>
+        <v>1.055</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.999</v>
+        <v>1.073</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5445,39 +5438,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.73</v>
+        <v>4.02</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>0.0069</v>
+        <v>0.0308</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1586800</v>
+        <v>1842900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.99</v>
+        <v>0.52</v>
       </c>
       <c r="H110" t="n">
-        <v>44.16</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.5</v>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.739</v>
+        <v>3.726</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.753</v>
+        <v>3.374</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5490,28 +5483,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>-0.0102</v>
+        <v>0.355</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0.0143</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1579500</v>
+        <v>1824900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="H111" t="n">
-        <v>71.70999999999999</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
@@ -5519,10 +5512,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.442</v>
+        <v>0.334</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.402</v>
+        <v>0.318</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5535,39 +5528,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>4.01</v>
+        <v>1.28</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>0.0282</v>
+        <v>0.0159</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1567200</v>
+        <v>1820300</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H112" t="n">
-        <v>68.20999999999999</v>
-      </c>
-      <c r="I112" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.51</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>3.726</v>
+        <v>1.292</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>3.374</v>
+        <v>1.324</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5580,28 +5573,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>0.0492</v>
+        <v>1.98</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1552000</v>
+        <v>1798500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>1.88</v>
+        <v>0.26</v>
       </c>
       <c r="H113" t="n">
-        <v>71.23</v>
+        <v>49.25</v>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
@@ -5609,10 +5602,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.297</v>
+        <v>1.989</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.28</v>
+        <v>1.976</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5625,39 +5618,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>-0.0077</v>
+        <v>1.19</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1538900</v>
+        <v>1777500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H114" t="n">
-        <v>31.82</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.44</v>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>2.68</v>
+        <v>1.099</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2.796</v>
+        <v>0.999</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5670,28 +5663,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3.54</v>
+        <v>0.63</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>0.0381</v>
+        <v>0.0244</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1521100</v>
+        <v>1762500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H115" t="n">
-        <v>73.88</v>
+        <v>57.47</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5699,10 +5692,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>3.272</v>
+        <v>0.614</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.859</v>
+        <v>0.579</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5715,39 +5708,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1503200</v>
+        <v>1760100</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.97</v>
+        <v>1.35</v>
       </c>
       <c r="H116" t="n">
-        <v>46.56</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.89</v>
+      </c>
+      <c r="I116" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.295</v>
+        <v>0.257</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.297</v>
+        <v>0.259</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5760,39 +5753,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>7.47</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0.0013</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1492700</v>
+        <v>1755800</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="H117" t="n">
-        <v>42.59</v>
-      </c>
-      <c r="I117" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.48</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>6.319</v>
+        <v>7.709</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>6.506</v>
+        <v>7.853</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5805,28 +5798,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>0.012</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1479100</v>
+        <v>1755000</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H118" t="n">
-        <v>49.25</v>
+        <v>62.57</v>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
@@ -5834,10 +5827,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.989</v>
+        <v>0.408</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.976</v>
+        <v>0.409</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5850,39 +5843,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>-0.0116</v>
+        <v>-0.035</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1476600</v>
+        <v>1753100</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>1.87</v>
+        <v>0.77</v>
       </c>
       <c r="H119" t="n">
-        <v>56</v>
-      </c>
-      <c r="I119" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.07</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.652</v>
+        <v>1.416</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.727</v>
+        <v>1.315</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5895,39 +5888,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E120" s="16" t="n">
-        <v>-0.0058</v>
+        <v>0.41</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1476100</v>
+        <v>1737900</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.48</v>
+        <v>1.12</v>
       </c>
       <c r="H120" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.7</v>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.858</v>
+        <v>0.369</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.855</v>
+        <v>0.336</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5940,28 +5933,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>0.002</v>
+        <v>1.7</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1468200</v>
+        <v>1688700</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.08</v>
+        <v>2.14</v>
       </c>
       <c r="H121" t="n">
-        <v>44.52</v>
+        <v>54.71</v>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
@@ -5969,10 +5962,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>10.17</v>
+        <v>1.651</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>10.333</v>
+        <v>1.727</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5985,33 +5978,40 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>-0.0102</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1453200</v>
+        <v>1658200</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.08</v>
+        <v>0.51</v>
+      </c>
+      <c r="H122" t="n">
+        <v>71.70999999999999</v>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J122" s="9" t="n"/>
-      <c r="K122" s="9" t="n"/>
+      <c r="J122" s="9" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>0.402</v>
+      </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
     </row>
@@ -6023,28 +6023,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="E123" s="17" t="n">
-        <v>0.0123</v>
+        <v>0.525</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1449800</v>
+        <v>1632500</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="H123" t="n">
-        <v>34.04</v>
+        <v>57.22</v>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>13.506</v>
+        <v>0.511</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>14.083</v>
+        <v>0.461</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6068,28 +6068,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.41</v>
+        <v>7.9</v>
       </c>
       <c r="E124" s="16" t="n">
-        <v>-0.012</v>
+        <v>-0.0075</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1429200</v>
+        <v>1624100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="H124" t="n">
-        <v>53.93</v>
+        <v>57.81</v>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.399</v>
+        <v>7.786</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.398</v>
+        <v>7.724</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>7.47</v>
+        <v>0.32</v>
       </c>
       <c r="E125" s="17" t="n">
-        <v>0.0013</v>
+        <v>0.0492</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1418800</v>
+        <v>1607000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.19</v>
+        <v>1.95</v>
       </c>
       <c r="H125" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.23</v>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>7.709</v>
+        <v>0.297</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>7.853</v>
+        <v>0.28</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6158,28 +6158,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.36</v>
+        <v>10.16</v>
       </c>
       <c r="E126" s="17" t="n">
-        <v>0.0286</v>
+        <v>0.004</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1400400</v>
+        <v>1605700</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H126" t="n">
-        <v>65.7</v>
+        <v>46.29</v>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.334</v>
+        <v>10.171</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.318</v>
+        <v>10.334</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6203,39 +6203,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.945</v>
+        <v>0.73</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>0.0216</v>
+        <v>0.0069</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1348500</v>
+        <v>1586800</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="H127" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="I127" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.16</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.907</v>
+        <v>0.739</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.776</v>
+        <v>0.753</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6248,28 +6248,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.61</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1292300</v>
+        <v>1558800</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H128" t="n">
-        <v>41.55</v>
+        <v>59.86</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.292</v>
+        <v>0.608</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.324</v>
+        <v>0.587</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6293,28 +6293,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.35</v>
+        <v>2.99</v>
       </c>
       <c r="E129" s="16" t="n">
-        <v>-0.0541</v>
+        <v>-0.0033</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1284300</v>
+        <v>1548700</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H129" t="n">
-        <v>53.62</v>
+        <v>47.64</v>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.351</v>
+        <v>3.011</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.318</v>
+        <v>3.04</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6338,28 +6338,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.525</v>
+        <v>13.24</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0138</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1259900</v>
+        <v>1542800</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H130" t="n">
-        <v>52.8</v>
+        <v>34.97</v>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.518</v>
+        <v>13.508</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.53</v>
+        <v>14.083</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6383,39 +6383,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>0.0573</v>
+        <v>0.295</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1258300</v>
+        <v>1503200</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="H131" t="n">
-        <v>68.12</v>
-      </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.56</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>2.197</v>
+        <v>0.295</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>2.016</v>
+        <v>0.297</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6428,28 +6428,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.58</v>
+        <v>0.86</v>
       </c>
       <c r="E132" s="16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0058</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1256800</v>
+        <v>1476100</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="H132" t="n">
-        <v>43.05</v>
+        <v>52.97</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.588</v>
+        <v>0.858</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.587</v>
+        <v>0.855</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6473,28 +6473,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>-0.0059</v>
+        <v>-0.012</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1255900</v>
+        <v>1455000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="H133" t="n">
-        <v>64.22</v>
+        <v>53.93</v>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
@@ -6502,10 +6502,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.797</v>
+        <v>0.399</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.714</v>
+        <v>0.398</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6518,39 +6518,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>EPICON</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>0</v>
+        <v>1.89</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1233800</v>
+        <v>1430000</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>1.11</v>
+        <v>0.31</v>
       </c>
       <c r="H134" t="n">
-        <v>55.84</v>
-      </c>
-      <c r="I134" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.12</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.199</v>
+        <v>1.964</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.206</v>
+        <v>2.085</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6563,39 +6563,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.89</v>
+        <v>0.735</v>
       </c>
       <c r="E135" s="17" t="n">
-        <v>0.0053</v>
+        <v>0.028</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1230700</v>
+        <v>1387600</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="H135" t="n">
-        <v>36.12</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.70999999999999</v>
+      </c>
+      <c r="I135" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.964</v>
+        <v>0.667</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>2.085</v>
+        <v>0.61</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6608,39 +6608,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LAYHONG</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>-0.0209</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1223600</v>
+        <v>1381600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>2.11</v>
+        <v>0.21</v>
       </c>
       <c r="H136" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="I136" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.06</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.247</v>
+        <v>1.919</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.244</v>
+        <v>1.971</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6653,39 +6653,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>1374300</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H137" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="I137" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K137" s="9" t="n">
         <v>0.53</v>
-      </c>
-      <c r="E137" s="16" t="n">
-        <v>-0.009300000000000001</v>
-      </c>
-      <c r="F137" s="11" t="n">
-        <v>1220900</v>
-      </c>
-      <c r="G137" s="12" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H137" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="I137" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J137" s="9" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="K137" s="9" t="n">
-        <v>0.461</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6698,28 +6698,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>3.34</v>
+        <v>0.945</v>
       </c>
       <c r="E138" s="17" t="n">
-        <v>0.0091</v>
+        <v>0.0216</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1211700</v>
+        <v>1368700</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="H138" t="n">
-        <v>78.62</v>
+        <v>60.38</v>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>2.909</v>
+        <v>0.907</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>2.497</v>
+        <v>0.776</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6743,28 +6743,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="E139" s="17" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0573</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1194100</v>
+        <v>1364100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.19</v>
+        <v>0.98</v>
       </c>
       <c r="H139" t="n">
-        <v>47.91</v>
+        <v>68.12</v>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.77</v>
+        <v>2.197</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.807</v>
+        <v>2.016</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6788,39 +6788,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>0.0141</v>
+        <v>0.35</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1181600</v>
+        <v>1304300</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="H140" t="n">
-        <v>43.39</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I140" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.365</v>
+        <v>0.351</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.395</v>
+        <v>0.318</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6833,28 +6833,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>-0.0033</v>
+        <v>0.845</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1159100</v>
+        <v>1295300</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="H141" t="n">
-        <v>47.64</v>
+        <v>65.62</v>
       </c>
       <c r="I141" s="15" t="inlineStr">
         <is>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>3.011</v>
+        <v>0.797</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>3.04</v>
+        <v>0.714</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6878,39 +6878,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E142" s="16" t="n">
-        <v>-0.0157</v>
+        <v>3.35</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1142600</v>
+        <v>1279500</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H142" t="n">
-        <v>43.19</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.84</v>
+      </c>
+      <c r="I142" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1.92</v>
+        <v>2.91</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.971</v>
+        <v>2.497</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6923,39 +6923,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>EPICON</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.205</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1091800</v>
+        <v>1243800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.37</v>
+        <v>1.12</v>
       </c>
       <c r="H143" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.84</v>
+      </c>
+      <c r="I143" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.608</v>
+        <v>0.199</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.587</v>
+        <v>0.206</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6968,28 +6968,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>LAYHONG</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1077600</v>
+        <v>1223600</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.16</v>
+        <v>2.11</v>
       </c>
       <c r="H144" t="n">
-        <v>51.98</v>
+        <v>55.11</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>2.566</v>
+        <v>0.247</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>2.532</v>
+        <v>0.244</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7013,28 +7013,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.655</v>
+        <v>2.59</v>
       </c>
       <c r="E145" s="17" t="n">
-        <v>0.0077</v>
+        <v>0.0117</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1055900</v>
+        <v>1196200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="H145" t="n">
-        <v>72.5</v>
+        <v>53.03</v>
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
@@ -7042,10 +7042,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.633</v>
+        <v>2.567</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.589</v>
+        <v>2.532</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7058,28 +7058,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.4</v>
+        <v>0.36</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>0.0294</v>
+        <v>0.0141</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1021300</v>
+        <v>1181600</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.32</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H146" t="n">
-        <v>60.62</v>
+        <v>43.39</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.341</v>
+        <v>0.365</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.138</v>
+        <v>0.395</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7103,39 +7103,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.74</v>
+        <v>1.4</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.035</v>
+        <v>0.0294</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1001300</v>
+        <v>1168500</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H147" t="n">
-        <v>71.39</v>
-      </c>
-      <c r="I147" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.62</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.668</v>
+        <v>1.341</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.61</v>
+        <v>1.138</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7148,39 +7148,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="E148" s="16" t="n">
-        <v>-0.0103</v>
+        <v>2.67</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>939100</v>
+        <v>1164400</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="H148" t="n">
-        <v>49.01</v>
-      </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45</v>
+      </c>
+      <c r="I148" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>5.808</v>
+        <v>2.679</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>5.731</v>
+        <v>2.884</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7193,39 +7193,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E149" s="17" t="n">
-        <v>0.006999999999999999</v>
+        <v>5.73</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>901200</v>
+        <v>1073000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H149" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="I149" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.5</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.707</v>
+        <v>5.806</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.714</v>
+        <v>5.731</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7238,39 +7238,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E150" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.655</v>
+      </c>
+      <c r="E150" s="17" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>867300</v>
+        <v>1056900</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="H150" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.5</v>
+      </c>
+      <c r="I150" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
         <v>0.633</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.628</v>
+        <v>0.589</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7283,28 +7283,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>-0.0101</v>
+        <v>0.255</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>0.0408</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>857200</v>
+        <v>1038800</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="H151" t="n">
-        <v>56.57</v>
+        <v>48.64</v>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>7.784</v>
+        <v>0.252</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>7.723</v>
+        <v>0.272</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7328,28 +7328,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.615</v>
+        <v>1.08</v>
       </c>
       <c r="E152" s="16" t="n">
-        <v>-0.0315</v>
+        <v>-0.027</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>826300</v>
+        <v>938400</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="H152" t="n">
-        <v>72.16</v>
+        <v>44.61</v>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.552</v>
+        <v>1.102</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.489</v>
+        <v>1.12</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7373,39 +7373,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E153" s="17" t="n">
-        <v>0.0037</v>
+        <v>0.92</v>
+      </c>
+      <c r="E153" s="16" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>817700</v>
+        <v>926100</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.09</v>
+        <v>0.4</v>
       </c>
       <c r="H153" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="I153" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.46</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>2.68</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>2.884</v>
+        <v>0.954</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7418,28 +7418,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>2.02</v>
+        <v>0.72</v>
       </c>
       <c r="E154" s="17" t="n">
-        <v>0.0254</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>809700</v>
+        <v>917300</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
       <c r="H154" t="n">
-        <v>63.89</v>
+        <v>55.83</v>
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.87</v>
+        <v>0.707</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.869</v>
+        <v>0.714</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7463,39 +7463,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.62</v>
+        <v>7.72</v>
       </c>
       <c r="E155" s="17" t="n">
-        <v>0.0318</v>
+        <v>0.0198</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>756400</v>
+        <v>912000</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.55</v>
+        <v>0.23</v>
       </c>
       <c r="H155" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.83</v>
+      </c>
+      <c r="I155" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.632</v>
+        <v>7.651</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.694</v>
+        <v>7.801</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7508,28 +7508,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>7.73</v>
+        <v>2.03</v>
       </c>
       <c r="E156" s="17" t="n">
-        <v>0.0211</v>
+        <v>0.0305</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>748500</v>
+        <v>878000</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H156" t="n">
-        <v>51.05</v>
+        <v>64.48</v>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>7.652</v>
+        <v>1.871</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>7.801</v>
+        <v>1.869</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7553,28 +7553,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>3.19</v>
+        <v>0.63</v>
       </c>
       <c r="E157" s="16" t="n">
-        <v>-0.0031</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>745500</v>
+        <v>867300</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="H157" t="n">
-        <v>34.12</v>
+        <v>47.14</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>3.309</v>
+        <v>0.633</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>3.497</v>
+        <v>0.628</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7598,28 +7598,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E158" s="17" t="n">
-        <v>0.0114</v>
+        <v>0.615</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>718100</v>
+        <v>843700</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="H158" t="n">
-        <v>66.67</v>
+        <v>72.16</v>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.822</v>
+        <v>0.552</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.727</v>
+        <v>0.489</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7643,39 +7643,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>8.66</v>
+        <v>1.29</v>
       </c>
       <c r="E159" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.0238</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>702900</v>
+        <v>814800</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>2.36</v>
+        <v>0.2</v>
       </c>
       <c r="H159" t="n">
-        <v>61.01</v>
-      </c>
-      <c r="I159" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.59</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>8.339</v>
+        <v>1.236</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>8.127000000000001</v>
+        <v>1.133</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7688,39 +7688,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0366</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>ICENTS</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>0</v>
+        <v>0.88</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>700000</v>
+        <v>810700</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.72</v>
+        <v>0.22</v>
       </c>
       <c r="H160" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.05</v>
+      </c>
+      <c r="I160" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.631</v>
+        <v>0.821</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.637</v>
+        <v>0.727</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7742,19 +7742,19 @@
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E161" s="17" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>686000</v>
+        <v>804600</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H161" t="n">
-        <v>43.8</v>
+        <v>45.62</v>
       </c>
       <c r="I161" s="15" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>2.066</v>
+        <v>2.067</v>
       </c>
       <c r="K161" s="9" t="n">
         <v>2.11</v>
@@ -7778,39 +7778,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E162" s="16" t="n">
-        <v>-0.018</v>
+        <v>7.9</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>660400</v>
+        <v>797900</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="H162" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="I162" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.72</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>1.103</v>
+        <v>7.86</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.12</v>
+        <v>7.791</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7823,39 +7823,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E163" s="17" t="n">
-        <v>0.008399999999999999</v>
+        <v>3.2</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>658400</v>
+        <v>797500</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H163" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="I163" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.77</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.569</v>
+        <v>3.31</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.575</v>
+        <v>3.497</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7868,28 +7868,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>2.93</v>
+        <v>1.96</v>
       </c>
       <c r="E164" s="17" t="n">
-        <v>0.0245</v>
+        <v>0.0103</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>646600</v>
+        <v>793800</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="H164" t="n">
-        <v>60.11</v>
+        <v>47.39</v>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>2.781</v>
+        <v>1.962</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>2.673</v>
+        <v>2.026</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7913,28 +7913,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E165" s="17" t="n">
-        <v>0.0206</v>
+        <v>7.81</v>
+      </c>
+      <c r="E165" s="16" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>637400</v>
+        <v>793300</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H165" t="n">
-        <v>50.65</v>
+        <v>34.14</v>
       </c>
       <c r="I165" s="15" t="inlineStr">
         <is>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.964</v>
+        <v>7.992</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>2.026</v>
+        <v>8.272</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7958,39 +7958,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="E166" s="16" t="n">
-        <v>-0.0026</v>
+        <v>1.61</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>631600</v>
+        <v>785500</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.05</v>
+        <v>0.57</v>
       </c>
       <c r="H166" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="I166" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.92</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>7.992</v>
+        <v>1.631</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>8.272</v>
+        <v>1.694</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -8003,28 +8003,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E167" s="17" t="n">
-        <v>0.0238</v>
+        <v>6.7</v>
+      </c>
+      <c r="E167" s="16" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>625700</v>
+        <v>772400</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H167" t="n">
-        <v>58.59</v>
+        <v>42.59</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>1.236</v>
+        <v>6.785</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>1.133</v>
+        <v>6.79</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8048,28 +8048,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>EITA</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.75</v>
+        <v>2.93</v>
       </c>
       <c r="E168" s="17" t="n">
-        <v>0.0274</v>
+        <v>0.0245</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>621100</v>
+        <v>762600</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>4.88</v>
+        <v>0.25</v>
       </c>
       <c r="H168" t="n">
-        <v>74.87</v>
+        <v>60.11</v>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
@@ -8077,10 +8077,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.672</v>
+        <v>2.781</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.609</v>
+        <v>2.673</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8093,39 +8093,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E169" s="16" t="n">
-        <v>-0.003</v>
+        <v>5.02</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>615200</v>
+        <v>723500</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H169" t="n">
-        <v>42.59</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.93</v>
+      </c>
+      <c r="I169" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>6.785</v>
+        <v>4.979</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>6.79</v>
+        <v>5.035</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8138,28 +8138,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>0</v>
+        <v>4.61</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>598700</v>
+        <v>706800</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2.03</v>
+        <v>0.14</v>
       </c>
       <c r="H170" t="n">
-        <v>59.87</v>
+        <v>37.27</v>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.578</v>
+        <v>4.739</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.53</v>
+        <v>5.008</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8183,28 +8183,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>597800</v>
+        <v>706500</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>2.05</v>
+        <v>0.31</v>
       </c>
       <c r="H171" t="n">
-        <v>40.26</v>
+        <v>31.42</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.119</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>0.846</v>
+        <v>1.153</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8228,39 +8228,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>UMSINT</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>0</v>
+        <v>8.66</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>596300</v>
+        <v>702900</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.14</v>
+        <v>2.36</v>
       </c>
       <c r="H172" t="n">
-        <v>53.72</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.01</v>
+      </c>
+      <c r="I172" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>7.86</v>
+        <v>8.339</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>7.791</v>
+        <v>8.127000000000001</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8273,39 +8273,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="E173" s="16" t="n">
-        <v>-0.0022</v>
+        <v>0.63</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>588300</v>
+        <v>700000</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="H173" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="I173" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.01</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>4.742</v>
+        <v>0.631</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>5.008</v>
+        <v>0.637</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8318,39 +8318,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E174" s="17" t="n">
-        <v>0.0177</v>
+        <v>3.01</v>
+      </c>
+      <c r="E174" s="16" t="n">
+        <v>-0.0131</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>583500</v>
+        <v>680600</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="H174" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="I174" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.61</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.084</v>
+        <v>3.081</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.061</v>
+        <v>3.156</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8363,28 +8363,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E175" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>6.53</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>581400</v>
+        <v>679200</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="H175" t="n">
-        <v>48.14</v>
+        <v>30.16</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.64</v>
+        <v>6.739</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.632</v>
+        <v>6.874</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8408,39 +8408,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>3.01</v>
+        <v>5.57</v>
       </c>
       <c r="E176" s="16" t="n">
-        <v>-0.0131</v>
+        <v>-0.0124</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>581400</v>
+        <v>675900</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H176" t="n">
-        <v>36.61</v>
-      </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.03</v>
+      </c>
+      <c r="I176" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>3.081</v>
+        <v>5.723</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>3.156</v>
+        <v>6.099</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8453,28 +8453,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="E177" s="16" t="n">
-        <v>-0.0142</v>
+        <v>0.595</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>564600</v>
+        <v>670500</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H177" t="n">
-        <v>38.7</v>
+        <v>57.39</v>
       </c>
       <c r="I177" s="15" t="inlineStr">
         <is>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>5.722</v>
+        <v>0.569</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>6.099</v>
+        <v>0.574</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8498,28 +8498,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>4.98</v>
+        <v>1.27</v>
       </c>
       <c r="E178" s="17" t="n">
-        <v>0.0061</v>
+        <v>0.0242</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>525300</v>
+        <v>655700</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.1</v>
+        <v>0.44</v>
       </c>
       <c r="H178" t="n">
-        <v>49.76</v>
+        <v>45.78</v>
       </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>4.975</v>
+        <v>1.283</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>5.035</v>
+        <v>1.35</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8543,39 +8543,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>8.83</v>
+        <v>0.635</v>
       </c>
       <c r="E179" s="17" t="n">
-        <v>0.0068</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>505100</v>
+        <v>651400</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H179" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="I179" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.14</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>8.689</v>
+        <v>0.64</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>8.548999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8588,28 +8588,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>EITA</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E180" s="16" t="n">
-        <v>-0.0048</v>
+        <v>0.75</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>501400</v>
+        <v>628700</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.4</v>
+        <v>4.93</v>
       </c>
       <c r="H180" t="n">
-        <v>40.28</v>
+        <v>74.87</v>
       </c>
       <c r="I180" s="15" t="inlineStr">
         <is>
@@ -8617,16 +8617,511 @@
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>2.083</v>
+        <v>0.672</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>2.112</v>
+        <v>0.609</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>600300</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H181" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="I181" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TEOSENG</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>597800</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H182" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>595400</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H183" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="I183" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>8.696</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>8.551</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E184" s="17" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>583500</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H184" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="I184" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E185" s="16" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>570000</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H185" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="I185" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>539000</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H186" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="I186" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>2.084</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5293</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AME</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>534200</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H187" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>9822</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>526400</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H188" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>4.202</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>4.343</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>KLK</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>526300</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H189" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="I189" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>22.414</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>21.853</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="E190" s="16" t="n">
+        <v>-0.0452</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>514600</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H190" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>5.911</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>5.535</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>512800</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H191" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I191" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>1.681</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M180"/>
+  <autoFilter ref="A1:M191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$194</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -576,10 +576,10 @@
         <v>0.0263</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>14778000</v>
+        <v>14933000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>66.84999999999999</v>
@@ -629,10 +629,10 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>6696600</v>
+        <v>6766700</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>11.29</v>
+        <v>11.41</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>69.83</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.245高于50日均线0.197，EMA20与SAR均呈多头，T3突破信号偏强；但RSI达69.83，接近超买区，可靠性略受抑制。</t>
+          <t>现价0.245高于50日均线0.197，EMA20与SAR均呈多头，T3形态突破。RSI 69.83接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -682,10 +682,10 @@
         <v>0.125</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7372200</v>
+        <v>7577700</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>6.42</v>
+        <v>6.6</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>81.89</v>
@@ -708,7 +708,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>RSI达81.89，处超买区间；现价0.27高于50日均线0.208约30%，EMA20与SAR多头排列，T3突破信号偏强，但超买或加大回调风险。</t>
+          <t>RSI达81.89，处超买区间；现价0.27高于50日均线0.208约30%，EMA20与SAR多头信号虽确认，但短线过热，可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.56高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破。RSI 64.42接近超买区但未破70，信号偏强。</t>
+          <t>现价0.56高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破；RSI 64.42接近超买区但未破70，信号偏强。</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.895</v>
+        <v>0.85</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.017</v>
+        <v>0.1039</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1244100</v>
+        <v>24202700</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.15</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>73.56</v>
+        <v>72.67</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.705</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.794</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>现价0.895高于50日均线0.794，EMA20与SAR均呈多头，T3突破有效；但RSI达73.56，已进入超买区，信号可靠性偏中性。</t>
+          <t>现价0.85高于50日均线0.685，EMA20与SAR均呈多头，T3形态突破；但RSI达72.67，已进入超买区，信号可靠性需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -826,28 +826,28 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.865</v>
+        <v>1.41</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1234</v>
+        <v>0.0217</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>23676300</v>
+        <v>1322500</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.93</v>
+        <v>0.7</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>73.77</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.707</v>
+        <v>1.353</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.324</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -867,62 +867,45 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.865高于50日均线0.685，EMA20与SAR均呈多头，T3形态突破；但RSI达73.77，已进入超买区，信号可靠性需留意短线过热。</t>
+          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3形态突破；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>5271</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>PECCA</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.0217</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>1322500</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>1.353</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>1.324</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3形态突破；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0041</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AIMAX</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>396633500</v>
+      </c>
+      <c r="G8" s="12" t="n"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -932,31 +915,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.015</v>
+        <v>0.19</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>257407400</v>
-      </c>
-      <c r="G9" s="12" t="n"/>
+        <v>51387400</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22.61</v>
+      </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.502</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
     </row>
@@ -968,39 +960,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.19</v>
+        <v>0.025</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>50531300</v>
+        <v>27142700</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.08</v>
+        <v>1.45</v>
       </c>
       <c r="H10" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.85</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.284</v>
+        <v>0.025</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.502</v>
+        <v>0.024</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -1013,39 +1005,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>27142700</v>
+        <v>26559000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="H11" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.28</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.025</v>
+        <v>0.241</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.024</v>
+        <v>0.25</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1058,28 +1050,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0435</v>
+        <v>4.84</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>26044400</v>
+        <v>24465200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="H12" t="n">
-        <v>32.28</v>
+        <v>62.36</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1087,10 +1079,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.241</v>
+        <v>4.724</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.25</v>
+        <v>4.495</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1103,39 +1095,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0.0021</v>
+        <v>0.585</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>24416900</v>
+        <v>24248200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="H13" t="n">
-        <v>62.88</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.34</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>4.725</v>
+        <v>0.543</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>4.495</v>
+        <v>0.491</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1148,28 +1140,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.585</v>
+        <v>0.245</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0168</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>24215700</v>
+        <v>22853800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="H14" t="n">
-        <v>71.34</v>
+        <v>31.96</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
@@ -1177,10 +1169,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.543</v>
+        <v>0.279</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.491</v>
+        <v>0.33</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1193,28 +1185,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.04</v>
+        <v>0.78</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>22800200</v>
+        <v>18572700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="H15" t="n">
-        <v>30.84</v>
+        <v>63.44</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1222,10 +1214,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.279</v>
+        <v>0.739</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.33</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1253,7 +1245,7 @@
         <v>-0.0375</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>18156300</v>
+        <v>18295600</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>0.39</v>
@@ -1283,28 +1275,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.78</v>
+        <v>0.155</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>17841500</v>
+        <v>17923700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.42</v>
+        <v>0.87</v>
       </c>
       <c r="H17" t="n">
-        <v>63.44</v>
+        <v>44.71</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1312,10 +1304,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.739</v>
+        <v>0.156</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1337,19 +1329,19 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.31</v>
+        <v>0.305</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>-0.0313</v>
+        <v>-0.0469</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>16585700</v>
+        <v>16835600</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="H18" t="n">
-        <v>61.04</v>
+        <v>59.16</v>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
@@ -1357,7 +1349,7 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.28</v>
+        <v>0.279</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0.275</v>
@@ -1373,28 +1365,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.155</v>
+        <v>0.055</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>16073700</v>
+        <v>15911400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.78</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>44.71</v>
+        <v>56.29</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -1402,10 +1394,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.156</v>
+        <v>0.053</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.16</v>
+        <v>0.043</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1418,39 +1410,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>2.1</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>15511400</v>
+        <v>15298100</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.76</v>
+        <v>0.96</v>
       </c>
       <c r="H20" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.053</v>
+        <v>2.132</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.043</v>
+        <v>2.059</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1463,39 +1455,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>0.0145</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>15258800</v>
+        <v>14961000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.95</v>
+        <v>3.35</v>
       </c>
       <c r="H21" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>95.37</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>2.132</v>
+        <v>0.837</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>2.059</v>
+        <v>0.721</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1508,28 +1500,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.31</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>14871200</v>
+        <v>13943300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>3.33</v>
+        <v>0.73</v>
       </c>
       <c r="H22" t="n">
-        <v>95.37</v>
+        <v>59.8</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1537,10 +1529,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.837</v>
+        <v>0.303</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.721</v>
+        <v>0.29</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1553,28 +1545,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>-0.0159</v>
+        <v>1.85</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0.0335</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13943300</v>
+        <v>13647300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H23" t="n">
-        <v>59.8</v>
+        <v>64.91</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -1582,10 +1574,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.303</v>
+        <v>1.726</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.29</v>
+        <v>1.51</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1598,39 +1590,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.0391</v>
+        <v>0.795</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>13605700</v>
+        <v>13431000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.52</v>
+        <v>1.03</v>
       </c>
       <c r="H24" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.727</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.511</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1643,39 +1635,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>13431000</v>
+        <v>13236300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="H25" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1688,28 +1680,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0.0213</v>
+        <v>0.22</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>13072100</v>
+        <v>12840700</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H26" t="n">
-        <v>56.19</v>
+        <v>71.25</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -1717,10 +1709,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.232</v>
+        <v>0.2</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.233</v>
+        <v>0.183</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1733,28 +1725,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.22</v>
+        <v>0.475</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.0435</v>
+        <v>-0.0104</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>12776000</v>
+        <v>11715100</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="H27" t="n">
-        <v>71.25</v>
+        <v>52.83</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1762,10 +1754,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.2</v>
+        <v>0.468</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.183</v>
+        <v>0.47</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1787,19 +1779,19 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>0.0444</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>11601700</v>
+        <v>11703100</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0.93</v>
       </c>
       <c r="H28" t="n">
-        <v>72.83</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1823,39 +1815,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>-0.0104</v>
+        <v>0.525</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>11581700</v>
+        <v>11477300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.46</v>
+        <v>0.29</v>
       </c>
       <c r="H29" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.94</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.468</v>
+        <v>0.644</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.47</v>
+        <v>0.863</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1868,28 +1860,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>-0.0095</v>
+        <v>0.45</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>11428500</v>
+        <v>11146000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.29</v>
+        <v>1.44</v>
       </c>
       <c r="H30" t="n">
-        <v>25.6</v>
+        <v>54.08</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1897,10 +1889,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.644</v>
+        <v>0.444</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.863</v>
+        <v>0.403</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1928,7 +1920,7 @@
         <v>-0.005699999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>11049200</v>
+        <v>11140000</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0.62</v>
@@ -1958,39 +1950,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.45</v>
+        <v>2.86</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.1042</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>10633600</v>
+        <v>10525900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="H32" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.73</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.444</v>
+        <v>2.607</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.403</v>
+        <v>2.484</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -2003,28 +1995,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0.1081</v>
+        <v>0.765</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>10445500</v>
+        <v>10500400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.63</v>
+        <v>0.86</v>
       </c>
       <c r="H33" t="n">
-        <v>67.09999999999999</v>
+        <v>45.47</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
@@ -2032,10 +2024,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.608</v>
+        <v>0.773</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.485</v>
+        <v>0.774</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2093,39 +2085,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>-0.013</v>
+        <v>0.165</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>9936400</v>
+        <v>9230800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.82</v>
+        <v>0.32</v>
       </c>
       <c r="H35" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.16</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.773</v>
+        <v>0.183</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.774</v>
+        <v>0.224</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2153,7 +2145,7 @@
         <v>0.0361</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>9039400</v>
+        <v>9141100</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0.39</v>
@@ -2183,39 +2175,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>0.76</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8898100</v>
+        <v>8756500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.31</v>
+        <v>1.69</v>
       </c>
       <c r="H37" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.72</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.183</v>
+        <v>0.678</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.224</v>
+        <v>0.607</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2228,28 +2220,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.765</v>
+        <v>0.955</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.0132</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>8587000</v>
+        <v>8646500</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="H38" t="n">
-        <v>70.27</v>
+        <v>79.42</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2257,10 +2249,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.679</v>
+        <v>0.878</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.607</v>
+        <v>0.85</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2288,10 +2280,10 @@
         <v>-0.0432</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>8551500</v>
+        <v>8606700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H39" t="n">
         <v>45.67</v>
@@ -2318,39 +2310,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.19</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>8459500</v>
+        <v>8225100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>2.39</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>79.42</v>
-      </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.21</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.878</v>
+        <v>0.197</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.85</v>
+        <v>0.196</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2363,39 +2355,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>5.88</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0.0138</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8069100</v>
+        <v>8191400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.98</v>
+        <v>0.55</v>
       </c>
       <c r="H41" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.13</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.197</v>
+        <v>5.673</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.196</v>
+        <v>5.099</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2408,28 +2400,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>5.9</v>
+        <v>0.17</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0.0172</v>
+        <v>0.0303</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>7939100</v>
+        <v>7918000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.53</v>
+        <v>0.17</v>
       </c>
       <c r="H42" t="n">
-        <v>63.7</v>
+        <v>73.31</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -2437,10 +2429,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.675</v>
+        <v>0.142</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>5.1</v>
+        <v>0.114</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2453,28 +2445,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.17</v>
+        <v>2.41</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>0.0303</v>
+        <v>0.0299</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>7776300</v>
+        <v>7818700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.17</v>
+        <v>0.44</v>
       </c>
       <c r="H43" t="n">
-        <v>73.31</v>
+        <v>55.74</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2482,10 +2474,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.142</v>
+        <v>2.35</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.114</v>
+        <v>2.232</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2498,28 +2490,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0.0299</v>
+        <v>0.155</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>7773600</v>
+        <v>6895100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.44</v>
+        <v>0.17</v>
       </c>
       <c r="H44" t="n">
-        <v>55.74</v>
+        <v>49.56</v>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
@@ -2527,10 +2519,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>2.35</v>
+        <v>0.159</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.232</v>
+        <v>0.148</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2558,7 +2550,7 @@
         <v>-0.0185</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>6815700</v>
+        <v>6821400</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0.39</v>
@@ -2581,39 +2573,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.115</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>6756800</v>
+        <v>6490200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.16</v>
+        <v>0.52</v>
       </c>
       <c r="H46" t="n">
-        <v>49.56</v>
-      </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.46</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.159</v>
+        <v>0.119</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.148</v>
+        <v>0.106</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2626,39 +2618,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>6314300</v>
+        <v>6183500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="H47" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.81</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.119</v>
+        <v>0.197</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.106</v>
+        <v>0.171</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2671,28 +2663,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.235</v>
+        <v>0.785</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0682</v>
+        <v>0.0064</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>6143500</v>
+        <v>6108200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.42</v>
+        <v>1.08</v>
       </c>
       <c r="H48" t="n">
-        <v>68.06</v>
+        <v>86.31</v>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
@@ -2700,10 +2692,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.197</v>
+        <v>0.766</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.171</v>
+        <v>0.751</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2716,39 +2708,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.785</v>
+        <v>0.605</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.0168</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>6108200</v>
+        <v>6019500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="H49" t="n">
-        <v>86.31</v>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.06</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.766</v>
+        <v>0.608</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.751</v>
+        <v>0.603</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2761,39 +2753,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>6007500</v>
+        <v>5958600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.61</v>
+        <v>2.26</v>
       </c>
       <c r="H50" t="n">
-        <v>45.18</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.75</v>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.608</v>
+        <v>0.757</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.603</v>
+        <v>0.74</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2806,28 +2798,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.795</v>
+        <v>0.335</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>0.0258</v>
+        <v>0.0152</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>5918600</v>
+        <v>5590200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>2.24</v>
+        <v>0.62</v>
       </c>
       <c r="H51" t="n">
-        <v>59.89</v>
+        <v>95.37</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2835,10 +2827,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.756</v>
+        <v>0.262</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.74</v>
+        <v>0.218</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2851,28 +2843,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.33</v>
+        <v>0.295</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5575900</v>
+        <v>5383000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="H52" t="n">
-        <v>95.13</v>
+        <v>68.41</v>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
@@ -2880,10 +2872,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.261</v>
+        <v>0.273</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.218</v>
+        <v>0.269</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2896,28 +2888,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>0.0381</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>5382800</v>
+        <v>5178700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.89</v>
+        <v>0.35</v>
       </c>
       <c r="H53" t="n">
-        <v>68.41</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -2925,10 +2917,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.273</v>
+        <v>0.467</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.269</v>
+        <v>0.397</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2941,28 +2933,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>0.0286</v>
+        <v>1.04</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5178200</v>
+        <v>5158700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.35</v>
+        <v>0.64</v>
       </c>
       <c r="H54" t="n">
-        <v>68.8</v>
+        <v>77.8</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2970,10 +2962,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.466</v>
+        <v>0.875</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.397</v>
+        <v>0.752</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2986,28 +2978,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>-0.028</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>5158700</v>
+        <v>5118800</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.64</v>
+        <v>1.52</v>
       </c>
       <c r="H55" t="n">
-        <v>77.8</v>
+        <v>51.24</v>
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
@@ -3015,10 +3007,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.875</v>
+        <v>0.804</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.752</v>
+        <v>0.806</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -3031,39 +3023,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>0.0125</v>
+        <v>0.1</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>5118100</v>
+        <v>5028300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="H56" t="n">
-        <v>51.24</v>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.804</v>
+        <v>0.102</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.806</v>
+        <v>0.096</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3076,39 +3068,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0.0275</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>5028300</v>
+        <v>4821300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.11</v>
+        <v>0.39</v>
       </c>
       <c r="H57" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.83</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.102</v>
+        <v>0.998</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.096</v>
+        <v>0.837</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3121,28 +3113,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.11</v>
+        <v>4.17</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>0.0183</v>
+        <v>0.0692</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4773100</v>
+        <v>4635200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.39</v>
+        <v>1.05</v>
       </c>
       <c r="H58" t="n">
-        <v>80.11</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3150,10 +3142,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.997</v>
+        <v>3.49</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.837</v>
+        <v>3.205</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3166,28 +3158,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>4.18</v>
+        <v>2.9</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.0718</v>
+        <v>0.0781</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4613200</v>
+        <v>4439800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="H59" t="n">
-        <v>80.14</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -3195,10 +3187,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>3.491</v>
+        <v>2.117</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>3.205</v>
+        <v>1.74</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3211,28 +3203,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.9</v>
+        <v>0.225</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>0.0781</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4397200</v>
+        <v>4201800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.94</v>
+        <v>0.68</v>
       </c>
       <c r="H60" t="n">
-        <v>89.54000000000001</v>
+        <v>57.04</v>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
@@ -3240,10 +3232,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.117</v>
+        <v>0.214</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.74</v>
+        <v>0.211</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3301,28 +3293,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4136200</v>
+        <v>4084000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.67</v>
+        <v>0.35</v>
       </c>
       <c r="H62" t="n">
-        <v>57.04</v>
+        <v>39.54</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
@@ -3330,10 +3322,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.214</v>
+        <v>0.274</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.211</v>
+        <v>0.316</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3355,19 +3347,19 @@
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>-0.0086</v>
+        <v>1.16</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3875200</v>
+        <v>3989300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H63" t="n">
-        <v>46.5</v>
+        <v>47.72</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3375,7 +3367,7 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.181</v>
+        <v>1.182</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>1.135</v>
@@ -3391,28 +3383,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3851400</v>
+        <v>3936400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.51</v>
+        <v>1.15</v>
       </c>
       <c r="H64" t="n">
-        <v>61.25</v>
+        <v>54.65</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3420,10 +3412,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.307</v>
+        <v>0.337</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.294</v>
+        <v>0.332</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3436,39 +3428,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.11</v>
+        <v>2.21</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>-0.0263</v>
+        <v>-0.0391</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3769300</v>
+        <v>3861400</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="H65" t="n">
-        <v>56.51</v>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.04</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.085</v>
+        <v>2.221</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.023</v>
+        <v>2.099</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3481,39 +3473,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>-0.0391</v>
+        <v>0.31</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3721000</v>
+        <v>3851400</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H66" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.25</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.221</v>
+        <v>0.307</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.099</v>
+        <v>0.294</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3535,19 +3527,19 @@
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.535</v>
+        <v>0.54</v>
       </c>
       <c r="E67" s="17" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0189</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3510100</v>
+        <v>3832200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="H67" t="n">
-        <v>56.16</v>
+        <v>57.18</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3555,7 +3547,7 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.519</v>
+        <v>0.52</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>0.473</v>
@@ -3571,28 +3563,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3503000</v>
+        <v>3789200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="H68" t="n">
-        <v>39.54</v>
+        <v>58.3</v>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
@@ -3600,10 +3592,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.274</v>
+        <v>1.086</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.316</v>
+        <v>1.023</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3616,33 +3608,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0.0536</v>
+        <v>3.5</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3493100</v>
+        <v>3662800</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.15</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H69" t="n">
+        <v>37.22</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J69" s="9" t="n"/>
-      <c r="K69" s="9" t="n"/>
+      <c r="J69" s="9" t="n">
+        <v>3.628</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>3.708</v>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
     </row>
@@ -3654,40 +3653,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0.0536</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3443700</v>
+        <v>3495900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H70" t="n">
-        <v>46.15</v>
+        <v>0.15</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J70" s="9" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K70" s="9" t="n">
-        <v>0.773</v>
-      </c>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
     </row>
@@ -3699,39 +3691,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.765</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3417600</v>
+        <v>3469700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.15</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.434</v>
+        <v>0.774</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.267</v>
+        <v>0.773</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3744,39 +3736,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>-0.0171</v>
+        <v>2.48</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3362800</v>
+        <v>3432000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.74</v>
+        <v>0.21</v>
       </c>
       <c r="H72" t="n">
-        <v>34.09</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.9</v>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>3.623</v>
+        <v>2.434</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>3.707</v>
+        <v>2.267</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3789,33 +3781,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>0.895</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3357200</v>
+        <v>3413000</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I73" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
+        <v>1.13</v>
+      </c>
+      <c r="H73" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.969</v>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3827,40 +3826,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>-0.0515</v>
+        <v>0.48</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3279500</v>
+        <v>3358400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H74" t="n">
-        <v>67.95999999999999</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J74" s="9" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="K74" s="9" t="n">
-        <v>2.095</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3872,39 +3864,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0.08699999999999999</v>
+        <v>2.61</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0404</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3241000</v>
+        <v>3294500</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1.26</v>
+        <v>0.57</v>
       </c>
       <c r="H75" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="I75" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>71.06</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.023</v>
+        <v>2.427</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.876</v>
+        <v>2.095</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3917,28 +3909,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>3222800</v>
+        <v>3272100</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.26</v>
+        <v>1.27</v>
       </c>
       <c r="H76" t="n">
-        <v>35.36</v>
+        <v>83.5</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3946,10 +3938,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.333</v>
+        <v>1.023</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.452</v>
+        <v>0.876</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3971,19 +3963,19 @@
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>0.1098</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3210400</v>
+        <v>3258900</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H77" t="n">
-        <v>89.98</v>
+        <v>89.69</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3991,10 +3983,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.197</v>
+        <v>2.195</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.932</v>
+        <v>1.931</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -4007,28 +3999,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>3205400</v>
+        <v>3240300</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H78" t="n">
-        <v>50.52</v>
+        <v>33.75</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -4036,10 +4028,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.33</v>
+        <v>1.332</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.31</v>
+        <v>1.452</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4052,28 +4044,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>3117500</v>
+        <v>3233100</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.22</v>
+        <v>0.38</v>
       </c>
       <c r="H79" t="n">
-        <v>39.12</v>
+        <v>48.43</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4081,10 +4073,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.586</v>
+        <v>0.33</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1.65</v>
+        <v>0.31</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4097,39 +4089,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>3102100</v>
+        <v>3232800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H80" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.91</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.64</v>
+        <v>0.961</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.658</v>
+        <v>0.79</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4142,39 +4134,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.315</v>
+        <v>0.61</v>
       </c>
       <c r="E81" s="17" t="n">
-        <v>0.0161</v>
+        <v>0.0083</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>3065600</v>
+        <v>3212200</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="H81" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="I81" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.16</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.321</v>
+        <v>0.641</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.339</v>
+        <v>0.658</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4187,39 +4179,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.9</v>
+        <v>1.56</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>0.0112</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>3060800</v>
+        <v>3179100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="H82" t="n">
-        <v>35.53</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.51</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.928</v>
+        <v>1.587</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.969</v>
+        <v>1.65</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4232,39 +4224,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.335</v>
+        <v>0.315</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>0.0469</v>
+        <v>0.0161</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>3010000</v>
+        <v>3117000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.95</v>
+        <v>0.47</v>
       </c>
       <c r="H83" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.61</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.335</v>
+        <v>0.321</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.342</v>
+        <v>0.339</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4277,39 +4269,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>-0.0163</v>
+        <v>0.335</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0.0469</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2789900</v>
+        <v>3010000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.3</v>
+        <v>0.95</v>
       </c>
       <c r="H84" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.96</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>1.165</v>
+        <v>0.335</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.098</v>
+        <v>0.342</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4322,39 +4314,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0</v>
+        <v>4.41</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2786200</v>
+        <v>2945000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="H85" t="n">
-        <v>53.13</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.262</v>
+        <v>3.436</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.25</v>
+        <v>2.294</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4367,39 +4359,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>4.44</v>
+        <v>1.64</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>-0.022</v>
+        <v>-0.018</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2773500</v>
+        <v>2878000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
       <c r="H86" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.07</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>3.438</v>
+        <v>1.741</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.295</v>
+        <v>1.855</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4412,39 +4404,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>4.49</v>
+        <v>1.22</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.0197</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2772000</v>
+        <v>2849700</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H87" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.73</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>4.599</v>
+        <v>1.166</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>4.54</v>
+        <v>1.098</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4457,39 +4449,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0</v>
+        <v>4.8</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2763800</v>
+        <v>2836700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>4.77</v>
+        <v>0.13</v>
       </c>
       <c r="H88" t="n">
-        <v>55.34</v>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.253</v>
+        <v>4.851</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.264</v>
+        <v>4.967</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4502,38 +4494,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>2.92</v>
+        <v>4.48</v>
       </c>
       <c r="E89" s="16" t="n">
-        <v>-0.0168</v>
+        <v>-0.0218</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2710900</v>
+        <v>2797700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.86</v>
+        <v>0.37</v>
       </c>
       <c r="H89" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.81</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>2.853</v>
-      </c>
-      <c r="K89" s="9" t="n"/>
+        <v>4.598</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>4.539</v>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
     </row>
@@ -4545,28 +4539,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.265</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2686600</v>
+        <v>2786200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.13</v>
+        <v>0.88</v>
       </c>
       <c r="H90" t="n">
-        <v>40.8</v>
+        <v>53.13</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4574,10 +4568,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>4.851</v>
+        <v>0.262</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>4.967</v>
+        <v>0.25</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4590,39 +4584,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>-0.0396</v>
+        <v>0.26</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2611400</v>
+        <v>2763800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1.07</v>
+        <v>4.77</v>
       </c>
       <c r="H91" t="n">
-        <v>37.19</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.34</v>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.053</v>
+        <v>0.253</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.011</v>
+        <v>0.264</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4635,28 +4629,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0.0278</v>
+        <v>2.92</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2462100</v>
+        <v>2754600</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.53</v>
+        <v>0.87</v>
       </c>
       <c r="H92" t="n">
-        <v>84.40000000000001</v>
+        <v>53.97</v>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
@@ -4664,11 +4658,9 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K92" s="9" t="n">
-        <v>0.79</v>
-      </c>
+        <v>2.853</v>
+      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
     </row>
@@ -4680,28 +4672,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.65</v>
+        <v>0.97</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>-0.012</v>
+        <v>-0.0396</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2444900</v>
+        <v>2629900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.39</v>
+        <v>1.08</v>
       </c>
       <c r="H93" t="n">
-        <v>31.96</v>
+        <v>37.19</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4709,10 +4701,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.742</v>
+        <v>1.053</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.856</v>
+        <v>1.011</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4725,28 +4717,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.66</v>
+        <v>1.52</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>0.0233</v>
+        <v>0.034</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2419300</v>
+        <v>2470800</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.25</v>
+        <v>0.99</v>
       </c>
       <c r="H94" t="n">
-        <v>59.78</v>
+        <v>56.61</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
@@ -4754,10 +4746,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.63</v>
+        <v>1.479</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.571</v>
+        <v>1.536</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4770,39 +4762,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>0.0331</v>
+        <v>0.0233</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2397900</v>
+        <v>2464300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="H95" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.78</v>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.853</v>
+        <v>0.571</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4815,28 +4807,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.585</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2336200</v>
+        <v>2432900</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="H96" t="n">
-        <v>36.45</v>
+        <v>46.87</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4844,10 +4836,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.589</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.592</v>
+        <v>0.587</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4860,39 +4852,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="E97" s="17" t="n">
-        <v>0.0351</v>
+        <v>0.0199</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2332300</v>
+        <v>2418100</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="H97" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.99</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.592</v>
+        <v>0.799</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.611</v>
+        <v>0.852</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4905,39 +4897,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>0.034</v>
+        <v>0.535</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2298900</v>
+        <v>2339100</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.92</v>
+        <v>0.35</v>
       </c>
       <c r="H98" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.57</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.479</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.536</v>
+        <v>0.592</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4950,28 +4942,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="E99" s="17" t="n">
-        <v>0.0492</v>
+        <v>0.0351</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2240200</v>
+        <v>2332900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="H99" t="n">
-        <v>65.88</v>
+        <v>47.34</v>
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
@@ -4979,10 +4971,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.889</v>
+        <v>0.592</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.802</v>
+        <v>0.611</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -5004,19 +4996,19 @@
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.68</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>0.0074</v>
+        <v>0.0148</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2173800</v>
+        <v>2287100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H100" t="n">
-        <v>50.85</v>
+        <v>51.73</v>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
@@ -5040,39 +5032,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>-0.0115</v>
+        <v>0.96</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>0.0492</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2085000</v>
+        <v>2251100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="H101" t="n">
-        <v>30.98</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.88</v>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>2.679</v>
+        <v>0.889</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.795</v>
+        <v>0.802</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5085,28 +5077,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>2081400</v>
+        <v>2124000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.33</v>
+        <v>0.61</v>
       </c>
       <c r="H102" t="n">
-        <v>46.62</v>
+        <v>71.41</v>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
@@ -5114,10 +5106,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.769</v>
+        <v>1.1</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.807</v>
+        <v>0.999</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5130,28 +5122,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>-0.0016</v>
+        <v>1.75</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2022700</v>
+        <v>2117800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="H103" t="n">
-        <v>41.98</v>
+        <v>46.62</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5159,10 +5151,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>6.318</v>
+        <v>1.769</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>6.506</v>
+        <v>1.807</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5175,28 +5167,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>4.77</v>
+        <v>2.57</v>
       </c>
       <c r="E104" s="16" t="n">
-        <v>-0.0021</v>
+        <v>-0.0115</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1947200</v>
+        <v>2103000</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.23</v>
+        <v>0.66</v>
       </c>
       <c r="H104" t="n">
-        <v>55.72</v>
+        <v>30.98</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5204,10 +5196,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>4.746</v>
+        <v>2.679</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>4.584</v>
+        <v>2.795</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5220,39 +5212,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.58</v>
+        <v>6.24</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0016</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1944900</v>
+        <v>2079600</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.51</v>
+        <v>0.12</v>
       </c>
       <c r="H105" t="n">
-        <v>43.05</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.98</v>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.588</v>
+        <v>6.318</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.587</v>
+        <v>6.506</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5265,33 +5257,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.29</v>
+        <v>4.77</v>
       </c>
       <c r="E106" s="16" t="n">
-        <v>-0.0169</v>
+        <v>-0.0021</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1928100</v>
+        <v>2044000</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="H106" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>4.746</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>4.584</v>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5303,28 +5302,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>3.53</v>
+        <v>2.62</v>
       </c>
       <c r="E107" s="17" t="n">
-        <v>0.0352</v>
+        <v>0.0038</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1921200</v>
+        <v>1957400</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="H107" t="n">
-        <v>73.55</v>
+        <v>55.6</v>
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
@@ -5332,10 +5331,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>3.271</v>
+        <v>2.587</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.859</v>
+        <v>2.433</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5348,40 +5347,33 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1881400</v>
+        <v>1951500</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H108" t="n">
-        <v>54.87</v>
+        <v>0.1</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J108" s="9" t="n">
-        <v>2.586</v>
-      </c>
-      <c r="K108" s="9" t="n">
-        <v>2.432</v>
-      </c>
+      <c r="J108" s="9" t="n"/>
+      <c r="K108" s="9" t="n"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
     </row>
@@ -5393,39 +5385,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="E109" s="17" t="n">
-        <v>0.02</v>
+        <v>0.0411</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1880200</v>
+        <v>1921700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="H109" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.2</v>
+      </c>
+      <c r="I109" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.055</v>
+        <v>3.273</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.073</v>
+        <v>2.859</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5438,39 +5430,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>4.02</v>
+        <v>1.02</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>0.0308</v>
+        <v>0.02</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1842900</v>
+        <v>1884500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.52</v>
+        <v>0.38</v>
       </c>
       <c r="H110" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="I110" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.46</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>3.726</v>
+        <v>1.055</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>3.374</v>
+        <v>1.073</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5483,39 +5475,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.355</v>
+        <v>0.635</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>0.0143</v>
+        <v>0.0325</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1824900</v>
+        <v>1866700</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="H111" t="n">
-        <v>64.01000000000001</v>
-      </c>
-      <c r="I111" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.73</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.334</v>
+        <v>0.614</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.318</v>
+        <v>0.579</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5528,39 +5520,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.28</v>
+        <v>0.355</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>0.0159</v>
+        <v>0.0143</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1820300</v>
+        <v>1862700</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="H112" t="n">
-        <v>44.51</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.01000000000001</v>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.292</v>
+        <v>0.334</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.324</v>
+        <v>0.318</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5573,28 +5565,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0</v>
+        <v>4.01</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1798500</v>
+        <v>1846200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="H113" t="n">
-        <v>49.25</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
@@ -5602,10 +5594,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.989</v>
+        <v>3.726</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.976</v>
+        <v>3.374</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5618,39 +5610,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0159</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1777500</v>
+        <v>1833200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="H114" t="n">
-        <v>70.44</v>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.51</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.099</v>
+        <v>1.292</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.999</v>
+        <v>1.324</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5663,39 +5655,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0.0244</v>
+        <v>1.98</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1762500</v>
+        <v>1814000</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="H115" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.25</v>
+      </c>
+      <c r="I115" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.614</v>
+        <v>1.989</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.579</v>
+        <v>1.976</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5708,39 +5700,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>0.0392</v>
+        <v>7.46</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1760100</v>
+        <v>1777600</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>1.35</v>
+        <v>0.24</v>
       </c>
       <c r="H116" t="n">
-        <v>59.89</v>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.95</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.257</v>
+        <v>7.708</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.259</v>
+        <v>7.853</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5753,39 +5745,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>7.47</v>
+        <v>10.16</v>
       </c>
       <c r="E117" s="17" t="n">
-        <v>0.0013</v>
+        <v>0.004</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1755800</v>
+        <v>1776300</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="H117" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.29</v>
+      </c>
+      <c r="I117" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>7.709</v>
+        <v>10.171</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>7.853</v>
+        <v>10.334</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5813,7 +5805,7 @@
         <v>0.012</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1755000</v>
+        <v>1761400</v>
       </c>
       <c r="G118" s="12" t="n">
         <v>0.16</v>
@@ -5843,39 +5835,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>-0.035</v>
+        <v>0.265</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1753100</v>
+        <v>1760100</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.77</v>
+        <v>1.35</v>
       </c>
       <c r="H119" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.89</v>
+      </c>
+      <c r="I119" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.416</v>
+        <v>0.257</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.315</v>
+        <v>0.259</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5888,39 +5880,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>1.37</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>-0.042</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1737900</v>
+        <v>1753400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>1.12</v>
+        <v>0.77</v>
       </c>
       <c r="H120" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.69</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.369</v>
+        <v>1.415</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.336</v>
+        <v>1.315</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5933,28 +5925,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>-0.0173</v>
+        <v>0.41</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1688700</v>
+        <v>1738900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>2.14</v>
+        <v>1.12</v>
       </c>
       <c r="H121" t="n">
-        <v>54.71</v>
+        <v>73.7</v>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
@@ -5962,10 +5954,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.651</v>
+        <v>0.369</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.727</v>
+        <v>0.336</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5978,28 +5970,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.485</v>
+        <v>0.53</v>
       </c>
       <c r="E122" s="16" t="n">
-        <v>-0.0102</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1658200</v>
+        <v>1710000</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="H122" t="n">
-        <v>71.70999999999999</v>
+        <v>58.87</v>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
@@ -6007,10 +5999,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.442</v>
+        <v>0.512</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.402</v>
+        <v>0.461</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6023,28 +6015,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.525</v>
+        <v>1.71</v>
       </c>
       <c r="E123" s="16" t="n">
-        <v>-0.0187</v>
+        <v>-0.0116</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1632500</v>
+        <v>1696200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.41</v>
+        <v>2.15</v>
       </c>
       <c r="H123" t="n">
-        <v>57.22</v>
+        <v>56</v>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
@@ -6052,10 +6044,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.511</v>
+        <v>1.652</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.461</v>
+        <v>1.727</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6068,28 +6060,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>7.9</v>
+        <v>0.485</v>
       </c>
       <c r="E124" s="16" t="n">
-        <v>-0.0075</v>
+        <v>-0.0102</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1624100</v>
+        <v>1693100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.12</v>
+        <v>0.53</v>
       </c>
       <c r="H124" t="n">
-        <v>57.81</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
@@ -6097,10 +6089,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>7.786</v>
+        <v>0.442</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>7.724</v>
+        <v>0.402</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6113,28 +6105,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0.0492</v>
+        <v>7.89</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1607000</v>
+        <v>1659300</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>1.95</v>
+        <v>0.12</v>
       </c>
       <c r="H125" t="n">
-        <v>71.23</v>
+        <v>57.19</v>
       </c>
       <c r="I125" s="15" t="inlineStr">
         <is>
@@ -6142,10 +6134,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.297</v>
+        <v>7.785</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.28</v>
+        <v>7.723</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6158,28 +6150,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0.004</v>
+        <v>3</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1605700</v>
+        <v>1608900</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.09</v>
+        <v>0.5</v>
       </c>
       <c r="H126" t="n">
-        <v>46.29</v>
+        <v>48.52</v>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
@@ -6187,10 +6179,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>10.171</v>
+        <v>3.012</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>10.334</v>
+        <v>3.04</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6203,39 +6195,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>0.0069</v>
+        <v>0.0492</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1586800</v>
+        <v>1607000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.99</v>
+        <v>1.95</v>
       </c>
       <c r="H127" t="n">
-        <v>44.16</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.23</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.739</v>
+        <v>0.297</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.753</v>
+        <v>0.28</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6248,28 +6240,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1558800</v>
+        <v>1586800</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H128" t="n">
-        <v>59.86</v>
+        <v>44.16</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6277,10 +6269,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.608</v>
+        <v>0.739</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.587</v>
+        <v>0.753</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6293,28 +6285,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>-0.0033</v>
+        <v>13.24</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0.0138</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1548700</v>
+        <v>1582600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.48</v>
+        <v>0.16</v>
       </c>
       <c r="H129" t="n">
-        <v>47.64</v>
+        <v>34.97</v>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
@@ -6322,10 +6314,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>3.011</v>
+        <v>13.508</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>3.04</v>
+        <v>14.083</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6338,39 +6330,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>13.24</v>
-      </c>
-      <c r="E130" s="17" t="n">
-        <v>0.0138</v>
+        <v>0.61</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1542800</v>
+        <v>1558800</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="H130" t="n">
-        <v>34.97</v>
-      </c>
-      <c r="I130" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.86</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>13.508</v>
+        <v>0.608</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>14.083</v>
+        <v>0.587</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6383,39 +6375,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1503200</v>
+        <v>1506100</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.97</v>
+        <v>0.26</v>
       </c>
       <c r="H131" t="n">
-        <v>46.56</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.93</v>
+      </c>
+      <c r="I131" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.295</v>
+        <v>0.399</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.297</v>
+        <v>0.398</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6428,28 +6420,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>-0.0058</v>
+        <v>0.295</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1476100</v>
+        <v>1503200</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="H132" t="n">
-        <v>52.97</v>
+        <v>46.56</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6457,10 +6449,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.858</v>
+        <v>0.295</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.855</v>
+        <v>0.297</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6473,39 +6465,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.41</v>
+        <v>0.86</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>-0.012</v>
+        <v>-0.0058</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1455000</v>
+        <v>1476100</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
       <c r="H133" t="n">
-        <v>53.93</v>
-      </c>
-      <c r="I133" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.97</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.399</v>
+        <v>0.858</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.398</v>
+        <v>0.855</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6533,10 +6525,10 @@
         <v>0.0053</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1430000</v>
+        <v>1458600</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H134" t="n">
         <v>36.12</v>
@@ -6563,39 +6555,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>0.028</v>
+        <v>1.87</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>-0.0209</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1387600</v>
+        <v>1437900</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H135" t="n">
-        <v>70.70999999999999</v>
-      </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.06</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.667</v>
+        <v>1.919</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.61</v>
+        <v>1.971</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6608,39 +6600,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>-0.0209</v>
+        <v>0.735</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>0.028</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1381600</v>
+        <v>1387600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H136" t="n">
-        <v>42.06</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.70999999999999</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.919</v>
+        <v>0.667</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.971</v>
+        <v>0.61</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6653,28 +6645,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0</v>
+        <v>2.41</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0.0617</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1374300</v>
+        <v>1377500</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.23</v>
+        <v>0.99</v>
       </c>
       <c r="H137" t="n">
-        <v>50.49</v>
+        <v>68.53</v>
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
@@ -6682,10 +6674,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.517</v>
+        <v>2.198</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.53</v>
+        <v>2.016</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6698,28 +6690,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>0.0216</v>
+        <v>0.52</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1368700</v>
+        <v>1374300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.79</v>
+        <v>0.23</v>
       </c>
       <c r="H138" t="n">
-        <v>60.38</v>
+        <v>50.49</v>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
@@ -6727,10 +6719,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.907</v>
+        <v>0.517</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.776</v>
+        <v>0.53</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6743,28 +6735,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0.0573</v>
+        <v>0.845</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1364100</v>
+        <v>1370600</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.98</v>
+        <v>0.48</v>
       </c>
       <c r="H139" t="n">
-        <v>68.12</v>
+        <v>65.62</v>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
@@ -6772,10 +6764,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>2.197</v>
+        <v>0.797</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>2.016</v>
+        <v>0.714</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6788,28 +6780,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>-0.0541</v>
+        <v>0.945</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0.0216</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1304300</v>
+        <v>1368700</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="H140" t="n">
-        <v>53.62</v>
+        <v>60.38</v>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
@@ -6817,10 +6809,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.351</v>
+        <v>0.907</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.318</v>
+        <v>0.776</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6833,28 +6825,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1295300</v>
+        <v>1304300</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.46</v>
+        <v>0.82</v>
       </c>
       <c r="H141" t="n">
-        <v>65.62</v>
+        <v>53.62</v>
       </c>
       <c r="I141" s="15" t="inlineStr">
         <is>
@@ -6862,10 +6854,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.797</v>
+        <v>0.351</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.714</v>
+        <v>0.318</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6893,7 +6885,7 @@
         <v>0.0121</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1279500</v>
+        <v>1293600</v>
       </c>
       <c r="G142" s="12" t="n">
         <v>0.46</v>
@@ -6923,28 +6915,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>EPICON</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1243800</v>
+        <v>1274200</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="H143" t="n">
-        <v>55.84</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
@@ -6952,10 +6944,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.199</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.206</v>
+        <v>0.794</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6968,28 +6960,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LAYHONG</t>
+          <t>EPICON</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.25</v>
+        <v>0.205</v>
       </c>
       <c r="E144" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1223600</v>
+        <v>1243800</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>2.11</v>
+        <v>1.12</v>
       </c>
       <c r="H144" t="n">
-        <v>55.11</v>
+        <v>55.84</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6997,10 +6989,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.247</v>
+        <v>0.199</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.244</v>
+        <v>0.206</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7013,28 +7005,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>LAYHONG</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>0.0117</v>
+        <v>0.25</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1196200</v>
+        <v>1224600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.18</v>
+        <v>2.11</v>
       </c>
       <c r="H145" t="n">
-        <v>53.03</v>
+        <v>55.11</v>
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
@@ -7042,10 +7034,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>2.567</v>
+        <v>0.247</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>2.532</v>
+        <v>0.244</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7058,28 +7050,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.36</v>
+        <v>1.39</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>0.0141</v>
+        <v>0.0221</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1181600</v>
+        <v>1200300</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="H146" t="n">
-        <v>43.39</v>
+        <v>59.81</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7087,10 +7079,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.365</v>
+        <v>1.34</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.395</v>
+        <v>1.138</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7103,39 +7095,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.4</v>
+        <v>2.68</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.0294</v>
+        <v>0.0037</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1168500</v>
+        <v>1196400</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="H147" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="I147" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.05</v>
+      </c>
+      <c r="I147" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.341</v>
+        <v>2.68</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.138</v>
+        <v>2.884</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7148,28 +7140,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>0</v>
+        <v>2.59</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>0.0117</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1164400</v>
+        <v>1196200</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="H148" t="n">
-        <v>45</v>
+        <v>53.03</v>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
@@ -7177,10 +7169,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>2.679</v>
+        <v>2.567</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>2.884</v>
+        <v>2.532</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7193,28 +7185,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>-0.0138</v>
+        <v>0.355</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1073000</v>
+        <v>1183000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.34</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H149" t="n">
-        <v>48.5</v>
+        <v>39.34</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7222,10 +7214,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>5.806</v>
+        <v>0.365</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>5.731</v>
+        <v>0.395</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7238,39 +7230,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E150" s="17" t="n">
-        <v>0.0077</v>
+        <v>5.74</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1056900</v>
+        <v>1076100</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H150" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="I150" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.75</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.633</v>
+        <v>5.807</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.589</v>
+        <v>5.731</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7283,28 +7275,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>0.0408</v>
+        <v>0.65</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1038800</v>
+        <v>1072700</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H151" t="n">
-        <v>48.64</v>
+        <v>70.55</v>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
@@ -7312,10 +7304,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.252</v>
+        <v>0.633</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.272</v>
+        <v>0.589</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7328,28 +7320,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E152" s="16" t="n">
-        <v>-0.027</v>
+        <v>0.26</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>0.0612</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>938400</v>
+        <v>1049300</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H152" t="n">
-        <v>44.61</v>
+        <v>51.5</v>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
@@ -7357,10 +7349,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.102</v>
+        <v>0.253</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>1.12</v>
+        <v>0.273</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7373,39 +7365,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>-0.0108</v>
+        <v>-0.027</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>926100</v>
+        <v>940000</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H153" t="n">
-        <v>42.46</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.61</v>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.102</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.954</v>
+        <v>1.12</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7418,39 +7410,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E154" s="17" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.92</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>917300</v>
+        <v>934000</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="H154" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="I154" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.46</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.707</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.714</v>
+        <v>0.954</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7463,28 +7455,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>0.0198</v>
+        <v>0.615</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>912000</v>
+        <v>924400</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.23</v>
+        <v>0.58</v>
       </c>
       <c r="H155" t="n">
-        <v>50.83</v>
+        <v>72.16</v>
       </c>
       <c r="I155" s="15" t="inlineStr">
         <is>
@@ -7492,10 +7484,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>7.651</v>
+        <v>0.552</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>7.801</v>
+        <v>0.489</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7508,28 +7500,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>2.03</v>
+        <v>0.72</v>
       </c>
       <c r="E156" s="17" t="n">
-        <v>0.0305</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>878000</v>
+        <v>917300</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="H156" t="n">
-        <v>64.48</v>
+        <v>55.83</v>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
@@ -7537,10 +7529,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.871</v>
+        <v>0.707</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.869</v>
+        <v>0.714</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7553,39 +7545,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E157" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>7.75</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>867300</v>
+        <v>915700</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.66</v>
+        <v>0.23</v>
       </c>
       <c r="H157" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.48</v>
+      </c>
+      <c r="I157" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.633</v>
+        <v>7.653</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.628</v>
+        <v>7.802</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7598,28 +7590,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E158" s="16" t="n">
-        <v>-0.0315</v>
+        <v>2.03</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>0.0305</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>843700</v>
+        <v>893600</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H158" t="n">
-        <v>72.16</v>
+        <v>64.48</v>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
@@ -7627,10 +7619,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.552</v>
+        <v>1.871</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.489</v>
+        <v>1.869</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7643,28 +7635,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E159" s="17" t="n">
-        <v>0.0238</v>
+        <v>0.63</v>
+      </c>
+      <c r="E159" s="16" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>814800</v>
+        <v>867300</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="H159" t="n">
-        <v>58.59</v>
+        <v>47.14</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -7672,10 +7664,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.236</v>
+        <v>0.633</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.133</v>
+        <v>0.628</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7688,39 +7680,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E160" s="17" t="n">
-        <v>0.005699999999999999</v>
+        <v>3.2</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>810700</v>
+        <v>849100</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H160" t="n">
-        <v>66.05</v>
-      </c>
-      <c r="I160" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.77</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.821</v>
+        <v>3.31</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.727</v>
+        <v>3.497</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7748,10 +7740,10 @@
         <v>0.0049</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>804600</v>
+        <v>848300</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H161" t="n">
         <v>45.62</v>
@@ -7778,28 +7770,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E162" s="17" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>797900</v>
+        <v>832400</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H162" t="n">
-        <v>53.72</v>
+        <v>58.59</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7807,10 +7799,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>7.86</v>
+        <v>1.236</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>7.791</v>
+        <v>1.133</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7823,39 +7815,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>0</v>
+        <v>7.82</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>797500</v>
+        <v>819300</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H163" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="I163" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.56</v>
+      </c>
+      <c r="I163" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>3.31</v>
+        <v>7.993</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>3.497</v>
+        <v>8.272</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7868,28 +7860,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>0366</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>ICENTS</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>1.96</v>
+        <v>0.89</v>
       </c>
       <c r="E164" s="17" t="n">
-        <v>0.0103</v>
+        <v>0.0171</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>793800</v>
+        <v>813200</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="H164" t="n">
-        <v>47.39</v>
+        <v>67.27</v>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
@@ -7897,10 +7889,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>1.962</v>
+        <v>0.822</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>2.026</v>
+        <v>0.727</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7913,39 +7905,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="E165" s="16" t="n">
-        <v>-0.0026</v>
+        <v>7.9</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>793300</v>
+        <v>812300</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H165" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="I165" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.72</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>7.992</v>
+        <v>7.86</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>8.272</v>
+        <v>7.791</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7958,28 +7950,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>APEX</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E166" s="17" t="n">
-        <v>0.0255</v>
+        <v>0.635</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>785500</v>
+        <v>803500</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.57</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H166" t="n">
-        <v>44.92</v>
+        <v>47.79</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7987,10 +7979,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>1.631</v>
+        <v>0.639</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.694</v>
+        <v>0.645</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -8003,39 +7995,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E167" s="16" t="n">
-        <v>-0.003</v>
+        <v>1.98</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>0.0206</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>772400</v>
+        <v>797900</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="H167" t="n">
-        <v>42.59</v>
-      </c>
-      <c r="I167" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.65</v>
+      </c>
+      <c r="I167" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>6.785</v>
+        <v>1.964</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>6.79</v>
+        <v>2.026</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8048,39 +8040,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>2.93</v>
+        <v>1.61</v>
       </c>
       <c r="E168" s="17" t="n">
-        <v>0.0245</v>
+        <v>0.0255</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>762600</v>
+        <v>789900</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.25</v>
+        <v>0.57</v>
       </c>
       <c r="H168" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="I168" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.92</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>2.781</v>
+        <v>1.631</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>2.673</v>
+        <v>1.694</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8093,39 +8085,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>0.0141</v>
+        <v>6.7</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>723500</v>
+        <v>785200</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H169" t="n">
-        <v>51.93</v>
-      </c>
-      <c r="I169" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.59</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>4.979</v>
+        <v>6.785</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>5.035</v>
+        <v>6.79</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8138,28 +8130,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="E170" s="16" t="n">
-        <v>-0.0086</v>
+        <v>2.94</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>0.028</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>706800</v>
+        <v>768900</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="H170" t="n">
-        <v>37.27</v>
+        <v>60.52</v>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
@@ -8167,10 +8159,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>4.739</v>
+        <v>2.782</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>5.008</v>
+        <v>2.673</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8183,39 +8175,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E171" s="16" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.595</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>706500</v>
+        <v>761600</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="H171" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.39</v>
+      </c>
+      <c r="I171" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.119</v>
+        <v>0.569</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.153</v>
+        <v>0.574</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8228,28 +8220,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>8.66</v>
+        <v>5.04</v>
       </c>
       <c r="E172" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.0182</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>702900</v>
+        <v>741200</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2.36</v>
+        <v>0.14</v>
       </c>
       <c r="H172" t="n">
-        <v>61.01</v>
+        <v>52.94</v>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
@@ -8257,10 +8249,10 @@
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>8.339</v>
+        <v>4.981</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>8.127000000000001</v>
+        <v>5.036</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8273,28 +8265,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>0</v>
+        <v>6.54</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>700000</v>
+        <v>738200</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.72</v>
+        <v>0.15</v>
       </c>
       <c r="H173" t="n">
-        <v>48.01</v>
+        <v>30.62</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -8302,10 +8294,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>0.631</v>
+        <v>6.74</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>0.637</v>
+        <v>6.874</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8318,39 +8310,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>3.01</v>
+        <v>4.64</v>
       </c>
       <c r="E174" s="16" t="n">
-        <v>-0.0131</v>
+        <v>-0.0022</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>680600</v>
+        <v>726300</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.66</v>
+        <v>0.15</v>
       </c>
       <c r="H174" t="n">
-        <v>36.61</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.73</v>
+      </c>
+      <c r="I174" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>3.081</v>
+        <v>4.742</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>3.156</v>
+        <v>5.008</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8363,28 +8355,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>6.53</v>
+        <v>3.01</v>
       </c>
       <c r="E175" s="16" t="n">
-        <v>-0.0061</v>
+        <v>-0.0131</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>679200</v>
+        <v>724600</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.14</v>
+        <v>0.7</v>
       </c>
       <c r="H175" t="n">
-        <v>30.16</v>
+        <v>36.61</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -8392,10 +8384,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>6.739</v>
+        <v>3.081</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>6.874</v>
+        <v>3.156</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8408,39 +8400,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="E176" s="16" t="n">
-        <v>-0.0124</v>
+        <v>1.07</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>675900</v>
+        <v>722200</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H176" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="I176" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.09</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>5.723</v>
+        <v>1.12</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>6.099</v>
+        <v>1.153</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8453,28 +8445,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E177" s="10" t="n">
-        <v>0</v>
+        <v>5.56</v>
+      </c>
+      <c r="E177" s="16" t="n">
+        <v>-0.0142</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>670500</v>
+        <v>705700</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="H177" t="n">
-        <v>57.39</v>
+        <v>38.7</v>
       </c>
       <c r="I177" s="15" t="inlineStr">
         <is>
@@ -8482,10 +8474,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.569</v>
+        <v>5.722</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.574</v>
+        <v>6.099</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8498,28 +8490,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>UMSINT</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>1.27</v>
+        <v>8.66</v>
       </c>
       <c r="E178" s="17" t="n">
-        <v>0.0242</v>
+        <v>0.0152</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>655700</v>
+        <v>702900</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.44</v>
+        <v>2.36</v>
       </c>
       <c r="H178" t="n">
-        <v>45.78</v>
+        <v>61.01</v>
       </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
@@ -8527,10 +8519,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>1.283</v>
+        <v>8.339</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>1.35</v>
+        <v>8.127000000000001</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8543,28 +8535,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E179" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.63</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>651400</v>
+        <v>700000</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.25</v>
+        <v>0.72</v>
       </c>
       <c r="H179" t="n">
-        <v>48.14</v>
+        <v>48.01</v>
       </c>
       <c r="I179" s="13" t="inlineStr">
         <is>
@@ -8572,10 +8564,10 @@
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>0.64</v>
+        <v>0.631</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>0.632</v>
+        <v>0.637</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8588,39 +8580,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>EITA</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E180" s="17" t="n">
-        <v>0.0274</v>
+        <v>0.63</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>628700</v>
+        <v>675200</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>4.93</v>
+        <v>0.26</v>
       </c>
       <c r="H180" t="n">
-        <v>74.87</v>
-      </c>
-      <c r="I180" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.08</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.672</v>
+        <v>0.639</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.609</v>
+        <v>0.632</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8633,28 +8625,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E181" s="10" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>600300</v>
+        <v>663600</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>2.03</v>
+        <v>0.45</v>
       </c>
       <c r="H181" t="n">
-        <v>59.87</v>
+        <v>45.78</v>
       </c>
       <c r="I181" s="15" t="inlineStr">
         <is>
@@ -8662,10 +8654,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.578</v>
+        <v>1.283</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8678,39 +8670,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>EITA</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E182" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E182" s="17" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>597800</v>
+        <v>656200</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>2.05</v>
+        <v>5.15</v>
       </c>
       <c r="H182" t="n">
-        <v>40.26</v>
-      </c>
-      <c r="I182" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.87</v>
+      </c>
+      <c r="I182" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.672</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.846</v>
+        <v>0.609</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8738,10 +8730,10 @@
         <v>0.0148</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>595400</v>
+        <v>626600</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H183" t="n">
         <v>56.81</v>
@@ -8768,28 +8760,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E184" s="17" t="n">
-        <v>0.0177</v>
+        <v>1.6</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>583500</v>
+        <v>600300</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.31</v>
+        <v>2.03</v>
       </c>
       <c r="H184" t="n">
-        <v>61.75</v>
+        <v>59.87</v>
       </c>
       <c r="I184" s="15" t="inlineStr">
         <is>
@@ -8797,10 +8789,10 @@
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>1.084</v>
+        <v>1.578</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>1.061</v>
+        <v>1.53</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8813,39 +8805,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>TEOSENG</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E185" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.805</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>570000</v>
+        <v>597800</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.44</v>
+        <v>2.05</v>
       </c>
       <c r="H185" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="I185" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.26</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>0.627</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>0.605</v>
+        <v>0.846</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8858,28 +8850,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E186" s="10" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E186" s="17" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>539000</v>
+        <v>583500</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="H186" t="n">
-        <v>42.86</v>
+        <v>61.75</v>
       </c>
       <c r="I186" s="15" t="inlineStr">
         <is>
@@ -8887,10 +8879,10 @@
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>2.084</v>
+        <v>1.084</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>2.112</v>
+        <v>1.061</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8903,39 +8895,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>1.3</v>
+        <v>0.635</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>-0.0076</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>534200</v>
+        <v>572600</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>1.27</v>
+        <v>0.44</v>
       </c>
       <c r="H187" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="I187" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.81</v>
+      </c>
+      <c r="I187" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>1.32</v>
+        <v>0.627</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>1.345</v>
+        <v>0.605</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8948,39 +8940,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="E188" s="10" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="E188" s="16" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>526400</v>
+        <v>558900</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H188" t="n">
-        <v>40.54</v>
-      </c>
-      <c r="I188" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.28</v>
+      </c>
+      <c r="I188" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>4.202</v>
+        <v>2.083</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>4.343</v>
+        <v>2.112</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8993,28 +8985,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>KLK</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E189" s="17" t="n">
-        <v>0.0009</v>
+        <v>1.5</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>526300</v>
+        <v>545000</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="H189" t="n">
-        <v>54.75</v>
+        <v>30.43</v>
       </c>
       <c r="I189" s="15" t="inlineStr">
         <is>
@@ -9022,10 +9014,10 @@
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>22.414</v>
+        <v>1.565</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>21.853</v>
+        <v>1.681</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -9038,28 +9030,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SOP</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>5.71</v>
+        <v>1.3</v>
       </c>
       <c r="E190" s="16" t="n">
-        <v>-0.0452</v>
+        <v>-0.0076</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>514600</v>
+        <v>536300</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.84</v>
+        <v>1.28</v>
       </c>
       <c r="H190" t="n">
-        <v>45.69</v>
+        <v>37.92</v>
       </c>
       <c r="I190" s="13" t="inlineStr">
         <is>
@@ -9067,10 +9059,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>5.911</v>
+        <v>1.32</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>5.535</v>
+        <v>1.345</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9083,45 +9075,180 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E191" s="10" t="n">
-        <v>0</v>
+        <v>4.02</v>
+      </c>
+      <c r="E191" s="16" t="n">
+        <v>-0.0025</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>512800</v>
+        <v>529800</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.21</v>
+        <v>0.61</v>
       </c>
       <c r="H191" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="I191" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.2</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>1.565</v>
+        <v>4.201</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>1.681</v>
+        <v>4.343</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>KLK</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E192" s="17" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>528500</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H192" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>22.414</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>21.853</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E193" s="16" t="n">
+        <v>-0.04679999999999999</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>516600</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H193" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>5.535</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E194" s="16" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>502200</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H194" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="I194" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M191"/>
+  <autoFilter ref="A1:M194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -597,12 +597,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.66高于50日均线0.579，EMA20与SAR均呈多头，T3形态突破；RSI 64.07偏强但未超买，信号技术面较可靠。</t>
+          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面一致性尚可。</t>
         </is>
       </c>
     </row>
@@ -650,12 +650,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.25高于50日均线0.197，EMA20与SAR均呈多头，T3形态突破；但RSI达71.13，已进入超买区，信号可靠性需留意短线过热。</t>
+          <t>现价0.25高于50日均线0.197，且站上EMA20与SAR，T3突破偏多；但RSI达71.13，已进入超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.6略低于50日均线0.611，RSI 50.75处中性区间，无超买。EMA20与SAR多头叠加T3突破，信号偏多但受均线压制，可靠性中等。</t>
+          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏弱，可靠性一般。</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>RSI达79.67，处超买区；现价0.26高于50日均线0.207约25.6%，EMA20与SAR多头信号偏强，但短线过热。</t>
+          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3突破偏多；但RSI达79.67，已进入超买区，信号可靠性受高位制约。</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>现价0.55高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破；RSI 63.26未超买，信号技术面偏可靠。</t>
+          <t>现价0.55高于50日均线0.395，RSI 63.26未超买，配合EMA20与SAR多头信号，技术面偏强。</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.82高于50日均线0.684，EMA20与SAR均呈多头，T3形态突破。RSI 70.17已近超买区，信号偏强但需留意短线过热。</t>
+          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破形态成立；但RSI达70.17，已进入超买区，信号可靠性需留意短线过热风险。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面一致性尚可。</t>
+          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面尚属可靠。</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏弱，可靠性一般。</t>
+          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏积极，但均线压制下可靠性有限。</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3突破偏多；但RSI达79.67，已进入超买区，信号可靠性受高位制约。</t>
+          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3突破形态成立；但RSI达79.67，已处超买区，信号可靠性受此制约。</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破形态成立；但RSI达70.17，已进入超买区，信号可靠性需留意短线过热风险。</t>
+          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破偏多；但RSI达70.17，已近超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面尚属可靠。</t>
+          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面偏强。</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.25高于50日均线0.197，且站上EMA20与SAR，T3突破偏多；但RSI达71.13，已进入超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.25高于50日均线0.197，且站上EMA20与SAR，T3突破偏多；但RSI达71.13，已进入超买区，信号可靠性受高位制约。</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏积极，但均线压制下可靠性有限。</t>
+          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏弱，可靠性一般。</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3突破形态成立；但RSI达79.67，已处超买区，信号可靠性受此制约。</t>
+          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3形态突破；但RSI达79.67，已处超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破偏多；但RSI达70.17，已近超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破形态成立；但RSI达70.17，已进入超买区，信号可靠性需留意短线过热。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -561,28 +561,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.66</v>
+        <v>0.25</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.1111</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>10285000</v>
+        <v>8860700</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.95</v>
+        <v>14.93</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.06999999999999</v>
+        <v>71.13</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -590,19 +590,19 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.617</v>
+        <v>0.207</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.579</v>
+        <v>0.197</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面偏强。</t>
+          <t>现价0.25高于50日均线0.197，RSI达71.13已入超买区，EMA与SAR、Supertrend均偏多，但量能信号需配合观察。</t>
         </is>
       </c>
     </row>
@@ -614,28 +614,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.25</v>
+        <v>3.03</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.0341</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>8860700</v>
+        <v>29755500</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>14.93</v>
+        <v>2.37</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.13</v>
+        <v>71.33</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -643,19 +643,19 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.207</v>
+        <v>2.846</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.197</v>
+        <v>2.702</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.25高于50日均线0.197，且站上EMA20与SAR，T3突破偏多；但RSI达71.13，已进入超买区，信号可靠性受高位制约。</t>
+          <t>RSI 71.33已超买，现价高于50日均线约12%，EMA与Supertrend偏多，但超买下信号可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -667,28 +667,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0526</v>
+        <v>0.0649</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3461500</v>
+        <v>37327900</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1.26</v>
+        <v>4.62</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>50.75</v>
+        <v>70.17</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -696,180 +696,147 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.593</v>
+        <v>0.703</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.611</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏弱，可靠性一般。</t>
+          <t>RSI 70.17 刚进超买区，现价 0.82 高于 50 日均线 0.684 约 20%，均线多头排列，信号偏强但短线过热。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>0373</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>VERDANT</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>11636100</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>79.67</v>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3形态突破；但RSI达79.67，已处超买区，信号可靠性需谨慎看待。</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0041</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AIMAX</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>906454100</v>
+      </c>
+      <c r="G5" s="12" t="n"/>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>0455</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>BUSCAP</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0.05769999999999999</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>3286800</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>63.26</v>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>现价0.55高于50日均线0.395，RSI 63.26未超买，配合EMA20与SAR多头信号，技术面偏强。</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>94950300</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>5184</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>CYPARK</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.0649</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>37327900</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>70.17</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破形态成立；但RSI达70.17，已进入超买区，信号可靠性需留意短线过热。</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>67728900</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -879,31 +846,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.755</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0321</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>906454100</v>
-      </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+        <v>39996200</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.681</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
     </row>
@@ -915,39 +891,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.0447</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>94950300</v>
+        <v>34693600</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.16</v>
+        <v>1.33</v>
       </c>
       <c r="H9" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.284</v>
+        <v>1.728</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.502</v>
+        <v>1.511</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -960,39 +936,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0435</v>
+        <v>0.025</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>67728900</v>
+        <v>33018800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>3.41</v>
+        <v>1.77</v>
       </c>
       <c r="H10" t="n">
-        <v>32.28</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.85</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.241</v>
+        <v>0.025</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.25</v>
+        <v>0.024</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -1005,39 +981,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0321</v>
+        <v>4.88</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>39996200</v>
+        <v>31258300</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="H11" t="n">
-        <v>56.84</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.34</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.737</v>
+        <v>4.727</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.681</v>
+        <v>4.496</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1050,28 +1026,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.0447</v>
+        <v>0.38</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>34693600</v>
+        <v>29898900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.33</v>
+        <v>0.64</v>
       </c>
       <c r="H12" t="n">
-        <v>66</v>
+        <v>76.97</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1079,10 +1055,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.728</v>
+        <v>0.312</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.511</v>
+        <v>0.177</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1095,28 +1071,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>33018800</v>
+        <v>29693700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="H13" t="n">
-        <v>51.85</v>
+        <v>71.34</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1124,10 +1100,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.025</v>
+        <v>0.543</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.024</v>
+        <v>0.491</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1140,39 +1116,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0.0083</v>
+        <v>0.155</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>31258300</v>
+        <v>28515700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="H14" t="n">
-        <v>64.34</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.71</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>4.727</v>
+        <v>0.156</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>4.496</v>
+        <v>0.16</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1185,28 +1161,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.05</v>
+        <v>0.17</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>29898900</v>
+        <v>28206900</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="n">
-        <v>76.97</v>
+        <v>73.31</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1214,10 +1190,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.312</v>
+        <v>0.142</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.177</v>
+        <v>0.114</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1230,28 +1206,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.0341</v>
+        <v>0.32</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>29755500</v>
+        <v>27395700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="H16" t="n">
-        <v>71.33</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1259,10 +1235,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>2.846</v>
+        <v>0.281</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.702</v>
+        <v>0.276</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1275,28 +1251,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.585</v>
+        <v>0.15</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.0168</v>
+        <v>-0.0625</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>29693700</v>
+        <v>26335500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1.27</v>
+        <v>0.64</v>
       </c>
       <c r="H17" t="n">
-        <v>71.34</v>
+        <v>47.65</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1304,10 +1280,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.543</v>
+        <v>0.159</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.491</v>
+        <v>0.148</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1320,28 +1296,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>28515700</v>
+        <v>26303600</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.38</v>
+        <v>0.96</v>
       </c>
       <c r="H18" t="n">
-        <v>44.71</v>
+        <v>31.96</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1349,10 +1325,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.156</v>
+        <v>0.279</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1365,39 +1341,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0.0303</v>
+        <v>0.0682</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>28206900</v>
+        <v>24788800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.6</v>
+        <v>3.19</v>
       </c>
       <c r="H19" t="n">
-        <v>73.31</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.57</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.142</v>
+        <v>0.446</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.114</v>
+        <v>0.403</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1410,28 +1386,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.08470000000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>27395700</v>
+        <v>21362400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.68</v>
+        <v>4.79</v>
       </c>
       <c r="H20" t="n">
-        <v>65.18000000000001</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1439,10 +1415,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.281</v>
+        <v>0.836</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.276</v>
+        <v>0.721</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1455,28 +1431,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.15</v>
+        <v>0.475</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>-0.0625</v>
+        <v>-0.0104</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>26335500</v>
+        <v>21005100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H21" t="n">
-        <v>47.65</v>
+        <v>52.83</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1484,10 +1460,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.159</v>
+        <v>0.468</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.148</v>
+        <v>0.47</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1500,28 +1476,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-0.02</v>
+        <v>0.38</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>26303600</v>
+        <v>20474600</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.96</v>
+        <v>2.27</v>
       </c>
       <c r="H22" t="n">
-        <v>31.96</v>
+        <v>59.86</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1529,10 +1505,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.279</v>
+        <v>0.372</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.33</v>
+        <v>0.371</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1545,39 +1521,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0.0682</v>
+        <v>0.055</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>24788800</v>
+        <v>20422400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
       <c r="H23" t="n">
-        <v>58.57</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.446</v>
+        <v>0.053</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.403</v>
+        <v>0.043</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1590,28 +1566,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.08470000000000001</v>
+        <v>0.31</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>21362400</v>
+        <v>19746400</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>4.79</v>
+        <v>1.04</v>
       </c>
       <c r="H24" t="n">
-        <v>95.29000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1619,10 +1595,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.836</v>
+        <v>0.303</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.721</v>
+        <v>0.29</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1635,28 +1611,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>-0.0104</v>
+        <v>2.88</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.112</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>21005100</v>
+        <v>19159400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.84</v>
+        <v>2.99</v>
       </c>
       <c r="H25" t="n">
-        <v>52.83</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1664,10 +1640,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.468</v>
+        <v>2.609</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.47</v>
+        <v>2.485</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1680,28 +1656,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>20474600</v>
+        <v>18610300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>2.27</v>
+        <v>1.04</v>
       </c>
       <c r="H26" t="n">
-        <v>59.86</v>
+        <v>41.83</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1709,10 +1685,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.372</v>
+        <v>0.868</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.371</v>
+        <v>0.871</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1725,28 +1701,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>20422400</v>
+        <v>18388700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>2.32</v>
+        <v>0.91</v>
       </c>
       <c r="H27" t="n">
-        <v>56.29</v>
+        <v>71.25</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1754,10 +1730,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.053</v>
+        <v>0.2</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.043</v>
+        <v>0.183</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1770,39 +1746,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>-0.0159</v>
+        <v>2.09</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>19746400</v>
+        <v>18385700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="H28" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.303</v>
+        <v>2.131</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.29</v>
+        <v>2.059</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1815,39 +1791,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.88</v>
+        <v>0.53</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>0.112</v>
+        <v>0.0095</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>19159400</v>
+        <v>17063100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>2.99</v>
+        <v>0.44</v>
       </c>
       <c r="H29" t="n">
-        <v>67.45999999999999</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.92</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.609</v>
+        <v>0.645</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.485</v>
+        <v>0.863</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1860,39 +1836,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>-0.0115</v>
+        <v>0.42</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0.012</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>18610300</v>
+        <v>16720800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.04</v>
+        <v>0.71</v>
       </c>
       <c r="H30" t="n">
-        <v>41.83</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.36</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.868</v>
+        <v>0.38</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.871</v>
+        <v>0.318</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1905,28 +1881,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>-0.0435</v>
+        <v>0.235</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>18388700</v>
+        <v>16485900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="H31" t="n">
-        <v>71.25</v>
+        <v>53.3</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1934,10 +1910,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.2</v>
+        <v>0.231</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.183</v>
+        <v>0.232</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1950,39 +1926,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2.09</v>
+        <v>0.805</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.0097</v>
+        <v>0.0063</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>18385700</v>
+        <v>16426000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.15</v>
+        <v>4.87</v>
       </c>
       <c r="H32" t="n">
-        <v>47</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.91</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.131</v>
+        <v>0.804</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.059</v>
+        <v>0.806</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1995,28 +1971,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>0.0095</v>
+        <v>0.0189</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>17063100</v>
+        <v>15116900</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.44</v>
+        <v>1.16</v>
       </c>
       <c r="H33" t="n">
-        <v>26.92</v>
+        <v>50.2</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -2024,10 +2000,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.645</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.863</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2040,39 +2016,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.42</v>
+        <v>5.89</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0.012</v>
+        <v>0.0155</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>16720800</v>
+        <v>14858100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>64.36</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.42</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.38</v>
+        <v>5.674</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.318</v>
+        <v>5.1</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2085,39 +2061,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.065</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>16485900</v>
+        <v>14521600</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.88</v>
+        <v>4.81</v>
       </c>
       <c r="H35" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.17</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.231</v>
+        <v>0.065</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.232</v>
+        <v>0.074</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2130,28 +2106,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.805</v>
+        <v>0.775</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0.0063</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>16426000</v>
+        <v>14276200</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>4.87</v>
+        <v>1.18</v>
       </c>
       <c r="H36" t="n">
-        <v>49.91</v>
+        <v>50.16</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2159,10 +2135,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.804</v>
+        <v>0.774</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.806</v>
+        <v>0.774</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2175,28 +2151,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>0.0189</v>
+        <v>1.8</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>-0.0576</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>15116900</v>
+        <v>14074700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.16</v>
+        <v>2.11</v>
       </c>
       <c r="H37" t="n">
-        <v>50.2</v>
+        <v>35.55</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2204,10 +2180,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.913</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.969</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2220,28 +2196,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>5.89</v>
+        <v>0.95</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.0155</v>
+        <v>0.027</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>14858100</v>
+        <v>13807300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>3.91</v>
       </c>
       <c r="H38" t="n">
-        <v>63.42</v>
+        <v>78.73</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
@@ -2249,10 +2225,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>5.674</v>
+        <v>0.878</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>5.1</v>
+        <v>0.85</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2265,39 +2241,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TFP</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.065</v>
+        <v>0.35</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>0.0833</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>14521600</v>
+        <v>13658000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>4.81</v>
+        <v>3.99</v>
       </c>
       <c r="H39" t="n">
-        <v>48.17</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.98</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.065</v>
+        <v>0.338</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.074</v>
+        <v>0.332</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2310,28 +2286,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.75</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>14276200</v>
+        <v>13261000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.18</v>
+        <v>2.56</v>
       </c>
       <c r="H40" t="n">
-        <v>50.16</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2339,10 +2315,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.774</v>
+        <v>0.677</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.774</v>
+        <v>0.607</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2355,28 +2331,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>-0.0576</v>
+        <v>-0.0504</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>14074700</v>
+        <v>13112900</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>2.11</v>
+        <v>1.12</v>
       </c>
       <c r="H41" t="n">
-        <v>35.55</v>
+        <v>44.52</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2384,10 +2360,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.913</v>
+        <v>1.38</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.969</v>
+        <v>1.287</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2400,28 +2376,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.95</v>
+        <v>2.39</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0.027</v>
+        <v>0.0214</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>13807300</v>
+        <v>12998100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>3.91</v>
+        <v>0.73</v>
       </c>
       <c r="H42" t="n">
-        <v>78.73</v>
+        <v>54.48</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2429,10 +2405,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.878</v>
+        <v>2.348</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.85</v>
+        <v>2.232</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2445,39 +2421,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.165</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>13658000</v>
+        <v>12466000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>3.99</v>
+        <v>0.44</v>
       </c>
       <c r="H43" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.16</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.338</v>
+        <v>0.183</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.332</v>
+        <v>0.224</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2490,39 +2466,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>-0.0066</v>
+        <v>0.78</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>13261000</v>
+        <v>12439500</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>2.56</v>
+        <v>3.44</v>
       </c>
       <c r="H44" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.53</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.677</v>
+        <v>0.8</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.607</v>
+        <v>0.853</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2535,39 +2511,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>-0.0504</v>
+        <v>0.095</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>13112900</v>
+        <v>12331800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.12</v>
+        <v>2.15</v>
       </c>
       <c r="H45" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.43000000000001</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.38</v>
+        <v>0.078</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.287</v>
+        <v>0.067</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2580,28 +2556,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0.0214</v>
+        <v>1.06</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>12998100</v>
+        <v>12302200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.73</v>
+        <v>1.52</v>
       </c>
       <c r="H46" t="n">
-        <v>54.48</v>
+        <v>82.09</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2609,10 +2585,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.348</v>
+        <v>0.877</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.232</v>
+        <v>0.752</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2625,39 +2601,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>2.47</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>12466000</v>
+        <v>11833400</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="H47" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.91</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.183</v>
+        <v>2.433</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.224</v>
+        <v>2.266</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2670,39 +2646,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0331</v>
+        <v>0.0833</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>12439500</v>
+        <v>11636100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>3.44</v>
+        <v>10.13</v>
       </c>
       <c r="H48" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.67</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.8</v>
+        <v>0.219</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.853</v>
+        <v>0.207</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2715,39 +2691,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0.0556</v>
+        <v>0.19</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>12331800</v>
+        <v>11477400</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>2.15</v>
+        <v>1.39</v>
       </c>
       <c r="H49" t="n">
-        <v>79.43000000000001</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.21</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.078</v>
+        <v>0.197</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.067</v>
+        <v>0.196</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2760,39 +2736,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0116</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>FOCUS</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.005</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>12302200</v>
+        <v>11329300</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="H50" t="n">
-        <v>82.09</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.48</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.877</v>
+        <v>0.006</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.752</v>
+        <v>0.006</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2805,28 +2781,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0.004099999999999999</v>
+        <v>1.95</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>11833400</v>
+        <v>10434800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.72</v>
+        <v>1.52</v>
       </c>
       <c r="H51" t="n">
-        <v>58.91</v>
+        <v>45.48</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2834,10 +2810,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.433</v>
+        <v>1.986</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.266</v>
+        <v>1.976</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2850,39 +2826,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0.019</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>11477400</v>
+        <v>10323000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.39</v>
+        <v>0.7</v>
       </c>
       <c r="H52" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.18000000000001</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.197</v>
+        <v>0.466</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.196</v>
+        <v>0.397</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2895,28 +2871,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0116</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FOCUS</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>-0.125</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>11329300</v>
+        <v>10320700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="H53" t="n">
-        <v>47.48</v>
+        <v>36.98</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2924,10 +2900,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.006</v>
+        <v>0.078</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.006</v>
+        <v>0.077</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2940,28 +2916,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>-0.0152</v>
+        <v>0.66</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0.0732</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>10434800</v>
+        <v>10285000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.52</v>
+        <v>2.95</v>
       </c>
       <c r="H54" t="n">
-        <v>45.48</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2969,10 +2945,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.986</v>
+        <v>0.617</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.976</v>
+        <v>0.579</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2985,39 +2961,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>0.019</v>
+        <v>4.76</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>10323000</v>
+        <v>9819800</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.7</v>
+        <v>1.18</v>
       </c>
       <c r="H55" t="n">
-        <v>68.18000000000001</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.73</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.466</v>
+        <v>4.745</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.397</v>
+        <v>4.584</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -3030,40 +3006,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OMESTI</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>-0.125</v>
+        <v>-0.0556</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>10320700</v>
+        <v>9738400</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H56" t="n">
-        <v>36.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J56" s="9" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="K56" s="9" t="n">
-        <v>0.077</v>
-      </c>
+      <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
     </row>
@@ -3075,39 +3044,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>-0.0042</v>
+        <v>0.605</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9819800</v>
+        <v>9471200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="H57" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.06</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>4.745</v>
+        <v>0.608</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>4.584</v>
+        <v>0.603</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3120,33 +3089,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.255</v>
+        <v>4.8</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>-0.0556</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>9738400</v>
+        <v>9095700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
+      </c>
+      <c r="H58" t="n">
+        <v>40.8</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
+      <c r="J58" s="9" t="n">
+        <v>4.851</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>4.967</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
     </row>
@@ -3158,28 +3134,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.605</v>
+        <v>0.78</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.0168</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>9471200</v>
+        <v>9088500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.97</v>
+        <v>3.44</v>
       </c>
       <c r="H59" t="n">
-        <v>48.06</v>
+        <v>57.08</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3187,10 +3163,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.608</v>
+        <v>0.755</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.603</v>
+        <v>0.74</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3203,28 +3179,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.14</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>9095700</v>
+        <v>9051900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.43</v>
+        <v>2.82</v>
       </c>
       <c r="H60" t="n">
-        <v>40.8</v>
+        <v>38.65</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3232,10 +3208,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>4.851</v>
+        <v>0.147</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>4.967</v>
+        <v>0.153</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3248,28 +3224,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0092</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>9088500</v>
+        <v>8863700</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>3.44</v>
+        <v>0.72</v>
       </c>
       <c r="H61" t="n">
-        <v>57.08</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3277,10 +3253,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.755</v>
+        <v>0.996</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.74</v>
+        <v>0.837</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3293,39 +3269,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>BINTAI</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>9051900</v>
+        <v>8540000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>2.82</v>
+        <v>4.41</v>
       </c>
       <c r="H62" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.23</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.147</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.153</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3338,28 +3314,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.1</v>
+        <v>0.18</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>0.0092</v>
+        <v>0.1613</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>8863700</v>
+        <v>8506600</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.72</v>
+        <v>1.71</v>
       </c>
       <c r="H63" t="n">
-        <v>79.31999999999999</v>
+        <v>63.41</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3367,10 +3343,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.996</v>
+        <v>0.161</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.837</v>
+        <v>0.165</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3383,39 +3359,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BINTAI</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>8540000</v>
+        <v>8451400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>4.41</v>
+        <v>0.61</v>
       </c>
       <c r="H64" t="n">
-        <v>47.23</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.15</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.473</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3428,39 +3404,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0.1613</v>
+        <v>2.23</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>-0.0304</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>8506600</v>
+        <v>8307700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="H65" t="n">
-        <v>63.41</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.43</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.161</v>
+        <v>2.223</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.165</v>
+        <v>2.1</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3473,39 +3449,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0.0283</v>
+        <v>0.325</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>8451400</v>
+        <v>8186100</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
       <c r="H66" t="n">
-        <v>58.15</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>90.43000000000001</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.52</v>
+        <v>0.261</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.473</v>
+        <v>0.218</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3518,39 +3494,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>-0.0304</v>
+        <v>4.06</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0.04099999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>8307700</v>
+        <v>7951900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.16</v>
+        <v>1.79</v>
       </c>
       <c r="H67" t="n">
-        <v>52.43</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.22</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.223</v>
+        <v>3.48</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.1</v>
+        <v>3.203</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3563,28 +3539,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>-0.0152</v>
+        <v>2.66</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>8186100</v>
+        <v>7628300</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.91</v>
+        <v>0.38</v>
       </c>
       <c r="H68" t="n">
-        <v>90.43000000000001</v>
+        <v>58.31</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3592,10 +3568,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.261</v>
+        <v>2.591</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.218</v>
+        <v>2.433</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3608,28 +3584,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>4.06</v>
+        <v>0.23</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0455</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>7951900</v>
+        <v>7560300</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.79</v>
+        <v>0.51</v>
       </c>
       <c r="H69" t="n">
-        <v>78.22</v>
+        <v>66.81</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3637,10 +3613,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>3.48</v>
+        <v>0.197</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>3.203</v>
+        <v>0.171</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3653,28 +3629,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0.0192</v>
+        <v>1.1</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>-0.0351</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>7628300</v>
+        <v>7456900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="H70" t="n">
-        <v>58.31</v>
+        <v>54.83</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3682,10 +3658,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.591</v>
+        <v>1.084</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.433</v>
+        <v>1.023</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3698,28 +3674,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0.0455</v>
+        <v>1.16</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>7560300</v>
+        <v>7434000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H71" t="n">
-        <v>66.81</v>
+        <v>47.72</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3727,10 +3703,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.197</v>
+        <v>1.182</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.171</v>
+        <v>1.135</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3743,39 +3719,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>-0.0351</v>
+        <v>0.9</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>7456900</v>
+        <v>7389600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.65</v>
+        <v>2.44</v>
       </c>
       <c r="H72" t="n">
-        <v>54.83</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.53</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.084</v>
+        <v>0.928</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1.023</v>
+        <v>0.969</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3788,28 +3764,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>2.86</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0.06320000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>7434000</v>
+        <v>7329400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>1.07</v>
+        <v>3.24</v>
       </c>
       <c r="H73" t="n">
-        <v>47.72</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3817,10 +3793,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.182</v>
+        <v>2.113</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.135</v>
+        <v>1.739</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3833,39 +3809,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.9</v>
+        <v>0.785</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>0.0112</v>
+        <v>0.0064</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>7389600</v>
+        <v>7277600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>2.44</v>
+        <v>1.28</v>
       </c>
       <c r="H74" t="n">
-        <v>35.53</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.31</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.928</v>
+        <v>0.766</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.969</v>
+        <v>0.751</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3878,39 +3854,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>PERMAJU</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.01</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>7329400</v>
+        <v>7209300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>3.24</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>89.18000000000001</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.65</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.113</v>
+        <v>0.007</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.739</v>
+        <v>0.008</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3923,39 +3899,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0.0064</v>
+        <v>1.63</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>7277600</v>
+        <v>7202300</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="H76" t="n">
-        <v>86.31</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.24</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.766</v>
+        <v>1.74</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.751</v>
+        <v>1.855</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3968,28 +3944,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PERMAJU</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0.0187</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>7209300</v>
+        <v>7131600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>78.23999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="H77" t="n">
-        <v>58.65</v>
+        <v>39.08</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3997,10 +3973,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.007</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.008</v>
+        <v>0.592</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -4013,28 +3989,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.115</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>7202300</v>
+        <v>7024200</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>30.24</v>
+        <v>48.46</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4042,10 +4018,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.74</v>
+        <v>0.119</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.855</v>
+        <v>0.106</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4058,39 +4034,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0.0187</v>
+        <v>0.29</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>7131600</v>
+        <v>6973800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="H79" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.81</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.273</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.592</v>
+        <v>0.269</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4103,40 +4079,38 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0</v>
+        <v>2.96</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>7024200</v>
+        <v>6719400</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="H80" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.05</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="K80" s="9" t="n">
-        <v>0.106</v>
-      </c>
+        <v>2.857</v>
+      </c>
+      <c r="K80" s="9" t="n"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
     </row>
@@ -4148,28 +4122,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>-0.0169</v>
+        <v>-0.0133</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>6973800</v>
+        <v>6554300</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="H81" t="n">
-        <v>63.81</v>
+        <v>52.41</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4177,10 +4151,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.273</v>
+        <v>0.367</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.269</v>
+        <v>0.366</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4193,38 +4167,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>-0.0034</v>
+        <v>0.61</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>6719400</v>
+        <v>6510000</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="H82" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.16</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.857</v>
-      </c>
-      <c r="K82" s="9" t="n"/>
+        <v>0.641</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.658</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
     </row>
@@ -4236,39 +4212,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>-0.0133</v>
+        <v>-0.0169</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>6554300</v>
+        <v>6474800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="H83" t="n">
-        <v>52.41</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.28</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.367</v>
+        <v>0.295</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.366</v>
+        <v>0.297</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4281,39 +4257,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>0.0083</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>6510000</v>
+        <v>6464300</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="H84" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.91</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.641</v>
+        <v>0.961</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.658</v>
+        <v>0.79</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4326,28 +4302,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.29</v>
+        <v>0.765</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>-0.0169</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>6474800</v>
+        <v>6443400</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="H85" t="n">
-        <v>31.28</v>
+        <v>46.15</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4355,10 +4331,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.295</v>
+        <v>0.774</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.297</v>
+        <v>0.773</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4371,39 +4347,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0.03700000000000001</v>
+        <v>4.49</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>-0.0197</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>6464300</v>
+        <v>6418400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1.39</v>
+        <v>0.85</v>
       </c>
       <c r="H86" t="n">
-        <v>84.91</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.1</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.961</v>
+        <v>4.599</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.79</v>
+        <v>4.54</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4416,39 +4392,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PESTEC</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.055</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>6443400</v>
+        <v>6318100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="H87" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.3</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.774</v>
+        <v>0.057</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.773</v>
+        <v>0.06</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4461,39 +4437,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>-0.0197</v>
+        <v>0.175</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0.09369999999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>6418400</v>
+        <v>6313200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.85</v>
+        <v>8.1</v>
       </c>
       <c r="H88" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.93000000000001</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>4.599</v>
+        <v>0.149</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>4.54</v>
+        <v>0.145</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4506,28 +4482,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PESTEC</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0.0682</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>6318100</v>
+        <v>6298900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>1.45</v>
+        <v>3.33</v>
       </c>
       <c r="H89" t="n">
-        <v>39.3</v>
+        <v>88.84</v>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
@@ -4535,10 +4511,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.057</v>
+        <v>2.187</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.06</v>
+        <v>1.93</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4551,39 +4527,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>0.09369999999999999</v>
+        <v>7.46</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>6313200</v>
+        <v>6268000</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>8.1</v>
+        <v>0.86</v>
       </c>
       <c r="H90" t="n">
-        <v>79.93000000000001</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.95</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.149</v>
+        <v>7.708</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.145</v>
+        <v>7.853</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4596,28 +4572,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.82</v>
+        <v>0.22</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>0.0682</v>
+        <v>0.0233</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>6298900</v>
+        <v>6254900</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>3.33</v>
+        <v>1.02</v>
       </c>
       <c r="H91" t="n">
-        <v>88.84</v>
+        <v>54.39</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4625,10 +4601,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.187</v>
+        <v>0.214</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.93</v>
+        <v>0.211</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4641,39 +4617,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>7.46</v>
+        <v>0.26</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>6268000</v>
+        <v>6180200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="H92" t="n">
-        <v>36.95</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.54</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>7.708</v>
+        <v>0.274</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>7.853</v>
+        <v>0.316</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4686,39 +4662,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0.0233</v>
+        <v>3.49</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>-0.0029</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>6254900</v>
+        <v>6126900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="H93" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.66</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.214</v>
+        <v>3.627</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.211</v>
+        <v>3.708</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4731,39 +4707,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>6180200</v>
+        <v>6123100</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.52</v>
+        <v>1.35</v>
       </c>
       <c r="H94" t="n">
-        <v>39.54</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.274</v>
+        <v>0.102</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.316</v>
+        <v>0.096</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4776,28 +4752,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>JADI</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>-0.0029</v>
+        <v>0.03</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>0.2</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>6126900</v>
+        <v>6000000</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.35</v>
+        <v>30</v>
       </c>
       <c r="H95" t="n">
-        <v>36.66</v>
+        <v>48.54</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4805,10 +4781,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>3.627</v>
+        <v>0.03</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>3.708</v>
+        <v>0.034</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4821,39 +4797,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>6.24</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>6123100</v>
+        <v>5968700</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.35</v>
+        <v>0.34</v>
       </c>
       <c r="H96" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.98</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.102</v>
+        <v>6.318</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.096</v>
+        <v>6.506</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4866,39 +4842,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>0452</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JADI</t>
+          <t>GOLDLI</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>0.2</v>
+        <v>0.095</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>6000000</v>
+        <v>5876700</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>30</v>
+        <v>6.11</v>
       </c>
       <c r="H97" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.2</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.03</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.034</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4911,28 +4887,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>-0.0016</v>
+        <v>13.14</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>5968700</v>
+        <v>5767700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.34</v>
+        <v>0.6</v>
       </c>
       <c r="H98" t="n">
-        <v>41.98</v>
+        <v>30.03</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4940,10 +4916,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>6.318</v>
+        <v>13.498</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>6.506</v>
+        <v>14.081</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4956,28 +4932,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0452</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GOLDLI</t>
+          <t>CFM</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.095</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>5876700</v>
+        <v>5704000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>6.11</v>
+        <v>2.85</v>
       </c>
       <c r="H99" t="n">
-        <v>63.2</v>
+        <v>67.5</v>
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
@@ -4985,10 +4961,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -5001,39 +4977,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>0.0061</v>
+        <v>2.57</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>5767700</v>
+        <v>5630600</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.6</v>
+        <v>1.77</v>
       </c>
       <c r="H100" t="n">
-        <v>30.03</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.98</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>13.498</v>
+        <v>2.679</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>14.081</v>
+        <v>2.795</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5046,28 +5022,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CFM</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>1.56</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>5704000</v>
+        <v>5614200</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="H101" t="n">
-        <v>67.5</v>
+        <v>41.51</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5075,10 +5051,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.075</v>
+        <v>1.587</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5091,39 +5067,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.57</v>
+        <v>4.35</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>-0.0115</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>5630600</v>
+        <v>5580200</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>1.77</v>
+        <v>0.47</v>
       </c>
       <c r="H102" t="n">
-        <v>30.98</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.81</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.679</v>
+        <v>3.43</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.795</v>
+        <v>2.293</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5136,28 +5112,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.56</v>
+        <v>0.695</v>
       </c>
       <c r="E103" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0296</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>5614200</v>
+        <v>5519800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>2.2</v>
+        <v>0.53</v>
       </c>
       <c r="H103" t="n">
-        <v>41.51</v>
+        <v>53.42</v>
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
@@ -5165,10 +5141,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.587</v>
+        <v>0.678</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.65</v>
+        <v>0.66</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5181,40 +5157,33 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>-0.04190000000000001</v>
+        <v>0.48</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>5580200</v>
+        <v>5465000</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H104" t="n">
-        <v>78.81</v>
+        <v>0.23</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J104" s="9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="K104" s="9" t="n">
-        <v>2.293</v>
-      </c>
+      <c r="J104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
     </row>
@@ -5226,28 +5195,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>0.0296</v>
+        <v>1.2</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>5519800</v>
+        <v>5453300</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="H105" t="n">
-        <v>53.42</v>
+        <v>58.08</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
@@ -5255,10 +5224,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.678</v>
+        <v>1.164</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.66</v>
+        <v>1.098</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5271,33 +5240,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SINARAN</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.48</v>
+        <v>0.105</v>
       </c>
       <c r="E106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>5465000</v>
+        <v>5409700</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.23</v>
+        <v>2.42</v>
+      </c>
+      <c r="H106" t="n">
+        <v>51.1</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
+      <c r="J106" s="9" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.102</v>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5309,39 +5285,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>-0.0244</v>
+        <v>0.115</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>5453300</v>
+        <v>5320600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H107" t="n">
-        <v>58.08</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.81</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.164</v>
+        <v>0.123</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.098</v>
+        <v>0.122</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5354,28 +5330,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SINARAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>7.9</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>5409700</v>
+        <v>5245700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>2.42</v>
+        <v>0.39</v>
       </c>
       <c r="H108" t="n">
-        <v>51.1</v>
+        <v>57.81</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5383,10 +5359,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.104</v>
+        <v>7.786</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.102</v>
+        <v>7.724</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5399,39 +5375,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>5320600</v>
+        <v>5094400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.55</v>
+        <v>2.03</v>
       </c>
       <c r="H109" t="n">
-        <v>41.81</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.87</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.123</v>
+        <v>1.477</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.122</v>
+        <v>1.536</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5444,28 +5420,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>-0.0075</v>
+        <v>0.42</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>0.012</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>5245700</v>
+        <v>5066900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="H110" t="n">
-        <v>57.81</v>
+        <v>62.57</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5473,10 +5449,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>7.786</v>
+        <v>0.408</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>7.724</v>
+        <v>0.409</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5489,28 +5465,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.5</v>
+        <v>10.22</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>0.0204</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>5094400</v>
+        <v>4990400</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>2.03</v>
+        <v>0.29</v>
       </c>
       <c r="H111" t="n">
-        <v>52.87</v>
+        <v>50.98</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5518,10 +5494,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.477</v>
+        <v>10.177</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.536</v>
+        <v>10.335</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5534,28 +5510,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>0.012</v>
+        <v>1.29</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>5066900</v>
+        <v>4912700</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="H112" t="n">
-        <v>62.57</v>
+        <v>33.75</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5563,10 +5539,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.408</v>
+        <v>1.332</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.409</v>
+        <v>1.452</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5579,39 +5555,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0363</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>PMCK</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>10.22</v>
+        <v>0.195</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0263</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>4990400</v>
+        <v>4850800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.29</v>
+        <v>11.17</v>
       </c>
       <c r="H113" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="I113" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>10.177</v>
+        <v>0.198</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>10.335</v>
+        <v>0.2</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5624,40 +5600,33 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>-0.0077</v>
+        <v>0.29</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>4912700</v>
+        <v>4691000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H114" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="I114" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J114" s="9" t="n">
-        <v>1.332</v>
-      </c>
-      <c r="K114" s="9" t="n">
-        <v>1.452</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
     </row>
@@ -5669,39 +5638,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0363</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PMCK</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0.0263</v>
+        <v>0.325</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>4850800</v>
+        <v>4688000</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>11.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.52</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.198</v>
+        <v>0.33</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5714,33 +5683,40 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.29</v>
+        <v>0.98</v>
       </c>
       <c r="E116" s="17" t="n">
-        <v>0.0357</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>4691000</v>
+        <v>4473500</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J116" s="9" t="n"/>
-      <c r="K116" s="9" t="n"/>
+        <v>1.56</v>
+      </c>
+      <c r="H116" t="n">
+        <v>67.97</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>0.802</v>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
     </row>
@@ -5752,39 +5728,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0.02</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>4688000</v>
+        <v>4472100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="H117" t="n">
-        <v>50.52</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.46</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.33</v>
+        <v>1.055</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.31</v>
+        <v>1.073</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5797,28 +5773,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>0.07099999999999999</v>
+        <v>2.67</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>4473500</v>
+        <v>4405600</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>1.56</v>
+        <v>0.46</v>
       </c>
       <c r="H118" t="n">
-        <v>67.97</v>
+        <v>45</v>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
@@ -5826,10 +5802,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.891</v>
+        <v>2.679</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.802</v>
+        <v>2.884</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5842,28 +5818,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>0.02</v>
+        <v>2.7</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>-0.0074</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>4472100</v>
+        <v>4361300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="H119" t="n">
-        <v>38.46</v>
+        <v>82.33</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5871,10 +5847,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.055</v>
+        <v>2.436</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.073</v>
+        <v>2.097</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5887,28 +5863,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>4405600</v>
+        <v>4272100</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.46</v>
+        <v>1.22</v>
       </c>
       <c r="H120" t="n">
-        <v>45</v>
+        <v>71.41</v>
       </c>
       <c r="I120" s="16" t="inlineStr">
         <is>
@@ -5916,10 +5892,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>2.679</v>
+        <v>1.1</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>2.884</v>
+        <v>0.999</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5932,39 +5908,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>-0.0074</v>
+        <v>0.845</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>4361300</v>
+        <v>4260100</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.76</v>
+        <v>1.51</v>
       </c>
       <c r="H121" t="n">
-        <v>82.33</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.62</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.436</v>
+        <v>0.797</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.097</v>
+        <v>0.714</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5977,39 +5953,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="E122" s="17" t="n">
-        <v>0.0169</v>
+        <v>0.0159</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>4272100</v>
+        <v>4150400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.22</v>
+        <v>0.78</v>
       </c>
       <c r="H122" t="n">
-        <v>71.41</v>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.51</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.1</v>
+        <v>1.292</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.999</v>
+        <v>1.324</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6022,28 +5998,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>4260100</v>
+        <v>4123800</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>1.51</v>
+        <v>0.62</v>
       </c>
       <c r="H123" t="n">
-        <v>65.62</v>
+        <v>47.42</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -6051,10 +6027,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.797</v>
+        <v>0.321</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.714</v>
+        <v>0.339</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6067,39 +6043,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.28</v>
+        <v>0.425</v>
       </c>
       <c r="E124" s="17" t="n">
-        <v>0.0159</v>
+        <v>0.0241</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>4150400</v>
+        <v>4118500</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="H124" t="n">
-        <v>44.51</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.85</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.292</v>
+        <v>0.4</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.324</v>
+        <v>0.399</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6112,40 +6088,33 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0.0323</v>
+        <v>0.285</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>4123800</v>
+        <v>4029500</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H125" t="n">
-        <v>47.42</v>
+        <v>0.21</v>
       </c>
       <c r="I125" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J125" s="9" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="K125" s="9" t="n">
-        <v>0.339</v>
-      </c>
+      <c r="J125" s="9" t="n"/>
+      <c r="K125" s="9" t="n"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
     </row>
@@ -6157,39 +6126,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0.0241</v>
+        <v>0.98</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>-0.0297</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>4118500</v>
+        <v>3988400</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.7</v>
+        <v>1.64</v>
       </c>
       <c r="H126" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.36</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.4</v>
+        <v>1.054</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.399</v>
+        <v>1.011</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6202,33 +6171,40 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>-0.0339</v>
+        <v>0.29</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>4029500</v>
+        <v>3985400</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.21</v>
+        <v>0.51</v>
+      </c>
+      <c r="H127" t="n">
+        <v>39.09</v>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J127" s="9" t="n"/>
-      <c r="K127" s="9" t="n"/>
+      <c r="J127" s="9" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>0.312</v>
+      </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
     </row>
@@ -6240,39 +6216,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>-0.0297</v>
+        <v>1.39</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>3988400</v>
+        <v>3910600</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="H128" t="n">
-        <v>38.36</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.28</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.054</v>
+        <v>1.351</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.011</v>
+        <v>1.323</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6285,39 +6261,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>3985400</v>
+        <v>3908400</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.51</v>
+        <v>1.24</v>
       </c>
       <c r="H129" t="n">
-        <v>39.09</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.299</v>
+        <v>0.262</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.312</v>
+        <v>0.25</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6330,39 +6306,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E130" s="17" t="n">
-        <v>0.0072</v>
+        <v>0.715</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>3910600</v>
+        <v>3903800</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="H130" t="n">
-        <v>68.28</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.09</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.351</v>
+        <v>0.737</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.323</v>
+        <v>0.753</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6375,39 +6351,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>-0.0189</v>
+        <v>3.63</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>0.0645</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>3908400</v>
+        <v>3894700</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="H131" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.5</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.262</v>
+        <v>3.281</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.25</v>
+        <v>2.861</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6420,39 +6396,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>-0.0138</v>
+        <v>1.24</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0.07829999999999999</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>3903800</v>
+        <v>3892000</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>2.44</v>
+        <v>1.51</v>
       </c>
       <c r="H132" t="n">
-        <v>38.09</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.737</v>
+        <v>1.023</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.753</v>
+        <v>0.876</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6465,28 +6441,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>0.0645</v>
+        <v>0.31</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>3894700</v>
+        <v>3852400</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>1.27</v>
+        <v>0.51</v>
       </c>
       <c r="H133" t="n">
-        <v>76.5</v>
+        <v>61.25</v>
       </c>
       <c r="I133" s="16" t="inlineStr">
         <is>
@@ -6494,10 +6470,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>3.281</v>
+        <v>0.307</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>2.861</v>
+        <v>0.294</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6510,28 +6486,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.24</v>
+        <v>0.66</v>
       </c>
       <c r="E134" s="17" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0233</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>3892000</v>
+        <v>3817500</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>1.51</v>
+        <v>0.4</v>
       </c>
       <c r="H134" t="n">
-        <v>83.09999999999999</v>
+        <v>59.78</v>
       </c>
       <c r="I134" s="16" t="inlineStr">
         <is>
@@ -6539,10 +6515,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.023</v>
+        <v>0.63</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.876</v>
+        <v>0.571</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6555,28 +6531,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
+        <v>1.78</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>3852400</v>
+        <v>3806300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H135" t="n">
-        <v>61.25</v>
+        <v>50.3</v>
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
@@ -6584,10 +6560,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.307</v>
+        <v>1.772</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.294</v>
+        <v>1.808</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6600,39 +6576,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E136" s="17" t="n">
-        <v>0.0233</v>
+        <v>6.69</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>3817500</v>
+        <v>3792700</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.4</v>
+        <v>0.89</v>
       </c>
       <c r="H136" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.9</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.63</v>
+        <v>6.785</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.571</v>
+        <v>6.79</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6645,28 +6621,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.78</v>
+        <v>0.16</v>
       </c>
       <c r="E137" s="17" t="n">
-        <v>0.0171</v>
+        <v>0.0667</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>3806300</v>
+        <v>3783100</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.61</v>
+        <v>1.56</v>
       </c>
       <c r="H137" t="n">
-        <v>50.3</v>
+        <v>63.84</v>
       </c>
       <c r="I137" s="16" t="inlineStr">
         <is>
@@ -6674,10 +6650,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.772</v>
+        <v>0.146</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.808</v>
+        <v>0.138</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6690,39 +6666,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>-0.004500000000000001</v>
+        <v>2.62</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>0.0234</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>3792700</v>
+        <v>3729800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H138" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.93</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>6.785</v>
+        <v>2.57</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>6.79</v>
+        <v>2.532</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6735,28 +6711,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0.0667</v>
+        <v>0.49</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>3783100</v>
+        <v>3700200</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="H139" t="n">
-        <v>63.84</v>
+        <v>74.59</v>
       </c>
       <c r="I139" s="16" t="inlineStr">
         <is>
@@ -6764,10 +6740,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.146</v>
+        <v>0.443</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.138</v>
+        <v>0.402</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6780,39 +6756,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>0.0234</v>
+        <v>0.58</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>3729800</v>
+        <v>3683600</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="H140" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.05</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.57</v>
+        <v>0.588</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.532</v>
+        <v>0.587</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6825,39 +6801,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>0.105</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>3700200</v>
+        <v>3642200</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>1.15</v>
+        <v>0.14</v>
       </c>
       <c r="H141" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.42</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.443</v>
+        <v>0.137</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.402</v>
+        <v>0.164</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6870,39 +6846,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>CJCEN</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.185</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>3683600</v>
+        <v>3616700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.96</v>
+        <v>13.77</v>
       </c>
       <c r="H142" t="n">
-        <v>43.05</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.75</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.588</v>
+        <v>0.169</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.587</v>
+        <v>0.162</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6915,39 +6891,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>-0.0455</v>
+        <v>5.05</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>3642200</v>
+        <v>3569500</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.14</v>
+        <v>0.65</v>
       </c>
       <c r="H143" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.43</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.137</v>
+        <v>4.982</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.164</v>
+        <v>5.036</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6960,28 +6936,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CJCEN</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.185</v>
+        <v>2.17</v>
       </c>
       <c r="E144" s="17" t="n">
-        <v>0.0571</v>
+        <v>0.1015</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>3616700</v>
+        <v>3530500</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>13.77</v>
+        <v>1.8</v>
       </c>
       <c r="H144" t="n">
-        <v>74.75</v>
+        <v>71.16</v>
       </c>
       <c r="I144" s="16" t="inlineStr">
         <is>
@@ -6989,10 +6965,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.169</v>
+        <v>1.884</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.162</v>
+        <v>1.872</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7005,28 +6981,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>5.05</v>
+        <v>3.01</v>
       </c>
       <c r="E145" s="17" t="n">
-        <v>0.0202</v>
+        <v>0.0033</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>3569500</v>
+        <v>3468000</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.65</v>
+        <v>1.07</v>
       </c>
       <c r="H145" t="n">
-        <v>53.43</v>
+        <v>49.45</v>
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
@@ -7034,10 +7010,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>4.982</v>
+        <v>3.013</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>5.036</v>
+        <v>3.041</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7050,28 +7026,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>2.17</v>
+        <v>0.6</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>0.1015</v>
+        <v>0.0526</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>3530500</v>
+        <v>3461500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="H146" t="n">
-        <v>71.16</v>
+        <v>50.75</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7079,10 +7055,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.884</v>
+        <v>0.593</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.872</v>
+        <v>0.611</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7095,28 +7071,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>3.01</v>
+        <v>0.525</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.0033</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>3468000</v>
+        <v>3369900</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>1.07</v>
+        <v>0.55</v>
       </c>
       <c r="H147" t="n">
-        <v>49.45</v>
+        <v>52.8</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7124,10 +7100,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>3.013</v>
+        <v>0.518</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>3.041</v>
+        <v>0.53</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7140,28 +7116,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.525</v>
+        <v>0.885</v>
       </c>
       <c r="E148" s="17" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>3369900</v>
+        <v>3343400</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.55</v>
+        <v>3.1</v>
       </c>
       <c r="H148" t="n">
-        <v>52.8</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7169,10 +7145,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.518</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.53</v>
+        <v>0.793</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7185,28 +7161,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.885</v>
+        <v>0.265</v>
       </c>
       <c r="E149" s="17" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>3343400</v>
+        <v>3341500</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="H149" t="n">
-        <v>72.20999999999999</v>
+        <v>54.05</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7214,10 +7190,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.253</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.793</v>
+        <v>0.273</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7230,39 +7206,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.265</v>
+        <v>0.615</v>
       </c>
       <c r="E150" s="17" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>3341500</v>
+        <v>3299500</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="H150" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.06</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.253</v>
+        <v>0.608</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.273</v>
+        <v>0.587</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7275,39 +7251,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.615</v>
+        <v>0.55</v>
       </c>
       <c r="E151" s="17" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.05769999999999999</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>3299500</v>
+        <v>3286800</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="H151" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.26</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.608</v>
+        <v>0.493</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.587</v>
+        <v>0.395</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-25'!$A$1:$M$304</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -563,28 +563,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HPMT</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.23</v>
+        <v>0.435</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0698</v>
+        <v>0.0357</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5696100</v>
+        <v>5168600</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>25.81</v>
+        <v>2.79</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>74.75</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.199</v>
+        <v>0.394</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.186</v>
+        <v>0.38</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>RSI达74.75，已进入超买区；现价0.23高于50日均线0.186约24%，短期均线多头排列，信号偏强但需留意超买风险。</t>
+          <t>现价0.435高于50日均线0.38，均线呈多头排列；但RSI达72.15已入超买区，短期动能偏强而回撤风险上升，信号可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -616,95 +616,103 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>5291</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>HPMT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.04650000000000001</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>5817900</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>现价0.225高于50日均线0.186，均线多头排列；但RSI达72.9已入超买区，短期动能偏热，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>7204</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>D&amp;O</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.0467</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>5874800</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>71.27</v>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
+      <c r="D4" s="3" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7249400</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.475</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K4" s="3" t="n">
         <v>0.401</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>现价0.56高于50日均线0.401，RSI达71.27已入超买区，EMA与Supertrend偏多，但RSI偏高，信号可靠性需谨慎看待。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>-0.0263</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>45871700</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22.18</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="14" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>RSI达71.82，已进入超买区；现价0.565远高于50日均线0.401，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -714,31 +722,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>44333700</v>
-      </c>
-      <c r="G5" s="12" t="n"/>
+        <v>80425100</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>22.18</v>
+      </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.491</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
     </row>
@@ -750,40 +767,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.135</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>40917900</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.116</v>
-      </c>
+        <v>49582000</v>
+      </c>
+      <c r="G6" s="12" t="n"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
     </row>
@@ -795,39 +803,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-0.0414</v>
+        <v>0.18</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>28253900</v>
+        <v>44534600</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.48</v>
+        <v>0.98</v>
       </c>
       <c r="H7" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.5</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2.587</v>
+        <v>0.146</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2.44</v>
+        <v>0.116</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -840,28 +848,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.72</v>
+        <v>2.55</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>-0.0464</v>
+        <v>-0.0414</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18113200</v>
+        <v>30021300</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.42</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>49.15</v>
+        <v>49.39</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -869,10 +877,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.735</v>
+        <v>2.587</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -885,39 +893,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.0571</v>
+        <v>0.725</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0397</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>14113000</v>
+        <v>22738200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>3.38</v>
+        <v>0.52</v>
       </c>
       <c r="H9" t="n">
-        <v>55.81</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.12</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.18</v>
+        <v>0.736</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.189</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -930,39 +938,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.395</v>
+        <v>0.355</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>-0.0595</v>
+        <v>-0.0658</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>10029600</v>
+        <v>17498600</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="H10" t="n">
-        <v>56.63</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.56999999999999</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.382</v>
+        <v>0.316</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.32</v>
+        <v>0.183</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -975,28 +983,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.55</v>
+        <v>0.19</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.0857</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9921000</v>
+        <v>14737500</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.7</v>
+        <v>3.53</v>
       </c>
       <c r="H11" t="n">
-        <v>62.28</v>
+        <v>61.83</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
@@ -1004,10 +1012,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.521</v>
+        <v>0.18</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.531</v>
+        <v>0.189</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1020,39 +1028,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CJCEN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.395</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0595</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>9491200</v>
+        <v>13802200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>22.43</v>
+        <v>0.63</v>
       </c>
       <c r="H12" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.63</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.172</v>
+        <v>0.382</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.163</v>
+        <v>0.32</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1065,28 +1073,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.0213</v>
+        <v>0.0275</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9485400</v>
+        <v>11178600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.53</v>
+        <v>0.83</v>
       </c>
       <c r="H13" t="n">
-        <v>56.39</v>
+        <v>60.99</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -1094,10 +1102,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.232</v>
+        <v>0.524</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.233</v>
+        <v>0.477</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1110,28 +1118,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.0263</v>
+        <v>0.555</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9449500</v>
+        <v>10579800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.21</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>72.92</v>
+        <v>63.74</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1139,10 +1147,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.318</v>
+        <v>0.521</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.183</v>
+        <v>0.531</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1155,39 +1163,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.0367</v>
+        <v>0.53</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8919600</v>
+        <v>10195600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.66</v>
+        <v>0.27</v>
       </c>
       <c r="H15" t="n">
-        <v>61.86</v>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.93</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.525</v>
+        <v>0.634</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.477</v>
+        <v>0.851</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1200,28 +1208,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.72</v>
+        <v>0.245</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.036</v>
+        <v>0.0426</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8763800</v>
+        <v>9868500</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.95</v>
+        <v>0.55</v>
       </c>
       <c r="H16" t="n">
-        <v>57.43</v>
+        <v>59.1</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1229,10 +1237,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.663</v>
+        <v>0.233</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1245,39 +1253,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>-0.0158</v>
+        <v>-0.0171</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8734500</v>
+        <v>9810200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.15</v>
+        <v>0.41</v>
       </c>
       <c r="H17" t="n">
-        <v>71.01000000000001</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.27</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.883</v>
+        <v>0.546</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.851</v>
+        <v>0.493</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1290,28 +1298,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CJCEN</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.0321</v>
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0.08109999999999999</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8371800</v>
+        <v>9756400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.34</v>
+        <v>23.06</v>
       </c>
       <c r="H18" t="n">
-        <v>59.95</v>
+        <v>82.14</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1319,10 +1327,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.735</v>
+        <v>0.172</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.524</v>
+        <v>0.163</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1335,28 +1343,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.58</v>
+        <v>1.82</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0267</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7286400</v>
+        <v>9173300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="H19" t="n">
-        <v>68.72</v>
+        <v>60.88</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1364,10 +1372,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.547</v>
+        <v>1.736</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.493</v>
+        <v>1.524</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1380,28 +1388,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0</v>
+        <v>0.715</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0.0288</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7119000</v>
+        <v>9163300</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.74</v>
+        <v>0.99</v>
       </c>
       <c r="H20" t="n">
-        <v>56.29</v>
+        <v>56.69</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -1409,10 +1417,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.053</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.043</v>
+        <v>0.663</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1425,28 +1433,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.0143</v>
+        <v>0.22</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6412500</v>
+        <v>9089700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.6</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="n">
-        <v>57.32</v>
+        <v>71.25</v>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
@@ -1454,10 +1462,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.339</v>
+        <v>0.202</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.333</v>
+        <v>0.184</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1470,36 +1478,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.945</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6403200</v>
+        <v>8927500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.17</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>27.96</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.98999999999999</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.634</v>
+        <v>0.884</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0.851</v>
@@ -1515,40 +1523,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.005</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6215800</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H23" t="n">
-        <v>50.74</v>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0.471</v>
-      </c>
+        <v>8298300</v>
+      </c>
+      <c r="G23" s="12" t="n"/>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1560,39 +1559,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-0.0323</v>
+        <v>-0.0105</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6082600</v>
+        <v>7652700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H24" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.74</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.303</v>
+        <v>0.468</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.29</v>
+        <v>0.471</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1605,39 +1604,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.145</v>
+        <v>0.3</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>-0.0333</v>
+        <v>-0.0323</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6010000</v>
+        <v>7468700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H25" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.158</v>
+        <v>0.303</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.148</v>
+        <v>0.29</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1650,28 +1649,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.055</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5904000</v>
+        <v>7119000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>3.44</v>
+        <v>0.74</v>
       </c>
       <c r="H26" t="n">
-        <v>83.92</v>
+        <v>56.29</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -1679,10 +1678,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.225</v>
+        <v>0.053</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.209</v>
+        <v>0.043</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1695,28 +1694,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0.0132</v>
+        <v>0.145</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5482100</v>
+        <v>7029400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.57</v>
+        <v>0.17</v>
       </c>
       <c r="H27" t="n">
-        <v>63.96</v>
+        <v>45.75</v>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
@@ -1724,10 +1723,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.373</v>
+        <v>0.158</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.371</v>
+        <v>0.148</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1740,39 +1739,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0</v>
+        <v>3.51</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5326900</v>
+        <v>6960300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.54</v>
+        <v>1.48</v>
       </c>
       <c r="H28" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.66</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.608</v>
+        <v>3.616</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.604</v>
+        <v>3.704</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1785,31 +1784,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.005</v>
+        <v>0.245</v>
       </c>
       <c r="E29" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5218300</v>
-      </c>
-      <c r="G29" s="12" t="n"/>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
+        <v>6747600</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.328</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
     </row>
@@ -1821,28 +1829,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5019600</v>
+        <v>6726600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.24</v>
+        <v>3.92</v>
       </c>
       <c r="H30" t="n">
-        <v>71.25</v>
+        <v>83.92</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -1850,10 +1858,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.202</v>
+        <v>0.225</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.184</v>
+        <v>0.209</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1866,28 +1874,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0.0357</v>
+        <v>0.345</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4635100</v>
+        <v>6712400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="H31" t="n">
-        <v>72.15000000000001</v>
+        <v>57.32</v>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
@@ -1895,10 +1903,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.394</v>
+        <v>0.339</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.38</v>
+        <v>0.333</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1926,10 +1934,10 @@
         <v>-0.006500000000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4541500</v>
+        <v>6381500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.36</v>
+        <v>0.51</v>
       </c>
       <c r="H32" t="n">
         <v>47.75</v>
@@ -1971,10 +1979,10 @@
         <v>0.0058</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4431000</v>
+        <v>6013000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="H33" t="n">
         <v>46.9</v>
@@ -2001,39 +2009,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4427900</v>
+        <v>5677100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.38</v>
+        <v>0.59</v>
       </c>
       <c r="H34" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.96</v>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.154</v>
+        <v>0.373</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.147</v>
+        <v>0.371</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2046,28 +2054,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.245</v>
+        <v>0.605</v>
       </c>
       <c r="E35" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4364600</v>
+        <v>5350700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="H35" t="n">
-        <v>31.98</v>
+        <v>48.07</v>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
@@ -2075,10 +2083,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.276</v>
+        <v>0.608</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.328</v>
+        <v>0.604</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2091,39 +2099,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.795</v>
+        <v>4.86</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>-0.0124</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4337100</v>
+        <v>5297700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.04</v>
+        <v>0.28</v>
       </c>
       <c r="H36" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.59</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.803</v>
+        <v>4.74</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.806</v>
+        <v>4.509</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2136,39 +2144,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.002</v>
+        <v>0.155</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4227400</v>
+        <v>5150000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H37" t="n">
-        <v>63.46</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>4.741</v>
+        <v>0.156</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>4.509</v>
+        <v>0.159</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2181,28 +2189,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.165</v>
+        <v>0.47</v>
       </c>
       <c r="E38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3881500</v>
+        <v>4446100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="H38" t="n">
-        <v>34.17</v>
+        <v>58.56</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2210,10 +2218,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.182</v>
+        <v>0.448</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.221</v>
+        <v>0.407</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2226,28 +2234,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.155</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3749300</v>
+        <v>4427900</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="H39" t="n">
-        <v>49.23</v>
+        <v>52.85</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2255,10 +2263,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.295</v>
+        <v>0.154</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.297</v>
+        <v>0.147</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2271,28 +2279,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.98</v>
+        <v>0.8</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>-0.0165</v>
+        <v>-0.0062</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3546100</v>
+        <v>4374400</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.26</v>
+        <v>1.05</v>
       </c>
       <c r="H40" t="n">
-        <v>64.89</v>
+        <v>48.44</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -2300,10 +2308,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.858</v>
+        <v>0.803</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.716</v>
+        <v>0.806</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2316,28 +2324,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.295</v>
+        <v>0.83</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.0122</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3541000</v>
+        <v>4372700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="H41" t="n">
-        <v>66.27</v>
+        <v>71.11</v>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
@@ -2345,10 +2353,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.275</v>
+        <v>0.715</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.27</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2361,39 +2369,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.215</v>
+        <v>2.98</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>-0.0227</v>
+        <v>-0.0165</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3475900</v>
+        <v>4300200</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H42" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.89</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.238</v>
+        <v>2.858</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.249</v>
+        <v>2.716</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2406,39 +2414,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.0213</v>
+        <v>0.295</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3461700</v>
+        <v>4101000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="H43" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.27</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.447</v>
+        <v>0.275</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.407</v>
+        <v>0.27</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2451,28 +2459,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.18</v>
+        <v>1.3</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>0.0286</v>
+        <v>0.0156</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3407600</v>
+        <v>3929600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>3.13</v>
+        <v>0.72</v>
       </c>
       <c r="H44" t="n">
-        <v>81.90000000000001</v>
+        <v>95.47</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -2480,10 +2488,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.152</v>
+        <v>0.88</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.145</v>
+        <v>0.734</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2496,39 +2504,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
         <v>0.165</v>
       </c>
-      <c r="E45" s="16" t="n">
-        <v>0.0313</v>
+      <c r="E45" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3335700</v>
+        <v>3913100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.28</v>
+        <v>0.14</v>
       </c>
       <c r="H45" t="n">
-        <v>66.66</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.17</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.148</v>
+        <v>0.182</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.139</v>
+        <v>0.221</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2541,28 +2549,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.31</v>
+        <v>0.215</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>-0.0438</v>
+        <v>-0.0227</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3178900</v>
+        <v>3770200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1.37</v>
+        <v>0.17</v>
       </c>
       <c r="H46" t="n">
-        <v>38.43</v>
+        <v>29.99</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2570,10 +2578,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.405</v>
+        <v>0.238</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.317</v>
+        <v>0.249</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2586,39 +2594,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0192</v>
+        <v>0.295</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2899500</v>
+        <v>3749300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.24</v>
+        <v>2.02</v>
       </c>
       <c r="H47" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.272</v>
+        <v>0.295</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.314</v>
+        <v>0.297</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2631,28 +2639,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>-0.0076</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2833500</v>
+        <v>3457300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.24</v>
+        <v>1.49</v>
       </c>
       <c r="H48" t="n">
-        <v>43.34</v>
+        <v>37.44</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2660,10 +2668,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.374</v>
+        <v>1.404</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.29</v>
+        <v>1.317</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2676,28 +2684,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.175</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2803300</v>
+        <v>3440600</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.17</v>
+        <v>3.16</v>
       </c>
       <c r="H49" t="n">
-        <v>52.86</v>
+        <v>79.92</v>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
@@ -2705,10 +2713,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.35</v>
+        <v>0.151</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.239</v>
+        <v>0.145</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2721,28 +2729,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.335</v>
+        <v>0.165</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>0.0308</v>
+        <v>0.0313</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2667900</v>
+        <v>3355700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.33</v>
+        <v>1.29</v>
       </c>
       <c r="H50" t="n">
-        <v>54.74</v>
+        <v>66.66</v>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
@@ -2750,10 +2758,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.331</v>
+        <v>0.148</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.311</v>
+        <v>0.139</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2766,39 +2774,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>0.0139</v>
+        <v>1.05</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2634600</v>
+        <v>3298500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H51" t="n">
-        <v>67.36</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.24</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.337</v>
+        <v>1.081</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.319</v>
+        <v>1.024</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2811,28 +2819,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0.0156</v>
+        <v>2.79</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0312</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2576900</v>
+        <v>3205000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H52" t="n">
-        <v>95.47</v>
+        <v>61.02</v>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
@@ -2840,10 +2848,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.88</v>
+        <v>2.626</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.734</v>
+        <v>2.495</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2856,28 +2864,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0135</v>
+        <v>0.325</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2563900</v>
+        <v>3162500</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
       <c r="H53" t="n">
-        <v>48.52</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
@@ -2885,10 +2893,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.367</v>
+        <v>0.285</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.366</v>
+        <v>0.277</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2901,39 +2909,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2528400</v>
+        <v>3157000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H54" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.34</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.714</v>
+        <v>1.374</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2946,28 +2954,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.72</v>
+        <v>0.255</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.0192</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2501600</v>
+        <v>2954600</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="H55" t="n">
-        <v>60.74</v>
+        <v>37.73</v>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
@@ -2975,10 +2983,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.681</v>
+        <v>0.272</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.611</v>
+        <v>0.314</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2991,28 +2999,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0119</v>
+        <v>0.33</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2452800</v>
+        <v>2856200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.22</v>
+        <v>0.36</v>
       </c>
       <c r="H56" t="n">
-        <v>56.5</v>
+        <v>52.72</v>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
@@ -3020,10 +3028,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.409</v>
+        <v>0.33</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.41</v>
+        <v>0.311</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3036,39 +3044,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.77</v>
+        <v>2.08</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>-0.0382</v>
+        <v>-0.0048</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2435400</v>
+        <v>2838900</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="H57" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.624</v>
+        <v>2.126</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.495</v>
+        <v>2.062</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3081,39 +3089,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0</v>
+        <v>0.72</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2276900</v>
+        <v>2829000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H58" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.74</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.244</v>
+        <v>0.681</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.243</v>
+        <v>0.611</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3126,39 +3134,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0.0062</v>
+        <v>2.37</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2241100</v>
+        <v>2806700</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H59" t="n">
-        <v>52.51</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.239</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3171,28 +3179,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0.023</v>
+        <v>0.365</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2184700</v>
+        <v>2774000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.18</v>
+        <v>0.46</v>
       </c>
       <c r="H60" t="n">
-        <v>79.79000000000001</v>
+        <v>48.52</v>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
@@ -3200,10 +3208,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>3.527</v>
+        <v>0.367</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.356</v>
+        <v>0.366</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3216,39 +3224,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0.0201</v>
+        <v>0.36</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2153000</v>
+        <v>2696600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H61" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.70999999999999</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>3.621</v>
+        <v>0.337</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>3.705</v>
+        <v>0.319</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3261,39 +3269,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>-0.0455</v>
+        <v>2.5</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2120000</v>
+        <v>2630600</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H62" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.94</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.081</v>
+        <v>2.439</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.024</v>
+        <v>2.276</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3306,28 +3314,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>0.0333</v>
+        <v>0.41</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2103400</v>
+        <v>2472800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="H63" t="n">
-        <v>47.25</v>
+        <v>51.48</v>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
@@ -3335,10 +3343,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.928</v>
+        <v>0.409</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.969</v>
+        <v>0.41</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3351,28 +3359,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0119</v>
+        <v>4.44</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0.0207</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2089600</v>
+        <v>2383700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="H64" t="n">
-        <v>59.92</v>
+        <v>79.69</v>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
@@ -3380,10 +3388,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>5.688</v>
+        <v>3.526</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>5.131</v>
+        <v>2.355</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3396,28 +3404,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0417</v>
+        <v>1.3</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2072900</v>
+        <v>2361300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H65" t="n">
-        <v>50.13</v>
+        <v>36.84</v>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
@@ -3425,10 +3433,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.163</v>
+        <v>1.329</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.1</v>
+        <v>1.444</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3441,28 +3449,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0</v>
+        <v>5.81</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.0136</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2005500</v>
+        <v>2352700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H66" t="n">
-        <v>39.08</v>
+        <v>59.45</v>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
@@ -3470,10 +3478,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.298</v>
+        <v>5.687</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.312</v>
+        <v>5.131</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3486,39 +3494,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>0.0121</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2003900</v>
+        <v>2312100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
-        <v>61.94</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.439</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.276</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3531,39 +3539,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.0222</v>
+        <v>0.26</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>0.04</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1946500</v>
+        <v>2304300</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.36</v>
+        <v>2.24</v>
       </c>
       <c r="H68" t="n">
-        <v>73.93000000000001</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.58</v>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.455</v>
+        <v>0.212</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2.118</v>
+        <v>0.198</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3576,39 +3584,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>0.0086</v>
+        <v>0.23</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1769000</v>
+        <v>2276900</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="H69" t="n">
-        <v>49.17</v>
-      </c>
-      <c r="I69" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.51</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.181</v>
+        <v>0.244</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.14</v>
+        <v>0.243</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3621,28 +3629,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>0.0152</v>
+        <v>0.29</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1766700</v>
+        <v>2261100</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>61.53</v>
+        <v>39.08</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -3650,10 +3658,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.634</v>
+        <v>0.298</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.575</v>
+        <v>0.312</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3666,39 +3674,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.1</v>
+        <v>0.93</v>
       </c>
       <c r="E71" s="16" t="n">
-        <v>0.0048</v>
+        <v>0.0333</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1766500</v>
+        <v>2234000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.11</v>
+        <v>0.68</v>
       </c>
       <c r="H71" t="n">
-        <v>48.16</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.25</v>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.128</v>
+        <v>0.928</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.062</v>
+        <v>0.969</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3711,28 +3719,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>0.04</v>
+        <v>1.15</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1703600</v>
+        <v>2207200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>1.65</v>
+        <v>0.24</v>
       </c>
       <c r="H72" t="n">
-        <v>73.58</v>
+        <v>50.13</v>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
@@ -3740,10 +3748,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.212</v>
+        <v>1.163</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.198</v>
+        <v>1.1</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3756,39 +3764,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.32</v>
+        <v>0.765</v>
       </c>
       <c r="E73" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1701300</v>
+        <v>2156200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.1</v>
+        <v>0.34</v>
       </c>
       <c r="H73" t="n">
-        <v>65.18000000000001</v>
-      </c>
-      <c r="I73" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.284</v>
+        <v>0.773</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.277</v>
+        <v>0.773</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3801,28 +3809,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.0229</v>
+        <v>0.67</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1669400</v>
+        <v>2097100</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H74" t="n">
-        <v>49.38</v>
+        <v>61.53</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -3830,10 +3838,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.569</v>
+        <v>0.634</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.535</v>
+        <v>0.575</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3846,39 +3854,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0</v>
+        <v>2.66</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0148</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1582900</v>
+        <v>2046900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="H75" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>76.54000000000001</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.402</v>
+        <v>2.457</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.4</v>
+        <v>2.118</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3891,39 +3899,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0204</v>
+        <v>0.425</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1581600</v>
+        <v>1930800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="H76" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.85</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.045</v>
+        <v>0.402</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.014</v>
+        <v>0.4</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3936,39 +3944,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1534000</v>
+        <v>1795100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H77" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.17</v>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.181</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3981,28 +3989,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.54</v>
+        <v>2.55</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>-0.0182</v>
+        <v>-0.0267</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1518000</v>
+        <v>1723500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="H78" t="n">
-        <v>61.11</v>
+        <v>48.43</v>
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
@@ -4010,10 +4018,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.497</v>
+        <v>2.568</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.401</v>
+        <v>2.535</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4026,39 +4034,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0</v>
+        <v>4.11</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1466400</v>
+        <v>1690200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="H79" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.13</v>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.773</v>
+        <v>3.54</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.773</v>
+        <v>3.224</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4086,10 +4094,10 @@
         <v>-0.0039</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1450500</v>
+        <v>1666500</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H80" t="n">
         <v>47.99</v>
@@ -4116,39 +4124,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>-0.0112</v>
+        <v>0.545</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1433400</v>
+        <v>1659000</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H81" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.08</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.771</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.806</v>
+        <v>0.59</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4161,28 +4169,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>-0.0164</v>
+        <v>-0.0204</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1363300</v>
+        <v>1620900</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.27</v>
+        <v>0.65</v>
       </c>
       <c r="H82" t="n">
-        <v>35.76</v>
+        <v>35.93</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4190,10 +4198,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.637</v>
+        <v>1.045</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.657</v>
+        <v>1.014</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4206,39 +4214,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0.0155</v>
+        <v>0.26</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1349700</v>
+        <v>1602800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.11</v>
+        <v>0.58</v>
       </c>
       <c r="H83" t="n">
-        <v>39.66</v>
-      </c>
-      <c r="I83" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.33</v>
+        <v>0.262</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.445</v>
+        <v>0.251</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4251,33 +4259,40 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.245</v>
+        <v>1.04</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>-0.0392</v>
+        <v>-0.0189</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1349400</v>
+        <v>1588700</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
+        <v>0.19</v>
+      </c>
+      <c r="H84" t="n">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.759</v>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
     </row>
@@ -4289,28 +4304,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1347900</v>
+        <v>1538800</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.4</v>
+        <v>0.86</v>
       </c>
       <c r="H85" t="n">
-        <v>70.55</v>
+        <v>60.09</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4318,10 +4333,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.634</v>
+        <v>0.497</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.591</v>
+        <v>0.401</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4334,28 +4349,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="E86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1299900</v>
+        <v>1534900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="H86" t="n">
-        <v>50.51</v>
+        <v>38.17</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4363,10 +4378,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.262</v>
+        <v>0.638</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.251</v>
+        <v>0.658</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4379,28 +4394,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.25</v>
+        <v>0.865</v>
       </c>
       <c r="E87" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1246100</v>
+        <v>1529100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="H87" t="n">
-        <v>49.72</v>
+        <v>59.03</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4408,10 +4423,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.249</v>
+        <v>0.859</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.253</v>
+        <v>0.856</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4424,39 +4439,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0189</v>
+        <v>1.63</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1232100</v>
+        <v>1519800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="H88" t="n">
-        <v>55.42</v>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.25</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.512</v>
+        <v>1.73</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.464</v>
+        <v>1.847</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4469,28 +4484,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>-0.0283</v>
+        <v>-0.0112</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1220900</v>
+        <v>1460200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H89" t="n">
-        <v>75.38</v>
+        <v>47.93</v>
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
@@ -4498,10 +4513,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.892</v>
+        <v>1.771</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.759</v>
+        <v>1.806</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4514,28 +4529,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.67</v>
+        <v>0.21</v>
       </c>
       <c r="E90" s="16" t="n">
-        <v>0.0373</v>
+        <v>0.0244</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1169800</v>
+        <v>1428600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>3.41</v>
+        <v>0.52</v>
       </c>
       <c r="H90" t="n">
-        <v>71.34999999999999</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -4543,10 +4558,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.588</v>
+        <v>0.187</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1.536</v>
+        <v>0.156</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4559,39 +4574,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0049</v>
+        <v>1.89</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1163100</v>
+        <v>1418800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="H91" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.25</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>3.533</v>
+        <v>1.956</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>3.223</v>
+        <v>2.078</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4604,39 +4619,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0.0394</v>
+        <v>0.36</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1158000</v>
+        <v>1408400</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H92" t="n">
-        <v>53.02</v>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.286</v>
+        <v>0.354</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.345</v>
+        <v>0.319</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4649,28 +4664,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.65</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1140100</v>
+        <v>1383100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="H93" t="n">
-        <v>71.81999999999999</v>
+        <v>70.55</v>
       </c>
       <c r="I93" s="17" t="inlineStr">
         <is>
@@ -4678,10 +4693,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.187</v>
+        <v>0.634</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.156</v>
+        <v>0.591</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4694,39 +4709,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>INSAS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>0.0226</v>
+        <v>0.52</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1134000</v>
+        <v>1367700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.96</v>
+        <v>0.37</v>
       </c>
       <c r="H94" t="n">
-        <v>57.27</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.42</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.895</v>
+        <v>0.512</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.9</v>
+        <v>0.464</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4739,40 +4754,33 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>-0.0137</v>
+        <v>-0.0196</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1108400</v>
+        <v>1364400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H95" t="n">
-        <v>59.96</v>
+        <v>0.08</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J95" s="9" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="K95" s="9" t="n">
-        <v>0.319</v>
-      </c>
+      <c r="J95" s="9" t="n"/>
+      <c r="K95" s="9" t="n"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
     </row>
@@ -4784,39 +4792,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.9</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E96" s="16" t="n">
-        <v>0.0106</v>
+        <v>0.018</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1108100</v>
+        <v>1363300</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="H96" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.24</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.957</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.079</v>
+        <v>0.595</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4829,28 +4837,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.0189</v>
+        <v>1.32</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1091800</v>
+        <v>1344400</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="H97" t="n">
-        <v>51.19</v>
+        <v>53.02</v>
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
@@ -4858,10 +4866,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.254</v>
+        <v>1.286</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.271</v>
+        <v>1.345</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4874,28 +4882,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>-0.0268</v>
+        <v>1.68</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1073700</v>
+        <v>1301500</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.23</v>
+        <v>3.79</v>
       </c>
       <c r="H98" t="n">
-        <v>76.75</v>
+        <v>72.48</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -4903,10 +4911,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.973</v>
+        <v>1.589</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.8</v>
+        <v>1.536</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4919,39 +4927,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0156</v>
+        <v>0.25</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1070300</v>
+        <v>1257000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H99" t="n">
-        <v>44.97</v>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.72</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.321</v>
+        <v>0.249</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.339</v>
+        <v>0.253</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4964,39 +4972,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1052600</v>
+        <v>1213200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.33</v>
+        <v>0.32</v>
       </c>
       <c r="H100" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.69</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.261</v>
+        <v>0.62</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.266</v>
+        <v>0.581</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5009,39 +5017,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.345</v>
+        <v>0.315</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>-0.0143</v>
+        <v>-0.0156</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1030000</v>
+        <v>1201700</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H101" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.97</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.352</v>
+        <v>0.321</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5054,33 +5062,40 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>INSAS</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>0</v>
+        <v>0.905</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1022600</v>
+        <v>1191000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J102" s="9" t="n"/>
-      <c r="K102" s="9" t="n"/>
+        <v>2.05</v>
+      </c>
+      <c r="H102" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
     </row>
@@ -5092,33 +5107,40 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>0.0351</v>
+        <v>0.785</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1012500</v>
+        <v>1183900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>86.31</v>
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J103" s="9" t="n"/>
-      <c r="K103" s="9" t="n"/>
+      <c r="J103" s="9" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0.752</v>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
     </row>
@@ -5130,28 +5152,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.65</v>
+        <v>1.09</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.0152</v>
+        <v>-0.0268</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1003500</v>
+        <v>1141900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H104" t="n">
-        <v>60.69</v>
+        <v>76.75</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -5159,10 +5181,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.62</v>
+        <v>0.973</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.581</v>
+        <v>0.8</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5190,10 +5212,10 @@
         <v>-0.0252</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>976600</v>
+        <v>1127700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H105" t="n">
         <v>52.94</v>
@@ -5220,40 +5242,33 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.48</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>930200</v>
+        <v>1125100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H106" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="n">
-        <v>1.729</v>
-      </c>
-      <c r="K106" s="9" t="n">
-        <v>1.847</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5265,28 +5280,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.645</v>
+        <v>0.26</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0529</v>
+        <v>-0.0189</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>898100</v>
+        <v>1093800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.72</v>
+        <v>0.35</v>
       </c>
       <c r="H107" t="n">
-        <v>57.44</v>
+        <v>51.19</v>
       </c>
       <c r="I107" s="17" t="inlineStr">
         <is>
@@ -5294,10 +5309,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.628</v>
+        <v>0.254</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.612</v>
+        <v>0.271</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5310,28 +5325,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>IWCITY</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>841900</v>
+        <v>1065000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.15</v>
+        <v>2.18</v>
       </c>
       <c r="H108" t="n">
-        <v>86.31</v>
+        <v>48.08</v>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
@@ -5339,10 +5354,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.767</v>
+        <v>0.215</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.752</v>
+        <v>0.225</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5355,40 +5370,33 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>-0.0058</v>
+        <v>0.29</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>810000</v>
+        <v>1063500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H109" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J109" s="9" t="n">
-        <v>0.859</v>
-      </c>
-      <c r="K109" s="9" t="n">
-        <v>0.856</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
     </row>
@@ -5400,28 +5408,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>789400</v>
+        <v>1059900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H110" t="n">
-        <v>79.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -5429,10 +5437,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>1.006</v>
+        <v>0.446</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.845</v>
+        <v>0.404</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5445,39 +5453,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>0.003</v>
+        <v>0.26</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>769700</v>
+        <v>1052600</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.08</v>
+        <v>1.33</v>
       </c>
       <c r="H111" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>13.468</v>
+        <v>0.261</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>14.059</v>
+        <v>0.266</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5490,39 +5498,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>3.61</v>
+        <v>0.345</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0143</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>748700</v>
+        <v>1031200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H112" t="n">
-        <v>74.70999999999999</v>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>3.312</v>
+        <v>0.352</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.885</v>
+        <v>0.35</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5535,28 +5543,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.77</v>
+        <v>13.22</v>
       </c>
       <c r="E113" s="16" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>739200</v>
+        <v>999000</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.51</v>
+        <v>0.1</v>
       </c>
       <c r="H113" t="n">
-        <v>52.54</v>
+        <v>34.32</v>
       </c>
       <c r="I113" s="17" t="inlineStr">
         <is>
@@ -5564,10 +5572,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.765</v>
+        <v>13.472</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.755</v>
+        <v>14.06</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5580,28 +5588,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>732500</v>
+        <v>990300</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H114" t="n">
-        <v>69.25</v>
+        <v>80.17</v>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
@@ -5609,10 +5617,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.672</v>
+        <v>1.007</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.615</v>
+        <v>0.845</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5625,28 +5633,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>0</v>
+        <v>4.39</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>700000</v>
+        <v>970500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.72</v>
+        <v>0.13</v>
       </c>
       <c r="H115" t="n">
-        <v>48.02</v>
+        <v>44.19</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5654,10 +5662,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.631</v>
+        <v>4.579</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.637</v>
+        <v>4.537</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5670,39 +5678,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E116" s="16" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.65</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>675400</v>
+        <v>938400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.17</v>
+        <v>0.76</v>
       </c>
       <c r="H116" t="n">
-        <v>59.48</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.12</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>1.242</v>
+        <v>0.629</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1.139</v>
+        <v>0.612</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5715,28 +5723,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>0.009000000000000001</v>
+        <v>4.78</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>670900</v>
+        <v>918400</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H117" t="n">
-        <v>53.76</v>
+        <v>38.75</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5744,10 +5752,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.226</v>
+        <v>4.844</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.104</v>
+        <v>4.96</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5760,28 +5768,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.17</v>
+        <v>3.59</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>-0.025</v>
+        <v>-0.011</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>656100</v>
+        <v>853900</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="H118" t="n">
-        <v>64.58</v>
+        <v>73</v>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
@@ -5789,10 +5797,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.107</v>
+        <v>3.31</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.007</v>
+        <v>2.884</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5805,39 +5813,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>2.23</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>649100</v>
+        <v>820300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="H119" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="I119" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.41</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>4.414</v>
+        <v>2.224</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>4.431</v>
+        <v>2.104</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5850,28 +5858,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0.98</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>644500</v>
+        <v>817000</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.13</v>
+        <v>0.43</v>
       </c>
       <c r="H120" t="n">
-        <v>34.67</v>
+        <v>43.55</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5879,10 +5887,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.049</v>
+        <v>0.996</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.074</v>
+        <v>1.012</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5895,28 +5903,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>0.0161</v>
+        <v>4.54</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>641300</v>
+        <v>806000</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H121" t="n">
-        <v>83.94</v>
+        <v>55.25</v>
       </c>
       <c r="I121" s="17" t="inlineStr">
         <is>
@@ -5924,10 +5932,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.045</v>
+        <v>4.414</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.888</v>
+        <v>4.431</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5940,28 +5948,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v>0</v>
+        <v>2.87</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>625800</v>
+        <v>799400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="H122" t="n">
-        <v>88.84999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -5969,10 +5977,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.247</v>
+        <v>2.185</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.951</v>
+        <v>1.768</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5994,19 +6002,19 @@
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.0052</v>
+        <v>0.965</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>615400</v>
+        <v>788400</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H123" t="n">
-        <v>35.25</v>
+        <v>37.8</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6014,7 +6022,7 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>1.047</v>
@@ -6030,39 +6038,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.0143</v>
+        <v>0.77</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>611700</v>
+        <v>764300</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="H124" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.54</v>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.345</v>
+        <v>0.765</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.148</v>
+        <v>0.755</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6075,28 +6083,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0035</v>
+        <v>7.93</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>589700</v>
+        <v>755900</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="H125" t="n">
-        <v>88.36</v>
+        <v>59.27</v>
       </c>
       <c r="I125" s="17" t="inlineStr">
         <is>
@@ -6104,10 +6112,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>2.183</v>
+        <v>7.8</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1.768</v>
+        <v>7.73</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6120,39 +6128,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.0042</v>
+        <v>2.84</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>578600</v>
+        <v>755300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="H126" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.09</v>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>4.844</v>
+        <v>2.249</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>4.96</v>
+        <v>1.951</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6165,28 +6173,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>-0.0128</v>
+        <v>-0.0367</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>562800</v>
+        <v>740700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="H127" t="n">
-        <v>54.35</v>
+        <v>39.35</v>
       </c>
       <c r="I127" s="17" t="inlineStr">
         <is>
@@ -6194,10 +6202,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.756</v>
+        <v>1.098</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.74</v>
+        <v>1.119</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6210,28 +6218,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E128" s="16" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.725</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>536500</v>
+        <v>734500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="H128" t="n">
-        <v>42.85</v>
+        <v>69.25</v>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
@@ -6239,10 +6247,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.672</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.595</v>
+        <v>0.615</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6255,39 +6263,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>0.023</v>
+        <v>0.77</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>529300</v>
+        <v>732200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1.4</v>
+        <v>0.26</v>
       </c>
       <c r="H129" t="n">
-        <v>30.61</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.35</v>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.182</v>
+        <v>0.756</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.285</v>
+        <v>0.74</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6300,45 +6308,1080 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>-0.0134</v>
+        <v>1.27</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>523100</v>
+        <v>715200</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H130" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.34</v>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>4.583</v>
+        <v>1.046</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>4.538</v>
+        <v>0.888</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>705700</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H131" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H132" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>679600</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H133" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>1.693</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>679200</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H134" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>676100</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H135" t="n">
+        <v>64.58</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>649600</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H136" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>1.903</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>1.966</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>644200</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>2.674</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>635300</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H138" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>7.975</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>8.260999999999999</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>635100</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H139" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>629600</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H140" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>626600</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H141" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="I141" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>1.974</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>617700</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H142" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0178</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>613300</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H143" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>600300</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H144" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>7.951</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>8.151999999999999</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>592600</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H145" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="I145" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>5.282</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>5.276</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>570500</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H146" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>5.803</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>5.754</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>558000</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H147" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>538700</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H148" t="n">
+        <v>68.31</v>
+      </c>
+      <c r="I148" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>535500</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H149" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>529300</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H150" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>522500</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H151" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>3.071</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.0262</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>512200</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H152" t="n">
+        <v>53.59</v>
+      </c>
+      <c r="I152" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>6.571</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>6.496</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.0289</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>505400</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H153" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>1.701</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M130"/>
+  <autoFilter ref="A1:M153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-28'!$A$1:$M$205</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-25'!$A$1:$M$304</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M192"/>
+  <dimension ref="A1:M205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -578,10 +578,10 @@
         <v>0.0357</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5476300</v>
+        <v>5775900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>72.15000000000001</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.435高于50日均线0.38，均线多头排列；但RSI达72.15已入超买区，短期动能偏强而追高风险上升，信号可靠性中等。</t>
+          <t>现价0.435高于50日均线0.38，均线结构偏多；但RSI达72.15已入超买区，短期动能偏热，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>0.04650000000000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>5841900</v>
+        <v>5983700</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>26.47</v>
+        <v>27.11</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>72.90000000000001</v>
@@ -657,7 +657,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.225高于50日均线0.186，均线多头排列；但RSI达72.9已入超买区，短期动能偏热，信号可靠性需谨慎看待。</t>
+          <t>RSI 72.9已超买，现价高于50日均线约21%，EMA与SAR、Supertrend均偏多，但量能信号需确认。</t>
         </is>
       </c>
     </row>
@@ -684,10 +684,10 @@
         <v>0.0561</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8549600</v>
+        <v>9059000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>71.81999999999999</v>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>91053300</v>
+        <v>99140200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H5" t="n">
         <v>22.61</v>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>58888600</v>
+        <v>63159800</v>
       </c>
       <c r="G6" s="12" t="n"/>
       <c r="I6" s="13" t="inlineStr">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0882</v>
+        <v>0.0588</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>56178800</v>
+        <v>56847800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H7" t="n">
-        <v>77.83</v>
+        <v>76.5</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>55808400</v>
+        <v>56519500</v>
       </c>
       <c r="G8" s="12" t="n"/>
       <c r="I8" s="13" t="inlineStr">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>-0.0526</v>
+        <v>-0.0451</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>34398200</v>
+        <v>36587700</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="H9" t="n">
-        <v>47.42</v>
+        <v>48.72</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.584</v>
+        <v>2.586</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2.44</v>
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>-0.0526</v>
+        <v>-0.0395</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>26428800</v>
+        <v>26751800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="H10" t="n">
-        <v>69.26000000000001</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -974,39 +974,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0857</v>
+        <v>0.72</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.0464</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>24687800</v>
+        <v>26587500</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>5.91</v>
+        <v>0.61</v>
       </c>
       <c r="H11" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.18</v>
+        <v>0.735</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.189</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1019,39 +1019,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0331</v>
+        <v>0.185</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>23598000</v>
+        <v>25339900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.54</v>
+        <v>6.07</v>
       </c>
       <c r="H12" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.81</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.736</v>
+        <v>0.18</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.189</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
         <v>-0.0256</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>16462100</v>
+        <v>17463200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="H13" t="n">
         <v>64</v>
@@ -1109,39 +1109,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.0213</v>
+        <v>0.395</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.0595</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>14737800</v>
+        <v>15401300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="H14" t="n">
-        <v>56.39</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.63</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.232</v>
+        <v>0.382</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.233</v>
+        <v>0.32</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1154,39 +1154,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>-0.0595</v>
+        <v>0.24</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>14699000</v>
+        <v>15304800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="H15" t="n">
-        <v>56.63</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.39</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.382</v>
+        <v>0.232</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.32</v>
+        <v>0.233</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>-0.0321</v>
+        <v>-0.0267</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>13579600</v>
+        <v>13999300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>59.95</v>
+        <v>60.88</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.735</v>
+        <v>1.736</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>1.524</v>
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.555</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.0183</v>
+        <v>0.0275</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>13065400</v>
+        <v>13868100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="H17" t="n">
-        <v>60.08</v>
+        <v>60.99</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>0.524</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
         <v>-0.0323</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11864400</v>
+        <v>12967800</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H18" t="n">
         <v>49.23</v>
@@ -1334,39 +1334,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.0227</v>
+        <v>0.865</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>11210200</v>
+        <v>12954400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.51</v>
+        <v>0.72</v>
       </c>
       <c r="H19" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.9</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.238</v>
+        <v>0.868</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.249</v>
+        <v>0.871</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1379,28 +1379,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.77</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>11139800</v>
+        <v>11948700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.91</v>
+        <v>0.96</v>
       </c>
       <c r="H20" t="n">
-        <v>62.28</v>
+        <v>47.75</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.521</v>
+        <v>0.774</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.531</v>
+        <v>0.774</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1424,28 +1424,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.21</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10892600</v>
+        <v>11699400</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="H21" t="n">
-        <v>27.96</v>
+        <v>28.01</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.634</v>
+        <v>0.238</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.851</v>
+        <v>0.249</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1469,28 +1469,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.55</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>10249000</v>
+        <v>11630100</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.82</v>
+        <v>1.99</v>
       </c>
       <c r="H22" t="n">
-        <v>47.75</v>
+        <v>62.28</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.774</v>
+        <v>0.521</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.774</v>
+        <v>0.531</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1514,36 +1514,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.95</v>
+        <v>0.53</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>10116000</v>
+        <v>11518300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2.49</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.93</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.885</v>
+        <v>0.634</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0.851</v>
@@ -1559,28 +1559,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CJCEN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.2</v>
+        <v>0.705</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>10020500</v>
+        <v>10877000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>23.69</v>
+        <v>1.18</v>
       </c>
       <c r="H24" t="n">
-        <v>82.14</v>
+        <v>55.12</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.172</v>
+        <v>0.681</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.163</v>
+        <v>0.662</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1604,28 +1604,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CJCEN</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.715</v>
+        <v>0.195</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0288</v>
+        <v>0.0541</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9908400</v>
+        <v>10571000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.07</v>
+        <v>24.99</v>
       </c>
       <c r="H25" t="n">
-        <v>56.69</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.663</v>
+        <v>0.163</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1649,28 +1649,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.215</v>
+        <v>0.945</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>-0.0227</v>
+        <v>-0.0053</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9901600</v>
+        <v>10122900</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.47</v>
+        <v>2.49</v>
       </c>
       <c r="H26" t="n">
-        <v>65.40000000000001</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.202</v>
+        <v>0.884</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.184</v>
+        <v>0.851</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1694,28 +1694,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0058</v>
+        <v>0.22</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9515100</v>
+        <v>9946400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="H27" t="n">
-        <v>46.9</v>
+        <v>71.25</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.868</v>
+        <v>0.202</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.871</v>
+        <v>0.184</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8989000</v>
+        <v>9382200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H28" t="n">
         <v>31.98</v>
@@ -1784,39 +1784,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>-0.0211</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8557100</v>
+        <v>8802000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.35</v>
+        <v>0.68</v>
       </c>
       <c r="H29" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.51</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.468</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.471</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8469100</v>
+        <v>8686100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H30" t="n">
-        <v>46.97</v>
+        <v>45.92</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>2.127</v>
+        <v>2.126</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>2.062</v>
@@ -1874,28 +1874,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.465</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>8134600</v>
+        <v>8668500</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4.74</v>
+        <v>0.36</v>
       </c>
       <c r="H31" t="n">
-        <v>83.03</v>
+        <v>48.8</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.224</v>
+        <v>0.468</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.209</v>
+        <v>0.471</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1919,39 +1919,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>2.5</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>8056600</v>
+        <v>8403900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="H32" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.94</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.448</v>
+        <v>2.439</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.407</v>
+        <v>2.276</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1964,28 +1964,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>3.49</v>
+        <v>0.47</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7781200</v>
+        <v>8370000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.66</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>36.67</v>
+        <v>58.56</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>3.614</v>
+        <v>0.448</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>3.703</v>
+        <v>0.407</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2009,39 +2009,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>-0.09519999999999999</v>
+        <v>0.28</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7764200</v>
+        <v>8254400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.3</v>
+        <v>4.81</v>
       </c>
       <c r="H34" t="n">
-        <v>33</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.92</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.133</v>
+        <v>0.225</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.162</v>
+        <v>0.209</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>-0.0061</v>
+        <v>0.82</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7759800</v>
+        <v>8183100</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H35" t="n">
-        <v>69.03</v>
+        <v>70.16</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.713</v>
+        <v>0.714</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0.6870000000000001</v>
@@ -2099,39 +2099,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>-0.0143</v>
+        <v>3.5</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0029</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7608100</v>
+        <v>8092100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="H36" t="n">
-        <v>57.32</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.68</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.339</v>
+        <v>3.615</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.333</v>
+        <v>3.704</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2144,28 +2144,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>2.78</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>-0.0347</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7406400</v>
+        <v>7904000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.18</v>
+        <v>1.13</v>
       </c>
       <c r="H37" t="n">
-        <v>47.65</v>
+        <v>60.38</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.158</v>
+        <v>2.625</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.148</v>
+        <v>2.495</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2189,39 +2189,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.05</v>
+        <v>0.095</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.09519999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7184000</v>
+        <v>7857600</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="H38" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.053</v>
+        <v>0.133</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.043</v>
+        <v>0.162</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2234,28 +2234,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>7160000</v>
+        <v>7695400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.34</v>
+        <v>1.93</v>
       </c>
       <c r="H39" t="n">
-        <v>44.73</v>
+        <v>52.59</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.156</v>
+        <v>0.338</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.159</v>
+        <v>0.332</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2279,28 +2279,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.0243</v>
+        <v>0.15</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6945000</v>
+        <v>7534000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1</v>
+        <v>0.18</v>
       </c>
       <c r="H40" t="n">
-        <v>62.35</v>
+        <v>47.65</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.628</v>
+        <v>0.158</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.495</v>
+        <v>0.148</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2324,28 +2324,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0121</v>
+        <v>0.05</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>6841200</v>
+        <v>7184200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H41" t="n">
-        <v>61.94</v>
+        <v>48.92</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.439</v>
+        <v>0.053</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.276</v>
+        <v>0.043</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2369,39 +2369,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>6580500</v>
+        <v>7160000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="H42" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2414,39 +2414,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.39</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6527300</v>
+        <v>7059800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="H43" t="n">
-        <v>62.59</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.3</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>4.74</v>
+        <v>0.374</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>4.509</v>
+        <v>0.371</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2459,28 +2459,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0132</v>
+        <v>2.98</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>6238100</v>
+        <v>6756200</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="H44" t="n">
-        <v>63.96</v>
+        <v>64.89</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.373</v>
+        <v>2.858</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.371</v>
+        <v>2.716</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2504,39 +2504,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0083</v>
+        <v>4.88</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5966500</v>
+        <v>6727600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="H45" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.36</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.607</v>
+        <v>4.742</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.604</v>
+        <v>4.509</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2549,28 +2549,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.99</v>
+        <v>0.6</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>-0.0132</v>
+        <v>-0.0083</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5820500</v>
+        <v>5996900</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.43</v>
+        <v>0.61</v>
       </c>
       <c r="H46" t="n">
-        <v>66.08</v>
+        <v>45.5</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.859</v>
+        <v>0.607</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.716</v>
+        <v>0.604</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         <v>0.09519999999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5525200</v>
+        <v>5789100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>11.29</v>
+        <v>11.83</v>
       </c>
       <c r="H47" t="n">
         <v>58.72</v>
@@ -2639,28 +2639,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
+        <v>0.36</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5242500</v>
+        <v>5524500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H48" t="n">
-        <v>63.82</v>
+        <v>45.16</v>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.274</v>
+        <v>0.366</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.269</v>
+        <v>0.366</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         <v>0.0156</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4942000</v>
+        <v>5439000</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>95.47</v>
@@ -2729,28 +2729,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>-0.0126</v>
+        <v>0.29</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4866600</v>
+        <v>5342500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.29</v>
+        <v>0.84</v>
       </c>
       <c r="H50" t="n">
-        <v>52.09</v>
+        <v>63.82</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.349</v>
+        <v>0.274</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.239</v>
+        <v>0.269</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2774,28 +2774,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0135</v>
+        <v>4.19</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.032</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4594900</v>
+        <v>5314800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.77</v>
+        <v>1.11</v>
       </c>
       <c r="H51" t="n">
-        <v>48.52</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.367</v>
+        <v>3.547</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.366</v>
+        <v>3.226</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2819,28 +2819,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>0.0323</v>
+        <v>0.0286</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4522900</v>
+        <v>5033700</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.41</v>
+        <v>4.62</v>
       </c>
       <c r="H52" t="n">
-        <v>56.74</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I52" s="16" t="inlineStr">
         <is>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.154</v>
+        <v>0.152</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.147</v>
+        <v>0.145</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2864,28 +2864,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>2.35</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4507000</v>
+        <v>4922100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.08</v>
+        <v>0.3</v>
       </c>
       <c r="H53" t="n">
-        <v>49.87</v>
+        <v>51.33</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.804</v>
+        <v>2.348</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.806</v>
+        <v>2.239</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2909,28 +2909,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>-0.0385</v>
+        <v>0.16</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4314100</v>
+        <v>4522900</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.36</v>
+        <v>1.41</v>
       </c>
       <c r="H54" t="n">
-        <v>36.09</v>
+        <v>56.74</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.272</v>
+        <v>0.154</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.314</v>
+        <v>0.147</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2954,39 +2954,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>-0.0455</v>
+        <v>0.805</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4214400</v>
+        <v>4507000</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.38</v>
+        <v>1.08</v>
       </c>
       <c r="H55" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.87</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.081</v>
+        <v>0.804</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.024</v>
+        <v>0.806</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2999,28 +2999,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.0303</v>
+        <v>1.05</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4141100</v>
+        <v>4469200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H56" t="n">
-        <v>37.52</v>
+        <v>47.24</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.182</v>
+        <v>1.081</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.221</v>
+        <v>1.024</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3044,39 +3044,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.545</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4136600</v>
+        <v>4360600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>79.47</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.08</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>3.542</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>3.225</v>
+        <v>0.59</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3089,28 +3089,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3871200</v>
+        <v>4350200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>3.55</v>
+        <v>0.37</v>
       </c>
       <c r="H58" t="n">
-        <v>79.92</v>
+        <v>36.09</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.151</v>
+        <v>0.272</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.145</v>
+        <v>0.314</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3134,39 +3134,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>5.8</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.0153</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3844300</v>
+        <v>4314000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="H59" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.99</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.375</v>
+        <v>5.686</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.29</v>
+        <v>5.131</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3179,39 +3179,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>-0.017</v>
+        <v>0.17</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3835100</v>
+        <v>4158300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H60" t="n">
-        <v>58.54</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.52</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>5.685</v>
+        <v>0.182</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>5.131</v>
+        <v>0.221</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3224,28 +3224,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0172</v>
+        <v>1.31</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3749300</v>
+        <v>4013800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2.02</v>
+        <v>0.35</v>
       </c>
       <c r="H61" t="n">
-        <v>49.23</v>
+        <v>43.34</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.295</v>
+        <v>1.374</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.297</v>
+        <v>1.29</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3278,19 +3278,19 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.0584</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3748400</v>
+        <v>3802100</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H62" t="n">
-        <v>35.61</v>
+        <v>36.5</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.402</v>
+        <v>1.403</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>1.317</v>
@@ -3314,28 +3314,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.55</v>
+        <v>0.295</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0092</v>
+        <v>0.0172</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3675400</v>
+        <v>3749300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.58</v>
+        <v>2.02</v>
       </c>
       <c r="H63" t="n">
-        <v>41.68</v>
+        <v>49.23</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.295</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.59</v>
+        <v>0.297</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3359,39 +3359,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3536700</v>
+        <v>3719700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.22</v>
+        <v>1.26</v>
       </c>
       <c r="H64" t="n">
-        <v>65.18000000000001</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.56</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.284</v>
+        <v>0.859</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.277</v>
+        <v>0.856</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3404,28 +3404,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.55</v>
+        <v>10.2</v>
       </c>
       <c r="E65" s="17" t="n">
-        <v>-0.0267</v>
+        <v>-0.002</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3399100</v>
+        <v>3660400</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="H65" t="n">
-        <v>48.43</v>
+        <v>49.44</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.568</v>
+        <v>10.179</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.535</v>
+        <v>10.321</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3449,28 +3449,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.18</v>
+        <v>0.255</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.02</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3364000</v>
+        <v>3619900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.5</v>
+        <v>3.51</v>
       </c>
       <c r="H66" t="n">
-        <v>50.53</v>
+        <v>72.41</v>
       </c>
       <c r="I66" s="16" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.181</v>
+        <v>0.212</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.14</v>
+        <v>0.198</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3494,28 +3494,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.165</v>
+        <v>1.18</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0313</v>
+        <v>0.0172</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3362700</v>
+        <v>3614700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.29</v>
+        <v>0.54</v>
       </c>
       <c r="H67" t="n">
-        <v>66.66</v>
+        <v>50.53</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.148</v>
+        <v>1.181</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.139</v>
+        <v>1.14</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3539,28 +3539,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3320800</v>
+        <v>3611700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="H68" t="n">
-        <v>63.42</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.163</v>
+        <v>0.284</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.165</v>
+        <v>0.277</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3584,28 +3584,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.0467</v>
+        <v>0.91</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3267800</v>
+        <v>3597700</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="H69" t="n">
-        <v>59.69</v>
+        <v>39.98</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.681</v>
+        <v>0.926</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.611</v>
+        <v>0.969</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3629,39 +3629,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>2.55</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3210700</v>
+        <v>3526100</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.09</v>
+        <v>0.61</v>
       </c>
       <c r="H70" t="n">
-        <v>59.03</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.43</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.859</v>
+        <v>2.568</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.856</v>
+        <v>2.535</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3674,28 +3674,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.0222</v>
+        <v>0.715</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>-0.0467</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3209200</v>
+        <v>3464500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.98</v>
+        <v>0.6</v>
       </c>
       <c r="H71" t="n">
-        <v>43.85</v>
+        <v>59.69</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.927</v>
+        <v>0.681</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.969</v>
+        <v>0.611</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3719,28 +3719,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>0.165</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3055800</v>
+        <v>3383500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.38</v>
+        <v>1.3</v>
       </c>
       <c r="H72" t="n">
-        <v>50.52</v>
+        <v>66.66</v>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.33</v>
+        <v>0.148</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.311</v>
+        <v>0.139</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3773,19 +3773,19 @@
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2986200</v>
+        <v>3347200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="H73" t="n">
-        <v>46.13</v>
+        <v>48.8</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0.773</v>
@@ -3809,28 +3809,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.002</v>
+        <v>0.18</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2971400</v>
+        <v>3320800</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.18</v>
+        <v>0.64</v>
       </c>
       <c r="H74" t="n">
-        <v>49.44</v>
+        <v>63.42</v>
       </c>
       <c r="I74" s="16" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>10.179</v>
+        <v>0.163</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>10.321</v>
+        <v>0.165</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3854,28 +3854,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.32</v>
+        <v>4.39</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.0233</v>
+        <v>0.0092</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2811700</v>
+        <v>3116800</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H75" t="n">
-        <v>42.24</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.331</v>
+        <v>3.521</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.445</v>
+        <v>2.354</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3899,28 +3899,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>4.41</v>
+        <v>0.33</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.0138</v>
+        <v>0.0154</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2806600</v>
+        <v>3067900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>79.41</v>
+        <v>52.72</v>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>3.523</v>
+        <v>0.33</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2.355</v>
+        <v>0.311</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3944,28 +3944,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>1.32</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2721500</v>
+        <v>2962400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H77" t="n">
-        <v>65.70999999999999</v>
+        <v>42.24</v>
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.337</v>
+        <v>1.331</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.319</v>
+        <v>1.445</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3989,39 +3989,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.0255</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2653800</v>
+        <v>2918500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H78" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.15</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.298</v>
+        <v>0.766</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.312</v>
+        <v>0.752</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4034,28 +4034,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>-0.0119</v>
+        <v>0.29</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2627100</v>
+        <v>2866800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H79" t="n">
-        <v>56.5</v>
+        <v>39.08</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.409</v>
+        <v>0.298</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.41</v>
+        <v>0.312</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4079,28 +4079,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.02</v>
+        <v>0.66</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2586000</v>
+        <v>2819600</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>2.51</v>
+        <v>0.3</v>
       </c>
       <c r="H80" t="n">
-        <v>72.41</v>
+        <v>59.78</v>
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.212</v>
+        <v>0.633</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.198</v>
+        <v>0.574</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4124,28 +4124,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.0076</v>
+        <v>0.36</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2555800</v>
+        <v>2796500</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H81" t="n">
-        <v>60.68</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.634</v>
+        <v>0.337</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.574</v>
+        <v>0.319</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4169,28 +4169,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.15</v>
+        <v>0.415</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.0417</v>
+        <v>-0.0119</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2283600</v>
+        <v>2680400</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H82" t="n">
-        <v>50.13</v>
+        <v>56.5</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.163</v>
+        <v>0.409</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.1</v>
+        <v>0.41</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4214,28 +4214,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2276900</v>
+        <v>2563300</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
-        <v>31.51</v>
+        <v>34.08</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.244</v>
+        <v>1.732</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.243</v>
+        <v>1.847</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4259,28 +4259,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.42</v>
+        <v>1.09</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>-0.0118</v>
+        <v>-0.0268</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2230900</v>
+        <v>2472700</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
       <c r="H84" t="n">
-        <v>56.23</v>
+        <v>76.75</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.402</v>
+        <v>0.973</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4304,28 +4304,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>-0.0064</v>
+        <v>-0.0118</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2225100</v>
+        <v>2390000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="H85" t="n">
-        <v>74.67</v>
+        <v>56.23</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.767</v>
+        <v>0.402</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.752</v>
+        <v>0.4</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4349,39 +4349,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0.0123</v>
+        <v>0.51</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2222700</v>
+        <v>2382200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="H86" t="n">
-        <v>34.08</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.34</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.732</v>
+        <v>0.512</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.847</v>
+        <v>0.464</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4403,19 +4403,19 @@
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="E87" s="17" t="n">
-        <v>-0.0259</v>
+        <v>-0.0148</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2221900</v>
+        <v>2353500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="H87" t="n">
-        <v>72.69</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.454</v>
+        <v>2.457</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>2.118</v>
@@ -4439,28 +4439,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.51</v>
+        <v>1.15</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>-0.0377</v>
+        <v>-0.0417</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2207700</v>
+        <v>2342100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.59</v>
+        <v>0.26</v>
       </c>
       <c r="H88" t="n">
-        <v>52.34</v>
+        <v>50.13</v>
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.512</v>
+        <v>1.163</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.464</v>
+        <v>1.1</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4484,39 +4484,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.0268</v>
+        <v>0.23</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2206500</v>
+        <v>2276900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.46</v>
+        <v>0.75</v>
       </c>
       <c r="H89" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.51</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.973</v>
+        <v>0.244</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.8</v>
+        <v>0.243</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         <v>-0.0112</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2176500</v>
+        <v>2194500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H90" t="n">
         <v>47.93</v>
@@ -4589,7 +4589,7 @@
         <v>0.018</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2123100</v>
+        <v>2136100</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0.5600000000000001</v>
@@ -4634,10 +4634,10 @@
         <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2002000</v>
+        <v>2108100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H92" t="n">
         <v>79.33</v>
@@ -4664,39 +4664,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E93" s="15" t="n">
-        <v>0.04969999999999999</v>
+        <v>4.79</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1950100</v>
+        <v>2059100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>5.68</v>
+        <v>0.11</v>
       </c>
       <c r="H93" t="n">
-        <v>73.53</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.75</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.59</v>
+        <v>4.845</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.536</v>
+        <v>4.96</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4709,28 +4709,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.55</v>
+        <v>1.65</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1862600</v>
+        <v>2034300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="H94" t="n">
-        <v>63.26</v>
+        <v>50.17</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.498</v>
+        <v>1.636</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.401</v>
+        <v>1.692</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4754,28 +4754,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1846400</v>
+        <v>1954400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.24</v>
+        <v>5.7</v>
       </c>
       <c r="H95" t="n">
-        <v>51.42</v>
+        <v>73.53</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.637</v>
+        <v>1.59</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.693</v>
+        <v>1.536</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4799,39 +4799,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0189</v>
+        <v>1.91</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.016</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1838700</v>
+        <v>1915600</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="H96" t="n">
-        <v>77.48999999999999</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.51</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.893</v>
+        <v>1.958</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.759</v>
+        <v>2.079</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4844,39 +4844,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0.016</v>
+        <v>1.04</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1814400</v>
+        <v>1914200</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="H97" t="n">
-        <v>39.51</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.48999999999999</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.958</v>
+        <v>0.893</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2.079</v>
+        <v>0.759</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4889,39 +4889,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>-0.0204</v>
+        <v>0.555</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1724900</v>
+        <v>1909200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="H98" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.89</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.045</v>
+        <v>0.499</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.014</v>
+        <v>0.401</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4934,28 +4934,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1671600</v>
+        <v>1897200</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="H99" t="n">
-        <v>38.17</v>
+        <v>46.04</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.638</v>
+        <v>0.248</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.658</v>
+        <v>0.253</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4979,28 +4979,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.3</v>
+        <v>2.88</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>0.0236</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1604500</v>
+        <v>1861200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.07</v>
+        <v>0.75</v>
       </c>
       <c r="H100" t="n">
-        <v>50.37</v>
+        <v>89.38</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.284</v>
+        <v>2.186</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.345</v>
+        <v>1.768</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5024,28 +5024,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1602800</v>
+        <v>1845400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H101" t="n">
-        <v>50.51</v>
+        <v>42.31</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.262</v>
+        <v>0.394</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.251</v>
+        <v>0.372</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5069,28 +5069,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>-0.04</v>
+        <v>1.8</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1597000</v>
+        <v>1819100</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="H102" t="n">
-        <v>46.04</v>
+        <v>35.54</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.248</v>
+        <v>1.902</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.253</v>
+        <v>1.966</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5114,39 +5114,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0.0213</v>
+        <v>0.955</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>-0.0255</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1590300</v>
+        <v>1771800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H103" t="n">
-        <v>89.54000000000001</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.37</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.253</v>
+        <v>1.045</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.952</v>
+        <v>1.014</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5159,39 +5159,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>-0.0137</v>
+        <v>13.18</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1561400</v>
+        <v>1752600</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.92</v>
+        <v>0.18</v>
       </c>
       <c r="H104" t="n">
-        <v>59.96</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.24</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.354</v>
+        <v>13.468</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.319</v>
+        <v>14.059</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5204,33 +5204,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1543100</v>
+        <v>1745500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.46</v>
+      </c>
+      <c r="H105" t="n">
+        <v>57.65</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
+      <c r="J105" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0.581</v>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
     </row>
@@ -5242,28 +5249,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0</v>
+        <v>2.86</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.0142</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1534600</v>
+        <v>1734400</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H106" t="n">
-        <v>41.51</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5271,10 +5278,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.584</v>
+        <v>2.251</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.647</v>
+        <v>1.951</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5287,28 +5294,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1532400</v>
+        <v>1728400</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.35</v>
+        <v>0.58</v>
       </c>
       <c r="H107" t="n">
-        <v>42.29</v>
+        <v>57.09</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5316,10 +5323,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.377</v>
+        <v>0.608</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.391</v>
+        <v>0.588</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5332,39 +5339,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.605</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1528600</v>
+        <v>1692600</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="H108" t="n">
-        <v>71.81999999999999</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.92</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.187</v>
+        <v>0.637</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.156</v>
+        <v>0.657</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5377,28 +5384,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0.0046</v>
+        <v>3.6</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1500500</v>
+        <v>1662400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.15</v>
+        <v>0.52</v>
       </c>
       <c r="H109" t="n">
-        <v>33.3</v>
+        <v>73.84</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5406,10 +5413,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>13.47</v>
+        <v>3.311</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>14.059</v>
+        <v>2.885</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5422,39 +5429,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0.014</v>
+        <v>0.36</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1491100</v>
+        <v>1631400</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="H110" t="n">
-        <v>89.56999999999999</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.188</v>
+        <v>0.354</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1.769</v>
+        <v>0.319</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5467,33 +5474,40 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>-0.0392</v>
+        <v>0.26</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1480600</v>
+        <v>1612800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.09</v>
+        <v>0.58</v>
+      </c>
+      <c r="H111" t="n">
+        <v>50.51</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J111" s="9" t="n"/>
-      <c r="K111" s="9" t="n"/>
+      <c r="J111" s="9" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0.251</v>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
     </row>
@@ -5505,39 +5519,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0</v>
+        <v>1.55</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1476100</v>
+        <v>1612000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.08</v>
+        <v>0.57</v>
       </c>
       <c r="H112" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.82</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>4.846</v>
+        <v>1.584</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>4.96</v>
+        <v>1.647</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5550,28 +5564,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>-0.0227</v>
+        <v>1.3</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1435200</v>
+        <v>1609500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.38</v>
+        <v>1.07</v>
       </c>
       <c r="H113" t="n">
-        <v>59.13</v>
+        <v>50.37</v>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
@@ -5579,10 +5593,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.619</v>
+        <v>1.284</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.581</v>
+        <v>1.345</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5595,39 +5609,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.79</v>
+        <v>4.96</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0178</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1435200</v>
+        <v>1595400</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="H114" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.52</v>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.901</v>
+        <v>4.98</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.966</v>
+        <v>5.04</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5640,40 +5654,33 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>4.96</v>
+        <v>0.475</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>-0.0178</v>
+        <v>-0.0104</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1386900</v>
+        <v>1563100</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H115" t="n">
-        <v>48.52</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I115" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J115" s="9" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="K115" s="9" t="n">
-        <v>5.04</v>
-      </c>
+      <c r="J115" s="9" t="n"/>
+      <c r="K115" s="9" t="n"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
     </row>
@@ -5685,39 +5692,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.65</v>
+        <v>0.37</v>
       </c>
       <c r="E116" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1385100</v>
+        <v>1542400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H116" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.29</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.634</v>
+        <v>0.377</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.591</v>
+        <v>0.391</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5730,28 +5737,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>-0.0449</v>
+        <v>0.21</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1325500</v>
+        <v>1528600</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H117" t="n">
-        <v>45.13</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
@@ -5759,10 +5766,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.439</v>
+        <v>0.187</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.432</v>
+        <v>0.156</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5775,28 +5782,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>-0.0143</v>
+        <v>2.24</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1313500</v>
+        <v>1510300</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H118" t="n">
-        <v>43.18</v>
+        <v>53.1</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5804,10 +5811,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.352</v>
+        <v>2.225</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.35</v>
+        <v>2.104</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5820,39 +5827,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0307</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>KENERGY</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>3.6</v>
+        <v>0.345</v>
       </c>
       <c r="E119" s="17" t="n">
-        <v>-0.0083</v>
+        <v>-0.0548</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1312400</v>
+        <v>1485200</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.41</v>
+        <v>2.8</v>
       </c>
       <c r="H119" t="n">
-        <v>73.84</v>
-      </c>
-      <c r="I119" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.82</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>3.311</v>
+        <v>0.382</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.885</v>
+        <v>0.385</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5865,40 +5872,33 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.215</v>
+        <v>0.245</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>-0.0227</v>
+        <v>-0.0392</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1297500</v>
+        <v>1484000</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H120" t="n">
-        <v>51</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="K120" s="9" t="n">
-        <v>0.212</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n"/>
+      <c r="K120" s="9" t="n"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
     </row>
@@ -5910,39 +5910,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>-0.0204</v>
+        <v>7.49</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1292800</v>
+        <v>1447900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="H121" t="n">
-        <v>68.65000000000001</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.61</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.446</v>
+        <v>7.687</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.404</v>
+        <v>7.843</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5955,28 +5955,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.96</v>
+        <v>7.96</v>
       </c>
       <c r="E122" s="15" t="n">
-        <v>0.0051</v>
+        <v>0.0076</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1284800</v>
+        <v>1438800</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="H122" t="n">
-        <v>46.89</v>
+        <v>60.62</v>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.984</v>
+        <v>7.803</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.974</v>
+        <v>7.73</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6000,28 +6000,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.315</v>
+        <v>0.215</v>
       </c>
       <c r="E123" s="17" t="n">
-        <v>-0.0156</v>
+        <v>-0.0227</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1253200</v>
+        <v>1406700</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H123" t="n">
-        <v>44.97</v>
+        <v>51</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.321</v>
+        <v>0.214</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.339</v>
+        <v>0.212</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6045,39 +6045,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>INSAS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>0.0169</v>
+        <v>0.645</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1246800</v>
+        <v>1394100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>2.15</v>
+        <v>0.42</v>
       </c>
       <c r="H124" t="n">
-        <v>53.79</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.54000000000001</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.895</v>
+        <v>0.634</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.9</v>
+        <v>0.591</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6090,39 +6090,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>0.0027</v>
+        <v>0.48</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1207600</v>
+        <v>1370100</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="H125" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.65000000000001</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>7.686</v>
+        <v>0.446</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>7.843</v>
+        <v>0.404</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6135,28 +6135,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0.0408</v>
+        <v>1.95</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1198300</v>
+        <v>1369300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.58</v>
+        <v>0.19</v>
       </c>
       <c r="H126" t="n">
-        <v>53.99</v>
+        <v>45.43</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.248</v>
+        <v>1.983</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.261</v>
+        <v>1.974</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6180,39 +6180,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0307</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KENERGY</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>-0.0274</v>
+        <v>0.245</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1194800</v>
+        <v>1365000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>2.25</v>
+        <v>0.66</v>
       </c>
       <c r="H127" t="n">
-        <v>34.74</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.33</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.383</v>
+        <v>0.247</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.385</v>
+        <v>0.261</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6225,28 +6225,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>-0.0262</v>
+        <v>0.725</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1182700</v>
+        <v>1361500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.51</v>
+        <v>0.23</v>
       </c>
       <c r="H128" t="n">
-        <v>52.25</v>
+        <v>69.25</v>
       </c>
       <c r="I128" s="16" t="inlineStr">
         <is>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>4.407</v>
+        <v>0.672</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>4.429</v>
+        <v>0.615</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6270,33 +6270,40 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>4.48</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>-0.0218</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1164200</v>
+        <v>1360100</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.59</v>
+      </c>
+      <c r="H129" t="n">
+        <v>52.97</v>
       </c>
       <c r="I129" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J129" s="9" t="n"/>
-      <c r="K129" s="9" t="n"/>
+      <c r="J129" s="9" t="n">
+        <v>4.408</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>4.429</v>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
     </row>
@@ -6308,39 +6315,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>2.96</v>
+        <v>0.31</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>-0.0166</v>
+        <v>-0.0313</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1156900</v>
+        <v>1355400</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="H130" t="n">
-        <v>45.05</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.76</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>3.008</v>
+        <v>0.32</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>3.04</v>
+        <v>0.339</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6353,39 +6360,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.0449</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1155700</v>
+        <v>1350500</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="H131" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.13</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.996</v>
+        <v>0.439</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.012</v>
+        <v>0.432</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6398,28 +6405,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.0063</v>
+        <v>1.16</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1153800</v>
+        <v>1330400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="H132" t="n">
-        <v>60.18</v>
+        <v>62.58</v>
       </c>
       <c r="I132" s="16" t="inlineStr">
         <is>
@@ -6427,10 +6434,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>7.802</v>
+        <v>1.106</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>7.73</v>
+        <v>1.006</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6443,39 +6450,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.58</v>
+        <v>0.775</v>
       </c>
       <c r="E133" s="17" t="n">
-        <v>-0.0252</v>
+        <v>-0.0064</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1127700</v>
+        <v>1325000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H133" t="n">
-        <v>52.94</v>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.33</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.57</v>
+        <v>0.797</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.575</v>
+        <v>0.849</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6488,39 +6495,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>5.2</v>
+        <v>0.345</v>
       </c>
       <c r="E134" s="17" t="n">
-        <v>-0.0207</v>
+        <v>-0.0143</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1117700</v>
+        <v>1314400</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.46</v>
+        <v>0.19</v>
       </c>
       <c r="H134" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>5.279</v>
+        <v>0.352</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>5.275</v>
+        <v>0.35</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6533,28 +6540,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>-0.02</v>
+        <v>4.77</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1094700</v>
+        <v>1282200</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H135" t="n">
-        <v>44.46</v>
+        <v>55.58</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6562,10 +6569,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>4.58</v>
+        <v>4.747</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>4.537</v>
+        <v>4.589</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6578,39 +6585,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>2.63</v>
+        <v>5.2</v>
       </c>
       <c r="E136" s="17" t="n">
-        <v>-0.015</v>
+        <v>-0.0207</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1094100</v>
+        <v>1275700</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.12</v>
+        <v>0.53</v>
       </c>
       <c r="H136" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.674</v>
+        <v>5.279</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.872</v>
+        <v>5.275</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6623,39 +6630,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>INSAS</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0</v>
+        <v>0.905</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1093900</v>
+        <v>1259800</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.35</v>
+        <v>2.17</v>
       </c>
       <c r="H137" t="n">
-        <v>54.09</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.27</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.254</v>
+        <v>0.895</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.271</v>
+        <v>0.9</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6668,28 +6675,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0</v>
+        <v>2.64</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1085900</v>
+        <v>1233200</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="H138" t="n">
-        <v>57.08</v>
+        <v>42.35</v>
       </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
@@ -6697,10 +6704,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.757</v>
+        <v>2.675</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.74</v>
+        <v>2.872</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6728,10 +6735,10 @@
         <v>-0.031</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1062900</v>
+        <v>1212100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H139" t="n">
         <v>45.53</v>
@@ -6758,39 +6765,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.43</v>
+        <v>2.95</v>
       </c>
       <c r="E140" s="17" t="n">
-        <v>-0.0227</v>
+        <v>-0.0199</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1055100</v>
+        <v>1206200</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H140" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.26</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.434</v>
+        <v>3.007</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.452</v>
+        <v>3.04</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6803,39 +6810,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>0.84</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1052600</v>
+        <v>1199900</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="H141" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.11</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.261</v>
+        <v>0.801</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.266</v>
+        <v>0.72</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6848,28 +6855,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0.004500000000000001</v>
+        <v>4.4</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1034700</v>
+        <v>1191800</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H142" t="n">
-        <v>53.1</v>
+        <v>44.46</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6877,10 +6884,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>2.225</v>
+        <v>4.58</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>2.104</v>
+        <v>4.537</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6893,39 +6900,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>-0.0455</v>
+        <v>0.98</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1030800</v>
+        <v>1169900</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="H143" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.55</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.629</v>
+        <v>0.996</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.612</v>
+        <v>1.012</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6938,40 +6945,33 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>-0.0267</v>
+        <v>0.285</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1016700</v>
+        <v>1168700</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H144" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J144" s="9" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="K144" s="9" t="n">
-        <v>0.372</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n"/>
+      <c r="K144" s="9" t="n"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
     </row>
@@ -6983,28 +6983,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.05</v>
+        <v>8</v>
       </c>
       <c r="E145" s="17" t="n">
-        <v>-0.0367</v>
+        <v>-0.0037</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>956800</v>
+        <v>1159200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="H145" t="n">
-        <v>39.35</v>
+        <v>50.63</v>
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.098</v>
+        <v>7.949</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.119</v>
+        <v>8.151</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7028,28 +7028,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.595</v>
+        <v>2.85</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>-0.0083</v>
+        <v>-0.024</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>954000</v>
+        <v>1138500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H146" t="n">
-        <v>49.07</v>
+        <v>55.28</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.593</v>
+        <v>2.787</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.61</v>
+        <v>2.685</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7073,28 +7073,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>2.85</v>
+        <v>0.43</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>-0.024</v>
+        <v>-0.0227</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>947800</v>
+        <v>1133800</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H147" t="n">
-        <v>55.28</v>
+        <v>47.37</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>2.787</v>
+        <v>0.434</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.685</v>
+        <v>0.452</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7118,28 +7118,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>8</v>
+        <v>0.58</v>
       </c>
       <c r="E148" s="17" t="n">
-        <v>-0.0037</v>
+        <v>-0.0252</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>947000</v>
+        <v>1127700</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="H148" t="n">
-        <v>50.63</v>
+        <v>52.94</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>7.949</v>
+        <v>0.57</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>8.151</v>
+        <v>0.575</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7163,28 +7163,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.84</v>
+        <v>0.26</v>
       </c>
       <c r="E149" s="17" t="n">
-        <v>-0.0059</v>
+        <v>-0.0189</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>925100</v>
+        <v>1102000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="H149" t="n">
-        <v>64.11</v>
+        <v>51.19</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7192,10 +7192,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.801</v>
+        <v>0.254</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.72</v>
+        <v>0.271</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7208,39 +7208,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.765</v>
+        <v>0.775</v>
       </c>
       <c r="E150" s="17" t="n">
-        <v>-0.0192</v>
+        <v>-0.0064</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>918800</v>
+        <v>1098500</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="H150" t="n">
-        <v>37.15</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.68</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.796</v>
+        <v>0.757</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.849</v>
+        <v>0.74</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7253,39 +7253,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>4.77</v>
+        <v>0.38</v>
       </c>
       <c r="E151" s="15" t="n">
-        <v>0.0021</v>
+        <v>0.0133</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>916200</v>
+        <v>1096500</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.11</v>
+        <v>1.34</v>
       </c>
       <c r="H151" t="n">
-        <v>55.58</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.79</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>4.747</v>
+        <v>0.378</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>4.589</v>
+        <v>0.381</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7298,39 +7298,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>0</v>
+        <v>1.05</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>-0.0367</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>910200</v>
+        <v>1080700</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="H152" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.35</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.609</v>
+        <v>1.098</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.589</v>
+        <v>1.119</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7343,39 +7343,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>3.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E153" s="17" t="n">
-        <v>-0.0227</v>
+        <v>-0.0408</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>905700</v>
+        <v>1073500</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>1.01</v>
+        <v>0.35</v>
       </c>
       <c r="H153" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.04</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>2.944</v>
+        <v>0.895</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>2.902</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7388,39 +7388,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.28</v>
+        <v>0.645</v>
       </c>
       <c r="E154" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0529</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>897100</v>
+        <v>1060400</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.23</v>
+        <v>0.86</v>
       </c>
       <c r="H154" t="n">
-        <v>57.33</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.44</v>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.24</v>
+        <v>0.628</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.138</v>
+        <v>0.612</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7433,39 +7433,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>-0.013</v>
+        <v>0.26</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>881700</v>
+        <v>1052600</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.17</v>
+        <v>1.33</v>
       </c>
       <c r="H155" t="n">
-        <v>35.27</v>
-      </c>
-      <c r="I155" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>4.724</v>
+        <v>0.261</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>4.993</v>
+        <v>0.266</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7478,28 +7478,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.715</v>
+        <v>0.595</v>
       </c>
       <c r="E156" s="17" t="n">
-        <v>-0.0069</v>
+        <v>-0.0083</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>879800</v>
+        <v>1041200</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="H156" t="n">
-        <v>53.25</v>
+        <v>49.07</v>
       </c>
       <c r="I156" s="16" t="inlineStr">
         <is>
@@ -7507,10 +7507,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.708</v>
+        <v>0.593</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.713</v>
+        <v>0.61</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7523,28 +7523,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="E157" s="17" t="n">
-        <v>-0.0167</v>
+        <v>-0.0181</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>877600</v>
+        <v>1030800</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="H157" t="n">
-        <v>66.7</v>
+        <v>73.03</v>
       </c>
       <c r="I157" s="16" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>1.108</v>
+        <v>2.939</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.007</v>
+        <v>2.522</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7568,39 +7568,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>MFCB</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.51</v>
+        <v>3.01</v>
       </c>
       <c r="E158" s="17" t="n">
-        <v>-0.0286</v>
+        <v>-0.0227</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>867800</v>
+        <v>1016600</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="H158" t="n">
-        <v>42.12</v>
-      </c>
-      <c r="I158" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.2</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.524</v>
+        <v>2.944</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.532</v>
+        <v>2.902</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7613,28 +7613,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.58</v>
       </c>
       <c r="E159" s="17" t="n">
-        <v>-0.0408</v>
+        <v>-0.0108</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>865800</v>
+        <v>965800</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="H159" t="n">
-        <v>60.04</v>
+        <v>35.73</v>
       </c>
       <c r="I159" s="16" t="inlineStr">
         <is>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.895</v>
+        <v>4.725</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>4.993</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7658,28 +7658,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="E160" s="17" t="n">
-        <v>-0.0196</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>860700</v>
+        <v>944500</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H160" t="n">
-        <v>34.67</v>
+        <v>57.33</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>1.049</v>
+        <v>1.24</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>1.074</v>
+        <v>1.138</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7703,28 +7703,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E161" s="17" t="n">
-        <v>-0.0135</v>
+        <v>7.83</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>859700</v>
+        <v>925700</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="H161" t="n">
-        <v>53.82</v>
+        <v>36.58</v>
       </c>
       <c r="I161" s="16" t="inlineStr">
         <is>
@@ -7732,9 +7732,11 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>2.863</v>
-      </c>
-      <c r="K161" s="9" t="n"/>
+        <v>7.975</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>8.260999999999999</v>
+      </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
     </row>
@@ -7746,39 +7748,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>852900</v>
+        <v>921800</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="H162" t="n">
-        <v>36.18</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.94</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.998</v>
+        <v>1.045</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.047</v>
+        <v>0.888</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7791,28 +7793,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.26</v>
+        <v>0.77</v>
       </c>
       <c r="E163" s="15" t="n">
-        <v>0.0161</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>832100</v>
+        <v>909500</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.31</v>
+        <v>0.62</v>
       </c>
       <c r="H163" t="n">
-        <v>83.94</v>
+        <v>52.54</v>
       </c>
       <c r="I163" s="16" t="inlineStr">
         <is>
@@ -7820,10 +7822,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.045</v>
+        <v>0.765</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.888</v>
+        <v>0.755</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7836,28 +7838,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.72</v>
+        <v>2.91</v>
       </c>
       <c r="E164" s="17" t="n">
-        <v>-0.0069</v>
+        <v>-0.0169</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>825500</v>
+        <v>909500</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H164" t="n">
-        <v>67.44</v>
+        <v>53.29</v>
       </c>
       <c r="I164" s="16" t="inlineStr">
         <is>
@@ -7865,11 +7867,9 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="K164" s="9" t="n">
-        <v>0.614</v>
-      </c>
+        <v>2.862</v>
+      </c>
+      <c r="K164" s="9" t="n"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
     </row>
@@ -7881,39 +7881,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E165" s="15" t="n">
-        <v>0.0072</v>
+        <v>2.97</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>813400</v>
+        <v>900800</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.42</v>
+        <v>0.84</v>
       </c>
       <c r="H165" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="I165" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.8</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.356</v>
+        <v>3.07</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.325</v>
+        <v>3.152</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7926,28 +7926,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>2.97</v>
+        <v>1</v>
       </c>
       <c r="E166" s="17" t="n">
-        <v>-0.01</v>
+        <v>-0.0196</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>807900</v>
+        <v>895600</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.75</v>
+        <v>0.19</v>
       </c>
       <c r="H166" t="n">
-        <v>32.8</v>
+        <v>34.67</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>3.07</v>
+        <v>1.049</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>3.152</v>
+        <v>1.074</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7971,39 +7971,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E167" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.96</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>795100</v>
+        <v>892700</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.54</v>
+        <v>0.19</v>
       </c>
       <c r="H167" t="n">
-        <v>52.54</v>
-      </c>
-      <c r="I167" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.18</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.765</v>
+        <v>0.998</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.755</v>
+        <v>1.047</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8016,28 +8016,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="E168" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.715</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>766000</v>
+        <v>880200</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="H168" t="n">
-        <v>35.8</v>
+        <v>53.25</v>
       </c>
       <c r="I168" s="16" t="inlineStr">
         <is>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>7.974</v>
+        <v>0.708</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>8.26</v>
+        <v>0.713</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8061,28 +8061,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>6.67</v>
+        <v>0.51</v>
       </c>
       <c r="E169" s="17" t="n">
-        <v>-0.0305</v>
+        <v>-0.0286</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>757700</v>
+        <v>867800</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.22</v>
+        <v>0.71</v>
       </c>
       <c r="H169" t="n">
-        <v>52.86</v>
+        <v>42.12</v>
       </c>
       <c r="I169" s="16" t="inlineStr">
         <is>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>6.569</v>
+        <v>0.524</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>6.495</v>
+        <v>0.532</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8106,39 +8106,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.38</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E170" s="17" t="n">
-        <v>-0.0143</v>
+        <v>-0.005</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>743000</v>
+        <v>824900</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H170" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="I170" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.77</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.345</v>
+        <v>9.532999999999999</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.148</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8151,28 +8151,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="E171" s="17" t="n">
-        <v>-0.0091</v>
+        <v>1.4</v>
+      </c>
+      <c r="E171" s="15" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>718700</v>
+        <v>813400</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="H171" t="n">
-        <v>62.34</v>
+        <v>70.67</v>
       </c>
       <c r="I171" s="16" t="inlineStr">
         <is>
@@ -8180,10 +8180,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>9.529999999999999</v>
+        <v>1.356</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>9.061</v>
+        <v>1.325</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8196,39 +8196,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>0</v>
+        <v>6.67</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>-0.0305</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>700000</v>
+        <v>788300</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="H172" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.631</v>
+        <v>6.569</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>0.637</v>
+        <v>6.495</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8241,39 +8241,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E173" s="17" t="n">
-        <v>-0.0173</v>
+        <v>1.5</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>692300</v>
+        <v>775900</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="H173" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.85</v>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.703</v>
+        <v>1.48</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.614</v>
+        <v>1.532</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8286,28 +8286,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.08</v>
+        <v>1.68</v>
       </c>
       <c r="E174" s="17" t="n">
-        <v>-0.0046</v>
+        <v>-0.0289</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>657200</v>
+        <v>754300</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>1.74</v>
+        <v>0.58</v>
       </c>
       <c r="H174" t="n">
-        <v>22.96</v>
+        <v>49.53</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8315,10 +8315,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.179</v>
+        <v>1.701</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.285</v>
+        <v>1.614</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8331,39 +8331,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>3.17</v>
+        <v>1.38</v>
       </c>
       <c r="E175" s="17" t="n">
-        <v>-0.0423</v>
+        <v>-0.0143</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>650000</v>
+        <v>743000</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H175" t="n">
-        <v>67.34999999999999</v>
-      </c>
-      <c r="I175" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.09</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>2.931</v>
+        <v>1.345</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>2.521</v>
+        <v>1.148</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8376,28 +8376,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="E176" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.985</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>644900</v>
+        <v>739900</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.04</v>
+        <v>1.46</v>
       </c>
       <c r="H176" t="n">
-        <v>40.13</v>
+        <v>53.67</v>
       </c>
       <c r="I176" s="16" t="inlineStr">
         <is>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>6.308</v>
+        <v>0.98</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>6.496</v>
+        <v>0.974</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8421,39 +8421,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.27</v>
+        <v>6.21</v>
       </c>
       <c r="E177" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0048</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>638800</v>
+        <v>739200</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="H177" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="I177" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.13</v>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.29</v>
+        <v>6.308</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.322</v>
+        <v>6.496</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8466,39 +8466,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0</v>
+        <v>3.93</v>
+      </c>
+      <c r="E178" s="17" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>631100</v>
+        <v>716200</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.48</v>
+        <v>0.21</v>
       </c>
       <c r="H178" t="n">
-        <v>54.14</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.35</v>
+      </c>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.633</v>
+        <v>3.744</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.629</v>
+        <v>3.395</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8511,39 +8511,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="E179" s="17" t="n">
-        <v>-0.02</v>
+        <v>1.28</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>622000</v>
+        <v>706700</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="H179" t="n">
-        <v>62.75</v>
-      </c>
-      <c r="I179" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.52</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>3.743</v>
+        <v>1.291</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>3.395</v>
+        <v>1.322</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8556,39 +8556,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E180" s="17" t="n">
-        <v>-0.0074</v>
+        <v>0.63</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>617700</v>
+        <v>700000</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>1.48</v>
+        <v>0.72</v>
       </c>
       <c r="H180" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="I180" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.655</v>
+        <v>0.631</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.647</v>
+        <v>0.637</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8601,28 +8601,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E181" s="10" t="n">
-        <v>0</v>
+        <v>5.48</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>593500</v>
+        <v>669100</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H181" t="n">
-        <v>52.85</v>
+        <v>36.18</v>
       </c>
       <c r="I181" s="16" t="inlineStr">
         <is>
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.48</v>
+        <v>5.696</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>1.532</v>
+        <v>6.083</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8646,39 +8646,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E182" s="17" t="n">
-        <v>-0.0172</v>
+        <v>4.6</v>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>588400</v>
+        <v>664400</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H182" t="n">
-        <v>40.98</v>
-      </c>
-      <c r="I182" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.65</v>
+      </c>
+      <c r="I182" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>1.757</v>
+        <v>4.441</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>1.857</v>
+        <v>4.489</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8691,39 +8691,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>GESHEN</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>585500</v>
+        <v>657200</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.25</v>
+        <v>1.74</v>
       </c>
       <c r="H183" t="n">
-        <v>48.38</v>
-      </c>
-      <c r="I183" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.96</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>1.179</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.285</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8736,39 +8736,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="E184" s="15" t="n">
-        <v>0.0031</v>
+        <v>0.625</v>
+      </c>
+      <c r="E184" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>575500</v>
+        <v>631100</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="H184" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="I184" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.12</v>
+      </c>
+      <c r="I184" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>3.301</v>
+        <v>0.627</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>3.487</v>
+        <v>0.604</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8781,39 +8781,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>0.63</v>
+        <v>0.635</v>
       </c>
       <c r="E185" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>573500</v>
+        <v>631100</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="H185" t="n">
-        <v>78.42</v>
-      </c>
-      <c r="I185" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.14</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>0.492</v>
+        <v>0.629</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8826,39 +8826,39 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E186" s="17" t="n">
-        <v>-0.0054</v>
+        <v>3.21</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.0031</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>570200</v>
+        <v>630000</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="H186" t="n">
-        <v>36.48</v>
-      </c>
-      <c r="I186" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.09</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>5.697</v>
+        <v>3.301</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>6.083</v>
+        <v>3.487</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8880,19 +8880,19 @@
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="E187" s="17" t="n">
-        <v>-0.0451</v>
+        <v>-0.0504</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>560400</v>
+        <v>621400</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="H187" t="n">
-        <v>50.54</v>
+        <v>49.13</v>
       </c>
       <c r="I187" s="13" t="inlineStr">
         <is>
@@ -8900,10 +8900,10 @@
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>3.655</v>
+        <v>3.654</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>3.324</v>
+        <v>3.323</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8916,39 +8916,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>QL</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E188" s="17" t="n">
-        <v>-0.0336</v>
+        <v>4.02</v>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.0025</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>550700</v>
+        <v>619800</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="H188" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I188" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.04</v>
+      </c>
+      <c r="I188" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>2.974</v>
+        <v>3.934</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>2.798</v>
+        <v>3.93</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8961,39 +8961,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E189" s="15" t="n">
-        <v>0.0189</v>
+        <v>0.67</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>-0.0074</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>549600</v>
+        <v>617700</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.98</v>
+        <v>1.48</v>
       </c>
       <c r="H189" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="I189" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.6</v>
+      </c>
+      <c r="I189" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>0.53</v>
+        <v>0.655</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>0.527</v>
+        <v>0.647</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -9006,39 +9006,39 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E190" s="10" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E190" s="15" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>541300</v>
+        <v>606300</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.14</v>
+        <v>0.41</v>
       </c>
       <c r="H190" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="I190" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="I190" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>0.587</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>0.587</v>
+        <v>0.492</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9051,39 +9051,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>0.985</v>
+        <v>0.58</v>
       </c>
       <c r="E191" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>523900</v>
+        <v>606200</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>1.03</v>
+        <v>0.16</v>
       </c>
       <c r="H191" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="I191" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.06</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>0.98</v>
+        <v>0.587</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>0.974</v>
+        <v>0.587</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9096,45 +9096,630 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="E192" s="15" t="n">
-        <v>0.011</v>
+        <v>1.71</v>
+      </c>
+      <c r="E192" s="17" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>523800</v>
+        <v>599400</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="H192" t="n">
-        <v>58.67</v>
-      </c>
-      <c r="I192" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.98</v>
+      </c>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>4.439</v>
+        <v>1.757</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>4.489</v>
+        <v>1.857</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E193" s="17" t="n">
+        <v>-0.0302</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>597000</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H193" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>585500</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H194" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="I194" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E195" s="17" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>572600</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H195" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="9" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="K195" s="9" t="n">
+        <v>2.788</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="14" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E196" s="15" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>565300</v>
+      </c>
+      <c r="G196" s="12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H196" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="9" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="K196" s="9" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="14" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E197" s="15" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>553400</v>
+      </c>
+      <c r="G197" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H197" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="I197" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="K197" s="9" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="14" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>546300</v>
+      </c>
+      <c r="G198" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H198" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="I198" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="n">
+        <v>2.064</v>
+      </c>
+      <c r="K198" s="9" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="14" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>538300</v>
+      </c>
+      <c r="G199" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H199" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J199" s="9" t="n">
+        <v>7.666</v>
+      </c>
+      <c r="K199" s="9" t="n">
+        <v>7.808</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="14" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E200" s="17" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="F200" s="11" t="n">
+        <v>527900</v>
+      </c>
+      <c r="G200" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H200" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="I200" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J200" s="9" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="K200" s="9" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" s="14" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E201" s="17" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>517000</v>
+      </c>
+      <c r="G201" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H201" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="I201" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J201" s="9" t="n">
+        <v>8.709</v>
+      </c>
+      <c r="K201" s="9" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" s="14" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" s="11" t="n">
+        <v>513800</v>
+      </c>
+      <c r="G202" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H202" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="I202" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J202" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K202" s="9" t="n">
+        <v>1.675</v>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" s="14" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E203" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>509000</v>
+      </c>
+      <c r="G203" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H203" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="I203" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J203" s="9" t="n">
+        <v>2.054</v>
+      </c>
+      <c r="K203" s="9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" s="14" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E204" s="15" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F204" s="11" t="n">
+        <v>506400</v>
+      </c>
+      <c r="G204" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H204" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="I204" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J204" s="9" t="n">
+        <v>6.781</v>
+      </c>
+      <c r="K204" s="9" t="n">
+        <v>6.804</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" s="14" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>THETA</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E205" s="17" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>503300</v>
+      </c>
+      <c r="G205" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H205" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="I205" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J205" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K205" s="9" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M192"/>
+  <autoFilter ref="A1:M205"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/bursa-report-last7.xlsx
+++ b/docs/downloads/bursa-report-last7.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-09-28'!$A$1:$M$257</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026-09-25'!$A$1:$M$304</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2026-09-24'!$A$1:$M$275</definedName>
@@ -46,10 +46,10 @@
       <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="000CA30C"/>
     </font>
   </fonts>
   <fills count="4">
@@ -96,14 +96,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -565,28 +565,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.58</v>
+        <v>0.18</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0526</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>23550100</v>
+        <v>59906100</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.98</v>
+        <v>0.11</v>
       </c>
       <c r="H2" t="n">
-        <v>68.72</v>
+        <v>21.7</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.547</v>
+        <v>0.266</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.493</v>
+        <v>0.481</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -610,39 +610,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>-0.0526</v>
+        <v>0.185</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>14855000</v>
+        <v>24749700</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.03</v>
+        <v>0.54</v>
       </c>
       <c r="H3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.83</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.266</v>
+        <v>0.15</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.481</v>
+        <v>0.118</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -655,39 +655,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>7755100</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H4" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.19</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>5345300</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.118</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -700,45 +700,2243 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E5" s="10" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>689700</v>
+        <v>5971500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="H5" t="n">
-        <v>73.42</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.06</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.889</v>
+        <v>0.449</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.852</v>
+        <v>0.41</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0468</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UNIPAC</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5306800</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NEXG</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4744600</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H7" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0213</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MTAG</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>4743800</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>4349600</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>68.72</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>3437400</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H10" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>2952700</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2951200</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2710000</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2496200</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H14" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2341000</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H15" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2320600</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H16" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2207500</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H17" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2018200</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H18" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1954700</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1788000</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <